--- a/Översikt DEGERFORS.xlsx
+++ b/Översikt DEGERFORS.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE241"/>
+  <dimension ref="A1:AE242"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>46160</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>46051</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
         <v>46160</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>46107</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>46190</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>46190</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>46161</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>45089</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>45175</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>46160</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>45384</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
         <v>45384</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 73321-2021</t>
+          <t>A 38916-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44550</v>
+        <v>45163</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2089,46 +2089,284 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>17</v>
+        <v>4.3</v>
       </c>
       <c r="J14" t="n">
         <v>3</v>
       </c>
       <c r="K14" t="n">
+        <v>3</v>
+      </c>
+      <c r="L14" t="n">
         <v>1</v>
       </c>
-      <c r="L14" t="n">
-        <v>3</v>
-      </c>
       <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
         <v>1</v>
       </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>4</v>
-      </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>6</v>
       </c>
       <c r="T14" t="n">
+        <v>27</v>
+      </c>
+      <c r="U14" t="n">
+        <v>27</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett
+Grönpyrola
+Thomsons trägnagare
+Vågbandad barkbock
+Spillkråka
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 38916-2023 artfynd.xlsx", "A 38916-2023")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 38916-2023 karta.png", "A 38916-2023")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 38916-2023 georefererad karta.tif", "A 38916-2023")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 38916-2023 FSC-klagomål.docx", "A 38916-2023")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 38916-2023 FSC-klagomål mail.docx", "A 38916-2023")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 38916-2023 tillsynsbegäran.docx", "A 38916-2023")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 38916-2023 tillsynsbegäran mail.docx", "A 38916-2023")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 38916-2023 prioriterade fågelarter.docx", "A 38916-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 29553-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>DEGERFORS</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>4</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>5</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1</v>
+      </c>
+      <c r="S15" t="n">
+        <v>6</v>
+      </c>
+      <c r="T15" t="n">
+        <v>6</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Skuggblåslav
+Talltita
+Ullticka
+Vedskivlav
+Tofsmes</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 29553-2026 artfynd.xlsx", "A 29553-2026")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 29553-2026 karta.png", "A 29553-2026")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 29553-2026 georefererad karta.tif", "A 29553-2026")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 29553-2026 FSC-klagomål.docx", "A 29553-2026")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 29553-2026 FSC-klagomål mail.docx", "A 29553-2026")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 29553-2026 tillsynsbegäran.docx", "A 29553-2026")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 29553-2026 tillsynsbegäran mail.docx", "A 29553-2026")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 29553-2026 prioriterade fågelarter.docx", "A 29553-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 73321-2021</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>44550</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>DEGERFORS</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>17</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>3</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>4</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" t="n">
+        <v>6</v>
+      </c>
+      <c r="T16" t="n">
         <v>8</v>
       </c>
-      <c r="U14" t="n">
+      <c r="U16" t="n">
         <v>8</v>
       </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Grynig filtlav
@@ -2138,278 +2376,40 @@
 Spillkråka</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 73321-2021 artfynd.xlsx", "A 73321-2021")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 73321-2021 karta.png", "A 73321-2021")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 73321-2021 georefererad karta.tif", "A 73321-2021")</f>
         <v/>
       </c>
-      <c r="Z14">
+      <c r="Z16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/knärot/A 73321-2021 karta knärot.png", "A 73321-2021")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 73321-2021 FSC-klagomål.docx", "A 73321-2021")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 73321-2021 FSC-klagomål mail.docx", "A 73321-2021")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 73321-2021 tillsynsbegäran.docx", "A 73321-2021")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 73321-2021 tillsynsbegäran mail.docx", "A 73321-2021")</f>
         <v/>
       </c>
-      <c r="AE14">
+      <c r="AE16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 73321-2021 prioriterade fågelarter.docx", "A 73321-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 38916-2023</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45163</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>DEGERFORS</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J15" t="n">
-        <v>3</v>
-      </c>
-      <c r="K15" t="n">
-        <v>3</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>6</v>
-      </c>
-      <c r="T15" t="n">
-        <v>27</v>
-      </c>
-      <c r="U15" t="n">
-        <v>27</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett
-Grönpyrola
-Thomsons trägnagare
-Vågbandad barkbock
-Spillkråka
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 38916-2023 artfynd.xlsx", "A 38916-2023")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 38916-2023 karta.png", "A 38916-2023")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 38916-2023 georefererad karta.tif", "A 38916-2023")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 38916-2023 FSC-klagomål.docx", "A 38916-2023")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 38916-2023 FSC-klagomål mail.docx", "A 38916-2023")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 38916-2023 tillsynsbegäran.docx", "A 38916-2023")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 38916-2023 tillsynsbegäran mail.docx", "A 38916-2023")</f>
-        <v/>
-      </c>
-      <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 38916-2023 prioriterade fågelarter.docx", "A 38916-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 29553-2026</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>DEGERFORS</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>4</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>5</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1</v>
-      </c>
-      <c r="S16" t="n">
-        <v>6</v>
-      </c>
-      <c r="T16" t="n">
-        <v>6</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Skuggblåslav
-Talltita
-Ullticka
-Vedskivlav
-Tofsmes</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 29553-2026 artfynd.xlsx", "A 29553-2026")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 29553-2026 karta.png", "A 29553-2026")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 29553-2026 georefererad karta.tif", "A 29553-2026")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 29553-2026 FSC-klagomål.docx", "A 29553-2026")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 29553-2026 FSC-klagomål mail.docx", "A 29553-2026")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 29553-2026 tillsynsbegäran.docx", "A 29553-2026")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 29553-2026 tillsynsbegäran mail.docx", "A 29553-2026")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 29553-2026 prioriterade fågelarter.docx", "A 29553-2026")</f>
         <v/>
       </c>
     </row>
@@ -2433,7 +2433,7 @@
         <v>45175</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         <v>45866</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>45932</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         <v>45163</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         <v>45205</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
         <v>45351</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>45559</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>45931</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>45384</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>46190</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 47785-2025</t>
+          <t>A 4256-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3580,10 +3580,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45931</v>
+        <v>46045</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3596,31 +3596,31 @@
         </is>
       </c>
       <c r="I27" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
         <v>2</v>
       </c>
-      <c r="J27" t="n">
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
         <v>2</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -3632,495 +3632,495 @@
         <v>2</v>
       </c>
       <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>Skogsklocka
+Slåtterfibbla</t>
+        </is>
+      </c>
+      <c r="W27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 4256-2026 artfynd.xlsx", "A 4256-2026")</f>
+        <v/>
+      </c>
+      <c r="X27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 4256-2026 karta.png", "A 4256-2026")</f>
+        <v/>
+      </c>
+      <c r="Y27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 4256-2026 georefererad karta.tif", "A 4256-2026")</f>
+        <v/>
+      </c>
+      <c r="AA27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 4256-2026 FSC-klagomål.docx", "A 4256-2026")</f>
+        <v/>
+      </c>
+      <c r="AB27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 4256-2026 FSC-klagomål mail.docx", "A 4256-2026")</f>
+        <v/>
+      </c>
+      <c r="AC27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 4256-2026 tillsynsbegäran.docx", "A 4256-2026")</f>
+        <v/>
+      </c>
+      <c r="AD27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 4256-2026 tillsynsbegäran mail.docx", "A 4256-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>A 47785-2025</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>DEGERFORS</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
         <v>2</v>
       </c>
-      <c r="V27" s="2" t="inlineStr">
+      <c r="J28" t="n">
+        <v>2</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
         <is>
           <t>Spillkråka
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W27">
+      <c r="W28">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 47785-2025 artfynd.xlsx", "A 47785-2025")</f>
         <v/>
       </c>
-      <c r="X27">
+      <c r="X28">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 47785-2025 karta.png", "A 47785-2025")</f>
         <v/>
       </c>
-      <c r="Y27">
+      <c r="Y28">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 47785-2025 georefererad karta.tif", "A 47785-2025")</f>
         <v/>
       </c>
-      <c r="AA27">
+      <c r="AA28">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 47785-2025 FSC-klagomål.docx", "A 47785-2025")</f>
         <v/>
       </c>
-      <c r="AB27">
+      <c r="AB28">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 47785-2025 FSC-klagomål mail.docx", "A 47785-2025")</f>
         <v/>
       </c>
-      <c r="AC27">
+      <c r="AC28">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 47785-2025 tillsynsbegäran.docx", "A 47785-2025")</f>
         <v/>
       </c>
-      <c r="AD27">
+      <c r="AD28">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 47785-2025 tillsynsbegäran mail.docx", "A 47785-2025")</f>
         <v/>
       </c>
-      <c r="AE27">
+      <c r="AE28">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 47785-2025 prioriterade fågelarter.docx", "A 47785-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" t="inlineStr">
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>A 40870-2024</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="n">
+        <v>45558</v>
+      </c>
+      <c r="E29" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>DEGERFORS</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 40870-2024 artfynd.xlsx", "A 40870-2024")</f>
+        <v/>
+      </c>
+      <c r="X29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 40870-2024 karta.png", "A 40870-2024")</f>
+        <v/>
+      </c>
+      <c r="Y29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 40870-2024 georefererad karta.tif", "A 40870-2024")</f>
+        <v/>
+      </c>
+      <c r="AA29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 40870-2024 FSC-klagomål.docx", "A 40870-2024")</f>
+        <v/>
+      </c>
+      <c r="AB29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 40870-2024 FSC-klagomål mail.docx", "A 40870-2024")</f>
+        <v/>
+      </c>
+      <c r="AC29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 40870-2024 tillsynsbegäran.docx", "A 40870-2024")</f>
+        <v/>
+      </c>
+      <c r="AD29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 40870-2024 tillsynsbegäran mail.docx", "A 40870-2024")</f>
+        <v/>
+      </c>
+      <c r="AE29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 40870-2024 prioriterade fågelarter.docx", "A 40870-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" t="inlineStr">
         <is>
           <t>A 38910-2023</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D28" s="1" t="n">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D30" s="1" t="n">
         <v>45163</v>
       </c>
-      <c r="E28" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>DEGERFORS</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
+      <c r="E30" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>DEGERFORS</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I28" t="n">
+      <c r="I30" t="n">
         <v>2.8</v>
       </c>
-      <c r="J28" t="n">
+      <c r="J30" t="n">
         <v>2</v>
       </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
         <v>2</v>
       </c>
-      <c r="T28" t="n">
+      <c r="T30" t="n">
         <v>3</v>
       </c>
-      <c r="U28" t="n">
+      <c r="U30" t="n">
         <v>3</v>
       </c>
-      <c r="V28" s="2" t="inlineStr">
+      <c r="V30" s="2" t="inlineStr">
         <is>
           <t>Tjäder
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W28">
+      <c r="W30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 38910-2023 artfynd.xlsx", "A 38910-2023")</f>
         <v/>
       </c>
-      <c r="X28">
+      <c r="X30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 38910-2023 karta.png", "A 38910-2023")</f>
         <v/>
       </c>
-      <c r="Y28">
+      <c r="Y30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 38910-2023 georefererad karta.tif", "A 38910-2023")</f>
         <v/>
       </c>
-      <c r="AA28">
+      <c r="AA30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 38910-2023 FSC-klagomål.docx", "A 38910-2023")</f>
         <v/>
       </c>
-      <c r="AB28">
+      <c r="AB30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 38910-2023 FSC-klagomål mail.docx", "A 38910-2023")</f>
         <v/>
       </c>
-      <c r="AC28">
+      <c r="AC30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 38910-2023 tillsynsbegäran.docx", "A 38910-2023")</f>
         <v/>
       </c>
-      <c r="AD28">
+      <c r="AD30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 38910-2023 tillsynsbegäran mail.docx", "A 38910-2023")</f>
         <v/>
       </c>
-      <c r="AE28">
+      <c r="AE30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 38910-2023 prioriterade fågelarter.docx", "A 38910-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>A 40870-2024</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D29" s="1" t="n">
-        <v>45558</v>
-      </c>
-      <c r="E29" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>DEGERFORS</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>A 38912-2023</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D31" s="1" t="n">
+        <v>45163</v>
+      </c>
+      <c r="E31" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>DEGERFORS</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I29" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J29" t="n">
+      <c r="I31" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J31" t="n">
         <v>2</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
         <v>1</v>
       </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
         <v>1</v>
       </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
         <v>2</v>
       </c>
-      <c r="T29" t="n">
+      <c r="T31" t="n">
         <v>2</v>
       </c>
-      <c r="U29" t="n">
+      <c r="U31" t="n">
         <v>2</v>
       </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 40870-2024 artfynd.xlsx", "A 40870-2024")</f>
-        <v/>
-      </c>
-      <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 40870-2024 karta.png", "A 40870-2024")</f>
-        <v/>
-      </c>
-      <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 40870-2024 georefererad karta.tif", "A 40870-2024")</f>
-        <v/>
-      </c>
-      <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 40870-2024 FSC-klagomål.docx", "A 40870-2024")</f>
-        <v/>
-      </c>
-      <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 40870-2024 FSC-klagomål mail.docx", "A 40870-2024")</f>
-        <v/>
-      </c>
-      <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 40870-2024 tillsynsbegäran.docx", "A 40870-2024")</f>
-        <v/>
-      </c>
-      <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 40870-2024 tillsynsbegäran mail.docx", "A 40870-2024")</f>
-        <v/>
-      </c>
-      <c r="AE29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 40870-2024 prioriterade fågelarter.docx", "A 40870-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>A 38912-2023</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D30" s="1" t="n">
-        <v>45163</v>
-      </c>
-      <c r="E30" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>DEGERFORS</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="J30" t="n">
-        <v>2</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>1</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>1</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2</v>
-      </c>
-      <c r="U30" t="n">
-        <v>2</v>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
+      <c r="V31" s="2" t="inlineStr">
         <is>
           <t>Tretåig hackspett
 Tjäder</t>
         </is>
       </c>
-      <c r="W30">
+      <c r="W31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 38912-2023 artfynd.xlsx", "A 38912-2023")</f>
         <v/>
       </c>
-      <c r="X30">
+      <c r="X31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 38912-2023 karta.png", "A 38912-2023")</f>
         <v/>
       </c>
-      <c r="Y30">
+      <c r="Y31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 38912-2023 georefererad karta.tif", "A 38912-2023")</f>
         <v/>
       </c>
-      <c r="AA30">
+      <c r="AA31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 38912-2023 FSC-klagomål.docx", "A 38912-2023")</f>
         <v/>
       </c>
-      <c r="AB30">
+      <c r="AB31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 38912-2023 FSC-klagomål mail.docx", "A 38912-2023")</f>
         <v/>
       </c>
-      <c r="AC30">
+      <c r="AC31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 38912-2023 tillsynsbegäran.docx", "A 38912-2023")</f>
         <v/>
       </c>
-      <c r="AD30">
+      <c r="AD31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 38912-2023 tillsynsbegäran mail.docx", "A 38912-2023")</f>
         <v/>
       </c>
-      <c r="AE30">
+      <c r="AE31">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 38912-2023 prioriterade fågelarter.docx", "A 38912-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>A 4256-2026</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D31" s="1" t="n">
-        <v>46045</v>
-      </c>
-      <c r="E31" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>DEGERFORS</t>
-        </is>
-      </c>
-      <c r="I31" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>2</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>2</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>Skogsklocka
-Slåtterfibbla</t>
-        </is>
-      </c>
-      <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 4256-2026 artfynd.xlsx", "A 4256-2026")</f>
-        <v/>
-      </c>
-      <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 4256-2026 karta.png", "A 4256-2026")</f>
-        <v/>
-      </c>
-      <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 4256-2026 georefererad karta.tif", "A 4256-2026")</f>
-        <v/>
-      </c>
-      <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 4256-2026 FSC-klagomål.docx", "A 4256-2026")</f>
-        <v/>
-      </c>
-      <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 4256-2026 FSC-klagomål mail.docx", "A 4256-2026")</f>
-        <v/>
-      </c>
-      <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 4256-2026 tillsynsbegäran.docx", "A 4256-2026")</f>
-        <v/>
-      </c>
-      <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 4256-2026 tillsynsbegäran mail.docx", "A 4256-2026")</f>
         <v/>
       </c>
     </row>
@@ -4144,7 +4144,7 @@
         <v>45163</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>46199</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>44470</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>44487</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>44470</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 47915-2024</t>
+          <t>A 33297-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4701,10 +4701,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45589</v>
+        <v>45116</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4716,26 +4716,21 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
         <v>1</v>
       </c>
-      <c r="K37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" t="n">
-        <v>0</v>
-      </c>
       <c r="N37" t="n">
         <v>0</v>
       </c>
@@ -4746,10 +4741,10 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4758,46 +4753,46 @@
         <v>1</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 47915-2024 artfynd.xlsx", "A 47915-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 33297-2023 artfynd.xlsx", "A 33297-2023")</f>
         <v/>
       </c>
       <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 47915-2024 karta.png", "A 47915-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 33297-2023 karta.png", "A 33297-2023")</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 47915-2024 georefererad karta.tif", "A 47915-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 33297-2023 georefererad karta.tif", "A 33297-2023")</f>
         <v/>
       </c>
       <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 47915-2024 FSC-klagomål.docx", "A 47915-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 33297-2023 FSC-klagomål.docx", "A 33297-2023")</f>
         <v/>
       </c>
       <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 47915-2024 FSC-klagomål mail.docx", "A 47915-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 33297-2023 FSC-klagomål mail.docx", "A 33297-2023")</f>
         <v/>
       </c>
       <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 47915-2024 tillsynsbegäran.docx", "A 47915-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 33297-2023 tillsynsbegäran.docx", "A 33297-2023")</f>
         <v/>
       </c>
       <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 47915-2024 tillsynsbegäran mail.docx", "A 47915-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 33297-2023 tillsynsbegäran mail.docx", "A 33297-2023")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 49306-2025</t>
+          <t>A 38904-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4811,10 +4806,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45938</v>
+        <v>45163</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4826,14 +4821,19 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>5.8</v>
+        <v>2.9</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -4863,46 +4863,50 @@
         <v>1</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 49306-2025 artfynd.xlsx", "A 49306-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 38904-2023 artfynd.xlsx", "A 38904-2023")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 49306-2025 karta.png", "A 49306-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 38904-2023 karta.png", "A 38904-2023")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 49306-2025 georefererad karta.tif", "A 49306-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 38904-2023 georefererad karta.tif", "A 38904-2023")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 49306-2025 FSC-klagomål.docx", "A 49306-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 38904-2023 FSC-klagomål.docx", "A 38904-2023")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 49306-2025 FSC-klagomål mail.docx", "A 49306-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 38904-2023 FSC-klagomål mail.docx", "A 38904-2023")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 49306-2025 tillsynsbegäran.docx", "A 49306-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 38904-2023 tillsynsbegäran.docx", "A 38904-2023")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 49306-2025 tillsynsbegäran mail.docx", "A 49306-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 38904-2023 tillsynsbegäran mail.docx", "A 38904-2023")</f>
+        <v/>
+      </c>
+      <c r="AE38">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 38904-2023 prioriterade fågelarter.docx", "A 38904-2023")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 38904-2023</t>
+          <t>A 27093-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4916,10 +4920,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45163</v>
+        <v>45096</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4937,7 +4941,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.9</v>
+        <v>5.9</v>
       </c>
       <c r="J39" t="n">
         <v>1</v>
@@ -4981,42 +4985,42 @@
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 38904-2023 artfynd.xlsx", "A 38904-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 27093-2023 artfynd.xlsx", "A 27093-2023")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 38904-2023 karta.png", "A 38904-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 27093-2023 karta.png", "A 27093-2023")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 38904-2023 georefererad karta.tif", "A 38904-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 27093-2023 georefererad karta.tif", "A 27093-2023")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 38904-2023 FSC-klagomål.docx", "A 38904-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 27093-2023 FSC-klagomål.docx", "A 27093-2023")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 38904-2023 FSC-klagomål mail.docx", "A 38904-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 27093-2023 FSC-klagomål mail.docx", "A 27093-2023")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 38904-2023 tillsynsbegäran.docx", "A 38904-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 27093-2023 tillsynsbegäran.docx", "A 27093-2023")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 38904-2023 tillsynsbegäran mail.docx", "A 38904-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 27093-2023 tillsynsbegäran mail.docx", "A 27093-2023")</f>
         <v/>
       </c>
       <c r="AE39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 38904-2023 prioriterade fågelarter.docx", "A 38904-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 27093-2023 prioriterade fågelarter.docx", "A 27093-2023")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 14177-2026</t>
+          <t>A 49306-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5030,10 +5034,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46099</v>
+        <v>45938</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5045,22 +5049,17 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>2.2</v>
+        <v>5.8</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
@@ -5075,7 +5074,7 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
@@ -5091,42 +5090,42 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 14177-2026 artfynd.xlsx", "A 14177-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 49306-2025 artfynd.xlsx", "A 49306-2025")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 14177-2026 karta.png", "A 14177-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 49306-2025 karta.png", "A 49306-2025")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 14177-2026 georefererad karta.tif", "A 14177-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 49306-2025 georefererad karta.tif", "A 49306-2025")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 14177-2026 FSC-klagomål.docx", "A 14177-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 49306-2025 FSC-klagomål.docx", "A 49306-2025")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 14177-2026 FSC-klagomål mail.docx", "A 14177-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 49306-2025 FSC-klagomål mail.docx", "A 49306-2025")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 14177-2026 tillsynsbegäran.docx", "A 14177-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 49306-2025 tillsynsbegäran.docx", "A 49306-2025")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 14177-2026 tillsynsbegäran mail.docx", "A 14177-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 49306-2025 tillsynsbegäran mail.docx", "A 49306-2025")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 48285-2023</t>
+          <t>A 14177-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5140,10 +5139,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45205</v>
+        <v>46099</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5161,17 +5160,17 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
         <v>1</v>
       </c>
-      <c r="K41" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" t="n">
-        <v>0</v>
-      </c>
       <c r="M41" t="n">
         <v>0</v>
       </c>
@@ -5185,7 +5184,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -5197,43 +5196,39 @@
         <v>1</v>
       </c>
       <c r="U41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 48285-2023 artfynd.xlsx", "A 48285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 14177-2026 artfynd.xlsx", "A 14177-2026")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 48285-2023 karta.png", "A 48285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 14177-2026 karta.png", "A 14177-2026")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 48285-2023 georefererad karta.tif", "A 48285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 14177-2026 georefererad karta.tif", "A 14177-2026")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 48285-2023 FSC-klagomål.docx", "A 48285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 14177-2026 FSC-klagomål.docx", "A 14177-2026")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 48285-2023 FSC-klagomål mail.docx", "A 48285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 14177-2026 FSC-klagomål mail.docx", "A 14177-2026")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 48285-2023 tillsynsbegäran.docx", "A 48285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 14177-2026 tillsynsbegäran.docx", "A 14177-2026")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 48285-2023 tillsynsbegäran mail.docx", "A 48285-2023")</f>
-        <v/>
-      </c>
-      <c r="AE41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 48285-2023 prioriterade fågelarter.docx", "A 48285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 14177-2026 tillsynsbegäran mail.docx", "A 14177-2026")</f>
         <v/>
       </c>
     </row>
@@ -5257,7 +5252,7 @@
         <v>45931</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5349,7 +5344,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 27093-2023</t>
+          <t>A 38907-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5363,10 +5358,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45096</v>
+        <v>45163</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5384,7 +5379,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>5.9</v>
+        <v>2.9</v>
       </c>
       <c r="J43" t="n">
         <v>1</v>
@@ -5428,42 +5423,42 @@
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 27093-2023 artfynd.xlsx", "A 27093-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 38907-2023 artfynd.xlsx", "A 38907-2023")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 27093-2023 karta.png", "A 27093-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 38907-2023 karta.png", "A 38907-2023")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 27093-2023 georefererad karta.tif", "A 27093-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 38907-2023 georefererad karta.tif", "A 38907-2023")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 27093-2023 FSC-klagomål.docx", "A 27093-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 38907-2023 FSC-klagomål.docx", "A 38907-2023")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 27093-2023 FSC-klagomål mail.docx", "A 27093-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 38907-2023 FSC-klagomål mail.docx", "A 38907-2023")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 27093-2023 tillsynsbegäran.docx", "A 27093-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 38907-2023 tillsynsbegäran.docx", "A 38907-2023")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 27093-2023 tillsynsbegäran mail.docx", "A 27093-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 38907-2023 tillsynsbegäran mail.docx", "A 38907-2023")</f>
         <v/>
       </c>
       <c r="AE43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 27093-2023 prioriterade fågelarter.docx", "A 27093-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 38907-2023 prioriterade fågelarter.docx", "A 38907-2023")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 38907-2023</t>
+          <t>A 48285-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5477,10 +5472,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45163</v>
+        <v>45205</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5498,7 +5493,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J44" t="n">
         <v>1</v>
@@ -5542,42 +5537,42 @@
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 38907-2023 artfynd.xlsx", "A 38907-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 48285-2023 artfynd.xlsx", "A 48285-2023")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 38907-2023 karta.png", "A 38907-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 48285-2023 karta.png", "A 48285-2023")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 38907-2023 georefererad karta.tif", "A 38907-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 48285-2023 georefererad karta.tif", "A 48285-2023")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 38907-2023 FSC-klagomål.docx", "A 38907-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 48285-2023 FSC-klagomål.docx", "A 48285-2023")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 38907-2023 FSC-klagomål mail.docx", "A 38907-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 48285-2023 FSC-klagomål mail.docx", "A 48285-2023")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 38907-2023 tillsynsbegäran.docx", "A 38907-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 48285-2023 tillsynsbegäran.docx", "A 48285-2023")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 38907-2023 tillsynsbegäran mail.docx", "A 38907-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 48285-2023 tillsynsbegäran mail.docx", "A 48285-2023")</f>
         <v/>
       </c>
       <c r="AE44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 38907-2023 prioriterade fågelarter.docx", "A 38907-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 48285-2023 prioriterade fågelarter.docx", "A 48285-2023")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 47941-2024</t>
+          <t>A 14121-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5591,10 +5586,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45589</v>
+        <v>44651</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5606,16 +5601,11 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>1.4</v>
+        <v>4.4</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -5624,7 +5614,7 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
         <v>0</v>
@@ -5636,10 +5626,10 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>1</v>
@@ -5648,46 +5638,46 @@
         <v>1</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Brunfläckig pärlemorfjäril</t>
+          <t>Hårklomossa</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 47941-2024 artfynd.xlsx", "A 47941-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 14121-2022 artfynd.xlsx", "A 14121-2022")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 47941-2024 karta.png", "A 47941-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 14121-2022 karta.png", "A 14121-2022")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 47941-2024 georefererad karta.tif", "A 47941-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 14121-2022 georefererad karta.tif", "A 14121-2022")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 47941-2024 FSC-klagomål.docx", "A 47941-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 14121-2022 FSC-klagomål.docx", "A 14121-2022")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 47941-2024 FSC-klagomål mail.docx", "A 47941-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 14121-2022 FSC-klagomål mail.docx", "A 14121-2022")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 47941-2024 tillsynsbegäran.docx", "A 47941-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 14121-2022 tillsynsbegäran.docx", "A 14121-2022")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 47941-2024 tillsynsbegäran mail.docx", "A 47941-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 14121-2022 tillsynsbegäran mail.docx", "A 14121-2022")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 14121-2022</t>
+          <t>A 27071-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5701,10 +5691,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44651</v>
+        <v>46186</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5716,14 +5706,19 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I46" t="n">
-        <v>4.4</v>
+        <v>9.9</v>
       </c>
       <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
         <v>1</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -5753,46 +5748,46 @@
         <v>1</v>
       </c>
       <c r="U46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>Hårklomossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 14121-2022 artfynd.xlsx", "A 14121-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 27071-2026 artfynd.xlsx", "A 27071-2026")</f>
         <v/>
       </c>
       <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 14121-2022 karta.png", "A 14121-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 27071-2026 karta.png", "A 27071-2026")</f>
         <v/>
       </c>
       <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 14121-2022 georefererad karta.tif", "A 14121-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 27071-2026 georefererad karta.tif", "A 27071-2026")</f>
         <v/>
       </c>
       <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 14121-2022 FSC-klagomål.docx", "A 14121-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 27071-2026 FSC-klagomål.docx", "A 27071-2026")</f>
         <v/>
       </c>
       <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 14121-2022 FSC-klagomål mail.docx", "A 14121-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 27071-2026 FSC-klagomål mail.docx", "A 27071-2026")</f>
         <v/>
       </c>
       <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 14121-2022 tillsynsbegäran.docx", "A 14121-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 27071-2026 tillsynsbegäran.docx", "A 27071-2026")</f>
         <v/>
       </c>
       <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 14121-2022 tillsynsbegäran mail.docx", "A 14121-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 27071-2026 tillsynsbegäran mail.docx", "A 27071-2026")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 33297-2023</t>
+          <t>A 27072-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5806,10 +5801,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45116</v>
+        <v>46186</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5821,11 +5816,16 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K47" t="n">
         <v>0</v>
@@ -5834,7 +5834,7 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
         <v>0</v>
@@ -5846,10 +5846,10 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>1</v>
@@ -5862,42 +5862,46 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 33297-2023 artfynd.xlsx", "A 33297-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 27072-2026 artfynd.xlsx", "A 27072-2026")</f>
         <v/>
       </c>
       <c r="X47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 33297-2023 karta.png", "A 33297-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 27072-2026 karta.png", "A 27072-2026")</f>
         <v/>
       </c>
       <c r="Y47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 33297-2023 georefererad karta.tif", "A 33297-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 27072-2026 georefererad karta.tif", "A 27072-2026")</f>
         <v/>
       </c>
       <c r="AA47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 33297-2023 FSC-klagomål.docx", "A 33297-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 27072-2026 FSC-klagomål.docx", "A 27072-2026")</f>
         <v/>
       </c>
       <c r="AB47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 33297-2023 FSC-klagomål mail.docx", "A 33297-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 27072-2026 FSC-klagomål mail.docx", "A 27072-2026")</f>
         <v/>
       </c>
       <c r="AC47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 33297-2023 tillsynsbegäran.docx", "A 33297-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 27072-2026 tillsynsbegäran.docx", "A 27072-2026")</f>
         <v/>
       </c>
       <c r="AD47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 33297-2023 tillsynsbegäran mail.docx", "A 33297-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 27072-2026 tillsynsbegäran mail.docx", "A 27072-2026")</f>
+        <v/>
+      </c>
+      <c r="AE47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 27072-2026 prioriterade fågelarter.docx", "A 27072-2026")</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 27071-2026</t>
+          <t>A 26971-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5911,10 +5915,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46186</v>
+        <v>46185</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5926,13 +5930,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I48" t="n">
-        <v>9.9</v>
+        <v>2.1</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5972,42 +5971,42 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="W48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 27071-2026 artfynd.xlsx", "A 27071-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 26971-2026 artfynd.xlsx", "A 26971-2026")</f>
         <v/>
       </c>
       <c r="X48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 27071-2026 karta.png", "A 27071-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 26971-2026 karta.png", "A 26971-2026")</f>
         <v/>
       </c>
       <c r="Y48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 27071-2026 georefererad karta.tif", "A 27071-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 26971-2026 georefererad karta.tif", "A 26971-2026")</f>
         <v/>
       </c>
       <c r="AA48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 27071-2026 FSC-klagomål.docx", "A 27071-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 26971-2026 FSC-klagomål.docx", "A 26971-2026")</f>
         <v/>
       </c>
       <c r="AB48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 27071-2026 FSC-klagomål mail.docx", "A 27071-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 26971-2026 FSC-klagomål mail.docx", "A 26971-2026")</f>
         <v/>
       </c>
       <c r="AC48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 27071-2026 tillsynsbegäran.docx", "A 27071-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 26971-2026 tillsynsbegäran.docx", "A 26971-2026")</f>
         <v/>
       </c>
       <c r="AD48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 27071-2026 tillsynsbegäran mail.docx", "A 27071-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 26971-2026 tillsynsbegäran mail.docx", "A 26971-2026")</f>
         <v/>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 27072-2026</t>
+          <t>A 47941-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6021,10 +6020,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46186</v>
+        <v>45589</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6042,20 +6041,20 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>7.6</v>
+        <v>1.4</v>
       </c>
       <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
         <v>1</v>
       </c>
-      <c r="K49" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" t="n">
-        <v>0</v>
-      </c>
       <c r="N49" t="n">
         <v>0</v>
       </c>
@@ -6066,10 +6065,10 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S49" t="n">
         <v>1</v>
@@ -6078,50 +6077,46 @@
         <v>1</v>
       </c>
       <c r="U49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brunfläckig pärlemorfjäril</t>
         </is>
       </c>
       <c r="W49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 27072-2026 artfynd.xlsx", "A 27072-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 47941-2024 artfynd.xlsx", "A 47941-2024")</f>
         <v/>
       </c>
       <c r="X49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 27072-2026 karta.png", "A 27072-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 47941-2024 karta.png", "A 47941-2024")</f>
         <v/>
       </c>
       <c r="Y49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 27072-2026 georefererad karta.tif", "A 27072-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 47941-2024 georefererad karta.tif", "A 47941-2024")</f>
         <v/>
       </c>
       <c r="AA49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 27072-2026 FSC-klagomål.docx", "A 27072-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 47941-2024 FSC-klagomål.docx", "A 47941-2024")</f>
         <v/>
       </c>
       <c r="AB49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 27072-2026 FSC-klagomål mail.docx", "A 27072-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 47941-2024 FSC-klagomål mail.docx", "A 47941-2024")</f>
         <v/>
       </c>
       <c r="AC49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 27072-2026 tillsynsbegäran.docx", "A 27072-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 47941-2024 tillsynsbegäran.docx", "A 47941-2024")</f>
         <v/>
       </c>
       <c r="AD49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 27072-2026 tillsynsbegäran mail.docx", "A 27072-2026")</f>
-        <v/>
-      </c>
-      <c r="AE49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 27072-2026 prioriterade fågelarter.docx", "A 27072-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 47941-2024 tillsynsbegäran mail.docx", "A 47941-2024")</f>
         <v/>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 26971-2026</t>
+          <t>A 47915-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6135,10 +6130,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46185</v>
+        <v>45589</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6150,14 +6145,19 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>2.1</v>
+        <v>5.8</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
@@ -6191,42 +6191,42 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 26971-2026 artfynd.xlsx", "A 26971-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 47915-2024 artfynd.xlsx", "A 47915-2024")</f>
         <v/>
       </c>
       <c r="X50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 26971-2026 karta.png", "A 26971-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 47915-2024 karta.png", "A 47915-2024")</f>
         <v/>
       </c>
       <c r="Y50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 26971-2026 georefererad karta.tif", "A 26971-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 47915-2024 georefererad karta.tif", "A 47915-2024")</f>
         <v/>
       </c>
       <c r="AA50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 26971-2026 FSC-klagomål.docx", "A 26971-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 47915-2024 FSC-klagomål.docx", "A 47915-2024")</f>
         <v/>
       </c>
       <c r="AB50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 26971-2026 FSC-klagomål mail.docx", "A 26971-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 47915-2024 FSC-klagomål mail.docx", "A 47915-2024")</f>
         <v/>
       </c>
       <c r="AC50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 26971-2026 tillsynsbegäran.docx", "A 26971-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 47915-2024 tillsynsbegäran.docx", "A 47915-2024")</f>
         <v/>
       </c>
       <c r="AD50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 26971-2026 tillsynsbegäran mail.docx", "A 26971-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 47915-2024 tillsynsbegäran mail.docx", "A 47915-2024")</f>
         <v/>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 2357-2022</t>
+          <t>A 53838-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6240,10 +6240,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>44578</v>
+        <v>45614</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6256,7 +6256,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="J51" t="n">
         <v>1</v>
@@ -6300,42 +6300,42 @@
         </is>
       </c>
       <c r="W51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 2357-2022 artfynd.xlsx", "A 2357-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 53838-2024 artfynd.xlsx", "A 53838-2024")</f>
         <v/>
       </c>
       <c r="X51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 2357-2022 karta.png", "A 2357-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 53838-2024 karta.png", "A 53838-2024")</f>
         <v/>
       </c>
       <c r="Y51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 2357-2022 georefererad karta.tif", "A 2357-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 53838-2024 georefererad karta.tif", "A 53838-2024")</f>
         <v/>
       </c>
       <c r="AA51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 2357-2022 FSC-klagomål.docx", "A 2357-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 53838-2024 FSC-klagomål.docx", "A 53838-2024")</f>
         <v/>
       </c>
       <c r="AB51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 2357-2022 FSC-klagomål mail.docx", "A 2357-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 53838-2024 FSC-klagomål mail.docx", "A 53838-2024")</f>
         <v/>
       </c>
       <c r="AC51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 2357-2022 tillsynsbegäran.docx", "A 2357-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 53838-2024 tillsynsbegäran.docx", "A 53838-2024")</f>
         <v/>
       </c>
       <c r="AD51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 2357-2022 tillsynsbegäran mail.docx", "A 2357-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 53838-2024 tillsynsbegäran mail.docx", "A 53838-2024")</f>
         <v/>
       </c>
       <c r="AE51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 2357-2022 prioriterade fågelarter.docx", "A 2357-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 53838-2024 prioriterade fågelarter.docx", "A 53838-2024")</f>
         <v/>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 53838-2024</t>
+          <t>A 2357-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6349,10 +6349,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45614</v>
+        <v>44578</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6365,7 +6365,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="J52" t="n">
         <v>1</v>
@@ -6409,35 +6409,35 @@
         </is>
       </c>
       <c r="W52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 53838-2024 artfynd.xlsx", "A 53838-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 2357-2022 artfynd.xlsx", "A 2357-2022")</f>
         <v/>
       </c>
       <c r="X52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 53838-2024 karta.png", "A 53838-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 2357-2022 karta.png", "A 2357-2022")</f>
         <v/>
       </c>
       <c r="Y52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 53838-2024 georefererad karta.tif", "A 53838-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 2357-2022 georefererad karta.tif", "A 2357-2022")</f>
         <v/>
       </c>
       <c r="AA52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 53838-2024 FSC-klagomål.docx", "A 53838-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 2357-2022 FSC-klagomål.docx", "A 2357-2022")</f>
         <v/>
       </c>
       <c r="AB52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 53838-2024 FSC-klagomål mail.docx", "A 53838-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 2357-2022 FSC-klagomål mail.docx", "A 2357-2022")</f>
         <v/>
       </c>
       <c r="AC52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 53838-2024 tillsynsbegäran.docx", "A 53838-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 2357-2022 tillsynsbegäran.docx", "A 2357-2022")</f>
         <v/>
       </c>
       <c r="AD52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 53838-2024 tillsynsbegäran mail.docx", "A 53838-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 2357-2022 tillsynsbegäran mail.docx", "A 2357-2022")</f>
         <v/>
       </c>
       <c r="AE52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 53838-2024 prioriterade fågelarter.docx", "A 53838-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 2357-2022 prioriterade fågelarter.docx", "A 2357-2022")</f>
         <v/>
       </c>
     </row>
@@ -6461,7 +6461,7 @@
         <v>44805</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
         <v>44805</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6607,7 +6607,7 @@
         <v>44861</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6680,7 +6680,7 @@
         <v>44607</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         <v>44692</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
         <v>44470</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         <v>44609</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6982,7 +6982,7 @@
         <v>44497</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7055,7 +7055,7 @@
         <v>44594</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7128,7 +7128,7 @@
         <v>44853</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7201,7 +7201,7 @@
         <v>44515</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7274,7 +7274,7 @@
         <v>44466</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7352,7 +7352,7 @@
         <v>44643</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7425,7 +7425,7 @@
         <v>44470</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7503,7 +7503,7 @@
         <v>44529</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7581,7 +7581,7 @@
         <v>44525</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7654,7 +7654,7 @@
         <v>44509</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7732,7 +7732,7 @@
         <v>44505</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7793,7 +7793,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 45861-2023</t>
+          <t>A 7975-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7803,14 +7803,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45195</v>
+        <v>45707</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.7</v>
+        <v>5.3</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7871,7 +7871,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 6394-2024</t>
+          <t>A 18675-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7881,14 +7881,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45338</v>
+        <v>45763</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7900,13 +7900,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>0.9</v>
+        <v>6</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7949,7 +7944,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 18675-2025</t>
+          <t>A 29607-2022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7963,10 +7958,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45763</v>
+        <v>44754</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7978,8 +7973,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>6</v>
+        <v>2.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -8022,7 +8022,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 38743-2022</t>
+          <t>A 37672-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -8032,14 +8032,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44816</v>
+        <v>45541</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8057,7 +8057,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -8100,7 +8100,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 13405-2024</t>
+          <t>A 56478-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -8114,10 +8114,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45387</v>
+        <v>45624</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8130,7 +8130,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -8173,7 +8173,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 26176-2024</t>
+          <t>A 8062-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -8187,10 +8187,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45468</v>
+        <v>45351</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8208,7 +8208,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -8251,7 +8251,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 10321-2023</t>
+          <t>A 48118-2023</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8265,10 +8265,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44986</v>
+        <v>45205</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8280,8 +8280,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -8324,7 +8329,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 57234-2024</t>
+          <t>A 23460-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8338,10 +8343,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45629</v>
+        <v>45453</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8353,13 +8358,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -8402,7 +8402,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 6387-2024</t>
+          <t>A 24707-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -8412,14 +8412,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45338</v>
+        <v>45798</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8431,13 +8431,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -8480,7 +8475,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 59158-2022</t>
+          <t>A 5218-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8490,14 +8485,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44904</v>
+        <v>45330</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8515,7 +8510,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8558,7 +8553,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 5277-2024</t>
+          <t>A 38874-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8572,10 +8567,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45330</v>
+        <v>45887</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8587,8 +8582,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I81" t="n">
-        <v>0.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8631,7 +8631,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 3177-2022</t>
+          <t>A 10321-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8645,10 +8645,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44582</v>
+        <v>44986</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8661,7 +8661,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>3.7</v>
+        <v>1.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8704,7 +8704,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 50378-2024</t>
+          <t>A 26820-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8718,10 +8718,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45601</v>
+        <v>45810</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8733,13 +8733,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>4.9</v>
+        <v>0.7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8782,7 +8777,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 43768-2024</t>
+          <t>A 26783-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8796,10 +8791,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45569</v>
+        <v>45810</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8812,7 +8807,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8855,7 +8850,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 28367-2025</t>
+          <t>A 770-2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8869,10 +8864,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45819</v>
+        <v>46027</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8884,13 +8879,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I85" t="n">
-        <v>6.1</v>
+        <v>2.2</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8933,7 +8923,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 28368-2025</t>
+          <t>A 36437-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8947,10 +8937,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45819</v>
+        <v>45535</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8962,13 +8952,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>8.1</v>
+        <v>2.3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -9011,7 +8996,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 23066-2022</t>
+          <t>A 38921-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -9025,10 +9010,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>44719</v>
+        <v>45163</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9040,8 +9025,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -9084,7 +9074,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 38874-2025</t>
+          <t>A 28367-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -9098,10 +9088,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45887</v>
+        <v>45819</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9119,7 +9109,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>8.300000000000001</v>
+        <v>6.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -9162,7 +9152,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 38875-2025</t>
+          <t>A 28368-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -9176,10 +9166,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45887</v>
+        <v>45819</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9197,7 +9187,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.9</v>
+        <v>8.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -9240,7 +9230,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 47935-2024</t>
+          <t>A 41767-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -9254,10 +9244,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45589</v>
+        <v>45902</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9275,7 +9265,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -9318,7 +9308,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 21952-2024</t>
+          <t>A 41766-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -9328,14 +9318,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45443</v>
+        <v>45902</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9353,7 +9343,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.7</v>
+        <v>3.2</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -9396,7 +9386,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 33404-2025</t>
+          <t>A 23066-2022</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -9410,10 +9400,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45841</v>
+        <v>44719</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9426,7 +9416,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -9469,7 +9459,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 52566-2023</t>
+          <t>A 43694-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -9483,10 +9473,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45219</v>
+        <v>45912</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9498,8 +9488,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I93" t="n">
-        <v>1.5</v>
+        <v>6.6</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -9542,7 +9537,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 41766-2025</t>
+          <t>A 43691-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -9556,10 +9551,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45902</v>
+        <v>45912</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9577,7 +9572,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -9620,7 +9615,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 62972-2023</t>
+          <t>A 43689-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9634,10 +9629,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45272</v>
+        <v>45912</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9649,8 +9644,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I95" t="n">
-        <v>0.3</v>
+        <v>1.4</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -9693,7 +9693,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 41767-2025</t>
+          <t>A 33404-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9707,10 +9707,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45902</v>
+        <v>45841</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9722,13 +9722,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I96" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9771,7 +9766,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 59863-2024</t>
+          <t>A 2565-2022</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9785,10 +9780,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45639</v>
+        <v>44579</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9801,7 +9796,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9844,7 +9839,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 50377-2024</t>
+          <t>A 59863-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9858,10 +9853,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45601</v>
+        <v>45639</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9873,13 +9868,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I98" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9922,7 +9912,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 43691-2025</t>
+          <t>A 48625-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9936,10 +9926,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45912</v>
+        <v>45936</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9951,13 +9941,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I99" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -10000,7 +9985,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 43689-2025</t>
+          <t>A 37333-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -10010,14 +9995,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45912</v>
+        <v>45876</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10029,13 +10014,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I100" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -10078,7 +10058,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 43694-2025</t>
+          <t>A 37265-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -10092,10 +10072,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45912</v>
+        <v>45876</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10107,13 +10087,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>6.6</v>
+        <v>1.3</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -10156,7 +10131,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 37333-2025</t>
+          <t>A 60907-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -10170,10 +10145,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45876</v>
+        <v>45261</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10185,8 +10160,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -10229,7 +10209,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 37265-2025</t>
+          <t>A 15594-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -10243,10 +10223,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45876</v>
+        <v>45747</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10259,7 +10239,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -10302,7 +10282,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 15594-2025</t>
+          <t>A 9273-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -10316,10 +10296,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45747</v>
+        <v>46070</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10332,7 +10312,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -10375,7 +10355,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 11085-2023</t>
+          <t>A 12159-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -10389,10 +10369,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>44986</v>
+        <v>46086</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10404,8 +10384,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I105" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -10448,7 +10433,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 48625-2025</t>
+          <t>A 12160-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -10462,10 +10447,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45936</v>
+        <v>46086</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10477,8 +10462,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I106" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -10521,7 +10511,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 50764-2024</t>
+          <t>A 51040-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -10535,10 +10525,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45602</v>
+        <v>45947</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10556,7 +10546,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -10599,7 +10589,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 9273-2026</t>
+          <t>A 38875-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10613,10 +10603,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46070</v>
+        <v>45887</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10628,8 +10618,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I108" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -10672,7 +10667,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 12159-2026</t>
+          <t>A 26176-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10686,10 +10681,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46086</v>
+        <v>45468</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10707,7 +10702,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -10750,7 +10745,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 12160-2026</t>
+          <t>A 3177-2022</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10764,10 +10759,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46086</v>
+        <v>44582</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10779,13 +10774,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I110" t="n">
-        <v>0.9</v>
+        <v>3.7</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10828,7 +10818,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 13039-2026</t>
+          <t>A 50766-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10842,10 +10832,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46093</v>
+        <v>45602</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10863,7 +10853,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>5.1</v>
+        <v>2.1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10906,7 +10896,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 38921-2023</t>
+          <t>A 8184-2022</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10920,10 +10910,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45163</v>
+        <v>44609</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10935,13 +10925,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I112" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10984,7 +10969,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 13040-2026</t>
+          <t>A 52523-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10998,10 +10983,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46093</v>
+        <v>45609</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11019,7 +11004,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>7.1</v>
+        <v>4.4</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -11079,7 +11064,7 @@
         <v>46092</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11140,7 +11125,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 51040-2025</t>
+          <t>A 13293-2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -11154,10 +11139,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45947</v>
+        <v>46094</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11218,7 +11203,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 13293-2026</t>
+          <t>A 13040-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -11232,10 +11217,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46094</v>
+        <v>46093</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11253,7 +11238,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1.1</v>
+        <v>7.1</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -11296,7 +11281,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 52099-2025</t>
+          <t>A 13039-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -11310,10 +11295,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45952</v>
+        <v>46093</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11325,8 +11310,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I117" t="n">
-        <v>2.6</v>
+        <v>5.1</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -11369,7 +11359,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 63905-2021</t>
+          <t>A 52099-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -11383,10 +11373,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>44509</v>
+        <v>45952</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11398,13 +11388,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I118" t="n">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -11447,7 +11432,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 55341-2025</t>
+          <t>A 54515-2023</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -11461,10 +11446,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45971</v>
+        <v>45233</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11476,13 +11461,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I119" t="n">
-        <v>3.4</v>
+        <v>1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -11525,7 +11505,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 20577-2023</t>
+          <t>A 54994-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -11535,14 +11515,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45057</v>
+        <v>45621</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11560,7 +11540,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -11603,7 +11583,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 10797-2023</t>
+          <t>A 18913-2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -11617,10 +11597,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44989</v>
+        <v>46129</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11632,8 +11612,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I121" t="n">
-        <v>9.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -11676,7 +11661,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 44457-2022</t>
+          <t>A 55341-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -11690,10 +11675,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>44839</v>
+        <v>45971</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11705,8 +11690,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I122" t="n">
-        <v>6.8</v>
+        <v>3.4</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -11749,7 +11739,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 57086-2025</t>
+          <t>A 18506-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11759,14 +11749,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45979</v>
+        <v>46127</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11779,7 +11769,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>6.1</v>
+        <v>1.6</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -11822,7 +11812,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 29482-2023</t>
+          <t>A 19227-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11836,10 +11826,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45106</v>
+        <v>46132</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11852,7 +11842,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -11895,7 +11885,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 18506-2026</t>
+          <t>A 13236-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11909,10 +11899,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46127</v>
+        <v>45735</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11924,8 +11914,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I125" t="n">
-        <v>1.6</v>
+        <v>18.5</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11968,7 +11963,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 19227-2026</t>
+          <t>A 57086-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11978,14 +11973,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46132</v>
+        <v>45979</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11998,7 +11993,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>2.4</v>
+        <v>6.1</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -12041,7 +12036,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 18913-2026</t>
+          <t>A 38233-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -12051,14 +12046,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>46129</v>
+        <v>45160</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12070,13 +12065,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I127" t="n">
-        <v>8.300000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -12119,7 +12109,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 60708-2025</t>
+          <t>A 10674-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -12129,14 +12119,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45996</v>
+        <v>45369</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12148,8 +12138,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I128" t="n">
-        <v>1.9</v>
+        <v>0.3</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -12192,7 +12187,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 60736-2025</t>
+          <t>A 60933-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -12206,10 +12201,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45996</v>
+        <v>45645</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12221,8 +12216,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I129" t="n">
-        <v>5.8</v>
+        <v>1.9</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -12265,7 +12265,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 13236-2025</t>
+          <t>A 60736-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -12279,10 +12279,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45735</v>
+        <v>45996</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12294,13 +12294,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I130" t="n">
-        <v>18.5</v>
+        <v>5.8</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -12343,7 +12338,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 48118-2023</t>
+          <t>A 60708-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -12357,10 +12352,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45205</v>
+        <v>45996</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12372,13 +12367,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I131" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -12421,7 +12411,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 38917-2023</t>
+          <t>A 73693-2021</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -12435,10 +12425,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45163</v>
+        <v>44552</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12450,13 +12440,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I132" t="n">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -12499,7 +12484,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 11084-2023</t>
+          <t>A 38917-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -12513,10 +12498,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44986</v>
+        <v>45163</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12528,8 +12513,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I133" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -12572,7 +12562,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 56478-2024</t>
+          <t>A 60937-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -12586,10 +12576,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45624</v>
+        <v>45645</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12601,8 +12591,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I134" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -12645,7 +12640,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 43752-2025</t>
+          <t>A 60940-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -12659,10 +12654,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45912</v>
+        <v>45645</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12674,8 +12669,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I135" t="n">
-        <v>3.1</v>
+        <v>1.2</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -12718,7 +12718,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 770-2026</t>
+          <t>A 54082-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12732,10 +12732,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>46027</v>
+        <v>45616</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12748,7 +12748,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>2.2</v>
+        <v>6.3</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -12791,7 +12791,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 60933-2024</t>
+          <t>A 43752-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12805,10 +12805,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45645</v>
+        <v>45912</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12820,13 +12820,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I137" t="n">
-        <v>1.9</v>
+        <v>3.1</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -12869,7 +12864,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 61750-2021</t>
+          <t>A 52566-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12883,10 +12878,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44501</v>
+        <v>45219</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12898,13 +12893,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I138" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -12947,7 +12937,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 54082-2024</t>
+          <t>A 20567-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12961,10 +12951,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45616</v>
+        <v>46140</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12976,8 +12966,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I139" t="n">
-        <v>6.3</v>
+        <v>7.8</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -13020,7 +13015,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 29607-2022</t>
+          <t>A 20568-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -13034,10 +13029,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>44754</v>
+        <v>46140</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13055,7 +13050,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>2.1</v>
+        <v>6.3</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -13098,7 +13093,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 6240-2024</t>
+          <t>A 20478-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -13112,10 +13107,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45337</v>
+        <v>46140</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13127,8 +13122,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I141" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -13171,7 +13171,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 20478-2026</t>
+          <t>A 57234-2024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -13185,10 +13185,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46140</v>
+        <v>45629</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13206,7 +13206,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -13249,7 +13249,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 33658-2024</t>
+          <t>A 21440-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -13263,10 +13263,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45520</v>
+        <v>46148</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13278,8 +13278,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I143" t="n">
-        <v>2.2</v>
+        <v>6.5</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -13322,7 +13327,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 38233-2023</t>
+          <t>A 21402-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -13332,14 +13337,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45160</v>
+        <v>46148</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13352,7 +13357,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -13395,7 +13400,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 20567-2026</t>
+          <t>A 21660-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -13409,10 +13414,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46140</v>
+        <v>46149</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13430,7 +13435,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>7.8</v>
+        <v>2.9</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -13473,7 +13478,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 20568-2026</t>
+          <t>A 21442-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -13487,10 +13492,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46140</v>
+        <v>46148</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13508,7 +13513,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>6.3</v>
+        <v>4.1</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -13551,7 +13556,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 50766-2024</t>
+          <t>A 21401-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -13565,10 +13570,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45602</v>
+        <v>46148</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13580,13 +13585,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I147" t="n">
-        <v>2.1</v>
+        <v>3.5</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -13629,7 +13629,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 50207-2024</t>
+          <t>A 8074-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -13643,10 +13643,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45600</v>
+        <v>45351</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13658,8 +13658,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I148" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -13702,7 +13707,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 50208-2024</t>
+          <t>A 44841-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -13716,10 +13721,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45600</v>
+        <v>45190</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13731,8 +13736,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I149" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -13775,7 +13785,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 21402-2026</t>
+          <t>A 46222-2024</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -13789,10 +13799,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>46148</v>
+        <v>45581</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13804,8 +13814,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I150" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -13848,7 +13863,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 21440-2026</t>
+          <t>A 46219-2024</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -13862,10 +13877,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46148</v>
+        <v>45581</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13883,7 +13898,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>6.5</v>
+        <v>2.4</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -13926,7 +13941,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 21442-2026</t>
+          <t>A 23230-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13940,10 +13955,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46148</v>
+        <v>46162</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13961,7 +13976,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>4.1</v>
+        <v>0.9</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -14004,7 +14019,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 21401-2026</t>
+          <t>A 23229-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -14018,10 +14033,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46148</v>
+        <v>46162</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14033,8 +14048,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I153" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -14077,7 +14097,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 21660-2026</t>
+          <t>A 14678-2025</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -14087,14 +14107,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46149</v>
+        <v>45742</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14112,7 +14132,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -14155,7 +14175,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 44841-2023</t>
+          <t>A 23854-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -14169,10 +14189,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45190</v>
+        <v>46167</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14190,7 +14210,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.5</v>
+        <v>20.9</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -14233,7 +14253,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 46222-2024</t>
+          <t>A 21952-2024</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -14243,14 +14263,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45581</v>
+        <v>45443</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14268,7 +14288,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -14311,7 +14331,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 46219-2024</t>
+          <t>A 24460-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -14325,10 +14345,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45581</v>
+        <v>46170</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14340,13 +14360,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I157" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -14389,7 +14404,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 12143-2025</t>
+          <t>A 24462-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -14399,14 +14414,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45729</v>
+        <v>46170</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14418,13 +14433,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I158" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -14467,7 +14477,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 52523-2024</t>
+          <t>A 24689-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -14481,10 +14491,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45609</v>
+        <v>46171</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14502,7 +14512,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>4.4</v>
+        <v>15.5</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -14545,7 +14555,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 14678-2025</t>
+          <t>A 26857-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -14555,14 +14565,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45742</v>
+        <v>46185</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14580,7 +14590,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.9</v>
+        <v>15.1</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -14623,7 +14633,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 8184-2022</t>
+          <t>A 26946-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -14637,10 +14647,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>44609</v>
+        <v>46185</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14652,8 +14662,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I161" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -14696,7 +14711,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 60937-2024</t>
+          <t>A 26947-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -14710,10 +14725,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45645</v>
+        <v>46185</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14731,7 +14746,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -14774,7 +14789,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 60940-2024</t>
+          <t>A 27411-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -14788,10 +14803,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>45645</v>
+        <v>46189</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14809,7 +14824,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -14852,7 +14867,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 23230-2026</t>
+          <t>A 28789-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -14866,10 +14881,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46162</v>
+        <v>46195</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14881,13 +14896,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I164" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -14930,7 +14940,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 23229-2026</t>
+          <t>A 27745-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -14944,10 +14954,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46162</v>
+        <v>46191</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14965,7 +14975,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>2.9</v>
+        <v>1.7</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -15008,7 +15018,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 23854-2026</t>
+          <t>A 27746-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -15022,10 +15032,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46167</v>
+        <v>46191</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15043,7 +15053,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>20.9</v>
+        <v>1</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -15086,7 +15096,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 44807-2023</t>
+          <t>A 32506-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -15100,10 +15110,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45190</v>
+        <v>46239</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15121,7 +15131,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>5.4</v>
+        <v>1.1</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -15164,7 +15174,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 51652-2023</t>
+          <t>A 32508-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -15178,10 +15188,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45222</v>
+        <v>46239</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15199,7 +15209,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>1.7</v>
+        <v>1.1</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -15242,7 +15252,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 24462-2026</t>
+          <t>A 28696-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -15256,10 +15266,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46170</v>
+        <v>46198</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15271,8 +15281,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I169" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -15315,7 +15330,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 24689-2026</t>
+          <t>A 28708-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -15329,10 +15344,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46171</v>
+        <v>46198</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15350,7 +15365,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>15.5</v>
+        <v>2.8</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -15393,7 +15408,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 24460-2026</t>
+          <t>A 32810-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -15407,10 +15422,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46170</v>
+        <v>46241</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15423,7 +15438,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1.1</v>
+        <v>6.1</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -15466,7 +15481,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 33293-2023</t>
+          <t>A 28695-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -15480,10 +15495,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45116</v>
+        <v>46198</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15495,8 +15510,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I172" t="n">
-        <v>17.2</v>
+        <v>2.7</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -15539,7 +15559,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 32154-2023</t>
+          <t>A 62972-2023</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -15553,10 +15573,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45119</v>
+        <v>45272</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15569,7 +15589,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>2.3</v>
+        <v>0.3</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -15612,7 +15632,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 26857-2026</t>
+          <t>A 29130-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -15626,10 +15646,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46185</v>
+        <v>46202</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15647,7 +15667,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>15.1</v>
+        <v>10.3</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -15690,7 +15710,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 8062-2024</t>
+          <t>A 28930-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -15704,10 +15724,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45351</v>
+        <v>46199</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15719,13 +15739,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I175" t="n">
-        <v>0.8</v>
+        <v>2.7</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -15768,7 +15783,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 8074-2024</t>
+          <t>A 29132-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -15782,10 +15797,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45351</v>
+        <v>46202</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15803,7 +15818,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>0.7</v>
+        <v>11.9</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -15846,7 +15861,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 60907-2023</t>
+          <t>A 12143-2025</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -15856,14 +15871,14 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45261</v>
+        <v>45729</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15881,7 +15896,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -15924,7 +15939,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 26947-2026</t>
+          <t>A 29552-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -15938,10 +15953,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46185</v>
+        <v>46204</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15959,7 +15974,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -16002,7 +16017,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 26946-2026</t>
+          <t>A 51653-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -16016,10 +16031,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46185</v>
+        <v>45222</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16037,7 +16052,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1.8</v>
+        <v>3.9</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -16080,7 +16095,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 27411-2026</t>
+          <t>A 20577-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -16090,14 +16105,14 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46189</v>
+        <v>45057</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16115,7 +16130,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -16158,7 +16173,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 32211-2022</t>
+          <t>A 45365-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -16172,10 +16187,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>44781</v>
+        <v>45192</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16188,7 +16203,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>2.3</v>
+        <v>5</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -16231,7 +16246,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 27745-2026</t>
+          <t>A 6387-2024</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -16241,14 +16256,14 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46191</v>
+        <v>45338</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16266,7 +16281,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -16309,7 +16324,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 27746-2026</t>
+          <t>A 35213-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -16323,10 +16338,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46191</v>
+        <v>46260</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16344,7 +16359,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>1</v>
+        <v>9.5</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -16387,7 +16402,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 28789-2026</t>
+          <t>A 6240-2024</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -16401,10 +16416,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46195</v>
+        <v>45337</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16417,7 +16432,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -16460,7 +16475,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 32508-2026</t>
+          <t>A 36339-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -16474,10 +16489,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46239</v>
+        <v>46268</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16489,13 +16504,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I185" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -16538,7 +16548,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 32506-2026</t>
+          <t>A 36345-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -16552,10 +16562,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46239</v>
+        <v>46268</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16567,13 +16577,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I186" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -16616,7 +16621,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 32810-2026</t>
+          <t>A 6394-2024</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -16626,14 +16631,14 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46241</v>
+        <v>45338</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16645,8 +16650,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I187" t="n">
-        <v>6.1</v>
+        <v>0.9</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -16689,7 +16699,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 73693-2021</t>
+          <t>A 36336-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -16703,10 +16713,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>44552</v>
+        <v>46268</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16719,7 +16729,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>3.6</v>
+        <v>1.1</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -16762,7 +16772,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 28696-2026</t>
+          <t>A 11085-2023</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -16776,10 +16786,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46198</v>
+        <v>44986</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16791,13 +16801,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I189" t="n">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -16840,7 +16845,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 28708-2026</t>
+          <t>A 31813-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -16854,10 +16859,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46198</v>
+        <v>46230</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16869,13 +16874,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I190" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -16918,7 +16918,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 36437-2024</t>
+          <t>A 31870-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -16932,10 +16932,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45535</v>
+        <v>46231</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16947,8 +16947,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I191" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -16991,7 +16996,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 28930-2026</t>
+          <t>A 31871-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -17005,10 +17010,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46199</v>
+        <v>46231</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17020,8 +17025,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I192" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -17064,7 +17074,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 28695-2026</t>
+          <t>A 31872-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -17078,10 +17088,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46198</v>
+        <v>46231</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17099,7 +17109,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>2.7</v>
+        <v>5.2</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -17142,7 +17152,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 29130-2026</t>
+          <t>A 5277-2024</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -17156,10 +17166,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46202</v>
+        <v>45330</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17171,13 +17181,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I194" t="n">
-        <v>10.3</v>
+        <v>0.5</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -17220,7 +17225,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 45365-2023</t>
+          <t>A 50378-2024</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -17234,10 +17239,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45192</v>
+        <v>45601</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17249,8 +17254,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I195" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -17293,7 +17303,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 29132-2026</t>
+          <t>A 37809-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -17307,10 +17317,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46202</v>
+        <v>46279</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17322,13 +17332,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I196" t="n">
-        <v>11.9</v>
+        <v>2.9</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -17371,7 +17376,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 52131-2021</t>
+          <t>A 33293-2023</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -17385,10 +17390,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>44463</v>
+        <v>45116</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17401,7 +17406,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>1.6</v>
+        <v>17.2</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -17444,7 +17449,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 37672-2024</t>
+          <t>A 44807-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -17454,14 +17459,14 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45541</v>
+        <v>45190</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17479,7 +17484,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>0.6</v>
+        <v>5.4</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -17522,7 +17527,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 29552-2026</t>
+          <t>A 51652-2023</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -17536,10 +17541,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46204</v>
+        <v>45222</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17557,7 +17562,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -17600,7 +17605,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 2565-2022</t>
+          <t>A 44457-2022</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -17614,10 +17619,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>44579</v>
+        <v>44839</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17630,7 +17635,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>1.4</v>
+        <v>6.8</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -17673,7 +17678,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 10674-2024</t>
+          <t>A 32211-2022</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -17683,14 +17688,14 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45369</v>
+        <v>44781</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17702,13 +17707,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H201" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I201" t="n">
-        <v>0.3</v>
+        <v>2.3</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -17751,7 +17751,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 18773-2025</t>
+          <t>A 13405-2024</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -17765,10 +17765,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45763</v>
+        <v>45387</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>13</v>
+        <v>0.9</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -17824,7 +17824,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 51653-2023</t>
+          <t>A 12729-2024</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -17838,10 +17838,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45222</v>
+        <v>45384</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17859,7 +17859,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>3.9</v>
+        <v>2.5</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -17902,7 +17902,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 12108-2024</t>
+          <t>A 63905-2021</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -17916,10 +17916,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45376</v>
+        <v>44509</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17931,8 +17931,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I204" t="n">
-        <v>7.7</v>
+        <v>3.7</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -17975,7 +17980,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 54994-2024</t>
+          <t>A 38743-2022</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -17989,10 +17994,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45621</v>
+        <v>44816</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18010,7 +18015,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -18053,7 +18058,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 35213-2026</t>
+          <t>A 47935-2024</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -18067,10 +18072,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>46260</v>
+        <v>45589</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18088,7 +18093,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>9.5</v>
+        <v>2.2</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -18131,7 +18136,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 8059-2024</t>
+          <t>A 50377-2024</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -18145,10 +18150,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45351</v>
+        <v>45601</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18166,7 +18171,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -18209,7 +18214,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 36339-2026</t>
+          <t>A 8059-2024</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -18223,10 +18228,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>46268</v>
+        <v>45351</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18238,8 +18243,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I208" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -18282,7 +18292,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 36336-2026</t>
+          <t>A 29482-2023</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -18296,10 +18306,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>46268</v>
+        <v>45106</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18312,7 +18322,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -18355,7 +18365,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 36345-2026</t>
+          <t>A 59158-2022</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -18365,14 +18375,14 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>46268</v>
+        <v>44904</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18384,8 +18394,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I210" t="n">
-        <v>0.3</v>
+        <v>3.7</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -18428,7 +18443,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 54515-2023</t>
+          <t>A 18773-2025</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -18442,10 +18457,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45233</v>
+        <v>45763</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18458,7 +18473,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -18501,7 +18516,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 38738-2022</t>
+          <t>A 10320-2023</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -18515,10 +18530,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>44816</v>
+        <v>44986</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18530,13 +18545,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H212" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I212" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -18579,7 +18589,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 31813-2026</t>
+          <t>A 10797-2023</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -18593,10 +18603,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>46230</v>
+        <v>44989</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18609,7 +18619,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>1.8</v>
+        <v>9.5</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -18652,7 +18662,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 31870-2026</t>
+          <t>A 11084-2023</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -18666,10 +18676,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>46231</v>
+        <v>44986</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18681,13 +18691,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I214" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -18730,7 +18735,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 31871-2026</t>
+          <t>A 50764-2024</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -18744,10 +18749,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>46231</v>
+        <v>45602</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18765,7 +18770,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -18808,7 +18813,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 31872-2026</t>
+          <t>A 33658-2024</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -18822,10 +18827,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>46231</v>
+        <v>45520</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18837,13 +18842,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I216" t="n">
-        <v>5.2</v>
+        <v>2.2</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -18886,7 +18886,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 12729-2024</t>
+          <t>A 45861-2023</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -18896,14 +18896,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45384</v>
+        <v>45195</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18921,7 +18921,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -18964,7 +18964,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 10320-2023</t>
+          <t>A 43768-2024</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -18978,10 +18978,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>44986</v>
+        <v>45569</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18994,7 +18994,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>2.6</v>
+        <v>7</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -19037,7 +19037,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 7472-2025</t>
+          <t>A 38738-2022</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -19051,10 +19051,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45705</v>
+        <v>44816</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19072,7 +19072,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>2.6</v>
+        <v>0.9</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -19115,7 +19115,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 7975-2025</t>
+          <t>A 52131-2021</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -19129,10 +19129,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45707</v>
+        <v>44463</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19144,13 +19144,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H220" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I220" t="n">
-        <v>5.3</v>
+        <v>1.6</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -19193,7 +19188,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 18831-2025</t>
+          <t>A 61750-2021</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -19207,10 +19202,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45764</v>
+        <v>44501</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19228,7 +19223,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>4.2</v>
+        <v>1.8</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -19271,7 +19266,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 58629-2024</t>
+          <t>A 7472-2025</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -19285,10 +19280,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45635</v>
+        <v>45705</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19306,7 +19301,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>1.4</v>
+        <v>2.6</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -19349,7 +19344,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 27438-2024</t>
+          <t>A 50207-2024</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -19363,10 +19358,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45474</v>
+        <v>45600</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19379,7 +19374,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -19422,7 +19417,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 50102-2023</t>
+          <t>A 50208-2024</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -19436,10 +19431,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45215</v>
+        <v>45600</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19451,13 +19446,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H224" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I224" t="n">
-        <v>3.9</v>
+        <v>0.4</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -19500,7 +19490,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 51996-2023</t>
+          <t>A 12108-2024</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -19514,10 +19504,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45223</v>
+        <v>45376</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19529,13 +19519,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H225" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I225" t="n">
-        <v>2</v>
+        <v>7.7</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -19578,7 +19563,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 62982-2023</t>
+          <t>A 18831-2025</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -19592,10 +19577,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45272</v>
+        <v>45764</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19607,8 +19592,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I226" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -19651,7 +19641,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 46288-2024</t>
+          <t>A 32154-2023</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -19665,10 +19655,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45581</v>
+        <v>45119</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19680,13 +19670,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H227" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I227" t="n">
-        <v>3.7</v>
+        <v>2.3</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -19729,7 +19714,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 21935-2024</t>
+          <t>A 27438-2024</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -19743,10 +19728,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45443</v>
+        <v>45474</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19758,13 +19743,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H228" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I228" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -19807,7 +19787,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 23460-2024</t>
+          <t>A 46288-2024</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -19821,10 +19801,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45453</v>
+        <v>45581</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19836,8 +19816,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I229" t="n">
-        <v>0.7</v>
+        <v>3.7</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -19880,7 +19865,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 5218-2024</t>
+          <t>A 51996-2023</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -19894,10 +19879,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45330</v>
+        <v>45223</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19915,7 +19900,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -19958,7 +19943,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 24707-2025</t>
+          <t>A 58629-2024</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -19972,10 +19957,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45798</v>
+        <v>45635</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19987,8 +19972,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I231" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -20031,7 +20021,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 26783-2025</t>
+          <t>A 50102-2023</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -20045,10 +20035,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45810</v>
+        <v>45215</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20060,8 +20050,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I232" t="n">
-        <v>2.5</v>
+        <v>3.9</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -20104,7 +20099,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 26820-2025</t>
+          <t>A 62982-2023</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -20118,10 +20113,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45810</v>
+        <v>45272</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20134,7 +20129,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>0.7</v>
+        <v>3.5</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -20177,24 +20172,24 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>S 479-2022</t>
+          <t>A 21935-2024</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Skogsbilväg</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>44587</v>
+        <v>45443</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20206,8 +20201,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I234" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -20250,7 +20250,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>S 1697-2025</t>
+          <t>S 479-2022</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -20260,14 +20260,14 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Skogsbilväg</t>
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45805</v>
+        <v>44587</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20279,13 +20279,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H235" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I235" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -20328,7 +20323,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>S 1694-2025</t>
+          <t>S 1697-2025</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -20345,7 +20340,7 @@
         <v>45805</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20363,7 +20358,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -20406,7 +20401,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>S 794-2025</t>
+          <t>S 1694-2025</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -20420,10 +20415,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45729</v>
+        <v>45805</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20441,7 +20436,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -20484,7 +20479,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>S 793-2025</t>
+          <t>S 794-2025</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -20501,7 +20496,7 @@
         <v>45729</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20519,7 +20514,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -20562,7 +20557,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>S 963-2025</t>
+          <t>S 793-2025</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -20576,10 +20571,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>45742</v>
+        <v>45729</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20597,7 +20592,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -20640,7 +20635,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>S 964-2025</t>
+          <t>S 963-2025</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -20657,7 +20652,7 @@
         <v>45742</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20675,123 +20670,201 @@
         </is>
       </c>
       <c r="I240" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J240" t="n">
+        <v>0</v>
+      </c>
+      <c r="K240" t="n">
+        <v>0</v>
+      </c>
+      <c r="L240" t="n">
+        <v>0</v>
+      </c>
+      <c r="M240" t="n">
+        <v>0</v>
+      </c>
+      <c r="N240" t="n">
+        <v>0</v>
+      </c>
+      <c r="O240" t="n">
+        <v>0</v>
+      </c>
+      <c r="P240" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q240" t="n">
+        <v>0</v>
+      </c>
+      <c r="R240" t="n">
+        <v>0</v>
+      </c>
+      <c r="S240" t="n">
+        <v>0</v>
+      </c>
+      <c r="T240" t="n">
+        <v>0</v>
+      </c>
+      <c r="U240" t="n">
+        <v>0</v>
+      </c>
+      <c r="V240" s="2" t="inlineStr"/>
+    </row>
+    <row r="241" ht="15" customHeight="1">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>S 964-2025</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Annan skogsbruksåtgärd</t>
+        </is>
+      </c>
+      <c r="D241" s="1" t="n">
+        <v>45742</v>
+      </c>
+      <c r="E241" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>DEGERFORS</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I241" t="n">
         <v>2.4</v>
       </c>
-      <c r="J240" t="n">
-        <v>0</v>
-      </c>
-      <c r="K240" t="n">
-        <v>0</v>
-      </c>
-      <c r="L240" t="n">
-        <v>0</v>
-      </c>
-      <c r="M240" t="n">
-        <v>0</v>
-      </c>
-      <c r="N240" t="n">
-        <v>0</v>
-      </c>
-      <c r="O240" t="n">
-        <v>0</v>
-      </c>
-      <c r="P240" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q240" t="n">
-        <v>0</v>
-      </c>
-      <c r="R240" t="n">
-        <v>0</v>
-      </c>
-      <c r="S240" t="n">
-        <v>0</v>
-      </c>
-      <c r="T240" t="n">
-        <v>0</v>
-      </c>
-      <c r="U240" t="n">
-        <v>0</v>
-      </c>
-      <c r="V240" s="2" t="inlineStr"/>
-    </row>
-    <row r="241">
-      <c r="A241" t="inlineStr">
+      <c r="J241" t="n">
+        <v>0</v>
+      </c>
+      <c r="K241" t="n">
+        <v>0</v>
+      </c>
+      <c r="L241" t="n">
+        <v>0</v>
+      </c>
+      <c r="M241" t="n">
+        <v>0</v>
+      </c>
+      <c r="N241" t="n">
+        <v>0</v>
+      </c>
+      <c r="O241" t="n">
+        <v>0</v>
+      </c>
+      <c r="P241" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q241" t="n">
+        <v>0</v>
+      </c>
+      <c r="R241" t="n">
+        <v>0</v>
+      </c>
+      <c r="S241" t="n">
+        <v>0</v>
+      </c>
+      <c r="T241" t="n">
+        <v>0</v>
+      </c>
+      <c r="U241" t="n">
+        <v>0</v>
+      </c>
+      <c r="V241" s="2" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
         <is>
           <t>S 2595-2025</t>
         </is>
       </c>
-      <c r="B241" t="inlineStr">
+      <c r="B242" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C241" t="inlineStr">
+      <c r="C242" t="inlineStr">
         <is>
           <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
-      <c r="D241" s="1" t="n">
+      <c r="D242" s="1" t="n">
         <v>45916</v>
       </c>
-      <c r="E241" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F241" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G241" t="inlineStr">
-        <is>
-          <t>DEGERFORS</t>
-        </is>
-      </c>
-      <c r="H241" t="inlineStr">
+      <c r="E242" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>DEGERFORS</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I241" t="n">
+      <c r="I242" t="n">
         <v>2.9</v>
       </c>
-      <c r="J241" t="n">
-        <v>0</v>
-      </c>
-      <c r="K241" t="n">
-        <v>0</v>
-      </c>
-      <c r="L241" t="n">
-        <v>0</v>
-      </c>
-      <c r="M241" t="n">
-        <v>0</v>
-      </c>
-      <c r="N241" t="n">
-        <v>0</v>
-      </c>
-      <c r="O241" t="n">
-        <v>0</v>
-      </c>
-      <c r="P241" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q241" t="n">
-        <v>0</v>
-      </c>
-      <c r="R241" t="n">
-        <v>0</v>
-      </c>
-      <c r="S241" t="n">
-        <v>0</v>
-      </c>
-      <c r="T241" t="n">
-        <v>0</v>
-      </c>
-      <c r="U241" t="n">
-        <v>0</v>
-      </c>
-      <c r="V241" s="2" t="inlineStr"/>
+      <c r="J242" t="n">
+        <v>0</v>
+      </c>
+      <c r="K242" t="n">
+        <v>0</v>
+      </c>
+      <c r="L242" t="n">
+        <v>0</v>
+      </c>
+      <c r="M242" t="n">
+        <v>0</v>
+      </c>
+      <c r="N242" t="n">
+        <v>0</v>
+      </c>
+      <c r="O242" t="n">
+        <v>0</v>
+      </c>
+      <c r="P242" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q242" t="n">
+        <v>0</v>
+      </c>
+      <c r="R242" t="n">
+        <v>0</v>
+      </c>
+      <c r="S242" t="n">
+        <v>0</v>
+      </c>
+      <c r="T242" t="n">
+        <v>0</v>
+      </c>
+      <c r="U242" t="n">
+        <v>0</v>
+      </c>
+      <c r="V242" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt DEGERFORS.xlsx
+++ b/Översikt DEGERFORS.xlsx
@@ -601,7 +601,7 @@
         <v>46160</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>46051</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
         <v>46160</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>46107</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>46190</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>46190</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>46161</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>45089</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>45175</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>46160</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>45384</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
         <v>45384</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>45163</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>44550</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>46204</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>45175</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         <v>45932</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>45163</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>45205</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2897,7 +2897,7 @@
         <v>45351</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
         <v>45866</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>45559</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>45931</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>45384</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>46190</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>45163</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>45931</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>45558</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>45163</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4038,7 +4038,7 @@
         <v>45163</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>46045</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>46199</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>44470</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>44487</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>44470</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4704,7 +4704,7 @@
         <v>45116</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>45163</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4923,7 +4923,7 @@
         <v>45096</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5037,7 +5037,7 @@
         <v>45205</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5151,7 +5151,7 @@
         <v>45938</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5256,7 +5256,7 @@
         <v>45931</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5365,7 +5365,7 @@
         <v>45163</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
         <v>45589</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         <v>44651</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5694,7 +5694,7 @@
         <v>46186</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5804,7 +5804,7 @@
         <v>46186</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
         <v>45589</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6028,7 +6028,7 @@
         <v>46099</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6138,7 +6138,7 @@
         <v>46185</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6243,7 +6243,7 @@
         <v>45614</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6352,7 +6352,7 @@
         <v>44578</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6461,7 +6461,7 @@
         <v>44805</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
         <v>44805</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6607,7 +6607,7 @@
         <v>44861</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6680,7 +6680,7 @@
         <v>44607</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         <v>44692</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
         <v>44470</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         <v>44609</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6982,7 +6982,7 @@
         <v>44497</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7055,7 +7055,7 @@
         <v>44594</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7128,7 +7128,7 @@
         <v>44853</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7201,7 +7201,7 @@
         <v>44515</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7274,7 +7274,7 @@
         <v>44466</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7352,7 +7352,7 @@
         <v>44643</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7425,7 +7425,7 @@
         <v>44470</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7503,7 +7503,7 @@
         <v>44529</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7581,7 +7581,7 @@
         <v>44525</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7654,7 +7654,7 @@
         <v>44509</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7732,7 +7732,7 @@
         <v>44505</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7810,7 +7810,7 @@
         <v>45707</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7888,7 +7888,7 @@
         <v>45763</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         <v>44754</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8039,7 +8039,7 @@
         <v>45541</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8117,7 +8117,7 @@
         <v>45624</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8190,7 +8190,7 @@
         <v>45351</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8268,7 +8268,7 @@
         <v>44986</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8341,7 +8341,7 @@
         <v>45535</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8414,7 +8414,7 @@
         <v>45163</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8492,7 +8492,7 @@
         <v>44579</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8565,7 +8565,7 @@
         <v>45261</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8643,7 +8643,7 @@
         <v>45468</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8721,7 +8721,7 @@
         <v>44582</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8794,7 +8794,7 @@
         <v>45602</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8872,7 +8872,7 @@
         <v>44609</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         <v>45609</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9023,7 +9023,7 @@
         <v>45233</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         <v>45621</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9174,7 +9174,7 @@
         <v>45887</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9252,7 +9252,7 @@
         <v>45735</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9330,7 +9330,7 @@
         <v>45160</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9403,7 +9403,7 @@
         <v>45887</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9481,7 +9481,7 @@
         <v>45369</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9559,7 +9559,7 @@
         <v>45645</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9637,7 +9637,7 @@
         <v>44552</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9710,7 +9710,7 @@
         <v>45645</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9788,7 +9788,7 @@
         <v>45645</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9866,7 +9866,7 @@
         <v>45616</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9939,7 +9939,7 @@
         <v>45219</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10012,7 +10012,7 @@
         <v>45902</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10090,7 +10090,7 @@
         <v>45902</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10168,7 +10168,7 @@
         <v>45912</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10241,7 +10241,7 @@
         <v>46140</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10319,7 +10319,7 @@
         <v>46140</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10397,7 +10397,7 @@
         <v>46140</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10475,7 +10475,7 @@
         <v>45912</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10553,7 +10553,7 @@
         <v>45629</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10631,7 +10631,7 @@
         <v>45912</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10709,7 +10709,7 @@
         <v>45912</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10787,7 +10787,7 @@
         <v>45936</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10860,7 +10860,7 @@
         <v>45351</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10938,7 +10938,7 @@
         <v>46148</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11016,7 +11016,7 @@
         <v>45443</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11094,7 +11094,7 @@
         <v>46148</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11167,7 +11167,7 @@
         <v>46149</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11245,7 +11245,7 @@
         <v>46148</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11323,7 +11323,7 @@
         <v>46148</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11396,7 +11396,7 @@
         <v>45947</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11474,7 +11474,7 @@
         <v>45952</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11547,7 +11547,7 @@
         <v>45272</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11620,7 +11620,7 @@
         <v>45729</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11698,7 +11698,7 @@
         <v>45222</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11776,7 +11776,7 @@
         <v>45190</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11854,7 +11854,7 @@
         <v>45057</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11932,7 +11932,7 @@
         <v>45192</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12005,7 +12005,7 @@
         <v>45581</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12083,7 +12083,7 @@
         <v>45338</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12161,7 +12161,7 @@
         <v>45971</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12239,7 +12239,7 @@
         <v>45979</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12312,7 +12312,7 @@
         <v>45337</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12385,7 +12385,7 @@
         <v>45581</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12463,7 +12463,7 @@
         <v>45338</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12541,7 +12541,7 @@
         <v>44986</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12614,7 +12614,7 @@
         <v>46162</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12692,7 +12692,7 @@
         <v>46162</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12770,7 +12770,7 @@
         <v>45742</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12848,7 +12848,7 @@
         <v>45996</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12921,7 +12921,7 @@
         <v>45996</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12994,7 +12994,7 @@
         <v>46167</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13072,7 +13072,7 @@
         <v>45163</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13150,7 +13150,7 @@
         <v>45330</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13223,7 +13223,7 @@
         <v>45601</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13301,7 +13301,7 @@
         <v>45116</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13374,7 +13374,7 @@
         <v>45205</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13452,7 +13452,7 @@
         <v>45190</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13530,7 +13530,7 @@
         <v>45222</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13608,7 +13608,7 @@
         <v>46170</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13681,7 +13681,7 @@
         <v>46027</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13754,7 +13754,7 @@
         <v>44839</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13827,7 +13827,7 @@
         <v>44781</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13900,7 +13900,7 @@
         <v>46170</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13973,7 +13973,7 @@
         <v>45387</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14046,7 +14046,7 @@
         <v>45384</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14124,7 +14124,7 @@
         <v>46171</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14202,7 +14202,7 @@
         <v>46070</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14275,7 +14275,7 @@
         <v>46086</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14353,7 +14353,7 @@
         <v>46086</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14431,7 +14431,7 @@
         <v>46185</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14509,7 +14509,7 @@
         <v>46185</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14587,7 +14587,7 @@
         <v>46185</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14665,7 +14665,7 @@
         <v>44509</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14743,7 +14743,7 @@
         <v>46092</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14821,7 +14821,7 @@
         <v>46094</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14899,7 +14899,7 @@
         <v>44816</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14977,7 +14977,7 @@
         <v>46093</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15055,7 +15055,7 @@
         <v>46093</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15133,7 +15133,7 @@
         <v>46189</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15211,7 +15211,7 @@
         <v>45589</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15289,7 +15289,7 @@
         <v>46195</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15362,7 +15362,7 @@
         <v>46191</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15440,7 +15440,7 @@
         <v>46191</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15518,7 +15518,7 @@
         <v>45601</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15596,7 +15596,7 @@
         <v>46198</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15674,7 +15674,7 @@
         <v>46198</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15752,7 +15752,7 @@
         <v>46198</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15830,7 +15830,7 @@
         <v>45351</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15908,7 +15908,7 @@
         <v>45106</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15981,7 +15981,7 @@
         <v>44904</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16059,7 +16059,7 @@
         <v>46202</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16137,7 +16137,7 @@
         <v>46199</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16210,7 +16210,7 @@
         <v>45763</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16283,7 +16283,7 @@
         <v>44986</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16356,7 +16356,7 @@
         <v>46202</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16434,7 +16434,7 @@
         <v>46129</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16512,7 +16512,7 @@
         <v>44989</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         <v>44986</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16658,7 +16658,7 @@
         <v>45602</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16736,7 +16736,7 @@
         <v>45520</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16809,7 +16809,7 @@
         <v>46127</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16882,7 +16882,7 @@
         <v>46132</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16955,7 +16955,7 @@
         <v>45195</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17033,7 +17033,7 @@
         <v>45569</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17106,7 +17106,7 @@
         <v>46204</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17184,7 +17184,7 @@
         <v>44816</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17262,7 +17262,7 @@
         <v>44463</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17335,7 +17335,7 @@
         <v>44501</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17413,7 +17413,7 @@
         <v>45705</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17491,7 +17491,7 @@
         <v>46260</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17569,7 +17569,7 @@
         <v>45600</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17642,7 +17642,7 @@
         <v>45600</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17715,7 +17715,7 @@
         <v>45376</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17788,7 +17788,7 @@
         <v>45764</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17866,7 +17866,7 @@
         <v>46268</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17939,7 +17939,7 @@
         <v>46268</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18012,7 +18012,7 @@
         <v>45119</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18085,7 +18085,7 @@
         <v>46268</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18158,7 +18158,7 @@
         <v>45474</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18231,7 +18231,7 @@
         <v>46230</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18304,7 +18304,7 @@
         <v>45581</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18382,7 +18382,7 @@
         <v>46231</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18460,7 +18460,7 @@
         <v>46231</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18538,7 +18538,7 @@
         <v>45223</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18616,7 +18616,7 @@
         <v>46231</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18694,7 +18694,7 @@
         <v>45635</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18772,7 +18772,7 @@
         <v>46279</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18845,7 +18845,7 @@
         <v>45215</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18923,7 +18923,7 @@
         <v>46281</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19001,7 +19001,7 @@
         <v>45272</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19074,7 +19074,7 @@
         <v>45443</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19152,7 +19152,7 @@
         <v>45453</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19225,7 +19225,7 @@
         <v>46239</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19303,7 +19303,7 @@
         <v>46283</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19381,7 +19381,7 @@
         <v>46282</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19454,7 +19454,7 @@
         <v>46239</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19532,7 +19532,7 @@
         <v>46283</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19610,7 +19610,7 @@
         <v>45798</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19683,7 +19683,7 @@
         <v>45330</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19761,7 +19761,7 @@
         <v>46241</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19834,7 +19834,7 @@
         <v>45810</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19907,7 +19907,7 @@
         <v>45810</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19980,7 +19980,7 @@
         <v>45819</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20058,7 +20058,7 @@
         <v>45819</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20136,7 +20136,7 @@
         <v>44719</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20209,7 +20209,7 @@
         <v>45841</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20282,7 +20282,7 @@
         <v>45639</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20355,7 +20355,7 @@
         <v>45876</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20428,7 +20428,7 @@
         <v>45876</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20501,7 +20501,7 @@
         <v>45747</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20574,7 +20574,7 @@
         <v>44587</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20647,7 +20647,7 @@
         <v>45805</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20725,7 +20725,7 @@
         <v>45805</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20803,7 +20803,7 @@
         <v>45729</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20881,7 +20881,7 @@
         <v>45729</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20959,7 +20959,7 @@
         <v>45742</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21037,7 +21037,7 @@
         <v>45742</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21115,7 +21115,7 @@
         <v>45916</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>

--- a/Översikt DEGERFORS.xlsx
+++ b/Översikt DEGERFORS.xlsx
@@ -601,7 +601,7 @@
         <v>46160</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>46051</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
         <v>46160</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>46107</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>46190</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>46190</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>46161</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>45089</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>45175</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>46160</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>45384</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
         <v>45384</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>45163</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 73321-2021</t>
+          <t>A 29553-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2193,10 +2193,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44550</v>
+        <v>46204</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2208,17 +2208,22 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>17</v>
+        <v>6.5</v>
       </c>
       <c r="J15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M15" t="n">
         <v>1</v>
@@ -2233,7 +2238,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R15" t="n">
         <v>1</v>
@@ -2242,12 +2247,126 @@
         <v>6</v>
       </c>
       <c r="T15" t="n">
+        <v>6</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Skuggblåslav
+Talltita
+Ullticka
+Vedskivlav
+Tofsmes</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 29553-2026 artfynd.xlsx", "A 29553-2026")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 29553-2026 karta.png", "A 29553-2026")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 29553-2026 georefererad karta.tif", "A 29553-2026")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 29553-2026 FSC-klagomål.docx", "A 29553-2026")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 29553-2026 FSC-klagomål mail.docx", "A 29553-2026")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 29553-2026 tillsynsbegäran.docx", "A 29553-2026")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 29553-2026 tillsynsbegäran mail.docx", "A 29553-2026")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 29553-2026 prioriterade fågelarter.docx", "A 29553-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 73321-2021</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>44550</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>DEGERFORS</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>17</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>3</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>4</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" t="n">
+        <v>6</v>
+      </c>
+      <c r="T16" t="n">
         <v>8</v>
       </c>
-      <c r="U15" t="n">
+      <c r="U16" t="n">
         <v>8</v>
       </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Grynig filtlav
@@ -2257,159 +2376,40 @@
 Spillkråka</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 73321-2021 artfynd.xlsx", "A 73321-2021")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 73321-2021 karta.png", "A 73321-2021")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 73321-2021 georefererad karta.tif", "A 73321-2021")</f>
         <v/>
       </c>
-      <c r="Z15">
+      <c r="Z16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/knärot/A 73321-2021 karta knärot.png", "A 73321-2021")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 73321-2021 FSC-klagomål.docx", "A 73321-2021")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 73321-2021 FSC-klagomål mail.docx", "A 73321-2021")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 73321-2021 tillsynsbegäran.docx", "A 73321-2021")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 73321-2021 tillsynsbegäran mail.docx", "A 73321-2021")</f>
         <v/>
       </c>
-      <c r="AE15">
+      <c r="AE16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 73321-2021 prioriterade fågelarter.docx", "A 73321-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 29553-2026</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46286</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>DEGERFORS</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>4</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>5</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1</v>
-      </c>
-      <c r="S16" t="n">
-        <v>6</v>
-      </c>
-      <c r="T16" t="n">
-        <v>6</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Skuggblåslav
-Talltita
-Ullticka
-Vedskivlav
-Tofsmes</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 29553-2026 artfynd.xlsx", "A 29553-2026")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 29553-2026 karta.png", "A 29553-2026")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 29553-2026 georefererad karta.tif", "A 29553-2026")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 29553-2026 FSC-klagomål.docx", "A 29553-2026")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 29553-2026 FSC-klagomål mail.docx", "A 29553-2026")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 29553-2026 tillsynsbegäran.docx", "A 29553-2026")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 29553-2026 tillsynsbegäran mail.docx", "A 29553-2026")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 29553-2026 prioriterade fågelarter.docx", "A 29553-2026")</f>
         <v/>
       </c>
     </row>
@@ -2433,7 +2433,7 @@
         <v>45175</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         <v>45932</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>45163</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>45205</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2897,7 +2897,7 @@
         <v>45351</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
         <v>45866</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>45559</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>45931</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>45384</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>46190</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>45163</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>45931</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>45558</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>45163</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4038,7 +4038,7 @@
         <v>45163</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>46045</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>46199</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>44470</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>44487</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>44470</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4704,7 +4704,7 @@
         <v>45116</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>45163</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4923,7 +4923,7 @@
         <v>45096</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5020,7 +5020,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 48285-2023</t>
+          <t>A 49306-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5034,10 +5034,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45205</v>
+        <v>45938</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5049,19 +5049,14 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>1.1</v>
+        <v>5.8</v>
       </c>
       <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
         <v>1</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -5091,50 +5086,46 @@
         <v>1</v>
       </c>
       <c r="U40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 48285-2023 artfynd.xlsx", "A 48285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 49306-2025 artfynd.xlsx", "A 49306-2025")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 48285-2023 karta.png", "A 48285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 49306-2025 karta.png", "A 49306-2025")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 48285-2023 georefererad karta.tif", "A 48285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 49306-2025 georefererad karta.tif", "A 49306-2025")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 48285-2023 FSC-klagomål.docx", "A 48285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 49306-2025 FSC-klagomål.docx", "A 49306-2025")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 48285-2023 FSC-klagomål mail.docx", "A 48285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 49306-2025 FSC-klagomål mail.docx", "A 49306-2025")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 48285-2023 tillsynsbegäran.docx", "A 48285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 49306-2025 tillsynsbegäran.docx", "A 49306-2025")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 48285-2023 tillsynsbegäran mail.docx", "A 48285-2023")</f>
-        <v/>
-      </c>
-      <c r="AE40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 48285-2023 prioriterade fågelarter.docx", "A 48285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 49306-2025 tillsynsbegäran mail.docx", "A 49306-2025")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 49306-2025</t>
+          <t>A 48285-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5148,10 +5139,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45938</v>
+        <v>45205</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5163,14 +5154,19 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>5.8</v>
+        <v>1.1</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -5200,39 +5196,43 @@
         <v>1</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 49306-2025 artfynd.xlsx", "A 49306-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 48285-2023 artfynd.xlsx", "A 48285-2023")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 49306-2025 karta.png", "A 49306-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 48285-2023 karta.png", "A 48285-2023")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 49306-2025 georefererad karta.tif", "A 49306-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 48285-2023 georefererad karta.tif", "A 48285-2023")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 49306-2025 FSC-klagomål.docx", "A 49306-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 48285-2023 FSC-klagomål.docx", "A 48285-2023")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 49306-2025 FSC-klagomål mail.docx", "A 49306-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 48285-2023 FSC-klagomål mail.docx", "A 48285-2023")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 49306-2025 tillsynsbegäran.docx", "A 49306-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 48285-2023 tillsynsbegäran.docx", "A 48285-2023")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 49306-2025 tillsynsbegäran mail.docx", "A 49306-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 48285-2023 tillsynsbegäran mail.docx", "A 48285-2023")</f>
+        <v/>
+      </c>
+      <c r="AE41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 48285-2023 prioriterade fågelarter.docx", "A 48285-2023")</f>
         <v/>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
         <v>45931</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 38907-2023</t>
+          <t>A 14121-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5362,10 +5362,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45163</v>
+        <v>44651</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5377,13 +5377,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>2.9</v>
+        <v>4.4</v>
       </c>
       <c r="J43" t="n">
         <v>1</v>
@@ -5423,46 +5418,42 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Hårklomossa</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 38907-2023 artfynd.xlsx", "A 38907-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 14121-2022 artfynd.xlsx", "A 14121-2022")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 38907-2023 karta.png", "A 38907-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 14121-2022 karta.png", "A 14121-2022")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 38907-2023 georefererad karta.tif", "A 38907-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 14121-2022 georefererad karta.tif", "A 14121-2022")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 38907-2023 FSC-klagomål.docx", "A 38907-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 14121-2022 FSC-klagomål.docx", "A 14121-2022")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 38907-2023 FSC-klagomål mail.docx", "A 38907-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 14121-2022 FSC-klagomål mail.docx", "A 14121-2022")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 38907-2023 tillsynsbegäran.docx", "A 38907-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 14121-2022 tillsynsbegäran.docx", "A 14121-2022")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 38907-2023 tillsynsbegäran mail.docx", "A 38907-2023")</f>
-        <v/>
-      </c>
-      <c r="AE43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 38907-2023 prioriterade fågelarter.docx", "A 38907-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 14121-2022 tillsynsbegäran mail.docx", "A 14121-2022")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 47941-2024</t>
+          <t>A 38907-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5476,10 +5467,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45589</v>
+        <v>45163</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5497,10 +5488,10 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" t="n">
         <v>0</v>
@@ -5509,7 +5500,7 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
         <v>0</v>
@@ -5521,10 +5512,10 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>
@@ -5533,46 +5524,50 @@
         <v>1</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Brunfläckig pärlemorfjäril</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 47941-2024 artfynd.xlsx", "A 47941-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 38907-2023 artfynd.xlsx", "A 38907-2023")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 47941-2024 karta.png", "A 47941-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 38907-2023 karta.png", "A 38907-2023")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 47941-2024 georefererad karta.tif", "A 47941-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 38907-2023 georefererad karta.tif", "A 38907-2023")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 47941-2024 FSC-klagomål.docx", "A 47941-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 38907-2023 FSC-klagomål.docx", "A 38907-2023")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 47941-2024 FSC-klagomål mail.docx", "A 47941-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 38907-2023 FSC-klagomål mail.docx", "A 38907-2023")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 47941-2024 tillsynsbegäran.docx", "A 47941-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 38907-2023 tillsynsbegäran.docx", "A 38907-2023")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 47941-2024 tillsynsbegäran mail.docx", "A 47941-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 38907-2023 tillsynsbegäran mail.docx", "A 38907-2023")</f>
+        <v/>
+      </c>
+      <c r="AE44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 38907-2023 prioriterade fågelarter.docx", "A 38907-2023")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 14121-2022</t>
+          <t>A 27071-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5586,10 +5581,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>44651</v>
+        <v>46186</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5601,14 +5596,19 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>4.4</v>
+        <v>9.9</v>
       </c>
       <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
         <v>1</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -5638,46 +5638,46 @@
         <v>1</v>
       </c>
       <c r="U45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Hårklomossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 14121-2022 artfynd.xlsx", "A 14121-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 27071-2026 artfynd.xlsx", "A 27071-2026")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 14121-2022 karta.png", "A 14121-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 27071-2026 karta.png", "A 27071-2026")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 14121-2022 georefererad karta.tif", "A 14121-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 27071-2026 georefererad karta.tif", "A 27071-2026")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 14121-2022 FSC-klagomål.docx", "A 14121-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 27071-2026 FSC-klagomål.docx", "A 27071-2026")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 14121-2022 FSC-klagomål mail.docx", "A 14121-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 27071-2026 FSC-klagomål mail.docx", "A 27071-2026")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 14121-2022 tillsynsbegäran.docx", "A 14121-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 27071-2026 tillsynsbegäran.docx", "A 27071-2026")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 14121-2022 tillsynsbegäran mail.docx", "A 14121-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 27071-2026 tillsynsbegäran mail.docx", "A 27071-2026")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 27071-2026</t>
+          <t>A 27072-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5694,7 +5694,7 @@
         <v>46186</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5712,13 +5712,13 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>9.9</v>
+        <v>7.6</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -5748,46 +5748,50 @@
         <v>1</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 27071-2026 artfynd.xlsx", "A 27071-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 27072-2026 artfynd.xlsx", "A 27072-2026")</f>
         <v/>
       </c>
       <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 27071-2026 karta.png", "A 27071-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 27072-2026 karta.png", "A 27072-2026")</f>
         <v/>
       </c>
       <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 27071-2026 georefererad karta.tif", "A 27071-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 27072-2026 georefererad karta.tif", "A 27072-2026")</f>
         <v/>
       </c>
       <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 27071-2026 FSC-klagomål.docx", "A 27071-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 27072-2026 FSC-klagomål.docx", "A 27072-2026")</f>
         <v/>
       </c>
       <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 27071-2026 FSC-klagomål mail.docx", "A 27071-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 27072-2026 FSC-klagomål mail.docx", "A 27072-2026")</f>
         <v/>
       </c>
       <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 27071-2026 tillsynsbegäran.docx", "A 27071-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 27072-2026 tillsynsbegäran.docx", "A 27072-2026")</f>
         <v/>
       </c>
       <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 27071-2026 tillsynsbegäran mail.docx", "A 27071-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 27072-2026 tillsynsbegäran mail.docx", "A 27072-2026")</f>
+        <v/>
+      </c>
+      <c r="AE46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 27072-2026 prioriterade fågelarter.docx", "A 27072-2026")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 27072-2026</t>
+          <t>A 47941-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5801,10 +5805,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46186</v>
+        <v>45589</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5822,20 +5826,20 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>7.6</v>
+        <v>1.4</v>
       </c>
       <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
         <v>1</v>
       </c>
-      <c r="K47" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" t="n">
-        <v>0</v>
-      </c>
-      <c r="M47" t="n">
-        <v>0</v>
-      </c>
       <c r="N47" t="n">
         <v>0</v>
       </c>
@@ -5846,10 +5850,10 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S47" t="n">
         <v>1</v>
@@ -5858,50 +5862,46 @@
         <v>1</v>
       </c>
       <c r="U47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brunfläckig pärlemorfjäril</t>
         </is>
       </c>
       <c r="W47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 27072-2026 artfynd.xlsx", "A 27072-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 47941-2024 artfynd.xlsx", "A 47941-2024")</f>
         <v/>
       </c>
       <c r="X47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 27072-2026 karta.png", "A 27072-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 47941-2024 karta.png", "A 47941-2024")</f>
         <v/>
       </c>
       <c r="Y47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 27072-2026 georefererad karta.tif", "A 27072-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 47941-2024 georefererad karta.tif", "A 47941-2024")</f>
         <v/>
       </c>
       <c r="AA47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 27072-2026 FSC-klagomål.docx", "A 27072-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 47941-2024 FSC-klagomål.docx", "A 47941-2024")</f>
         <v/>
       </c>
       <c r="AB47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 27072-2026 FSC-klagomål mail.docx", "A 27072-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 47941-2024 FSC-klagomål mail.docx", "A 47941-2024")</f>
         <v/>
       </c>
       <c r="AC47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 27072-2026 tillsynsbegäran.docx", "A 27072-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 47941-2024 tillsynsbegäran.docx", "A 47941-2024")</f>
         <v/>
       </c>
       <c r="AD47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 27072-2026 tillsynsbegäran mail.docx", "A 27072-2026")</f>
-        <v/>
-      </c>
-      <c r="AE47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 27072-2026 prioriterade fågelarter.docx", "A 27072-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 47941-2024 tillsynsbegäran mail.docx", "A 47941-2024")</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 47915-2024</t>
+          <t>A 14177-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5915,10 +5915,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45589</v>
+        <v>46099</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5936,17 +5936,17 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>5.8</v>
+        <v>2.2</v>
       </c>
       <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
         <v>1</v>
       </c>
-      <c r="K48" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" t="n">
-        <v>0</v>
-      </c>
       <c r="M48" t="n">
         <v>0</v>
       </c>
@@ -5960,7 +5960,7 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R48" t="n">
         <v>0</v>
@@ -5976,42 +5976,42 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="W48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 47915-2024 artfynd.xlsx", "A 47915-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 14177-2026 artfynd.xlsx", "A 14177-2026")</f>
         <v/>
       </c>
       <c r="X48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 47915-2024 karta.png", "A 47915-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 14177-2026 karta.png", "A 14177-2026")</f>
         <v/>
       </c>
       <c r="Y48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 47915-2024 georefererad karta.tif", "A 47915-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 14177-2026 georefererad karta.tif", "A 14177-2026")</f>
         <v/>
       </c>
       <c r="AA48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 47915-2024 FSC-klagomål.docx", "A 47915-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 14177-2026 FSC-klagomål.docx", "A 14177-2026")</f>
         <v/>
       </c>
       <c r="AB48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 47915-2024 FSC-klagomål mail.docx", "A 47915-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 14177-2026 FSC-klagomål mail.docx", "A 14177-2026")</f>
         <v/>
       </c>
       <c r="AC48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 47915-2024 tillsynsbegäran.docx", "A 47915-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 14177-2026 tillsynsbegäran.docx", "A 14177-2026")</f>
         <v/>
       </c>
       <c r="AD48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 47915-2024 tillsynsbegäran mail.docx", "A 47915-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 14177-2026 tillsynsbegäran mail.docx", "A 14177-2026")</f>
         <v/>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 14177-2026</t>
+          <t>A 26971-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6025,10 +6025,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46099</v>
+        <v>46185</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6040,22 +6040,17 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
         <v>0</v>
@@ -6070,7 +6065,7 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
         <v>0</v>
@@ -6086,42 +6081,42 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="W49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 14177-2026 artfynd.xlsx", "A 14177-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 26971-2026 artfynd.xlsx", "A 26971-2026")</f>
         <v/>
       </c>
       <c r="X49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 14177-2026 karta.png", "A 14177-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 26971-2026 karta.png", "A 26971-2026")</f>
         <v/>
       </c>
       <c r="Y49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 14177-2026 georefererad karta.tif", "A 14177-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 26971-2026 georefererad karta.tif", "A 26971-2026")</f>
         <v/>
       </c>
       <c r="AA49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 14177-2026 FSC-klagomål.docx", "A 14177-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 26971-2026 FSC-klagomål.docx", "A 26971-2026")</f>
         <v/>
       </c>
       <c r="AB49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 14177-2026 FSC-klagomål mail.docx", "A 14177-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 26971-2026 FSC-klagomål mail.docx", "A 26971-2026")</f>
         <v/>
       </c>
       <c r="AC49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 14177-2026 tillsynsbegäran.docx", "A 14177-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 26971-2026 tillsynsbegäran.docx", "A 26971-2026")</f>
         <v/>
       </c>
       <c r="AD49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 14177-2026 tillsynsbegäran mail.docx", "A 14177-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 26971-2026 tillsynsbegäran mail.docx", "A 26971-2026")</f>
         <v/>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 26971-2026</t>
+          <t>A 47915-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6135,10 +6130,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46185</v>
+        <v>45589</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6150,14 +6145,19 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I50" t="n">
-        <v>2.1</v>
+        <v>5.8</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
@@ -6191,35 +6191,35 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 26971-2026 artfynd.xlsx", "A 26971-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 47915-2024 artfynd.xlsx", "A 47915-2024")</f>
         <v/>
       </c>
       <c r="X50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 26971-2026 karta.png", "A 26971-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 47915-2024 karta.png", "A 47915-2024")</f>
         <v/>
       </c>
       <c r="Y50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 26971-2026 georefererad karta.tif", "A 26971-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 47915-2024 georefererad karta.tif", "A 47915-2024")</f>
         <v/>
       </c>
       <c r="AA50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 26971-2026 FSC-klagomål.docx", "A 26971-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 47915-2024 FSC-klagomål.docx", "A 47915-2024")</f>
         <v/>
       </c>
       <c r="AB50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 26971-2026 FSC-klagomål mail.docx", "A 26971-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 47915-2024 FSC-klagomål mail.docx", "A 47915-2024")</f>
         <v/>
       </c>
       <c r="AC50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 26971-2026 tillsynsbegäran.docx", "A 26971-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 47915-2024 tillsynsbegäran.docx", "A 47915-2024")</f>
         <v/>
       </c>
       <c r="AD50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 26971-2026 tillsynsbegäran mail.docx", "A 26971-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 47915-2024 tillsynsbegäran mail.docx", "A 47915-2024")</f>
         <v/>
       </c>
     </row>
@@ -6243,7 +6243,7 @@
         <v>45614</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6352,7 +6352,7 @@
         <v>44578</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6461,7 +6461,7 @@
         <v>44805</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
         <v>44805</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6607,7 +6607,7 @@
         <v>44861</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6680,7 +6680,7 @@
         <v>44607</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 19371-2022</t>
+          <t>A 54137-2021</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6755,10 +6755,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44692</v>
+        <v>44470</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6770,8 +6770,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I57" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -6814,7 +6819,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 54137-2021</t>
+          <t>A 19371-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6828,10 +6833,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44470</v>
+        <v>44692</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6843,13 +6848,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I58" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6909,7 +6909,7 @@
         <v>44609</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6982,7 +6982,7 @@
         <v>44497</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7055,7 +7055,7 @@
         <v>44594</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7128,7 +7128,7 @@
         <v>44853</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7201,7 +7201,7 @@
         <v>44515</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7274,7 +7274,7 @@
         <v>44466</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7352,7 +7352,7 @@
         <v>44643</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7425,7 +7425,7 @@
         <v>44470</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7503,7 +7503,7 @@
         <v>44529</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7564,7 +7564,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 67998-2021</t>
+          <t>A 63906-2021</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7578,10 +7578,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44525</v>
+        <v>44509</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7593,8 +7593,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7637,7 +7642,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 63906-2021</t>
+          <t>A 67998-2021</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7651,10 +7656,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44509</v>
+        <v>44525</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7666,13 +7671,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I69" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7732,7 +7732,7 @@
         <v>44505</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7810,7 +7810,7 @@
         <v>45707</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7888,7 +7888,7 @@
         <v>45763</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         <v>44754</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8039,7 +8039,7 @@
         <v>45541</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8117,7 +8117,7 @@
         <v>45624</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8190,7 +8190,7 @@
         <v>45351</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8268,7 +8268,7 @@
         <v>44986</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8341,7 +8341,7 @@
         <v>45535</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8414,7 +8414,7 @@
         <v>45163</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8492,7 +8492,7 @@
         <v>44579</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8565,7 +8565,7 @@
         <v>45261</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8643,7 +8643,7 @@
         <v>45468</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8704,7 +8704,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 3177-2022</t>
+          <t>A 8184-2022</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8718,10 +8718,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44582</v>
+        <v>44609</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8734,7 +8734,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>3.7</v>
+        <v>1.7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8794,7 +8794,7 @@
         <v>45602</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8855,7 +8855,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 8184-2022</t>
+          <t>A 3177-2022</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8869,10 +8869,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44609</v>
+        <v>44582</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8885,7 +8885,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.7</v>
+        <v>3.7</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8945,7 +8945,7 @@
         <v>45609</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9006,7 +9006,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 54515-2023</t>
+          <t>A 38874-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -9020,10 +9020,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45233</v>
+        <v>45887</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9035,8 +9035,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -9079,7 +9084,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 54994-2024</t>
+          <t>A 37333-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -9089,14 +9094,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45621</v>
+        <v>45876</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9108,13 +9113,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I88" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -9157,7 +9157,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 38874-2025</t>
+          <t>A 37265-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -9171,10 +9171,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45887</v>
+        <v>45876</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9186,13 +9186,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I89" t="n">
-        <v>8.300000000000001</v>
+        <v>1.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -9235,7 +9230,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 13236-2025</t>
+          <t>A 15594-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -9249,10 +9244,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45735</v>
+        <v>45747</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9264,13 +9259,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>18.5</v>
+        <v>1.5</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -9313,7 +9303,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 38233-2023</t>
+          <t>A 54515-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -9323,14 +9313,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45160</v>
+        <v>45233</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9343,7 +9333,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -9386,7 +9376,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 38875-2025</t>
+          <t>A 54994-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -9400,10 +9390,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45887</v>
+        <v>45621</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9421,7 +9411,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -9464,7 +9454,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 10674-2024</t>
+          <t>A 38875-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -9474,14 +9464,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45369</v>
+        <v>45887</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9499,7 +9489,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0.3</v>
+        <v>1.9</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -9542,7 +9532,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 60933-2024</t>
+          <t>A 13236-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -9556,10 +9546,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45645</v>
+        <v>45735</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9577,7 +9567,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.9</v>
+        <v>18.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -9620,7 +9610,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 73693-2021</t>
+          <t>A 41767-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9634,10 +9624,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44552</v>
+        <v>45902</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9649,8 +9639,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I95" t="n">
-        <v>3.6</v>
+        <v>1.1</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -9693,7 +9688,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 60937-2024</t>
+          <t>A 41766-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9707,10 +9702,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45645</v>
+        <v>45902</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9728,7 +9723,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.6</v>
+        <v>3.2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9771,7 +9766,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 60940-2024</t>
+          <t>A 54082-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9785,10 +9780,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45645</v>
+        <v>45616</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9800,13 +9795,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I97" t="n">
-        <v>1.2</v>
+        <v>6.3</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9849,7 +9839,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 54082-2024</t>
+          <t>A 43694-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9863,10 +9853,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45616</v>
+        <v>45912</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9878,8 +9868,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I98" t="n">
-        <v>6.3</v>
+        <v>6.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9922,7 +9917,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 52566-2023</t>
+          <t>A 43691-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9936,10 +9931,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45219</v>
+        <v>45912</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9951,8 +9946,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I99" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9995,7 +9995,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 41767-2025</t>
+          <t>A 43689-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -10009,10 +10009,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45902</v>
+        <v>45912</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10030,7 +10030,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -10073,7 +10073,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 41766-2025</t>
+          <t>A 38233-2023</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -10083,14 +10083,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45902</v>
+        <v>45160</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10102,13 +10102,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>3.2</v>
+        <v>0.6</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -10168,7 +10163,7 @@
         <v>45912</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10224,7 +10219,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 20567-2026</t>
+          <t>A 10674-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -10234,14 +10229,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>46140</v>
+        <v>45369</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10259,7 +10254,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>7.8</v>
+        <v>0.3</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -10302,7 +10297,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 20568-2026</t>
+          <t>A 60933-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -10316,10 +10311,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>46140</v>
+        <v>45645</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10337,7 +10332,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>6.3</v>
+        <v>1.9</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -10380,7 +10375,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 20478-2026</t>
+          <t>A 73693-2021</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -10394,10 +10389,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>46140</v>
+        <v>44552</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10409,13 +10404,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I105" t="n">
-        <v>1.1</v>
+        <v>3.6</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -10458,7 +10448,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 43694-2025</t>
+          <t>A 60937-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -10472,10 +10462,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45912</v>
+        <v>45645</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10493,7 +10483,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>6.6</v>
+        <v>0.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -10536,7 +10526,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 57234-2024</t>
+          <t>A 60940-2024</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -10550,10 +10540,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45629</v>
+        <v>45645</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10571,7 +10561,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -10614,7 +10604,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 43691-2025</t>
+          <t>A 48625-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10628,10 +10618,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45912</v>
+        <v>45936</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10643,13 +10633,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I108" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -10692,7 +10677,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 43689-2025</t>
+          <t>A 20567-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10706,10 +10691,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45912</v>
+        <v>46140</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10727,7 +10712,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1.4</v>
+        <v>7.8</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -10770,7 +10755,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 48625-2025</t>
+          <t>A 20568-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10784,10 +10769,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45936</v>
+        <v>46140</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10799,8 +10784,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I110" t="n">
-        <v>1.6</v>
+        <v>6.3</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10843,7 +10833,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 8074-2024</t>
+          <t>A 20478-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10857,10 +10847,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45351</v>
+        <v>46140</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10878,7 +10868,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10921,7 +10911,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 21440-2026</t>
+          <t>A 52566-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10935,10 +10925,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46148</v>
+        <v>45219</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10950,13 +10940,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I112" t="n">
-        <v>6.5</v>
+        <v>1.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10999,7 +10984,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 21952-2024</t>
+          <t>A 21440-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -11009,14 +10994,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45443</v>
+        <v>46148</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11034,7 +11019,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0.7</v>
+        <v>6.5</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -11094,7 +11079,7 @@
         <v>46148</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11167,7 +11152,7 @@
         <v>46149</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11245,7 +11230,7 @@
         <v>46148</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11323,7 +11308,7 @@
         <v>46148</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11379,7 +11364,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 51040-2025</t>
+          <t>A 44841-2023</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -11393,10 +11378,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45947</v>
+        <v>45190</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11414,7 +11399,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -11457,7 +11442,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 52099-2025</t>
+          <t>A 46222-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -11471,10 +11456,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45952</v>
+        <v>45581</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11486,8 +11471,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I119" t="n">
-        <v>2.6</v>
+        <v>0.9</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -11530,7 +11520,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 62972-2023</t>
+          <t>A 57234-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -11544,10 +11534,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45272</v>
+        <v>45629</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11559,8 +11549,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I120" t="n">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -11603,7 +11598,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 12143-2025</t>
+          <t>A 46219-2024</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -11613,14 +11608,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45729</v>
+        <v>45581</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11638,7 +11633,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -11681,7 +11676,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 51653-2023</t>
+          <t>A 51040-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -11695,10 +11690,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45222</v>
+        <v>45947</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11716,7 +11711,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>3.9</v>
+        <v>1.1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -11759,7 +11754,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 44841-2023</t>
+          <t>A 52099-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11773,10 +11768,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45190</v>
+        <v>45952</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11788,13 +11783,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I123" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -11837,7 +11827,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 20577-2023</t>
+          <t>A 23230-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11847,14 +11837,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45057</v>
+        <v>46162</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11872,7 +11862,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -11915,7 +11905,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 45365-2023</t>
+          <t>A 23229-2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11929,10 +11919,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45192</v>
+        <v>46162</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11944,8 +11934,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I125" t="n">
-        <v>5</v>
+        <v>2.9</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11988,7 +11983,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 46222-2024</t>
+          <t>A 14678-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11998,14 +11993,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45581</v>
+        <v>45742</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12023,7 +12018,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -12066,7 +12061,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 6387-2024</t>
+          <t>A 55341-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -12076,14 +12071,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45338</v>
+        <v>45971</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12101,7 +12096,7 @@
         </is>
       </c>
       <c r="I127" t="n">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -12144,7 +12139,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 55341-2025</t>
+          <t>A 23854-2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -12158,10 +12153,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45971</v>
+        <v>46167</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12179,7 +12174,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>3.4</v>
+        <v>20.9</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -12222,7 +12217,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 57086-2025</t>
+          <t>A 8074-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -12232,14 +12227,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45979</v>
+        <v>45351</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12251,8 +12246,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I129" t="n">
-        <v>6.1</v>
+        <v>0.7</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -12295,7 +12295,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 6240-2024</t>
+          <t>A 57086-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -12305,14 +12305,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45337</v>
+        <v>45979</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12325,7 +12325,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.9</v>
+        <v>6.1</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -12368,7 +12368,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 46219-2024</t>
+          <t>A 21952-2024</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -12378,14 +12378,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45581</v>
+        <v>45443</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12403,7 +12403,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -12446,7 +12446,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 6394-2024</t>
+          <t>A 24460-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -12456,14 +12456,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45338</v>
+        <v>46170</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12475,13 +12475,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I132" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -12524,7 +12519,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 11085-2023</t>
+          <t>A 24462-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -12538,10 +12533,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>44986</v>
+        <v>46170</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12597,7 +12592,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 23230-2026</t>
+          <t>A 62972-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -12611,10 +12606,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46162</v>
+        <v>45272</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12626,13 +12621,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I134" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -12675,7 +12665,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 23229-2026</t>
+          <t>A 12143-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -12685,14 +12675,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>46162</v>
+        <v>45729</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12710,7 +12700,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>2.9</v>
+        <v>1.3</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -12753,7 +12743,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 14678-2025</t>
+          <t>A 60736-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12763,14 +12753,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45742</v>
+        <v>45996</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12782,13 +12772,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I136" t="n">
-        <v>1.9</v>
+        <v>5.8</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -12831,7 +12816,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 60736-2025</t>
+          <t>A 60708-2025</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12848,7 +12833,7 @@
         <v>45996</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12861,7 +12846,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>5.8</v>
+        <v>1.9</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -12904,7 +12889,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 60708-2025</t>
+          <t>A 24689-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12918,10 +12903,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45996</v>
+        <v>46171</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12933,8 +12918,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I138" t="n">
-        <v>1.9</v>
+        <v>15.5</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -12977,7 +12967,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 23854-2026</t>
+          <t>A 51653-2023</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12991,10 +12981,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46167</v>
+        <v>45222</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13012,7 +13002,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>20.9</v>
+        <v>3.9</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -13072,7 +13062,7 @@
         <v>45163</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13133,7 +13123,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 5277-2024</t>
+          <t>A 48118-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -13147,10 +13137,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45330</v>
+        <v>45205</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13162,8 +13152,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I141" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -13206,7 +13201,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 50378-2024</t>
+          <t>A 20577-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -13216,14 +13211,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45601</v>
+        <v>45057</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13241,7 +13236,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>4.9</v>
+        <v>1.8</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -13284,7 +13279,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 33293-2023</t>
+          <t>A 45365-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -13298,10 +13293,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45116</v>
+        <v>45192</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13314,7 +13309,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>17.2</v>
+        <v>5</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -13357,7 +13352,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 48118-2023</t>
+          <t>A 6387-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -13367,14 +13362,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45205</v>
+        <v>45338</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13392,7 +13387,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -13435,7 +13430,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 44807-2023</t>
+          <t>A 770-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -13449,10 +13444,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45190</v>
+        <v>46027</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13464,13 +13459,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I145" t="n">
-        <v>5.4</v>
+        <v>2.2</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -13513,7 +13503,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 51652-2023</t>
+          <t>A 6240-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -13527,10 +13517,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45222</v>
+        <v>45337</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13542,13 +13532,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I146" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -13591,7 +13576,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 24460-2026</t>
+          <t>A 6394-2024</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -13601,14 +13586,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46170</v>
+        <v>45338</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13620,8 +13605,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I147" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -13664,7 +13654,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 770-2026</t>
+          <t>A 26857-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -13678,10 +13668,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46027</v>
+        <v>46185</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13693,8 +13683,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I148" t="n">
-        <v>2.2</v>
+        <v>15.1</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -13737,7 +13732,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 44457-2022</t>
+          <t>A 26946-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -13751,10 +13746,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>44839</v>
+        <v>46185</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13766,8 +13761,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I149" t="n">
-        <v>6.8</v>
+        <v>1.8</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -13810,7 +13810,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 32211-2022</t>
+          <t>A 11085-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -13824,10 +13824,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>44781</v>
+        <v>44986</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13840,7 +13840,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -13883,7 +13883,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 24462-2026</t>
+          <t>A 26947-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -13897,10 +13897,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46170</v>
+        <v>46185</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13912,8 +13912,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I151" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -13956,7 +13961,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 13405-2024</t>
+          <t>A 27411-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13970,10 +13975,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45387</v>
+        <v>46189</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13985,8 +13990,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I152" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -14029,7 +14039,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 12729-2024</t>
+          <t>A 28789-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -14043,10 +14053,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45384</v>
+        <v>46195</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14058,13 +14068,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I153" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -14107,7 +14112,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 24689-2026</t>
+          <t>A 27745-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -14121,10 +14126,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46171</v>
+        <v>46191</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14142,7 +14147,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>15.5</v>
+        <v>1.7</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -14185,7 +14190,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 9273-2026</t>
+          <t>A 27746-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -14199,10 +14204,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46070</v>
+        <v>46191</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14214,8 +14219,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I155" t="n">
-        <v>2.3</v>
+        <v>1</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -14258,7 +14268,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 12159-2026</t>
+          <t>A 28696-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -14272,10 +14282,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46086</v>
+        <v>46198</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14293,7 +14303,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -14336,7 +14346,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 12160-2026</t>
+          <t>A 28708-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -14350,10 +14360,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46086</v>
+        <v>46198</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14371,7 +14381,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>0.9</v>
+        <v>2.8</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -14414,7 +14424,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 26857-2026</t>
+          <t>A 5277-2024</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -14428,10 +14438,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46185</v>
+        <v>45330</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14443,13 +14453,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I158" t="n">
-        <v>15.1</v>
+        <v>0.5</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -14492,7 +14497,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 26946-2026</t>
+          <t>A 50378-2024</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -14506,10 +14511,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46185</v>
+        <v>45601</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14527,7 +14532,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1.8</v>
+        <v>4.9</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -14570,7 +14575,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 26947-2026</t>
+          <t>A 33293-2023</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -14584,10 +14589,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46185</v>
+        <v>45116</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14599,13 +14604,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I160" t="n">
-        <v>2</v>
+        <v>17.2</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -14648,7 +14648,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 63905-2021</t>
+          <t>A 28695-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -14662,10 +14662,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>44509</v>
+        <v>46198</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14683,7 +14683,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>3.7</v>
+        <v>2.7</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -14726,7 +14726,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 12936-2026</t>
+          <t>A 44807-2023</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -14740,10 +14740,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46092</v>
+        <v>45190</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14761,7 +14761,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>8.800000000000001</v>
+        <v>5.4</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -14804,7 +14804,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 13293-2026</t>
+          <t>A 51652-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -14818,10 +14818,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46094</v>
+        <v>45222</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -14882,7 +14882,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 38743-2022</t>
+          <t>A 29130-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -14896,10 +14896,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>44816</v>
+        <v>46202</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14917,7 +14917,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>1.6</v>
+        <v>10.3</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -14960,7 +14960,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 13040-2026</t>
+          <t>A 9273-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -14974,10 +14974,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46093</v>
+        <v>46070</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14989,13 +14989,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I165" t="n">
-        <v>7.1</v>
+        <v>2.3</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -15038,7 +15033,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 13039-2026</t>
+          <t>A 28930-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -15052,10 +15047,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46093</v>
+        <v>46199</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15067,13 +15062,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I166" t="n">
-        <v>5.1</v>
+        <v>2.7</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -15116,7 +15106,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 27411-2026</t>
+          <t>A 12159-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -15130,10 +15120,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46189</v>
+        <v>46086</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15151,7 +15141,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -15194,7 +15184,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 47935-2024</t>
+          <t>A 12160-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -15208,10 +15198,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45589</v>
+        <v>46086</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15229,7 +15219,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -15272,7 +15262,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 28789-2026</t>
+          <t>A 29132-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -15286,10 +15276,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15301,8 +15291,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I169" t="n">
-        <v>2.7</v>
+        <v>11.9</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -15345,7 +15340,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 27745-2026</t>
+          <t>A 44457-2022</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -15359,10 +15354,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46191</v>
+        <v>44839</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15374,13 +15369,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I170" t="n">
-        <v>1.7</v>
+        <v>6.8</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -15423,7 +15413,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 27746-2026</t>
+          <t>A 12936-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -15437,10 +15427,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46191</v>
+        <v>46092</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15458,7 +15448,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -15501,7 +15491,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 50377-2024</t>
+          <t>A 13293-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -15515,10 +15505,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45601</v>
+        <v>46094</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15536,7 +15526,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -15579,7 +15569,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 28696-2026</t>
+          <t>A 32211-2022</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -15593,10 +15583,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46198</v>
+        <v>44781</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15608,13 +15598,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I173" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -15657,7 +15642,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 28708-2026</t>
+          <t>A 13040-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -15671,10 +15656,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46198</v>
+        <v>46093</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15692,7 +15677,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>2.8</v>
+        <v>7.1</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -15735,7 +15720,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 28695-2026</t>
+          <t>A 13405-2024</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -15749,10 +15734,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46198</v>
+        <v>45387</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15764,13 +15749,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I175" t="n">
-        <v>2.7</v>
+        <v>0.9</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -15813,7 +15793,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 8059-2024</t>
+          <t>A 13039-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -15827,10 +15807,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45351</v>
+        <v>46093</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15848,7 +15828,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>1.6</v>
+        <v>5.1</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -15891,7 +15871,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 29482-2023</t>
+          <t>A 12729-2024</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -15905,10 +15885,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45106</v>
+        <v>45384</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15920,8 +15900,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I177" t="n">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -15964,7 +15949,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 59158-2022</t>
+          <t>A 29552-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -15974,14 +15959,14 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>44904</v>
+        <v>46204</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15999,7 +15984,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>3.7</v>
+        <v>2.3</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -16042,7 +16027,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 29130-2026</t>
+          <t>A 18913-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -16056,10 +16041,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46202</v>
+        <v>46129</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16077,7 +16062,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>10.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -16120,7 +16105,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 28930-2026</t>
+          <t>A 18506-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -16134,10 +16119,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46199</v>
+        <v>46127</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16150,7 +16135,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -16193,7 +16178,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 18773-2025</t>
+          <t>A 19227-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -16207,10 +16192,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45763</v>
+        <v>46132</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16223,7 +16208,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>13</v>
+        <v>2.4</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -16266,7 +16251,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 10320-2023</t>
+          <t>A 63905-2021</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -16280,10 +16265,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>44986</v>
+        <v>44509</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16295,8 +16280,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I182" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -16339,7 +16329,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 29132-2026</t>
+          <t>A 38743-2022</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -16353,10 +16343,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46202</v>
+        <v>44816</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16374,7 +16364,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>11.9</v>
+        <v>1.6</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -16417,7 +16407,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 18913-2026</t>
+          <t>A 47935-2024</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -16431,10 +16421,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46129</v>
+        <v>45589</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16452,7 +16442,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>8.300000000000001</v>
+        <v>2.2</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -16495,7 +16485,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 10797-2023</t>
+          <t>A 50377-2024</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -16509,10 +16499,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>44989</v>
+        <v>45601</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16524,8 +16514,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I185" t="n">
-        <v>9.5</v>
+        <v>0.7</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -16568,7 +16563,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 11084-2023</t>
+          <t>A 8059-2024</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -16582,10 +16577,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>44986</v>
+        <v>45351</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16597,8 +16592,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I186" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -16641,7 +16641,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 50764-2024</t>
+          <t>A 29482-2023</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -16655,10 +16655,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45602</v>
+        <v>45106</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16670,13 +16670,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I187" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -16719,7 +16714,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 33658-2024</t>
+          <t>A 59158-2022</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -16729,14 +16724,14 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45520</v>
+        <v>44904</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16748,8 +16743,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I188" t="n">
-        <v>2.2</v>
+        <v>3.7</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -16792,7 +16792,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 18506-2026</t>
+          <t>A 35213-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -16806,10 +16806,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46127</v>
+        <v>46260</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16821,8 +16821,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I189" t="n">
-        <v>1.6</v>
+        <v>9.5</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -16865,7 +16870,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 19227-2026</t>
+          <t>A 18773-2025</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -16879,10 +16884,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46132</v>
+        <v>45763</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16895,7 +16900,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>2.4</v>
+        <v>13</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -16938,7 +16943,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 45861-2023</t>
+          <t>A 10320-2023</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -16948,14 +16953,14 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45195</v>
+        <v>44986</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16967,13 +16972,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I191" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -17016,7 +17016,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 43768-2024</t>
+          <t>A 10797-2023</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -17030,10 +17030,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45569</v>
+        <v>44989</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17046,7 +17046,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>7</v>
+        <v>9.5</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -17089,7 +17089,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 29552-2026</t>
+          <t>A 11084-2023</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -17103,10 +17103,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46204</v>
+        <v>44986</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17118,13 +17118,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I193" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -17167,7 +17162,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 38738-2022</t>
+          <t>A 50764-2024</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -17181,10 +17176,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>44816</v>
+        <v>45602</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17202,7 +17197,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -17245,7 +17240,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 52131-2021</t>
+          <t>A 33658-2024</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -17259,10 +17254,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>44463</v>
+        <v>45520</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17275,7 +17270,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -17318,7 +17313,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 61750-2021</t>
+          <t>A 36339-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -17332,10 +17327,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>44501</v>
+        <v>46268</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17347,13 +17342,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I196" t="n">
-        <v>1.8</v>
+        <v>0.4</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -17396,7 +17386,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 7472-2025</t>
+          <t>A 36345-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -17410,10 +17400,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45705</v>
+        <v>46268</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17425,13 +17415,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I197" t="n">
-        <v>2.6</v>
+        <v>0.3</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -17474,7 +17459,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 35213-2026</t>
+          <t>A 45861-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -17484,14 +17469,14 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46260</v>
+        <v>45195</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17509,7 +17494,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>9.5</v>
+        <v>0.7</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -17552,7 +17537,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 50207-2024</t>
+          <t>A 36336-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -17566,10 +17551,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45600</v>
+        <v>46268</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17582,7 +17567,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -17625,7 +17610,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 50208-2024</t>
+          <t>A 43768-2024</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -17639,10 +17624,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45600</v>
+        <v>45569</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17655,7 +17640,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>0.4</v>
+        <v>7</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -17698,7 +17683,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 12108-2024</t>
+          <t>A 31813-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -17712,10 +17697,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45376</v>
+        <v>46230</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17728,7 +17713,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>7.7</v>
+        <v>1.8</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -17771,7 +17756,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 18831-2025</t>
+          <t>A 31870-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -17785,10 +17770,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45764</v>
+        <v>46231</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17806,7 +17791,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>4.2</v>
+        <v>1.5</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -17849,7 +17834,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 36339-2026</t>
+          <t>A 31871-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -17863,10 +17848,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>46268</v>
+        <v>46231</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17878,8 +17863,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I203" t="n">
-        <v>0.4</v>
+        <v>1.9</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -17922,7 +17912,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 36345-2026</t>
+          <t>A 38738-2022</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -17936,10 +17926,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>46268</v>
+        <v>44816</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17951,8 +17941,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I204" t="n">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -17995,7 +17990,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 32154-2023</t>
+          <t>A 31872-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -18009,10 +18004,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45119</v>
+        <v>46231</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18024,8 +18019,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I205" t="n">
-        <v>2.3</v>
+        <v>5.2</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -18068,7 +18068,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 36336-2026</t>
+          <t>A 37809-2026</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -18082,10 +18082,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>46268</v>
+        <v>46279</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18098,7 +18098,7 @@
         </is>
       </c>
       <c r="I206" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -18141,7 +18141,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 27438-2024</t>
+          <t>A 52131-2021</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -18155,10 +18155,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45474</v>
+        <v>44463</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18171,7 +18171,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -18214,7 +18214,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 31813-2026</t>
+          <t>A 38126-2026</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -18228,10 +18228,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>46230</v>
+        <v>46281</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18243,8 +18243,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I208" t="n">
-        <v>1.8</v>
+        <v>5.5</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -18287,7 +18292,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 46288-2024</t>
+          <t>A 32506-2026</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -18301,10 +18306,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45581</v>
+        <v>46239</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18322,7 +18327,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>3.7</v>
+        <v>1.1</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -18365,7 +18370,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 31870-2026</t>
+          <t>A 38651-2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -18379,10 +18384,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>46231</v>
+        <v>46283</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18400,7 +18405,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>1.5</v>
+        <v>11.3</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -18443,7 +18448,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 31871-2026</t>
+          <t>A 38463-2026</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -18457,10 +18462,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>46231</v>
+        <v>46282</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18472,13 +18477,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I211" t="n">
-        <v>1.9</v>
+        <v>3.4</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -18521,7 +18521,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 51996-2023</t>
+          <t>A 32508-2026</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -18535,10 +18535,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45223</v>
+        <v>46239</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18556,7 +18556,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -18599,7 +18599,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 31872-2026</t>
+          <t>A 38659-2026</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -18613,10 +18613,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>46231</v>
+        <v>46283</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18634,7 +18634,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -18677,7 +18677,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 58629-2024</t>
+          <t>A 61750-2021</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -18691,10 +18691,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45635</v>
+        <v>44501</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18712,7 +18712,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -18755,7 +18755,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 37809-2026</t>
+          <t>A 7472-2025</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -18769,10 +18769,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>46279</v>
+        <v>45705</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18784,8 +18784,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I215" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -18828,7 +18833,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 50102-2023</t>
+          <t>A 50207-2024</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -18842,10 +18847,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45215</v>
+        <v>45600</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18857,13 +18862,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I216" t="n">
-        <v>3.9</v>
+        <v>1.2</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -18906,7 +18906,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 38126-2026</t>
+          <t>A 50208-2024</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -18920,10 +18920,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>46281</v>
+        <v>45600</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18935,13 +18935,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H217" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I217" t="n">
-        <v>5.5</v>
+        <v>0.4</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -18984,7 +18979,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 62982-2023</t>
+          <t>A 32810-2026</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -18998,10 +18993,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45272</v>
+        <v>46241</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19014,7 +19009,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>3.5</v>
+        <v>6.1</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -19057,7 +19052,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 21935-2024</t>
+          <t>A 12108-2024</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -19071,10 +19066,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45443</v>
+        <v>45376</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19086,13 +19081,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H219" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I219" t="n">
-        <v>1.8</v>
+        <v>7.7</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -19135,7 +19125,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 23460-2024</t>
+          <t>A 18831-2025</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -19149,10 +19139,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45453</v>
+        <v>45764</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19164,8 +19154,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I220" t="n">
-        <v>0.7</v>
+        <v>4.2</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -19208,7 +19203,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 32506-2026</t>
+          <t>A 32154-2023</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -19222,10 +19217,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>46239</v>
+        <v>45119</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19237,13 +19232,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H221" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I221" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -19286,7 +19276,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 38651-2026</t>
+          <t>A 27438-2024</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -19300,10 +19290,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>46283</v>
+        <v>45474</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19315,13 +19305,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H222" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I222" t="n">
-        <v>11.3</v>
+        <v>2.6</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -19364,7 +19349,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 38463-2026</t>
+          <t>A 46288-2024</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -19378,10 +19363,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>46282</v>
+        <v>45581</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19393,8 +19378,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I223" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -19437,7 +19427,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 32508-2026</t>
+          <t>A 51996-2023</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -19451,10 +19441,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>46239</v>
+        <v>45223</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19472,7 +19462,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -19515,7 +19505,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 38659-2026</t>
+          <t>A 58629-2024</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -19529,10 +19519,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>46283</v>
+        <v>45635</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19550,7 +19540,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>4.6</v>
+        <v>1.4</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -19593,7 +19583,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 24707-2025</t>
+          <t>A 50102-2023</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -19607,10 +19597,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45798</v>
+        <v>45215</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19622,8 +19612,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I226" t="n">
-        <v>0.5</v>
+        <v>3.9</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -19666,7 +19661,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 5218-2024</t>
+          <t>A 62982-2023</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -19680,10 +19675,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45330</v>
+        <v>45272</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19695,13 +19690,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H227" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I227" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -19744,7 +19734,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 32810-2026</t>
+          <t>A 21935-2024</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -19758,10 +19748,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>46241</v>
+        <v>45443</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19773,8 +19763,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I228" t="n">
-        <v>6.1</v>
+        <v>1.8</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -19817,7 +19812,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 26820-2025</t>
+          <t>A 23460-2024</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -19831,10 +19826,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45810</v>
+        <v>45453</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19890,7 +19885,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 26783-2025</t>
+          <t>A 24707-2025</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -19904,10 +19899,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45810</v>
+        <v>45798</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19920,7 +19915,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -19963,7 +19958,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 28367-2025</t>
+          <t>A 5218-2024</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -19977,10 +19972,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45819</v>
+        <v>45330</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19998,7 +19993,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>6.1</v>
+        <v>3.3</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -20041,7 +20036,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 28368-2025</t>
+          <t>A 26820-2025</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -20055,10 +20050,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45819</v>
+        <v>45810</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20070,13 +20065,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H232" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I232" t="n">
-        <v>8.1</v>
+        <v>0.7</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -20119,7 +20109,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 23066-2022</t>
+          <t>A 26783-2025</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -20133,10 +20123,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>44719</v>
+        <v>45810</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20149,7 +20139,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -20192,7 +20182,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 33404-2025</t>
+          <t>A 28367-2025</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -20206,10 +20196,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45841</v>
+        <v>45819</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20221,8 +20211,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I234" t="n">
-        <v>1.5</v>
+        <v>6.1</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -20265,7 +20260,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 59863-2024</t>
+          <t>A 28368-2025</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -20279,10 +20274,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45639</v>
+        <v>45819</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20294,8 +20289,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I235" t="n">
-        <v>1.6</v>
+        <v>8.1</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -20338,7 +20338,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 37333-2025</t>
+          <t>A 23066-2022</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -20348,14 +20348,14 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45876</v>
+        <v>44719</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20368,7 +20368,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -20411,7 +20411,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 37265-2025</t>
+          <t>A 33404-2025</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -20425,10 +20425,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45876</v>
+        <v>45841</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20441,7 +20441,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -20484,7 +20484,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 15594-2025</t>
+          <t>A 59863-2024</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -20498,10 +20498,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45747</v>
+        <v>45639</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20514,7 +20514,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -20574,7 +20574,7 @@
         <v>44587</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20647,7 +20647,7 @@
         <v>45805</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20725,7 +20725,7 @@
         <v>45805</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20803,7 +20803,7 @@
         <v>45729</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20881,7 +20881,7 @@
         <v>45729</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20959,7 +20959,7 @@
         <v>45742</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21037,7 +21037,7 @@
         <v>45742</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21115,7 +21115,7 @@
         <v>45916</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>

--- a/Översikt DEGERFORS.xlsx
+++ b/Översikt DEGERFORS.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE245"/>
+  <dimension ref="A1:AE244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>46160</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>46051</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 22871-2026</t>
+          <t>A 15809-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -850,10 +850,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46160</v>
+        <v>46107</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -871,13 +871,13 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>3.2</v>
+        <v>9.5</v>
       </c>
       <c r="J4" t="n">
         <v>11</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>6</v>
@@ -904,12 +904,138 @@
         <v>13</v>
       </c>
       <c r="T4" t="n">
+        <v>21</v>
+      </c>
+      <c r="U4" t="n">
+        <v>20</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Tornseglare
+Dropptaggsvamp
+Duvhök
+Järnsparv
+Nordfladdermus
+Orange taggsvamp
+Talltita
+Spillkråka
+Tjäder
+Tofsmes
+Dvärgpipistrell
+Vattenfladdermus
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 15809-2026 artfynd.xlsx", "A 15809-2026")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 15809-2026 karta.png", "A 15809-2026")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 15809-2026 georefererad karta.tif", "A 15809-2026")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 15809-2026 FSC-klagomål.docx", "A 15809-2026")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 15809-2026 FSC-klagomål mail.docx", "A 15809-2026")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 15809-2026 tillsynsbegäran.docx", "A 15809-2026")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 15809-2026 tillsynsbegäran mail.docx", "A 15809-2026")</f>
+        <v/>
+      </c>
+      <c r="AE4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 15809-2026 prioriterade fågelarter.docx", "A 15809-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 22871-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>46160</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>DEGERFORS</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J5" t="n">
+        <v>11</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>6</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>7</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>13</v>
+      </c>
+      <c r="T5" t="n">
         <v>35</v>
       </c>
-      <c r="U4" t="n">
+      <c r="U5" t="n">
         <v>35</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Tornseglare
 Brunlångöra
@@ -926,162 +1052,36 @@
 Havsörn</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 22871-2026 artfynd.xlsx", "A 22871-2026")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 22871-2026 karta.png", "A 22871-2026")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 22871-2026 georefererad karta.tif", "A 22871-2026")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 22871-2026 FSC-klagomål.docx", "A 22871-2026")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 22871-2026 FSC-klagomål mail.docx", "A 22871-2026")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 22871-2026 tillsynsbegäran.docx", "A 22871-2026")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 22871-2026 tillsynsbegäran mail.docx", "A 22871-2026")</f>
         <v/>
       </c>
-      <c r="AE4">
+      <c r="AE5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 22871-2026 prioriterade fågelarter.docx", "A 22871-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 15809-2026</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>46107</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>DEGERFORS</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="J5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>6</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>7</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" t="n">
-        <v>13</v>
-      </c>
-      <c r="T5" t="n">
-        <v>21</v>
-      </c>
-      <c r="U5" t="n">
-        <v>20</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Tornseglare
-Dropptaggsvamp
-Duvhök
-Järnsparv
-Nordfladdermus
-Orange taggsvamp
-Talltita
-Spillkråka
-Tjäder
-Tofsmes
-Dvärgpipistrell
-Vattenfladdermus
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 15809-2026 artfynd.xlsx", "A 15809-2026")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 15809-2026 karta.png", "A 15809-2026")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 15809-2026 georefererad karta.tif", "A 15809-2026")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 15809-2026 FSC-klagomål.docx", "A 15809-2026")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 15809-2026 FSC-klagomål mail.docx", "A 15809-2026")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 15809-2026 tillsynsbegäran.docx", "A 15809-2026")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 15809-2026 tillsynsbegäran mail.docx", "A 15809-2026")</f>
-        <v/>
-      </c>
-      <c r="AE5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 15809-2026 prioriterade fågelarter.docx", "A 15809-2026")</f>
         <v/>
       </c>
     </row>
@@ -1105,7 +1105,7 @@
         <v>46190</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>46190</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>46161</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>45089</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>45175</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>46160</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>45384</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
         <v>45384</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>45163</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 29553-2026</t>
+          <t>A 73321-2021</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2193,10 +2193,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46204</v>
+        <v>44550</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2208,22 +2208,17 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>6.5</v>
+        <v>17</v>
       </c>
       <c r="J15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M15" t="n">
         <v>1</v>
@@ -2238,7 +2233,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R15" t="n">
         <v>1</v>
@@ -2247,12 +2242,135 @@
         <v>6</v>
       </c>
       <c r="T15" t="n">
+        <v>8</v>
+      </c>
+      <c r="U15" t="n">
+        <v>8</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Grynig filtlav
+Gulsparv
+Rynkskinn
+Vedticka
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 73321-2021 artfynd.xlsx", "A 73321-2021")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 73321-2021 karta.png", "A 73321-2021")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 73321-2021 georefererad karta.tif", "A 73321-2021")</f>
+        <v/>
+      </c>
+      <c r="Z15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/knärot/A 73321-2021 karta knärot.png", "A 73321-2021")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 73321-2021 FSC-klagomål.docx", "A 73321-2021")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 73321-2021 FSC-klagomål mail.docx", "A 73321-2021")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 73321-2021 tillsynsbegäran.docx", "A 73321-2021")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 73321-2021 tillsynsbegäran mail.docx", "A 73321-2021")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 73321-2021 prioriterade fågelarter.docx", "A 73321-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 29553-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>DEGERFORS</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>4</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>5</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" t="n">
         <v>6</v>
       </c>
-      <c r="U15" t="n">
+      <c r="T16" t="n">
+        <v>6</v>
+      </c>
+      <c r="U16" t="n">
         <v>2</v>
       </c>
-      <c r="V15" s="2" t="inlineStr">
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Skuggblåslav
@@ -2262,154 +2380,36 @@
 Tofsmes</t>
         </is>
       </c>
-      <c r="W15">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 29553-2026 artfynd.xlsx", "A 29553-2026")</f>
         <v/>
       </c>
-      <c r="X15">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 29553-2026 karta.png", "A 29553-2026")</f>
         <v/>
       </c>
-      <c r="Y15">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 29553-2026 georefererad karta.tif", "A 29553-2026")</f>
         <v/>
       </c>
-      <c r="AA15">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 29553-2026 FSC-klagomål.docx", "A 29553-2026")</f>
         <v/>
       </c>
-      <c r="AB15">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 29553-2026 FSC-klagomål mail.docx", "A 29553-2026")</f>
         <v/>
       </c>
-      <c r="AC15">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 29553-2026 tillsynsbegäran.docx", "A 29553-2026")</f>
         <v/>
       </c>
-      <c r="AD15">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 29553-2026 tillsynsbegäran mail.docx", "A 29553-2026")</f>
         <v/>
       </c>
-      <c r="AE15">
+      <c r="AE16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 29553-2026 prioriterade fågelarter.docx", "A 29553-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 73321-2021</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>44550</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>DEGERFORS</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>17</v>
-      </c>
-      <c r="J16" t="n">
-        <v>3</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>3</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>4</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1</v>
-      </c>
-      <c r="S16" t="n">
-        <v>6</v>
-      </c>
-      <c r="T16" t="n">
-        <v>8</v>
-      </c>
-      <c r="U16" t="n">
-        <v>8</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Grynig filtlav
-Gulsparv
-Rynkskinn
-Vedticka
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 73321-2021 artfynd.xlsx", "A 73321-2021")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 73321-2021 karta.png", "A 73321-2021")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 73321-2021 georefererad karta.tif", "A 73321-2021")</f>
-        <v/>
-      </c>
-      <c r="Z16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/knärot/A 73321-2021 karta knärot.png", "A 73321-2021")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 73321-2021 FSC-klagomål.docx", "A 73321-2021")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 73321-2021 FSC-klagomål mail.docx", "A 73321-2021")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 73321-2021 tillsynsbegäran.docx", "A 73321-2021")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 73321-2021 tillsynsbegäran mail.docx", "A 73321-2021")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 73321-2021 prioriterade fågelarter.docx", "A 73321-2021")</f>
         <v/>
       </c>
     </row>
@@ -2433,7 +2433,7 @@
         <v>45175</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         <v>45932</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>45163</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>45205</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2880,7 +2880,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 8063-2024</t>
+          <t>A 36081-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2894,10 +2894,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45351</v>
+        <v>45866</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
         <v>4</v>
       </c>
       <c r="U21" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
@@ -2962,38 +2962,38 @@
         </is>
       </c>
       <c r="W21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 8063-2024 artfynd.xlsx", "A 8063-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 36081-2025 artfynd.xlsx", "A 36081-2025")</f>
         <v/>
       </c>
       <c r="X21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 8063-2024 karta.png", "A 8063-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 36081-2025 karta.png", "A 36081-2025")</f>
         <v/>
       </c>
       <c r="Y21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 8063-2024 georefererad karta.tif", "A 8063-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 36081-2025 georefererad karta.tif", "A 36081-2025")</f>
         <v/>
       </c>
       <c r="AA21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 8063-2024 FSC-klagomål.docx", "A 8063-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 36081-2025 FSC-klagomål.docx", "A 36081-2025")</f>
         <v/>
       </c>
       <c r="AB21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 8063-2024 FSC-klagomål mail.docx", "A 8063-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 36081-2025 FSC-klagomål mail.docx", "A 36081-2025")</f>
         <v/>
       </c>
       <c r="AC21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 8063-2024 tillsynsbegäran.docx", "A 8063-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 36081-2025 tillsynsbegäran.docx", "A 36081-2025")</f>
         <v/>
       </c>
       <c r="AD21">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 8063-2024 tillsynsbegäran mail.docx", "A 8063-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 36081-2025 tillsynsbegäran mail.docx", "A 36081-2025")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 36081-2025</t>
+          <t>A 8063-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3007,10 +3007,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45866</v>
+        <v>45351</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
         <v>4</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
@@ -3075,31 +3075,31 @@
         </is>
       </c>
       <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 36081-2025 artfynd.xlsx", "A 36081-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 8063-2024 artfynd.xlsx", "A 8063-2024")</f>
         <v/>
       </c>
       <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 36081-2025 karta.png", "A 36081-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 8063-2024 karta.png", "A 8063-2024")</f>
         <v/>
       </c>
       <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 36081-2025 georefererad karta.tif", "A 36081-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 8063-2024 georefererad karta.tif", "A 8063-2024")</f>
         <v/>
       </c>
       <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 36081-2025 FSC-klagomål.docx", "A 36081-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 8063-2024 FSC-klagomål.docx", "A 8063-2024")</f>
         <v/>
       </c>
       <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 36081-2025 FSC-klagomål mail.docx", "A 36081-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 8063-2024 FSC-klagomål mail.docx", "A 8063-2024")</f>
         <v/>
       </c>
       <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 36081-2025 tillsynsbegäran.docx", "A 36081-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 8063-2024 tillsynsbegäran.docx", "A 8063-2024")</f>
         <v/>
       </c>
       <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 36081-2025 tillsynsbegäran mail.docx", "A 36081-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 8063-2024 tillsynsbegäran mail.docx", "A 8063-2024")</f>
         <v/>
       </c>
     </row>
@@ -3123,7 +3123,7 @@
         <v>45559</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>45931</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>45384</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>46190</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 38914-2023</t>
+          <t>A 4256-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3580,10 +3580,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45163</v>
+        <v>46045</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3595,23 +3595,18 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>5.4</v>
+        <v>2.9</v>
       </c>
       <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
         <v>2</v>
       </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>1</v>
-      </c>
       <c r="M27" t="n">
         <v>0</v>
       </c>
@@ -3625,7 +3620,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -3637,720 +3632,725 @@
         <v>2</v>
       </c>
       <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>Skogsklocka
+Slåtterfibbla</t>
+        </is>
+      </c>
+      <c r="W27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 4256-2026 artfynd.xlsx", "A 4256-2026")</f>
+        <v/>
+      </c>
+      <c r="X27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 4256-2026 karta.png", "A 4256-2026")</f>
+        <v/>
+      </c>
+      <c r="Y27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 4256-2026 georefererad karta.tif", "A 4256-2026")</f>
+        <v/>
+      </c>
+      <c r="AA27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 4256-2026 FSC-klagomål.docx", "A 4256-2026")</f>
+        <v/>
+      </c>
+      <c r="AB27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 4256-2026 FSC-klagomål mail.docx", "A 4256-2026")</f>
+        <v/>
+      </c>
+      <c r="AC27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 4256-2026 tillsynsbegäran.docx", "A 4256-2026")</f>
+        <v/>
+      </c>
+      <c r="AD27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 4256-2026 tillsynsbegäran mail.docx", "A 4256-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>A 47785-2025</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>DEGERFORS</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
         <v>2</v>
       </c>
-      <c r="V27" s="2" t="inlineStr">
+      <c r="J28" t="n">
+        <v>2</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 47785-2025 artfynd.xlsx", "A 47785-2025")</f>
+        <v/>
+      </c>
+      <c r="X28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 47785-2025 karta.png", "A 47785-2025")</f>
+        <v/>
+      </c>
+      <c r="Y28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 47785-2025 georefererad karta.tif", "A 47785-2025")</f>
+        <v/>
+      </c>
+      <c r="AA28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 47785-2025 FSC-klagomål.docx", "A 47785-2025")</f>
+        <v/>
+      </c>
+      <c r="AB28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 47785-2025 FSC-klagomål mail.docx", "A 47785-2025")</f>
+        <v/>
+      </c>
+      <c r="AC28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 47785-2025 tillsynsbegäran.docx", "A 47785-2025")</f>
+        <v/>
+      </c>
+      <c r="AD28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 47785-2025 tillsynsbegäran mail.docx", "A 47785-2025")</f>
+        <v/>
+      </c>
+      <c r="AE28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 47785-2025 prioriterade fågelarter.docx", "A 47785-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>A 38910-2023</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="n">
+        <v>45163</v>
+      </c>
+      <c r="E29" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>DEGERFORS</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>3</v>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>Tjäder
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 38910-2023 artfynd.xlsx", "A 38910-2023")</f>
+        <v/>
+      </c>
+      <c r="X29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 38910-2023 karta.png", "A 38910-2023")</f>
+        <v/>
+      </c>
+      <c r="Y29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 38910-2023 georefererad karta.tif", "A 38910-2023")</f>
+        <v/>
+      </c>
+      <c r="AA29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 38910-2023 FSC-klagomål.docx", "A 38910-2023")</f>
+        <v/>
+      </c>
+      <c r="AB29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 38910-2023 FSC-klagomål mail.docx", "A 38910-2023")</f>
+        <v/>
+      </c>
+      <c r="AC29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 38910-2023 tillsynsbegäran.docx", "A 38910-2023")</f>
+        <v/>
+      </c>
+      <c r="AD29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 38910-2023 tillsynsbegäran mail.docx", "A 38910-2023")</f>
+        <v/>
+      </c>
+      <c r="AE29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 38910-2023 prioriterade fågelarter.docx", "A 38910-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>A 40870-2024</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D30" s="1" t="n">
+        <v>45558</v>
+      </c>
+      <c r="E30" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>DEGERFORS</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 40870-2024 artfynd.xlsx", "A 40870-2024")</f>
+        <v/>
+      </c>
+      <c r="X30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 40870-2024 karta.png", "A 40870-2024")</f>
+        <v/>
+      </c>
+      <c r="Y30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 40870-2024 georefererad karta.tif", "A 40870-2024")</f>
+        <v/>
+      </c>
+      <c r="AA30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 40870-2024 FSC-klagomål.docx", "A 40870-2024")</f>
+        <v/>
+      </c>
+      <c r="AB30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 40870-2024 FSC-klagomål mail.docx", "A 40870-2024")</f>
+        <v/>
+      </c>
+      <c r="AC30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 40870-2024 tillsynsbegäran.docx", "A 40870-2024")</f>
+        <v/>
+      </c>
+      <c r="AD30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 40870-2024 tillsynsbegäran mail.docx", "A 40870-2024")</f>
+        <v/>
+      </c>
+      <c r="AE30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 40870-2024 prioriterade fågelarter.docx", "A 40870-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>A 38912-2023</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D31" s="1" t="n">
+        <v>45163</v>
+      </c>
+      <c r="E31" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>DEGERFORS</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
         <is>
           <t>Tretåig hackspett
 Tjäder</t>
         </is>
       </c>
-      <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 38914-2023 artfynd.xlsx", "A 38914-2023")</f>
-        <v/>
-      </c>
-      <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 38914-2023 karta.png", "A 38914-2023")</f>
-        <v/>
-      </c>
-      <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 38914-2023 georefererad karta.tif", "A 38914-2023")</f>
-        <v/>
-      </c>
-      <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 38914-2023 FSC-klagomål.docx", "A 38914-2023")</f>
-        <v/>
-      </c>
-      <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 38914-2023 FSC-klagomål mail.docx", "A 38914-2023")</f>
-        <v/>
-      </c>
-      <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 38914-2023 tillsynsbegäran.docx", "A 38914-2023")</f>
-        <v/>
-      </c>
-      <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 38914-2023 tillsynsbegäran mail.docx", "A 38914-2023")</f>
-        <v/>
-      </c>
-      <c r="AE27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 38914-2023 prioriterade fågelarter.docx", "A 38914-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>A 47785-2025</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D28" s="1" t="n">
-        <v>45931</v>
-      </c>
-      <c r="E28" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>DEGERFORS</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
+      <c r="W31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 38912-2023 artfynd.xlsx", "A 38912-2023")</f>
+        <v/>
+      </c>
+      <c r="X31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 38912-2023 karta.png", "A 38912-2023")</f>
+        <v/>
+      </c>
+      <c r="Y31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 38912-2023 georefererad karta.tif", "A 38912-2023")</f>
+        <v/>
+      </c>
+      <c r="AA31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 38912-2023 FSC-klagomål.docx", "A 38912-2023")</f>
+        <v/>
+      </c>
+      <c r="AB31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 38912-2023 FSC-klagomål mail.docx", "A 38912-2023")</f>
+        <v/>
+      </c>
+      <c r="AC31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 38912-2023 tillsynsbegäran.docx", "A 38912-2023")</f>
+        <v/>
+      </c>
+      <c r="AD31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 38912-2023 tillsynsbegäran mail.docx", "A 38912-2023")</f>
+        <v/>
+      </c>
+      <c r="AE31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 38912-2023 prioriterade fågelarter.docx", "A 38912-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>A 28976-2026</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D32" s="1" t="n">
+        <v>46199</v>
+      </c>
+      <c r="E32" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>DEGERFORS</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
         <v>2</v>
       </c>
-      <c r="J28" t="n">
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
         <v>2</v>
       </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
         <v>2</v>
       </c>
-      <c r="T28" t="n">
+      <c r="T32" t="n">
         <v>2</v>
       </c>
-      <c r="U28" t="n">
+      <c r="U32" t="n">
+        <v>1</v>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp
+Talltita</t>
+        </is>
+      </c>
+      <c r="W32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 28976-2026 artfynd.xlsx", "A 28976-2026")</f>
+        <v/>
+      </c>
+      <c r="X32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 28976-2026 karta.png", "A 28976-2026")</f>
+        <v/>
+      </c>
+      <c r="Y32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 28976-2026 georefererad karta.tif", "A 28976-2026")</f>
+        <v/>
+      </c>
+      <c r="AA32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 28976-2026 FSC-klagomål.docx", "A 28976-2026")</f>
+        <v/>
+      </c>
+      <c r="AB32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 28976-2026 FSC-klagomål mail.docx", "A 28976-2026")</f>
+        <v/>
+      </c>
+      <c r="AC32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 28976-2026 tillsynsbegäran.docx", "A 28976-2026")</f>
+        <v/>
+      </c>
+      <c r="AD32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 28976-2026 tillsynsbegäran mail.docx", "A 28976-2026")</f>
+        <v/>
+      </c>
+      <c r="AE32">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 28976-2026 prioriterade fågelarter.docx", "A 28976-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>A 38914-2023</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D33" s="1" t="n">
+        <v>45163</v>
+      </c>
+      <c r="E33" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>DEGERFORS</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J33" t="n">
         <v>2</v>
       </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 47785-2025 artfynd.xlsx", "A 47785-2025")</f>
-        <v/>
-      </c>
-      <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 47785-2025 karta.png", "A 47785-2025")</f>
-        <v/>
-      </c>
-      <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 47785-2025 georefererad karta.tif", "A 47785-2025")</f>
-        <v/>
-      </c>
-      <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 47785-2025 FSC-klagomål.docx", "A 47785-2025")</f>
-        <v/>
-      </c>
-      <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 47785-2025 FSC-klagomål mail.docx", "A 47785-2025")</f>
-        <v/>
-      </c>
-      <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 47785-2025 tillsynsbegäran.docx", "A 47785-2025")</f>
-        <v/>
-      </c>
-      <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 47785-2025 tillsynsbegäran mail.docx", "A 47785-2025")</f>
-        <v/>
-      </c>
-      <c r="AE28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 47785-2025 prioriterade fågelarter.docx", "A 47785-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>A 40870-2024</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D29" s="1" t="n">
-        <v>45558</v>
-      </c>
-      <c r="E29" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>DEGERFORS</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J29" t="n">
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
         <v>2</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>1</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>1</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
+      <c r="T33" t="n">
         <v>2</v>
       </c>
-      <c r="T29" t="n">
+      <c r="U33" t="n">
         <v>2</v>
       </c>
-      <c r="U29" t="n">
-        <v>2</v>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 40870-2024 artfynd.xlsx", "A 40870-2024")</f>
-        <v/>
-      </c>
-      <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 40870-2024 karta.png", "A 40870-2024")</f>
-        <v/>
-      </c>
-      <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 40870-2024 georefererad karta.tif", "A 40870-2024")</f>
-        <v/>
-      </c>
-      <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 40870-2024 FSC-klagomål.docx", "A 40870-2024")</f>
-        <v/>
-      </c>
-      <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 40870-2024 FSC-klagomål mail.docx", "A 40870-2024")</f>
-        <v/>
-      </c>
-      <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 40870-2024 tillsynsbegäran.docx", "A 40870-2024")</f>
-        <v/>
-      </c>
-      <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 40870-2024 tillsynsbegäran mail.docx", "A 40870-2024")</f>
-        <v/>
-      </c>
-      <c r="AE29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 40870-2024 prioriterade fågelarter.docx", "A 40870-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>A 38910-2023</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D30" s="1" t="n">
-        <v>45163</v>
-      </c>
-      <c r="E30" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>DEGERFORS</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J30" t="n">
-        <v>2</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2</v>
-      </c>
-      <c r="T30" t="n">
-        <v>3</v>
-      </c>
-      <c r="U30" t="n">
-        <v>3</v>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>Tjäder
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 38910-2023 artfynd.xlsx", "A 38910-2023")</f>
-        <v/>
-      </c>
-      <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 38910-2023 karta.png", "A 38910-2023")</f>
-        <v/>
-      </c>
-      <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 38910-2023 georefererad karta.tif", "A 38910-2023")</f>
-        <v/>
-      </c>
-      <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 38910-2023 FSC-klagomål.docx", "A 38910-2023")</f>
-        <v/>
-      </c>
-      <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 38910-2023 FSC-klagomål mail.docx", "A 38910-2023")</f>
-        <v/>
-      </c>
-      <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 38910-2023 tillsynsbegäran.docx", "A 38910-2023")</f>
-        <v/>
-      </c>
-      <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 38910-2023 tillsynsbegäran mail.docx", "A 38910-2023")</f>
-        <v/>
-      </c>
-      <c r="AE30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 38910-2023 prioriterade fågelarter.docx", "A 38910-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>A 38912-2023</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D31" s="1" t="n">
-        <v>45163</v>
-      </c>
-      <c r="E31" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>DEGERFORS</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I31" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="J31" t="n">
-        <v>2</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>1</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2</v>
-      </c>
-      <c r="U31" t="n">
-        <v>2</v>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
+      <c r="V33" s="2" t="inlineStr">
         <is>
           <t>Tretåig hackspett
 Tjäder</t>
         </is>
       </c>
-      <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 38912-2023 artfynd.xlsx", "A 38912-2023")</f>
-        <v/>
-      </c>
-      <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 38912-2023 karta.png", "A 38912-2023")</f>
-        <v/>
-      </c>
-      <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 38912-2023 georefererad karta.tif", "A 38912-2023")</f>
-        <v/>
-      </c>
-      <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 38912-2023 FSC-klagomål.docx", "A 38912-2023")</f>
-        <v/>
-      </c>
-      <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 38912-2023 FSC-klagomål mail.docx", "A 38912-2023")</f>
-        <v/>
-      </c>
-      <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 38912-2023 tillsynsbegäran.docx", "A 38912-2023")</f>
-        <v/>
-      </c>
-      <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 38912-2023 tillsynsbegäran mail.docx", "A 38912-2023")</f>
-        <v/>
-      </c>
-      <c r="AE31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 38912-2023 prioriterade fågelarter.docx", "A 38912-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="15" customHeight="1">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>A 4256-2026</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D32" s="1" t="n">
-        <v>46045</v>
-      </c>
-      <c r="E32" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>DEGERFORS</t>
-        </is>
-      </c>
-      <c r="I32" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>2</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>2</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>Skogsklocka
-Slåtterfibbla</t>
-        </is>
-      </c>
-      <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 4256-2026 artfynd.xlsx", "A 4256-2026")</f>
-        <v/>
-      </c>
-      <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 4256-2026 karta.png", "A 4256-2026")</f>
-        <v/>
-      </c>
-      <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 4256-2026 georefererad karta.tif", "A 4256-2026")</f>
-        <v/>
-      </c>
-      <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 4256-2026 FSC-klagomål.docx", "A 4256-2026")</f>
-        <v/>
-      </c>
-      <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 4256-2026 FSC-klagomål mail.docx", "A 4256-2026")</f>
-        <v/>
-      </c>
-      <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 4256-2026 tillsynsbegäran.docx", "A 4256-2026")</f>
-        <v/>
-      </c>
-      <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 4256-2026 tillsynsbegäran mail.docx", "A 4256-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>A 28976-2026</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D33" s="1" t="n">
-        <v>46199</v>
-      </c>
-      <c r="E33" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>DEGERFORS</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I33" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J33" t="n">
-        <v>1</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
-        <v>2</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>2</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
-        <v>2</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1</v>
-      </c>
-      <c r="V33" s="2" t="inlineStr">
-        <is>
-          <t>Orange taggsvamp
-Talltita</t>
-        </is>
-      </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 28976-2026 artfynd.xlsx", "A 28976-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 38914-2023 artfynd.xlsx", "A 38914-2023")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 28976-2026 karta.png", "A 28976-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 38914-2023 karta.png", "A 38914-2023")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 28976-2026 georefererad karta.tif", "A 28976-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 38914-2023 georefererad karta.tif", "A 38914-2023")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 28976-2026 FSC-klagomål.docx", "A 28976-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 38914-2023 FSC-klagomål.docx", "A 38914-2023")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 28976-2026 FSC-klagomål mail.docx", "A 28976-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 38914-2023 FSC-klagomål mail.docx", "A 38914-2023")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 28976-2026 tillsynsbegäran.docx", "A 28976-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 38914-2023 tillsynsbegäran.docx", "A 38914-2023")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 28976-2026 tillsynsbegäran mail.docx", "A 28976-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 38914-2023 tillsynsbegäran mail.docx", "A 38914-2023")</f>
         <v/>
       </c>
       <c r="AE33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 28976-2026 prioriterade fågelarter.docx", "A 28976-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 38914-2023 prioriterade fågelarter.docx", "A 38914-2023")</f>
         <v/>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
         <v>44470</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>44487</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>44470</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 33297-2023</t>
+          <t>A 49306-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4701,10 +4701,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45116</v>
+        <v>45938</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4717,19 +4717,19 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>7.2</v>
+        <v>5.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
         <v>0</v>
@@ -4741,10 +4741,10 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>1</v>
@@ -4753,46 +4753,46 @@
         <v>1</v>
       </c>
       <c r="U37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 33297-2023 artfynd.xlsx", "A 33297-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 49306-2025 artfynd.xlsx", "A 49306-2025")</f>
         <v/>
       </c>
       <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 33297-2023 karta.png", "A 33297-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 49306-2025 karta.png", "A 49306-2025")</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 33297-2023 georefererad karta.tif", "A 33297-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 49306-2025 georefererad karta.tif", "A 49306-2025")</f>
         <v/>
       </c>
       <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 33297-2023 FSC-klagomål.docx", "A 33297-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 49306-2025 FSC-klagomål.docx", "A 49306-2025")</f>
         <v/>
       </c>
       <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 33297-2023 FSC-klagomål mail.docx", "A 33297-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 49306-2025 FSC-klagomål mail.docx", "A 49306-2025")</f>
         <v/>
       </c>
       <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 33297-2023 tillsynsbegäran.docx", "A 33297-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 49306-2025 tillsynsbegäran.docx", "A 49306-2025")</f>
         <v/>
       </c>
       <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 33297-2023 tillsynsbegäran mail.docx", "A 33297-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 49306-2025 tillsynsbegäran mail.docx", "A 49306-2025")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 38904-2023</t>
+          <t>A 14177-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4806,10 +4806,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45163</v>
+        <v>46099</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4827,17 +4827,17 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
         <v>1</v>
       </c>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" t="n">
-        <v>0</v>
-      </c>
       <c r="M38" t="n">
         <v>0</v>
       </c>
@@ -4851,7 +4851,7 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -4863,50 +4863,46 @@
         <v>1</v>
       </c>
       <c r="U38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 38904-2023 artfynd.xlsx", "A 38904-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 14177-2026 artfynd.xlsx", "A 14177-2026")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 38904-2023 karta.png", "A 38904-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 14177-2026 karta.png", "A 14177-2026")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 38904-2023 georefererad karta.tif", "A 38904-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 14177-2026 georefererad karta.tif", "A 14177-2026")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 38904-2023 FSC-klagomål.docx", "A 38904-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 14177-2026 FSC-klagomål.docx", "A 14177-2026")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 38904-2023 FSC-klagomål mail.docx", "A 38904-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 14177-2026 FSC-klagomål mail.docx", "A 14177-2026")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 38904-2023 tillsynsbegäran.docx", "A 38904-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 14177-2026 tillsynsbegäran.docx", "A 14177-2026")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 38904-2023 tillsynsbegäran mail.docx", "A 38904-2023")</f>
-        <v/>
-      </c>
-      <c r="AE38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 38904-2023 prioriterade fågelarter.docx", "A 38904-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 14177-2026 tillsynsbegäran mail.docx", "A 14177-2026")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 27093-2023</t>
+          <t>A 47915-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4920,10 +4916,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45096</v>
+        <v>45589</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4941,7 +4937,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="J39" t="n">
         <v>1</v>
@@ -4977,50 +4973,46 @@
         <v>1</v>
       </c>
       <c r="U39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 27093-2023 artfynd.xlsx", "A 27093-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 47915-2024 artfynd.xlsx", "A 47915-2024")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 27093-2023 karta.png", "A 27093-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 47915-2024 karta.png", "A 47915-2024")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 27093-2023 georefererad karta.tif", "A 27093-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 47915-2024 georefererad karta.tif", "A 47915-2024")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 27093-2023 FSC-klagomål.docx", "A 27093-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 47915-2024 FSC-klagomål.docx", "A 47915-2024")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 27093-2023 FSC-klagomål mail.docx", "A 27093-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 47915-2024 FSC-klagomål mail.docx", "A 47915-2024")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 27093-2023 tillsynsbegäran.docx", "A 27093-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 47915-2024 tillsynsbegäran.docx", "A 47915-2024")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 27093-2023 tillsynsbegäran mail.docx", "A 27093-2023")</f>
-        <v/>
-      </c>
-      <c r="AE39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 27093-2023 prioriterade fågelarter.docx", "A 27093-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 47915-2024 tillsynsbegäran mail.docx", "A 47915-2024")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 49306-2025</t>
+          <t>A 47787-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5034,10 +5026,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45938</v>
+        <v>45931</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5050,17 +5042,17 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>5.8</v>
+        <v>4.1</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
         <v>1</v>
       </c>
-      <c r="L40" t="n">
-        <v>0</v>
-      </c>
       <c r="M40" t="n">
         <v>0</v>
       </c>
@@ -5074,7 +5066,7 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
@@ -5083,49 +5075,53 @@
         <v>1</v>
       </c>
       <c r="T40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 49306-2025 artfynd.xlsx", "A 49306-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 47787-2025 artfynd.xlsx", "A 47787-2025")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 49306-2025 karta.png", "A 49306-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 47787-2025 karta.png", "A 47787-2025")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 49306-2025 georefererad karta.tif", "A 49306-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 47787-2025 georefererad karta.tif", "A 47787-2025")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 49306-2025 FSC-klagomål.docx", "A 49306-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 47787-2025 FSC-klagomål.docx", "A 47787-2025")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 49306-2025 FSC-klagomål mail.docx", "A 49306-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 47787-2025 FSC-klagomål mail.docx", "A 47787-2025")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 49306-2025 tillsynsbegäran.docx", "A 49306-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 47787-2025 tillsynsbegäran.docx", "A 47787-2025")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 49306-2025 tillsynsbegäran mail.docx", "A 49306-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 47787-2025 tillsynsbegäran mail.docx", "A 47787-2025")</f>
+        <v/>
+      </c>
+      <c r="AE40">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 47787-2025 prioriterade fågelarter.docx", "A 47787-2025")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 48285-2023</t>
+          <t>A 38904-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5139,10 +5135,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45205</v>
+        <v>45163</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5160,7 +5156,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
       <c r="J41" t="n">
         <v>1</v>
@@ -5204,42 +5200,42 @@
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 48285-2023 artfynd.xlsx", "A 48285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 38904-2023 artfynd.xlsx", "A 38904-2023")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 48285-2023 karta.png", "A 48285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 38904-2023 karta.png", "A 38904-2023")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 48285-2023 georefererad karta.tif", "A 48285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 38904-2023 georefererad karta.tif", "A 38904-2023")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 48285-2023 FSC-klagomål.docx", "A 48285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 38904-2023 FSC-klagomål.docx", "A 38904-2023")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 48285-2023 FSC-klagomål mail.docx", "A 48285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 38904-2023 FSC-klagomål mail.docx", "A 38904-2023")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 48285-2023 tillsynsbegäran.docx", "A 48285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 38904-2023 tillsynsbegäran.docx", "A 38904-2023")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 48285-2023 tillsynsbegäran mail.docx", "A 48285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 38904-2023 tillsynsbegäran mail.docx", "A 38904-2023")</f>
         <v/>
       </c>
       <c r="AE41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 48285-2023 prioriterade fågelarter.docx", "A 48285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 38904-2023 prioriterade fågelarter.docx", "A 38904-2023")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 47787-2025</t>
+          <t>A 48285-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5253,10 +5249,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45931</v>
+        <v>45205</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5268,8 +5264,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>4.1</v>
+        <v>1.1</v>
       </c>
       <c r="J42" t="n">
         <v>1</v>
@@ -5278,7 +5279,7 @@
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -5293,7 +5294,7 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -5302,46 +5303,46 @@
         <v>1</v>
       </c>
       <c r="T42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 47787-2025 artfynd.xlsx", "A 47787-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 48285-2023 artfynd.xlsx", "A 48285-2023")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 47787-2025 karta.png", "A 47787-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 48285-2023 karta.png", "A 48285-2023")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 47787-2025 georefererad karta.tif", "A 47787-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 48285-2023 georefererad karta.tif", "A 48285-2023")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 47787-2025 FSC-klagomål.docx", "A 47787-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 48285-2023 FSC-klagomål.docx", "A 48285-2023")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 47787-2025 FSC-klagomål mail.docx", "A 47787-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 48285-2023 FSC-klagomål mail.docx", "A 48285-2023")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 47787-2025 tillsynsbegäran.docx", "A 47787-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 48285-2023 tillsynsbegäran.docx", "A 48285-2023")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 47787-2025 tillsynsbegäran mail.docx", "A 47787-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 48285-2023 tillsynsbegäran mail.docx", "A 48285-2023")</f>
         <v/>
       </c>
       <c r="AE42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 47787-2025 prioriterade fågelarter.docx", "A 47787-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 48285-2023 prioriterade fågelarter.docx", "A 48285-2023")</f>
         <v/>
       </c>
     </row>
@@ -5365,7 +5366,7 @@
         <v>45163</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5462,7 +5463,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 14121-2022</t>
+          <t>A 27093-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5476,10 +5477,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44651</v>
+        <v>45096</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5491,8 +5492,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>4.4</v>
+        <v>5.9</v>
       </c>
       <c r="J44" t="n">
         <v>1</v>
@@ -5532,42 +5538,46 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Hårklomossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 14121-2022 artfynd.xlsx", "A 14121-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 27093-2023 artfynd.xlsx", "A 27093-2023")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 14121-2022 karta.png", "A 14121-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 27093-2023 karta.png", "A 27093-2023")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 14121-2022 georefererad karta.tif", "A 14121-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 27093-2023 georefererad karta.tif", "A 27093-2023")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 14121-2022 FSC-klagomål.docx", "A 14121-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 27093-2023 FSC-klagomål.docx", "A 27093-2023")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 14121-2022 FSC-klagomål mail.docx", "A 14121-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 27093-2023 FSC-klagomål mail.docx", "A 27093-2023")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 14121-2022 tillsynsbegäran.docx", "A 14121-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 27093-2023 tillsynsbegäran.docx", "A 27093-2023")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 14121-2022 tillsynsbegäran mail.docx", "A 14121-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 27093-2023 tillsynsbegäran mail.docx", "A 27093-2023")</f>
+        <v/>
+      </c>
+      <c r="AE44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 27093-2023 prioriterade fågelarter.docx", "A 27093-2023")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 47941-2024</t>
+          <t>A 14121-2022</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5581,10 +5591,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45589</v>
+        <v>44651</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5596,16 +5606,11 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>1.4</v>
+        <v>4.4</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -5614,7 +5619,7 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
         <v>0</v>
@@ -5626,10 +5631,10 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>1</v>
@@ -5638,46 +5643,46 @@
         <v>1</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Brunfläckig pärlemorfjäril</t>
+          <t>Hårklomossa</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 47941-2024 artfynd.xlsx", "A 47941-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 14121-2022 artfynd.xlsx", "A 14121-2022")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 47941-2024 karta.png", "A 47941-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 14121-2022 karta.png", "A 14121-2022")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 47941-2024 georefererad karta.tif", "A 47941-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 14121-2022 georefererad karta.tif", "A 14121-2022")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 47941-2024 FSC-klagomål.docx", "A 47941-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 14121-2022 FSC-klagomål.docx", "A 14121-2022")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 47941-2024 FSC-klagomål mail.docx", "A 47941-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 14121-2022 FSC-klagomål mail.docx", "A 14121-2022")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 47941-2024 tillsynsbegäran.docx", "A 47941-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 14121-2022 tillsynsbegäran.docx", "A 14121-2022")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 47941-2024 tillsynsbegäran mail.docx", "A 47941-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 14121-2022 tillsynsbegäran mail.docx", "A 14121-2022")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 14177-2026</t>
+          <t>A 47941-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5691,10 +5696,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46099</v>
+        <v>45589</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5712,7 +5717,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -5721,10 +5726,10 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
         <v>1</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0</v>
       </c>
       <c r="N46" t="n">
         <v>0</v>
@@ -5739,7 +5744,7 @@
         <v>1</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S46" t="n">
         <v>1</v>
@@ -5752,35 +5757,35 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Brunfläckig pärlemorfjäril</t>
         </is>
       </c>
       <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 14177-2026 artfynd.xlsx", "A 14177-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 47941-2024 artfynd.xlsx", "A 47941-2024")</f>
         <v/>
       </c>
       <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 14177-2026 karta.png", "A 14177-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 47941-2024 karta.png", "A 47941-2024")</f>
         <v/>
       </c>
       <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 14177-2026 georefererad karta.tif", "A 14177-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 47941-2024 georefererad karta.tif", "A 47941-2024")</f>
         <v/>
       </c>
       <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 14177-2026 FSC-klagomål.docx", "A 14177-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 47941-2024 FSC-klagomål.docx", "A 47941-2024")</f>
         <v/>
       </c>
       <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 14177-2026 FSC-klagomål mail.docx", "A 14177-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 47941-2024 FSC-klagomål mail.docx", "A 47941-2024")</f>
         <v/>
       </c>
       <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 14177-2026 tillsynsbegäran.docx", "A 14177-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 47941-2024 tillsynsbegäran.docx", "A 47941-2024")</f>
         <v/>
       </c>
       <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 14177-2026 tillsynsbegäran mail.docx", "A 14177-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 47941-2024 tillsynsbegäran mail.docx", "A 47941-2024")</f>
         <v/>
       </c>
     </row>
@@ -5804,7 +5809,7 @@
         <v>46186</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5914,7 +5919,7 @@
         <v>46186</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6011,7 +6016,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 47915-2024</t>
+          <t>A 26971-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6025,10 +6030,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45589</v>
+        <v>46185</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6040,19 +6045,14 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I49" t="n">
-        <v>5.8</v>
+        <v>2.1</v>
       </c>
       <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
         <v>1</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -6086,42 +6086,42 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="W49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 47915-2024 artfynd.xlsx", "A 47915-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 26971-2026 artfynd.xlsx", "A 26971-2026")</f>
         <v/>
       </c>
       <c r="X49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 47915-2024 karta.png", "A 47915-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 26971-2026 karta.png", "A 26971-2026")</f>
         <v/>
       </c>
       <c r="Y49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 47915-2024 georefererad karta.tif", "A 47915-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 26971-2026 georefererad karta.tif", "A 26971-2026")</f>
         <v/>
       </c>
       <c r="AA49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 47915-2024 FSC-klagomål.docx", "A 47915-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 26971-2026 FSC-klagomål.docx", "A 26971-2026")</f>
         <v/>
       </c>
       <c r="AB49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 47915-2024 FSC-klagomål mail.docx", "A 47915-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 26971-2026 FSC-klagomål mail.docx", "A 26971-2026")</f>
         <v/>
       </c>
       <c r="AC49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 47915-2024 tillsynsbegäran.docx", "A 47915-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 26971-2026 tillsynsbegäran.docx", "A 26971-2026")</f>
         <v/>
       </c>
       <c r="AD49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 47915-2024 tillsynsbegäran mail.docx", "A 47915-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 26971-2026 tillsynsbegäran mail.docx", "A 26971-2026")</f>
         <v/>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 26971-2026</t>
+          <t>A 33297-2023</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6135,10 +6135,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46185</v>
+        <v>45116</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6151,20 +6151,20 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>2.1</v>
+        <v>7.2</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
         <v>1</v>
       </c>
-      <c r="L50" t="n">
-        <v>0</v>
-      </c>
-      <c r="M50" t="n">
-        <v>0</v>
-      </c>
       <c r="N50" t="n">
         <v>0</v>
       </c>
@@ -6175,10 +6175,10 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S50" t="n">
         <v>1</v>
@@ -6187,46 +6187,46 @@
         <v>1</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 26971-2026 artfynd.xlsx", "A 26971-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 33297-2023 artfynd.xlsx", "A 33297-2023")</f>
         <v/>
       </c>
       <c r="X50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 26971-2026 karta.png", "A 26971-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 33297-2023 karta.png", "A 33297-2023")</f>
         <v/>
       </c>
       <c r="Y50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 26971-2026 georefererad karta.tif", "A 26971-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 33297-2023 georefererad karta.tif", "A 33297-2023")</f>
         <v/>
       </c>
       <c r="AA50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 26971-2026 FSC-klagomål.docx", "A 26971-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 33297-2023 FSC-klagomål.docx", "A 33297-2023")</f>
         <v/>
       </c>
       <c r="AB50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 26971-2026 FSC-klagomål mail.docx", "A 26971-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 33297-2023 FSC-klagomål mail.docx", "A 33297-2023")</f>
         <v/>
       </c>
       <c r="AC50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 26971-2026 tillsynsbegäran.docx", "A 26971-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 33297-2023 tillsynsbegäran.docx", "A 33297-2023")</f>
         <v/>
       </c>
       <c r="AD50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 26971-2026 tillsynsbegäran mail.docx", "A 26971-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 33297-2023 tillsynsbegäran mail.docx", "A 33297-2023")</f>
         <v/>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 53838-2024</t>
+          <t>A 2357-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6240,10 +6240,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45614</v>
+        <v>44578</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6256,7 +6256,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="J51" t="n">
         <v>1</v>
@@ -6300,42 +6300,42 @@
         </is>
       </c>
       <c r="W51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 53838-2024 artfynd.xlsx", "A 53838-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 2357-2022 artfynd.xlsx", "A 2357-2022")</f>
         <v/>
       </c>
       <c r="X51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 53838-2024 karta.png", "A 53838-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 2357-2022 karta.png", "A 2357-2022")</f>
         <v/>
       </c>
       <c r="Y51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 53838-2024 georefererad karta.tif", "A 53838-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 2357-2022 georefererad karta.tif", "A 2357-2022")</f>
         <v/>
       </c>
       <c r="AA51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 53838-2024 FSC-klagomål.docx", "A 53838-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 2357-2022 FSC-klagomål.docx", "A 2357-2022")</f>
         <v/>
       </c>
       <c r="AB51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 53838-2024 FSC-klagomål mail.docx", "A 53838-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 2357-2022 FSC-klagomål mail.docx", "A 2357-2022")</f>
         <v/>
       </c>
       <c r="AC51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 53838-2024 tillsynsbegäran.docx", "A 53838-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 2357-2022 tillsynsbegäran.docx", "A 2357-2022")</f>
         <v/>
       </c>
       <c r="AD51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 53838-2024 tillsynsbegäran mail.docx", "A 53838-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 2357-2022 tillsynsbegäran mail.docx", "A 2357-2022")</f>
         <v/>
       </c>
       <c r="AE51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 53838-2024 prioriterade fågelarter.docx", "A 53838-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 2357-2022 prioriterade fågelarter.docx", "A 2357-2022")</f>
         <v/>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 2357-2022</t>
+          <t>A 53838-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6349,10 +6349,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44578</v>
+        <v>45614</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6365,7 +6365,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="J52" t="n">
         <v>1</v>
@@ -6409,35 +6409,35 @@
         </is>
       </c>
       <c r="W52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 2357-2022 artfynd.xlsx", "A 2357-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 53838-2024 artfynd.xlsx", "A 53838-2024")</f>
         <v/>
       </c>
       <c r="X52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 2357-2022 karta.png", "A 2357-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 53838-2024 karta.png", "A 53838-2024")</f>
         <v/>
       </c>
       <c r="Y52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 2357-2022 georefererad karta.tif", "A 2357-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 53838-2024 georefererad karta.tif", "A 53838-2024")</f>
         <v/>
       </c>
       <c r="AA52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 2357-2022 FSC-klagomål.docx", "A 2357-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 53838-2024 FSC-klagomål.docx", "A 53838-2024")</f>
         <v/>
       </c>
       <c r="AB52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 2357-2022 FSC-klagomål mail.docx", "A 2357-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 53838-2024 FSC-klagomål mail.docx", "A 53838-2024")</f>
         <v/>
       </c>
       <c r="AC52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 2357-2022 tillsynsbegäran.docx", "A 2357-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 53838-2024 tillsynsbegäran.docx", "A 53838-2024")</f>
         <v/>
       </c>
       <c r="AD52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 2357-2022 tillsynsbegäran mail.docx", "A 2357-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 53838-2024 tillsynsbegäran mail.docx", "A 53838-2024")</f>
         <v/>
       </c>
       <c r="AE52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 2357-2022 prioriterade fågelarter.docx", "A 2357-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 53838-2024 prioriterade fågelarter.docx", "A 53838-2024")</f>
         <v/>
       </c>
     </row>
@@ -6461,7 +6461,7 @@
         <v>44805</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
         <v>44805</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6607,7 +6607,7 @@
         <v>44861</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6680,7 +6680,7 @@
         <v>44607</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         <v>44692</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
         <v>44470</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         <v>44609</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6982,7 +6982,7 @@
         <v>44497</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7055,7 +7055,7 @@
         <v>44594</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7128,7 +7128,7 @@
         <v>44853</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7201,7 +7201,7 @@
         <v>44515</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7274,7 +7274,7 @@
         <v>44466</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7352,7 +7352,7 @@
         <v>44643</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7425,7 +7425,7 @@
         <v>44470</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7503,7 +7503,7 @@
         <v>44529</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7581,7 +7581,7 @@
         <v>44525</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7654,7 +7654,7 @@
         <v>44509</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7732,7 +7732,7 @@
         <v>44505</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7793,7 +7793,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 18675-2025</t>
+          <t>A 6394-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7803,14 +7803,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45763</v>
+        <v>45338</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7822,8 +7822,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I71" t="n">
-        <v>6</v>
+        <v>0.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7866,7 +7871,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 7975-2025</t>
+          <t>A 45861-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7876,14 +7881,14 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45707</v>
+        <v>45195</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7901,7 +7906,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>5.3</v>
+        <v>0.7</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7944,7 +7949,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 29607-2022</t>
+          <t>A 18675-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7958,10 +7963,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>44754</v>
+        <v>45763</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7973,13 +7978,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>2.1</v>
+        <v>6</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -8022,7 +8022,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 37672-2024</t>
+          <t>A 38743-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -8032,14 +8032,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45541</v>
+        <v>44816</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8057,7 +8057,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -8100,7 +8100,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 56478-2024</t>
+          <t>A 13405-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -8114,10 +8114,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45624</v>
+        <v>45387</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8130,7 +8130,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -8173,7 +8173,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 8062-2024</t>
+          <t>A 26176-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -8187,10 +8187,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45351</v>
+        <v>45468</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8208,7 +8208,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -8251,7 +8251,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 10321-2023</t>
+          <t>A 23460-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8265,10 +8265,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44986</v>
+        <v>45453</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8281,7 +8281,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -8324,7 +8324,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 36437-2024</t>
+          <t>A 3177-2022</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8338,10 +8338,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45535</v>
+        <v>44582</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8354,7 +8354,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -8397,7 +8397,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 38921-2023</t>
+          <t>A 770-2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -8411,10 +8411,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45163</v>
+        <v>46027</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8424,11 +8424,6 @@
       <c r="G79" t="inlineStr">
         <is>
           <t>DEGERFORS</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I79" t="n">
@@ -8475,7 +8470,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 2565-2022</t>
+          <t>A 50378-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8489,10 +8484,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>44579</v>
+        <v>45601</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8504,8 +8499,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>1.4</v>
+        <v>4.9</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8548,7 +8548,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 60907-2023</t>
+          <t>A 5218-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8558,14 +8558,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45261</v>
+        <v>45330</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8583,7 +8583,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0.6</v>
+        <v>3.3</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8626,7 +8626,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 26176-2024</t>
+          <t>A 38874-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8640,10 +8640,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45468</v>
+        <v>45887</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8661,7 +8661,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8704,7 +8704,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 3177-2022</t>
+          <t>A 38875-2025</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8718,10 +8718,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44582</v>
+        <v>45887</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8733,8 +8733,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>3.7</v>
+        <v>1.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8777,7 +8782,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 50766-2024</t>
+          <t>A 10321-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8791,10 +8796,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45602</v>
+        <v>44986</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8806,13 +8811,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8855,7 +8855,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 8184-2022</t>
+          <t>A 24707-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8869,10 +8869,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44609</v>
+        <v>45798</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8885,7 +8885,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.7</v>
+        <v>0.5</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8928,7 +8928,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 52523-2024</t>
+          <t>A 57234-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8942,10 +8942,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45609</v>
+        <v>45629</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8963,7 +8963,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>4.4</v>
+        <v>0.9</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -9006,7 +9006,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 38874-2025</t>
+          <t>A 6387-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -9016,14 +9016,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45887</v>
+        <v>45338</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9041,7 +9041,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>8.300000000000001</v>
+        <v>1.8</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -9084,7 +9084,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 37333-2025</t>
+          <t>A 41766-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -9094,14 +9094,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45876</v>
+        <v>45902</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9113,8 +9113,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>0.7</v>
+        <v>3.2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -9157,7 +9162,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 37265-2025</t>
+          <t>A 41767-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -9171,10 +9176,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45876</v>
+        <v>45902</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9186,8 +9191,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -9230,7 +9240,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 54515-2023</t>
+          <t>A 59158-2022</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -9240,14 +9250,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45233</v>
+        <v>44904</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9259,8 +9269,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>1</v>
+        <v>3.7</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -9303,7 +9318,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 15594-2025</t>
+          <t>A 43691-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -9317,10 +9332,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45747</v>
+        <v>45912</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9332,8 +9347,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I91" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -9376,7 +9396,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 54994-2024</t>
+          <t>A 43689-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -9390,10 +9410,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45621</v>
+        <v>45912</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9411,7 +9431,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -9454,7 +9474,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 13236-2025</t>
+          <t>A 43694-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -9468,10 +9488,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45735</v>
+        <v>45912</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9489,7 +9509,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>18.5</v>
+        <v>6.6</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -9532,7 +9552,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 41767-2025</t>
+          <t>A 5277-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -9546,10 +9566,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45902</v>
+        <v>45330</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9561,13 +9581,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I94" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -9610,7 +9625,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 41766-2025</t>
+          <t>A 43768-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9624,10 +9639,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45902</v>
+        <v>45569</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9639,13 +9654,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I95" t="n">
-        <v>3.2</v>
+        <v>7</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -9688,7 +9698,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 38875-2025</t>
+          <t>A 9273-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9702,10 +9712,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45887</v>
+        <v>46070</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9717,13 +9727,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I96" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9766,7 +9771,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 38233-2023</t>
+          <t>A 26783-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9776,14 +9781,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45160</v>
+        <v>45810</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9796,7 +9801,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9839,7 +9844,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 43694-2025</t>
+          <t>A 26820-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9853,10 +9858,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45912</v>
+        <v>45810</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9868,13 +9873,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I98" t="n">
-        <v>6.6</v>
+        <v>0.7</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9917,7 +9917,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 43691-2025</t>
+          <t>A 12159-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9931,10 +9931,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45912</v>
+        <v>46086</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9952,7 +9952,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.7</v>
+        <v>0.9</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9995,7 +9995,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 43689-2025</t>
+          <t>A 12160-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -10009,10 +10009,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45912</v>
+        <v>46086</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10030,7 +10030,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -10073,7 +10073,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 10674-2024</t>
+          <t>A 48625-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -10083,14 +10083,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45369</v>
+        <v>45936</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10102,13 +10102,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>0.3</v>
+        <v>1.6</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -10151,7 +10146,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 60933-2024</t>
+          <t>A 13039-2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -10165,10 +10160,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45645</v>
+        <v>46093</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10186,7 +10181,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.9</v>
+        <v>5.1</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -10229,7 +10224,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 73693-2021</t>
+          <t>A 13040-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -10243,10 +10238,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44552</v>
+        <v>46093</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10258,8 +10253,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I103" t="n">
-        <v>3.6</v>
+        <v>7.1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -10302,7 +10302,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 60937-2024</t>
+          <t>A 12936-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -10316,10 +10316,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45645</v>
+        <v>46092</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10337,7 +10337,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -10380,7 +10380,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 60940-2024</t>
+          <t>A 47935-2024</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -10394,10 +10394,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45645</v>
+        <v>45589</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10415,7 +10415,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -10458,7 +10458,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 52566-2023</t>
+          <t>A 21952-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -10468,14 +10468,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45219</v>
+        <v>45443</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10487,8 +10487,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I106" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -10531,7 +10536,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 48625-2025</t>
+          <t>A 13293-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -10545,10 +10550,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45936</v>
+        <v>46094</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10560,8 +10565,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I107" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -10604,7 +10614,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 57234-2024</t>
+          <t>A 52566-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10618,10 +10628,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45629</v>
+        <v>45219</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10633,13 +10643,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I108" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -10699,7 +10704,7 @@
         <v>45947</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10760,7 +10765,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 54082-2024</t>
+          <t>A 62972-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10774,10 +10779,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45616</v>
+        <v>45272</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10790,7 +10795,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>6.3</v>
+        <v>0.3</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10850,7 +10855,7 @@
         <v>45952</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10906,7 +10911,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 43752-2025</t>
+          <t>A 50377-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10920,10 +10925,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45912</v>
+        <v>45601</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10935,8 +10940,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I112" t="n">
-        <v>3.1</v>
+        <v>0.7</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10979,7 +10989,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 8074-2024</t>
+          <t>A 18506-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10993,10 +11003,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45351</v>
+        <v>46127</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11008,13 +11018,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I113" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -11057,7 +11062,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 20567-2026</t>
+          <t>A 55341-2025</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -11071,10 +11076,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46140</v>
+        <v>45971</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11092,7 +11097,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>7.8</v>
+        <v>3.4</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -11135,7 +11140,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 20568-2026</t>
+          <t>A 11085-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -11149,10 +11154,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>46140</v>
+        <v>44986</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11164,13 +11169,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I115" t="n">
-        <v>6.3</v>
+        <v>0.8</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -11213,7 +11213,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 20478-2026</t>
+          <t>A 19227-2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -11227,10 +11227,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>46140</v>
+        <v>46132</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11242,13 +11242,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I116" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -11291,7 +11286,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 55341-2025</t>
+          <t>A 18913-2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -11305,10 +11300,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45971</v>
+        <v>46129</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11326,7 +11321,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>3.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -11369,7 +11364,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 21952-2024</t>
+          <t>A 57086-2025</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -11383,10 +11378,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45443</v>
+        <v>45979</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11398,13 +11393,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I118" t="n">
-        <v>0.7</v>
+        <v>6.1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -11447,7 +11437,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 57086-2025</t>
+          <t>A 50764-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -11457,14 +11447,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45979</v>
+        <v>45602</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11476,8 +11466,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I119" t="n">
-        <v>6.1</v>
+        <v>2.4</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -11520,7 +11515,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 62972-2023</t>
+          <t>A 38921-2023</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -11534,10 +11529,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45272</v>
+        <v>45163</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11549,8 +11544,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I120" t="n">
-        <v>0.3</v>
+        <v>2.2</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -11593,7 +11593,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 12143-2025</t>
+          <t>A 60708-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -11603,14 +11603,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45729</v>
+        <v>45996</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11622,13 +11622,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I121" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -11671,7 +11666,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 21440-2026</t>
+          <t>A 43752-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -11685,10 +11680,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46148</v>
+        <v>45912</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11700,13 +11695,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I122" t="n">
-        <v>6.5</v>
+        <v>3.1</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -11749,7 +11739,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 21402-2026</t>
+          <t>A 60736-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11763,10 +11753,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46148</v>
+        <v>45996</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11779,7 +11769,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>1.4</v>
+        <v>5.8</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -11822,7 +11812,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 21660-2026</t>
+          <t>A 48118-2023</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11836,10 +11826,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46149</v>
+        <v>45205</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11857,7 +11847,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -11900,7 +11890,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 21442-2026</t>
+          <t>A 38917-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11914,10 +11904,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46148</v>
+        <v>45163</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11935,7 +11925,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>4.1</v>
+        <v>2.2</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11978,7 +11968,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 21401-2026</t>
+          <t>A 63905-2021</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11992,10 +11982,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46148</v>
+        <v>44509</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12007,8 +11997,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I126" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -12051,7 +12046,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 51653-2023</t>
+          <t>A 54082-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -12065,10 +12060,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45222</v>
+        <v>45616</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12080,13 +12075,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I127" t="n">
-        <v>3.9</v>
+        <v>6.3</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -12129,7 +12119,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 44841-2023</t>
+          <t>A 28367-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -12143,10 +12133,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45190</v>
+        <v>45819</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12164,7 +12154,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.5</v>
+        <v>6.1</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -12207,7 +12197,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 60736-2025</t>
+          <t>A 28368-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -12221,10 +12211,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45996</v>
+        <v>45819</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12236,8 +12226,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I129" t="n">
-        <v>5.8</v>
+        <v>8.1</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -12280,7 +12275,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 20577-2023</t>
+          <t>A 20478-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -12290,14 +12285,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45057</v>
+        <v>46140</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12315,7 +12310,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -12358,7 +12353,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 60708-2025</t>
+          <t>A 20567-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -12372,10 +12367,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45996</v>
+        <v>46140</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12387,8 +12382,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I131" t="n">
-        <v>1.9</v>
+        <v>7.8</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -12431,7 +12431,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 46222-2024</t>
+          <t>A 20568-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -12445,10 +12445,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45581</v>
+        <v>46140</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12466,7 +12466,7 @@
         </is>
       </c>
       <c r="I132" t="n">
-        <v>0.9</v>
+        <v>6.3</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -12509,7 +12509,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 45365-2023</t>
+          <t>A 20577-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -12519,14 +12519,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45192</v>
+        <v>45057</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12538,8 +12538,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I133" t="n">
-        <v>5</v>
+        <v>1.8</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -12582,7 +12587,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 6387-2024</t>
+          <t>A 23066-2022</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -12592,14 +12597,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45338</v>
+        <v>44719</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12611,13 +12616,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I134" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -12660,7 +12660,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 38917-2023</t>
+          <t>A 10797-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -12674,10 +12674,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45163</v>
+        <v>44989</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12689,13 +12689,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I135" t="n">
-        <v>2.2</v>
+        <v>9.5</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -12738,7 +12733,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 46219-2024</t>
+          <t>A 44457-2022</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12752,10 +12747,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45581</v>
+        <v>44839</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12767,13 +12762,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I136" t="n">
-        <v>2.4</v>
+        <v>6.8</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -12816,7 +12806,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 48118-2023</t>
+          <t>A 29482-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12830,10 +12820,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45205</v>
+        <v>45106</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12845,13 +12835,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I137" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -12894,7 +12879,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 6240-2024</t>
+          <t>A 21402-2026</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12908,10 +12893,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45337</v>
+        <v>46148</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12924,7 +12909,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -12967,7 +12952,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 770-2026</t>
+          <t>A 21440-2026</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12981,10 +12966,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46027</v>
+        <v>46148</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12996,8 +12981,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I139" t="n">
-        <v>2.2</v>
+        <v>6.5</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -13040,7 +13030,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 6394-2024</t>
+          <t>A 21442-2026</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -13050,14 +13040,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45338</v>
+        <v>46148</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13075,7 +13065,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0.9</v>
+        <v>4.1</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -13118,7 +13108,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 23230-2026</t>
+          <t>A 21401-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -13132,10 +13122,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46162</v>
+        <v>46148</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13147,13 +13137,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I141" t="n">
-        <v>0.9</v>
+        <v>3.5</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -13196,7 +13181,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 23229-2026</t>
+          <t>A 13236-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -13210,10 +13195,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46162</v>
+        <v>45735</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13231,7 +13216,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>2.9</v>
+        <v>18.5</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -13274,7 +13259,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 11085-2023</t>
+          <t>A 44841-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -13288,10 +13273,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>44986</v>
+        <v>45190</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13303,8 +13288,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I143" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -13347,7 +13337,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 14678-2025</t>
+          <t>A 46222-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -13357,14 +13347,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45742</v>
+        <v>45581</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13382,7 +13372,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.9</v>
+        <v>0.9</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -13425,7 +13415,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 23854-2026</t>
+          <t>A 46219-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -13439,10 +13429,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46167</v>
+        <v>45581</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13460,7 +13450,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>20.9</v>
+        <v>2.4</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -13503,7 +13493,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 5277-2024</t>
+          <t>A 14678-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -13513,14 +13503,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45330</v>
+        <v>45742</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13532,8 +13522,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I146" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -13576,7 +13571,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 50378-2024</t>
+          <t>A 11084-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -13590,10 +13585,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45601</v>
+        <v>44986</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13605,13 +13600,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I147" t="n">
-        <v>4.9</v>
+        <v>2.7</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -13654,7 +13644,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 33293-2023</t>
+          <t>A 56478-2024</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -13668,10 +13658,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45116</v>
+        <v>45624</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13684,7 +13674,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>17.2</v>
+        <v>1.4</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -13727,7 +13717,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 44807-2023</t>
+          <t>A 23230-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -13741,10 +13731,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45190</v>
+        <v>46162</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13762,7 +13752,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>5.4</v>
+        <v>0.9</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -13805,7 +13795,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 51652-2023</t>
+          <t>A 23229-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -13819,10 +13809,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45222</v>
+        <v>46162</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13840,7 +13830,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>1.7</v>
+        <v>2.9</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -13883,7 +13873,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 24460-2026</t>
+          <t>A 33404-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -13897,10 +13887,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46170</v>
+        <v>45841</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13913,7 +13903,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -13956,7 +13946,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 24462-2026</t>
+          <t>A 60933-2024</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13970,10 +13960,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46170</v>
+        <v>45645</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13985,8 +13975,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I152" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -14029,7 +14024,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 44457-2022</t>
+          <t>A 59863-2024</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -14043,10 +14038,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>44839</v>
+        <v>45639</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14059,7 +14054,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>6.8</v>
+        <v>1.6</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -14102,7 +14097,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 32211-2022</t>
+          <t>A 23854-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -14116,10 +14111,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>44781</v>
+        <v>46167</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14131,8 +14126,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I154" t="n">
-        <v>2.3</v>
+        <v>20.9</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -14175,7 +14175,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 13405-2024</t>
+          <t>A 61750-2021</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -14189,10 +14189,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45387</v>
+        <v>44501</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14204,8 +14204,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I155" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -14248,7 +14253,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 12729-2024</t>
+          <t>A 24462-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -14262,10 +14267,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45384</v>
+        <v>46170</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14277,13 +14282,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I156" t="n">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -14326,7 +14326,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 9273-2026</t>
+          <t>A 29607-2022</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -14340,10 +14340,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46070</v>
+        <v>44754</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14355,8 +14355,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I157" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -14399,7 +14404,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 12159-2026</t>
+          <t>A 24689-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -14413,10 +14418,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46086</v>
+        <v>46171</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14434,7 +14439,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0.9</v>
+        <v>15.5</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -14477,7 +14482,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 12160-2026</t>
+          <t>A 6240-2024</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -14491,10 +14496,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46086</v>
+        <v>45337</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14506,13 +14511,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I159" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -14555,7 +14555,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 24689-2026</t>
+          <t>A 24460-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -14569,10 +14569,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46171</v>
+        <v>46170</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14584,13 +14584,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I160" t="n">
-        <v>15.5</v>
+        <v>1.1</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -14633,7 +14628,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 12936-2026</t>
+          <t>A 33658-2024</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -14647,10 +14642,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46092</v>
+        <v>45520</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14662,13 +14657,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I161" t="n">
-        <v>8.800000000000001</v>
+        <v>2.2</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -14711,7 +14701,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 13293-2026</t>
+          <t>A 38233-2023</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -14721,14 +14711,14 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46094</v>
+        <v>45160</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14740,13 +14730,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I162" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -14789,7 +14774,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 13040-2026</t>
+          <t>A 26857-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -14803,10 +14788,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46093</v>
+        <v>46185</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14824,7 +14809,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>7.1</v>
+        <v>15.1</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -14867,7 +14852,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 13039-2026</t>
+          <t>A 50766-2024</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -14881,10 +14866,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46093</v>
+        <v>45602</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14902,7 +14887,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>5.1</v>
+        <v>2.1</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -14945,7 +14930,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 26857-2026</t>
+          <t>A 26947-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -14962,7 +14947,7 @@
         <v>46185</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14980,7 +14965,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>15.1</v>
+        <v>2</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -15040,7 +15025,7 @@
         <v>46185</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15101,7 +15086,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 26947-2026</t>
+          <t>A 27411-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -15115,10 +15100,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46185</v>
+        <v>46189</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15136,7 +15121,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -15179,7 +15164,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 27411-2026</t>
+          <t>A 50207-2024</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -15193,10 +15178,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46189</v>
+        <v>45600</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15208,13 +15193,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I168" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -15257,7 +15237,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 18913-2026</t>
+          <t>A 50208-2024</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -15271,10 +15251,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46129</v>
+        <v>45600</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15286,13 +15266,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I169" t="n">
-        <v>8.300000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -15335,7 +15310,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 28789-2026</t>
+          <t>A 27745-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -15349,10 +15324,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46195</v>
+        <v>46191</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15364,8 +15339,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I170" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -15408,7 +15388,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 27745-2026</t>
+          <t>A 27746-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -15425,7 +15405,7 @@
         <v>46191</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15443,7 +15423,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -15486,7 +15466,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 27746-2026</t>
+          <t>A 37333-2025</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -15496,14 +15476,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46191</v>
+        <v>45876</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15515,13 +15495,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I172" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -15564,7 +15539,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 18506-2026</t>
+          <t>A 28789-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -15578,10 +15553,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46127</v>
+        <v>46195</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15594,7 +15569,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -15637,7 +15612,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 19227-2026</t>
+          <t>A 37265-2025</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -15651,10 +15626,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46132</v>
+        <v>45876</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15667,7 +15642,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -15727,7 +15702,7 @@
         <v>46198</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15805,7 +15780,7 @@
         <v>46198</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15866,7 +15841,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 28695-2026</t>
+          <t>A 28930-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -15880,10 +15855,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15893,11 +15868,6 @@
       <c r="G177" t="inlineStr">
         <is>
           <t>DEGERFORS</t>
-        </is>
-      </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I177" t="n">
@@ -15944,7 +15914,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 63905-2021</t>
+          <t>A 28695-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -15958,10 +15928,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>44509</v>
+        <v>46198</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15979,7 +15949,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>3.7</v>
+        <v>2.7</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -16039,7 +16009,7 @@
         <v>46202</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16100,7 +16070,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 28930-2026</t>
+          <t>A 15594-2025</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -16114,10 +16084,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46199</v>
+        <v>45747</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16130,7 +16100,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>2.7</v>
+        <v>1.5</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -16173,7 +16143,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 38743-2022</t>
+          <t>A 29132-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -16187,10 +16157,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>44816</v>
+        <v>46202</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16208,7 +16178,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1.6</v>
+        <v>11.9</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -16251,7 +16221,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 29132-2026</t>
+          <t>A 29552-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -16265,10 +16235,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46202</v>
+        <v>46204</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16286,7 +16256,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>11.9</v>
+        <v>2.3</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -16329,7 +16299,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 47935-2024</t>
+          <t>A 12143-2025</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -16339,14 +16309,14 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>45589</v>
+        <v>45729</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16364,7 +16334,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -16407,7 +16377,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 29552-2026</t>
+          <t>A 52523-2024</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -16421,10 +16391,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46204</v>
+        <v>45609</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16442,7 +16412,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>2.3</v>
+        <v>4.4</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -16485,7 +16455,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 50377-2024</t>
+          <t>A 8184-2022</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -16499,10 +16469,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45601</v>
+        <v>44609</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16514,13 +16484,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I185" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -16563,7 +16528,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 8059-2024</t>
+          <t>A 60937-2024</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -16577,10 +16542,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45351</v>
+        <v>45645</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16598,7 +16563,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -16641,7 +16606,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 29482-2023</t>
+          <t>A 60940-2024</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -16655,10 +16620,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>45106</v>
+        <v>45645</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16670,8 +16635,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I187" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -16714,7 +16684,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 59158-2022</t>
+          <t>A 44807-2023</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -16724,14 +16694,14 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>44904</v>
+        <v>45190</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16749,7 +16719,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>3.7</v>
+        <v>5.4</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -16792,7 +16762,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 18773-2025</t>
+          <t>A 51652-2023</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -16806,10 +16776,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45763</v>
+        <v>45222</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16821,8 +16791,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I189" t="n">
-        <v>13</v>
+        <v>1.7</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -16865,7 +16840,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 10320-2023</t>
+          <t>A 35213-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -16879,10 +16854,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>44986</v>
+        <v>46260</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16894,8 +16869,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I190" t="n">
-        <v>2.6</v>
+        <v>9.5</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -16938,7 +16918,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 10797-2023</t>
+          <t>A 33293-2023</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -16952,10 +16932,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>44989</v>
+        <v>45116</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16968,7 +16948,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>9.5</v>
+        <v>17.2</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -17011,7 +16991,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 11084-2023</t>
+          <t>A 32154-2023</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -17025,10 +17005,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>44986</v>
+        <v>45119</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17041,7 +17021,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -17084,7 +17064,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 50764-2024</t>
+          <t>A 36339-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -17098,10 +17078,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>45602</v>
+        <v>46268</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17113,13 +17093,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I193" t="n">
-        <v>2.4</v>
+        <v>0.4</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -17162,7 +17137,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 33658-2024</t>
+          <t>A 36336-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -17176,10 +17151,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45520</v>
+        <v>46268</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17192,7 +17167,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -17235,7 +17210,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 45861-2023</t>
+          <t>A 36345-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -17245,14 +17220,14 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45195</v>
+        <v>46268</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17264,13 +17239,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I195" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -17313,7 +17283,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 43768-2024</t>
+          <t>A 8062-2024</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -17327,10 +17297,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45569</v>
+        <v>45351</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17342,8 +17312,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I196" t="n">
-        <v>7</v>
+        <v>0.8</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -17386,7 +17361,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 35213-2026</t>
+          <t>A 8074-2024</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -17400,10 +17375,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46260</v>
+        <v>45351</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17421,7 +17396,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>9.5</v>
+        <v>0.7</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -17464,7 +17439,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 38738-2022</t>
+          <t>A 60907-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -17474,14 +17449,14 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>44816</v>
+        <v>45261</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17499,7 +17474,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -17542,7 +17517,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 36339-2026</t>
+          <t>A 31813-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -17556,10 +17531,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46268</v>
+        <v>46230</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17572,7 +17547,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>0.4</v>
+        <v>1.8</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -17615,7 +17590,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 36345-2026</t>
+          <t>A 31870-2026</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -17629,10 +17604,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>46268</v>
+        <v>46231</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17644,8 +17619,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I200" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -17688,7 +17668,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 36336-2026</t>
+          <t>A 31871-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -17702,10 +17682,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46268</v>
+        <v>46231</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17717,8 +17697,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I201" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -17761,7 +17746,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 31813-2026</t>
+          <t>A 31872-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -17775,10 +17760,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17790,8 +17775,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I202" t="n">
-        <v>1.8</v>
+        <v>5.2</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -17834,7 +17824,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 61750-2021</t>
+          <t>A 32211-2022</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -17848,10 +17838,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>44501</v>
+        <v>44781</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17863,13 +17853,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H203" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I203" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -17912,7 +17897,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 7472-2025</t>
+          <t>A 37809-2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -17926,10 +17911,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45705</v>
+        <v>46279</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17941,13 +17926,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H204" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I204" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -17990,7 +17970,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 31870-2026</t>
+          <t>A 38126-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -18004,10 +17984,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46231</v>
+        <v>46281</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18025,7 +18005,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>1.5</v>
+        <v>5.5</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -18068,7 +18048,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 31871-2026</t>
+          <t>A 38463-2026</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -18082,10 +18062,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>46231</v>
+        <v>46282</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18097,13 +18077,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H206" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I206" t="n">
-        <v>1.9</v>
+        <v>3.4</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -18146,7 +18121,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 31872-2026</t>
+          <t>A 32508-2026</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -18160,10 +18135,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>46231</v>
+        <v>46239</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18181,7 +18156,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>5.2</v>
+        <v>1.1</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -18224,7 +18199,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 50207-2024</t>
+          <t>A 32506-2026</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -18238,10 +18213,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45600</v>
+        <v>46239</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18253,8 +18228,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I208" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -18297,7 +18277,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 50208-2024</t>
+          <t>A 38659-2026</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -18311,10 +18291,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45600</v>
+        <v>46283</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18326,8 +18306,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I209" t="n">
-        <v>0.4</v>
+        <v>4.6</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -18370,7 +18355,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 37809-2026</t>
+          <t>A 32810-2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -18384,10 +18369,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>46279</v>
+        <v>46241</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18400,7 +18385,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>2.9</v>
+        <v>6.1</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -18443,7 +18428,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 38126-2026</t>
+          <t>A 73693-2021</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -18457,10 +18442,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>46281</v>
+        <v>44552</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18472,13 +18457,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I211" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -18521,7 +18501,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 12108-2024</t>
+          <t>A 38651-2026</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -18535,10 +18515,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45376</v>
+        <v>46283</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18550,8 +18530,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I212" t="n">
-        <v>7.7</v>
+        <v>11.3</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -18594,7 +18579,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 18831-2025</t>
+          <t>A 36437-2024</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -18608,10 +18593,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45764</v>
+        <v>45535</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18623,13 +18608,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H213" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I213" t="n">
-        <v>4.2</v>
+        <v>2.3</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -18672,7 +18652,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 32506-2026</t>
+          <t>A 45365-2023</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -18686,10 +18666,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>46239</v>
+        <v>45192</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18701,13 +18681,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I214" t="n">
-        <v>1.1</v>
+        <v>5</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -18750,7 +18725,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 32154-2023</t>
+          <t>A 37672-2024</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -18760,14 +18735,14 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45119</v>
+        <v>45541</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18779,8 +18754,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I215" t="n">
-        <v>2.3</v>
+        <v>0.6</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -18823,7 +18803,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 38651-2026</t>
+          <t>A 2565-2022</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -18837,10 +18817,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>46283</v>
+        <v>44579</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18852,13 +18832,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I216" t="n">
-        <v>11.3</v>
+        <v>1.4</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -18901,7 +18876,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 38463-2026</t>
+          <t>A 10674-2024</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -18911,14 +18886,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>46282</v>
+        <v>45369</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18930,8 +18905,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I217" t="n">
-        <v>3.4</v>
+        <v>0.3</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -18974,7 +18954,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 32508-2026</t>
+          <t>A 18773-2025</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -18988,10 +18968,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>46239</v>
+        <v>45763</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19003,13 +18983,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H218" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I218" t="n">
-        <v>1.1</v>
+        <v>13</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -19052,7 +19027,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 38659-2026</t>
+          <t>A 51653-2023</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -19066,10 +19041,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>46283</v>
+        <v>45222</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19087,7 +19062,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -19130,7 +19105,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 27438-2024</t>
+          <t>A 12108-2024</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -19144,10 +19119,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45474</v>
+        <v>45376</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19160,7 +19135,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>2.6</v>
+        <v>7.7</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -19203,7 +19178,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 46288-2024</t>
+          <t>A 54994-2024</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -19217,10 +19192,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45581</v>
+        <v>45621</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19238,7 +19213,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>3.7</v>
+        <v>0.5</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -19281,7 +19256,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 51996-2023</t>
+          <t>A 8059-2024</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -19295,10 +19270,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45223</v>
+        <v>45351</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19316,7 +19291,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -19359,7 +19334,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 58629-2024</t>
+          <t>A 54515-2023</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -19373,10 +19348,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45635</v>
+        <v>45233</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19388,13 +19363,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H223" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I223" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -19437,7 +19407,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 50102-2023</t>
+          <t>A 38738-2022</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -19451,10 +19421,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45215</v>
+        <v>44816</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19472,7 +19442,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>3.9</v>
+        <v>0.9</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -19515,7 +19485,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 32810-2026</t>
+          <t>A 12729-2024</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -19529,10 +19499,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>46241</v>
+        <v>45384</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19544,8 +19514,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I225" t="n">
-        <v>6.1</v>
+        <v>2.5</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -19588,7 +19563,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 62982-2023</t>
+          <t>A 10320-2023</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -19602,10 +19577,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45272</v>
+        <v>44986</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19618,7 +19593,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -19661,7 +19636,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 21935-2024</t>
+          <t>A 7472-2025</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -19675,10 +19650,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45443</v>
+        <v>45705</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19696,7 +19671,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -19739,7 +19714,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 23460-2024</t>
+          <t>A 7975-2025</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -19753,10 +19728,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45453</v>
+        <v>45707</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19768,8 +19743,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I228" t="n">
-        <v>0.7</v>
+        <v>5.3</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -19812,7 +19792,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 24707-2025</t>
+          <t>A 18831-2025</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -19826,10 +19806,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45798</v>
+        <v>45764</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19841,8 +19821,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I229" t="n">
-        <v>0.5</v>
+        <v>4.2</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -19885,7 +19870,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 5218-2024</t>
+          <t>A 58629-2024</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -19899,10 +19884,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45330</v>
+        <v>45635</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19920,7 +19905,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>3.3</v>
+        <v>1.4</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -19963,7 +19948,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 26820-2025</t>
+          <t>A 27438-2024</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -19977,10 +19962,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45810</v>
+        <v>45474</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19993,7 +19978,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -20036,7 +20021,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 26783-2025</t>
+          <t>A 50102-2023</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -20050,10 +20035,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45810</v>
+        <v>45215</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20065,8 +20050,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I232" t="n">
-        <v>2.5</v>
+        <v>3.9</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -20109,7 +20099,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 28367-2025</t>
+          <t>A 51996-2023</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -20123,10 +20113,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45819</v>
+        <v>45223</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20144,7 +20134,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>6.1</v>
+        <v>2</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -20187,7 +20177,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 28368-2025</t>
+          <t>A 62982-2023</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -20201,10 +20191,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45819</v>
+        <v>45272</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20216,13 +20206,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H234" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I234" t="n">
-        <v>8.1</v>
+        <v>3.5</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -20265,7 +20250,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 23066-2022</t>
+          <t>A 46288-2024</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -20279,10 +20264,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>44719</v>
+        <v>45581</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20294,8 +20279,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I235" t="n">
-        <v>2.4</v>
+        <v>3.7</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -20338,7 +20328,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 33404-2025</t>
+          <t>A 21935-2024</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -20352,10 +20342,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45841</v>
+        <v>45443</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20367,8 +20357,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I236" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -20411,24 +20406,24 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 59863-2024</t>
+          <t>S 479-2022</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Skogsbilväg</t>
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>45639</v>
+        <v>44587</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20441,7 +20436,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -20484,7 +20479,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>S 479-2022</t>
+          <t>S 1697-2025</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -20494,14 +20489,14 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Skogsbilväg</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>44587</v>
+        <v>45805</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20513,8 +20508,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I238" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -20557,7 +20557,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>S 1697-2025</t>
+          <t>S 1694-2025</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -20574,7 +20574,7 @@
         <v>45805</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20592,7 +20592,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -20635,7 +20635,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>S 1694-2025</t>
+          <t>S 794-2025</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -20649,10 +20649,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45805</v>
+        <v>45729</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20670,7 +20670,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -20713,7 +20713,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>S 794-2025</t>
+          <t>S 793-2025</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -20730,7 +20730,7 @@
         <v>45729</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20748,7 +20748,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -20791,7 +20791,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>S 793-2025</t>
+          <t>S 963-2025</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -20805,10 +20805,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>45729</v>
+        <v>45742</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20826,7 +20826,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -20869,7 +20869,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>S 963-2025</t>
+          <t>S 964-2025</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -20886,7 +20886,7 @@
         <v>45742</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20904,7 +20904,7 @@
         </is>
       </c>
       <c r="I243" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -20944,10 +20944,10 @@
       </c>
       <c r="V243" s="2" t="inlineStr"/>
     </row>
-    <row r="244" ht="15" customHeight="1">
+    <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>S 964-2025</t>
+          <t>S 2595-2025</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -20961,10 +20961,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>45742</v>
+        <v>45916</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20982,7 +20982,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -21021,84 +21021,6 @@
         <v>0</v>
       </c>
       <c r="V244" s="2" t="inlineStr"/>
-    </row>
-    <row r="245">
-      <c r="A245" t="inlineStr">
-        <is>
-          <t>S 2595-2025</t>
-        </is>
-      </c>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C245" t="inlineStr">
-        <is>
-          <t>Annan skogsbruksåtgärd</t>
-        </is>
-      </c>
-      <c r="D245" s="1" t="n">
-        <v>45916</v>
-      </c>
-      <c r="E245" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F245" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G245" t="inlineStr">
-        <is>
-          <t>DEGERFORS</t>
-        </is>
-      </c>
-      <c r="H245" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I245" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J245" t="n">
-        <v>0</v>
-      </c>
-      <c r="K245" t="n">
-        <v>0</v>
-      </c>
-      <c r="L245" t="n">
-        <v>0</v>
-      </c>
-      <c r="M245" t="n">
-        <v>0</v>
-      </c>
-      <c r="N245" t="n">
-        <v>0</v>
-      </c>
-      <c r="O245" t="n">
-        <v>0</v>
-      </c>
-      <c r="P245" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q245" t="n">
-        <v>0</v>
-      </c>
-      <c r="R245" t="n">
-        <v>0</v>
-      </c>
-      <c r="S245" t="n">
-        <v>0</v>
-      </c>
-      <c r="T245" t="n">
-        <v>0</v>
-      </c>
-      <c r="U245" t="n">
-        <v>0</v>
-      </c>
-      <c r="V245" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt DEGERFORS.xlsx
+++ b/Översikt DEGERFORS.xlsx
@@ -601,7 +601,7 @@
         <v>46160</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>46051</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
         <v>46107</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>46160</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>46190</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>46190</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>46161</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>45089</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>45175</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>46160</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>45384</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
         <v>45384</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>45163</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>44550</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>46204</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>45175</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         <v>45932</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>45163</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>45205</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2897,7 +2897,7 @@
         <v>45866</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
         <v>45351</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>45559</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>45931</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>45384</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>46190</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>46045</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>45931</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3799,7 +3799,7 @@
         <v>45163</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3914,7 +3914,7 @@
         <v>45558</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
         <v>45163</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         <v>46199</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>45163</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>44470</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>44487</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>44470</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4704,7 +4704,7 @@
         <v>45938</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>46099</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4919,7 +4919,7 @@
         <v>45589</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
         <v>45931</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
         <v>45163</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         <v>45205</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
         <v>45163</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5480,7 +5480,7 @@
         <v>45096</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5594,7 +5594,7 @@
         <v>44651</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5699,7 +5699,7 @@
         <v>45589</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5809,7 +5809,7 @@
         <v>46186</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5919,7 +5919,7 @@
         <v>46186</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6033,7 +6033,7 @@
         <v>46185</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6138,7 +6138,7 @@
         <v>45116</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6243,7 +6243,7 @@
         <v>44578</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6352,7 +6352,7 @@
         <v>45614</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6461,7 +6461,7 @@
         <v>44805</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
         <v>44805</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6607,7 +6607,7 @@
         <v>44861</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6680,7 +6680,7 @@
         <v>44607</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         <v>44692</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
         <v>44470</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         <v>44609</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6982,7 +6982,7 @@
         <v>44497</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7055,7 +7055,7 @@
         <v>44594</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7128,7 +7128,7 @@
         <v>44853</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7201,7 +7201,7 @@
         <v>44515</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7274,7 +7274,7 @@
         <v>44466</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7352,7 +7352,7 @@
         <v>44643</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7425,7 +7425,7 @@
         <v>44470</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7503,7 +7503,7 @@
         <v>44529</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7581,7 +7581,7 @@
         <v>44525</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7654,7 +7654,7 @@
         <v>44509</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7732,7 +7732,7 @@
         <v>44505</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7810,7 +7810,7 @@
         <v>45338</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7888,7 +7888,7 @@
         <v>45195</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7966,7 +7966,7 @@
         <v>45763</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8039,7 +8039,7 @@
         <v>44816</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8117,7 +8117,7 @@
         <v>45387</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8190,7 +8190,7 @@
         <v>45468</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8268,7 +8268,7 @@
         <v>45453</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8341,7 +8341,7 @@
         <v>44582</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8414,7 +8414,7 @@
         <v>46027</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
         <v>45601</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8565,7 +8565,7 @@
         <v>45330</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8643,7 +8643,7 @@
         <v>45887</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8721,7 +8721,7 @@
         <v>45887</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8799,7 +8799,7 @@
         <v>44986</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8872,7 +8872,7 @@
         <v>45798</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         <v>45629</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9023,7 +9023,7 @@
         <v>45338</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9101,7 +9101,7 @@
         <v>45902</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9179,7 +9179,7 @@
         <v>45902</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9257,7 +9257,7 @@
         <v>44904</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9335,7 +9335,7 @@
         <v>45912</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9413,7 +9413,7 @@
         <v>45912</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
         <v>45912</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9569,7 +9569,7 @@
         <v>45330</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9642,7 +9642,7 @@
         <v>45569</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9715,7 +9715,7 @@
         <v>46070</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9788,7 +9788,7 @@
         <v>45810</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9861,7 +9861,7 @@
         <v>45810</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9934,7 +9934,7 @@
         <v>46086</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10012,7 +10012,7 @@
         <v>46086</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10090,7 +10090,7 @@
         <v>45936</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10163,7 +10163,7 @@
         <v>46093</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10241,7 +10241,7 @@
         <v>46093</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10319,7 +10319,7 @@
         <v>46092</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10397,7 +10397,7 @@
         <v>45589</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10475,7 +10475,7 @@
         <v>45443</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10553,7 +10553,7 @@
         <v>46094</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10631,7 +10631,7 @@
         <v>45219</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
         <v>45947</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10782,7 +10782,7 @@
         <v>45272</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10855,7 +10855,7 @@
         <v>45952</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10928,7 +10928,7 @@
         <v>45601</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11006,7 +11006,7 @@
         <v>46127</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11079,7 +11079,7 @@
         <v>45971</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11157,7 +11157,7 @@
         <v>44986</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11230,7 +11230,7 @@
         <v>46132</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11303,7 +11303,7 @@
         <v>46129</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11381,7 +11381,7 @@
         <v>45979</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11454,7 +11454,7 @@
         <v>45602</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11532,7 +11532,7 @@
         <v>45163</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11610,7 +11610,7 @@
         <v>45996</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11683,7 +11683,7 @@
         <v>45912</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11756,7 +11756,7 @@
         <v>45996</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11829,7 +11829,7 @@
         <v>45205</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11907,7 +11907,7 @@
         <v>45163</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11985,7 +11985,7 @@
         <v>44509</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12063,7 +12063,7 @@
         <v>45616</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12136,7 +12136,7 @@
         <v>45819</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12214,7 +12214,7 @@
         <v>45819</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12292,7 +12292,7 @@
         <v>46140</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12370,7 +12370,7 @@
         <v>46140</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12448,7 +12448,7 @@
         <v>46140</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12526,7 +12526,7 @@
         <v>45057</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12604,7 +12604,7 @@
         <v>44719</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
         <v>44989</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12750,7 +12750,7 @@
         <v>44839</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12823,7 +12823,7 @@
         <v>45106</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12896,7 +12896,7 @@
         <v>46148</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12969,7 +12969,7 @@
         <v>46148</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13047,7 +13047,7 @@
         <v>46148</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13125,7 +13125,7 @@
         <v>46148</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13198,7 +13198,7 @@
         <v>45735</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13276,7 +13276,7 @@
         <v>45190</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13354,7 +13354,7 @@
         <v>45581</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13432,7 +13432,7 @@
         <v>45581</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13510,7 +13510,7 @@
         <v>45742</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13588,7 +13588,7 @@
         <v>44986</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13661,7 +13661,7 @@
         <v>45624</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13734,7 +13734,7 @@
         <v>46162</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13812,7 +13812,7 @@
         <v>46162</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13890,7 +13890,7 @@
         <v>45841</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13963,7 +13963,7 @@
         <v>45645</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14041,7 +14041,7 @@
         <v>45639</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14114,7 +14114,7 @@
         <v>46167</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14192,7 +14192,7 @@
         <v>44501</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14270,7 +14270,7 @@
         <v>46170</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14343,7 +14343,7 @@
         <v>44754</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14421,7 +14421,7 @@
         <v>46171</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14499,7 +14499,7 @@
         <v>45337</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14572,7 +14572,7 @@
         <v>46170</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14645,7 +14645,7 @@
         <v>45520</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14718,7 +14718,7 @@
         <v>45160</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14791,7 +14791,7 @@
         <v>46185</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14869,7 +14869,7 @@
         <v>45602</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14947,7 +14947,7 @@
         <v>46185</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15025,7 +15025,7 @@
         <v>46185</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15103,7 +15103,7 @@
         <v>46189</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15181,7 +15181,7 @@
         <v>45600</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15254,7 +15254,7 @@
         <v>45600</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15327,7 +15327,7 @@
         <v>46191</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15405,7 +15405,7 @@
         <v>46191</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15483,7 +15483,7 @@
         <v>45876</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15556,7 +15556,7 @@
         <v>46195</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15629,7 +15629,7 @@
         <v>45876</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15702,7 +15702,7 @@
         <v>46198</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15780,7 +15780,7 @@
         <v>46198</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15858,7 +15858,7 @@
         <v>46199</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15931,7 +15931,7 @@
         <v>46198</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16009,7 +16009,7 @@
         <v>46202</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16087,7 +16087,7 @@
         <v>45747</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16160,7 +16160,7 @@
         <v>46202</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16238,7 +16238,7 @@
         <v>46204</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16316,7 +16316,7 @@
         <v>45729</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16394,7 +16394,7 @@
         <v>45609</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16472,7 +16472,7 @@
         <v>44609</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16545,7 +16545,7 @@
         <v>45645</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16623,7 +16623,7 @@
         <v>45645</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16701,7 +16701,7 @@
         <v>45190</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16779,7 +16779,7 @@
         <v>45222</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16857,7 +16857,7 @@
         <v>46260</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16935,7 +16935,7 @@
         <v>45116</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17008,7 +17008,7 @@
         <v>45119</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17081,7 +17081,7 @@
         <v>46268</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17154,7 +17154,7 @@
         <v>46268</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17227,7 +17227,7 @@
         <v>46268</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17300,7 +17300,7 @@
         <v>45351</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17378,7 +17378,7 @@
         <v>45351</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17456,7 +17456,7 @@
         <v>45261</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17534,7 +17534,7 @@
         <v>46230</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17607,7 +17607,7 @@
         <v>46231</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17685,7 +17685,7 @@
         <v>46231</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17763,7 +17763,7 @@
         <v>46231</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17841,7 +17841,7 @@
         <v>44781</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17914,7 +17914,7 @@
         <v>46279</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17987,7 +17987,7 @@
         <v>46281</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18065,7 +18065,7 @@
         <v>46282</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18138,7 +18138,7 @@
         <v>46239</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18216,7 +18216,7 @@
         <v>46239</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18294,7 +18294,7 @@
         <v>46283</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18372,7 +18372,7 @@
         <v>46241</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18445,7 +18445,7 @@
         <v>44552</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18518,7 +18518,7 @@
         <v>46283</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18596,7 +18596,7 @@
         <v>45535</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18669,7 +18669,7 @@
         <v>45192</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18742,7 +18742,7 @@
         <v>45541</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18820,7 +18820,7 @@
         <v>44579</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18893,7 +18893,7 @@
         <v>45369</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18971,7 +18971,7 @@
         <v>45763</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19044,7 +19044,7 @@
         <v>45222</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19122,7 +19122,7 @@
         <v>45376</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19195,7 +19195,7 @@
         <v>45621</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19273,7 +19273,7 @@
         <v>45351</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19351,7 +19351,7 @@
         <v>45233</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19424,7 +19424,7 @@
         <v>44816</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19502,7 +19502,7 @@
         <v>45384</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19580,7 +19580,7 @@
         <v>44986</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19653,7 +19653,7 @@
         <v>45705</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19731,7 +19731,7 @@
         <v>45707</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19809,7 +19809,7 @@
         <v>45764</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19887,7 +19887,7 @@
         <v>45635</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19965,7 +19965,7 @@
         <v>45474</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20038,7 +20038,7 @@
         <v>45215</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20116,7 +20116,7 @@
         <v>45223</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20194,7 +20194,7 @@
         <v>45272</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20267,7 +20267,7 @@
         <v>45581</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20345,7 +20345,7 @@
         <v>45443</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20423,7 +20423,7 @@
         <v>44587</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20496,7 +20496,7 @@
         <v>45805</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20574,7 +20574,7 @@
         <v>45805</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20652,7 +20652,7 @@
         <v>45729</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20730,7 +20730,7 @@
         <v>45729</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20808,7 +20808,7 @@
         <v>45742</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20886,7 +20886,7 @@
         <v>45742</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20964,7 +20964,7 @@
         <v>45916</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>

--- a/Översikt DEGERFORS.xlsx
+++ b/Översikt DEGERFORS.xlsx
@@ -601,7 +601,7 @@
         <v>46160</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>46051</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
         <v>46107</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>46160</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>46190</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>46190</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>46161</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>45089</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>45175</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>46160</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>45384</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
         <v>45384</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>45163</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>44550</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>46204</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>45175</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         <v>45932</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2663,7 +2663,7 @@
         <v>45163</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>45205</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2897,7 +2897,7 @@
         <v>45866</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
         <v>45351</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>45559</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>45931</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>45384</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>46190</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>46045</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>45931</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3799,7 +3799,7 @@
         <v>45163</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3914,7 +3914,7 @@
         <v>45558</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
         <v>45163</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         <v>46199</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>45163</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>44470</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>44487</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>44470</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4704,7 +4704,7 @@
         <v>45938</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>46099</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4919,7 +4919,7 @@
         <v>45589</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5029,7 +5029,7 @@
         <v>45931</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
         <v>45163</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         <v>45205</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
         <v>45163</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5480,7 +5480,7 @@
         <v>45096</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5594,7 +5594,7 @@
         <v>44651</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5699,7 +5699,7 @@
         <v>45589</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5809,7 +5809,7 @@
         <v>46186</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5919,7 +5919,7 @@
         <v>46186</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6033,7 +6033,7 @@
         <v>46185</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6138,7 +6138,7 @@
         <v>45116</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6243,7 +6243,7 @@
         <v>44578</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6352,7 +6352,7 @@
         <v>45614</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6461,7 +6461,7 @@
         <v>44805</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
         <v>44805</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6607,7 +6607,7 @@
         <v>44861</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6680,7 +6680,7 @@
         <v>44607</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         <v>44692</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
         <v>44470</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
         <v>44609</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6982,7 +6982,7 @@
         <v>44497</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7055,7 +7055,7 @@
         <v>44594</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7128,7 +7128,7 @@
         <v>44853</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7201,7 +7201,7 @@
         <v>44515</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7274,7 +7274,7 @@
         <v>44466</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7352,7 +7352,7 @@
         <v>44643</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7425,7 +7425,7 @@
         <v>44470</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7503,7 +7503,7 @@
         <v>44529</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7581,7 +7581,7 @@
         <v>44525</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7654,7 +7654,7 @@
         <v>44509</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7732,7 +7732,7 @@
         <v>44505</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7810,7 +7810,7 @@
         <v>45338</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7888,7 +7888,7 @@
         <v>45195</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7966,7 +7966,7 @@
         <v>45763</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8039,7 +8039,7 @@
         <v>44816</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8117,7 +8117,7 @@
         <v>45387</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8190,7 +8190,7 @@
         <v>45468</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8268,7 +8268,7 @@
         <v>45453</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8341,7 +8341,7 @@
         <v>44582</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8414,7 +8414,7 @@
         <v>46027</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
         <v>45601</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8565,7 +8565,7 @@
         <v>45330</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8643,7 +8643,7 @@
         <v>45887</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8721,7 +8721,7 @@
         <v>45887</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8799,7 +8799,7 @@
         <v>44986</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8872,7 +8872,7 @@
         <v>45798</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         <v>45629</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9023,7 +9023,7 @@
         <v>45338</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9101,7 +9101,7 @@
         <v>45902</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9179,7 +9179,7 @@
         <v>45902</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9257,7 +9257,7 @@
         <v>44904</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9335,7 +9335,7 @@
         <v>45912</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9413,7 +9413,7 @@
         <v>45912</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
         <v>45912</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9569,7 +9569,7 @@
         <v>45330</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9642,7 +9642,7 @@
         <v>45569</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9715,7 +9715,7 @@
         <v>46070</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9788,7 +9788,7 @@
         <v>45810</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9861,7 +9861,7 @@
         <v>45810</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9934,7 +9934,7 @@
         <v>46086</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10012,7 +10012,7 @@
         <v>46086</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10090,7 +10090,7 @@
         <v>45936</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10163,7 +10163,7 @@
         <v>46093</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10241,7 +10241,7 @@
         <v>46093</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10319,7 +10319,7 @@
         <v>46092</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10397,7 +10397,7 @@
         <v>45589</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10475,7 +10475,7 @@
         <v>45443</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10553,7 +10553,7 @@
         <v>46094</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10631,7 +10631,7 @@
         <v>45219</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10704,7 +10704,7 @@
         <v>45947</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10782,7 +10782,7 @@
         <v>45272</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10855,7 +10855,7 @@
         <v>45952</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10928,7 +10928,7 @@
         <v>45601</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11006,7 +11006,7 @@
         <v>46127</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11079,7 +11079,7 @@
         <v>45971</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11157,7 +11157,7 @@
         <v>44986</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11230,7 +11230,7 @@
         <v>46132</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11303,7 +11303,7 @@
         <v>46129</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11381,7 +11381,7 @@
         <v>45979</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11454,7 +11454,7 @@
         <v>45602</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11532,7 +11532,7 @@
         <v>45163</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11610,7 +11610,7 @@
         <v>45996</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11683,7 +11683,7 @@
         <v>45912</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11756,7 +11756,7 @@
         <v>45996</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11829,7 +11829,7 @@
         <v>45205</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11907,7 +11907,7 @@
         <v>45163</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11985,7 +11985,7 @@
         <v>44509</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12063,7 +12063,7 @@
         <v>45616</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12136,7 +12136,7 @@
         <v>45819</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12214,7 +12214,7 @@
         <v>45819</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12292,7 +12292,7 @@
         <v>46140</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12370,7 +12370,7 @@
         <v>46140</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12448,7 +12448,7 @@
         <v>46140</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12526,7 +12526,7 @@
         <v>45057</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12604,7 +12604,7 @@
         <v>44719</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12677,7 +12677,7 @@
         <v>44989</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12750,7 +12750,7 @@
         <v>44839</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12823,7 +12823,7 @@
         <v>45106</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12896,7 +12896,7 @@
         <v>46148</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12969,7 +12969,7 @@
         <v>46148</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13047,7 +13047,7 @@
         <v>46148</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13125,7 +13125,7 @@
         <v>46148</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13198,7 +13198,7 @@
         <v>45735</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13276,7 +13276,7 @@
         <v>45190</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13354,7 +13354,7 @@
         <v>45581</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13432,7 +13432,7 @@
         <v>45581</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13510,7 +13510,7 @@
         <v>45742</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13588,7 +13588,7 @@
         <v>44986</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13661,7 +13661,7 @@
         <v>45624</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13734,7 +13734,7 @@
         <v>46162</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13812,7 +13812,7 @@
         <v>46162</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13890,7 +13890,7 @@
         <v>45841</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13963,7 +13963,7 @@
         <v>45645</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14041,7 +14041,7 @@
         <v>45639</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14114,7 +14114,7 @@
         <v>46167</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14192,7 +14192,7 @@
         <v>44501</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14270,7 +14270,7 @@
         <v>46170</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14343,7 +14343,7 @@
         <v>44754</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14421,7 +14421,7 @@
         <v>46171</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14499,7 +14499,7 @@
         <v>45337</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14572,7 +14572,7 @@
         <v>46170</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14645,7 +14645,7 @@
         <v>45520</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14718,7 +14718,7 @@
         <v>45160</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14791,7 +14791,7 @@
         <v>46185</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14869,7 +14869,7 @@
         <v>45602</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14947,7 +14947,7 @@
         <v>46185</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15025,7 +15025,7 @@
         <v>46185</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15103,7 +15103,7 @@
         <v>46189</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15181,7 +15181,7 @@
         <v>45600</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15254,7 +15254,7 @@
         <v>45600</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15327,7 +15327,7 @@
         <v>46191</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15405,7 +15405,7 @@
         <v>46191</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15483,7 +15483,7 @@
         <v>45876</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15556,7 +15556,7 @@
         <v>46195</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15629,7 +15629,7 @@
         <v>45876</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15702,7 +15702,7 @@
         <v>46198</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15780,7 +15780,7 @@
         <v>46198</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15858,7 +15858,7 @@
         <v>46199</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15931,7 +15931,7 @@
         <v>46198</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16009,7 +16009,7 @@
         <v>46202</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16087,7 +16087,7 @@
         <v>45747</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16160,7 +16160,7 @@
         <v>46202</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16238,7 +16238,7 @@
         <v>46204</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16316,7 +16316,7 @@
         <v>45729</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16394,7 +16394,7 @@
         <v>45609</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16472,7 +16472,7 @@
         <v>44609</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16545,7 +16545,7 @@
         <v>45645</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16623,7 +16623,7 @@
         <v>45645</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16701,7 +16701,7 @@
         <v>45190</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16779,7 +16779,7 @@
         <v>45222</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16857,7 +16857,7 @@
         <v>46260</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16935,7 +16935,7 @@
         <v>45116</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17008,7 +17008,7 @@
         <v>45119</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17081,7 +17081,7 @@
         <v>46268</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17154,7 +17154,7 @@
         <v>46268</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17227,7 +17227,7 @@
         <v>46268</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17300,7 +17300,7 @@
         <v>45351</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17378,7 +17378,7 @@
         <v>45351</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17456,7 +17456,7 @@
         <v>45261</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17534,7 +17534,7 @@
         <v>46230</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17607,7 +17607,7 @@
         <v>46231</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17685,7 +17685,7 @@
         <v>46231</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17763,7 +17763,7 @@
         <v>46231</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17841,7 +17841,7 @@
         <v>44781</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17914,7 +17914,7 @@
         <v>46279</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17987,7 +17987,7 @@
         <v>46281</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18065,7 +18065,7 @@
         <v>46282</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18138,7 +18138,7 @@
         <v>46239</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18216,7 +18216,7 @@
         <v>46239</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18294,7 +18294,7 @@
         <v>46283</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18372,7 +18372,7 @@
         <v>46241</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18445,7 +18445,7 @@
         <v>44552</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18518,7 +18518,7 @@
         <v>46283</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18596,7 +18596,7 @@
         <v>45535</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18669,7 +18669,7 @@
         <v>45192</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18742,7 +18742,7 @@
         <v>45541</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18820,7 +18820,7 @@
         <v>44579</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18893,7 +18893,7 @@
         <v>45369</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18971,7 +18971,7 @@
         <v>45763</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19044,7 +19044,7 @@
         <v>45222</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19122,7 +19122,7 @@
         <v>45376</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19195,7 +19195,7 @@
         <v>45621</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19273,7 +19273,7 @@
         <v>45351</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19351,7 +19351,7 @@
         <v>45233</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19424,7 +19424,7 @@
         <v>44816</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19502,7 +19502,7 @@
         <v>45384</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19580,7 +19580,7 @@
         <v>44986</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19653,7 +19653,7 @@
         <v>45705</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19731,7 +19731,7 @@
         <v>45707</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19809,7 +19809,7 @@
         <v>45764</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19887,7 +19887,7 @@
         <v>45635</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19965,7 +19965,7 @@
         <v>45474</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20038,7 +20038,7 @@
         <v>45215</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20116,7 +20116,7 @@
         <v>45223</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20194,7 +20194,7 @@
         <v>45272</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20267,7 +20267,7 @@
         <v>45581</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20345,7 +20345,7 @@
         <v>45443</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20423,7 +20423,7 @@
         <v>44587</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20496,7 +20496,7 @@
         <v>45805</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20574,7 +20574,7 @@
         <v>45805</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20652,7 +20652,7 @@
         <v>45729</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20730,7 +20730,7 @@
         <v>45729</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20808,7 +20808,7 @@
         <v>45742</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20886,7 +20886,7 @@
         <v>45742</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20964,7 +20964,7 @@
         <v>45916</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>

--- a/Översikt DEGERFORS.xlsx
+++ b/Översikt DEGERFORS.xlsx
@@ -601,7 +601,7 @@
         <v>46160</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>46051</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
         <v>46160</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>46107</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>46190</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>46190</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>46161</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>45175</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>45089</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>46160</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>45384</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
         <v>45384</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>45163</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>44550</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>46204</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>45175</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         <v>45163</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>45205</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
         <v>45932</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2897,7 +2897,7 @@
         <v>45866</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
         <v>45351</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>45559</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>45384</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>45931</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>46190</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>45558</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>45163</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>45163</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         <v>46045</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         <v>45931</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         <v>45163</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>46199</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>44487</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>45163</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
         <v>45116</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
         <v>45163</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         <v>45096</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>45938</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
         <v>46099</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5146,7 +5146,7 @@
         <v>45931</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5255,7 +5255,7 @@
         <v>45205</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5369,7 +5369,7 @@
         <v>44651</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5474,7 +5474,7 @@
         <v>46186</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5584,7 +5584,7 @@
         <v>46186</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
         <v>45589</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         <v>46185</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5913,7 +5913,7 @@
         <v>45589</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6023,7 +6023,7 @@
         <v>45614</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6132,7 +6132,7 @@
         <v>44578</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6241,7 +6241,7 @@
         <v>44805</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6314,7 +6314,7 @@
         <v>44805</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6387,7 +6387,7 @@
         <v>44861</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6460,7 +6460,7 @@
         <v>44607</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>44692</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6611,7 +6611,7 @@
         <v>44609</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6684,7 +6684,7 @@
         <v>44497</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6757,7 +6757,7 @@
         <v>44594</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
         <v>44853</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
         <v>44515</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6976,7 +6976,7 @@
         <v>44643</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7049,7 +7049,7 @@
         <v>44529</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7127,7 +7127,7 @@
         <v>44509</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7205,7 +7205,7 @@
         <v>44525</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7278,7 +7278,7 @@
         <v>44505</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7356,7 +7356,7 @@
         <v>45707</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7434,7 +7434,7 @@
         <v>44754</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7512,7 +7512,7 @@
         <v>45541</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7590,7 +7590,7 @@
         <v>45763</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7663,7 +7663,7 @@
         <v>45215</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7741,7 +7741,7 @@
         <v>45163</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7819,7 +7819,7 @@
         <v>45272</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7892,7 +7892,7 @@
         <v>45624</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7965,7 +7965,7 @@
         <v>45205</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         <v>45887</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         <v>45443</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8199,7 +8199,7 @@
         <v>45351</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         <v>44986</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8350,7 +8350,7 @@
         <v>46027</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8423,7 +8423,7 @@
         <v>45535</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8496,7 +8496,7 @@
         <v>45163</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
         <v>45902</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8652,7 +8652,7 @@
         <v>45902</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8730,7 +8730,7 @@
         <v>45453</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8803,7 +8803,7 @@
         <v>45912</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         <v>45912</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8959,7 +8959,7 @@
         <v>45912</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9037,7 +9037,7 @@
         <v>45798</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9110,7 +9110,7 @@
         <v>45330</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9188,7 +9188,7 @@
         <v>45810</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9261,7 +9261,7 @@
         <v>44579</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>45936</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9407,7 +9407,7 @@
         <v>45810</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9480,7 +9480,7 @@
         <v>45947</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9558,7 +9558,7 @@
         <v>45261</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9636,7 +9636,7 @@
         <v>45952</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9709,7 +9709,7 @@
         <v>46070</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9782,7 +9782,7 @@
         <v>46086</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9860,7 +9860,7 @@
         <v>46086</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9938,7 +9938,7 @@
         <v>45468</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10016,7 +10016,7 @@
         <v>44582</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
         <v>46092</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10167,7 +10167,7 @@
         <v>45602</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10245,7 +10245,7 @@
         <v>46094</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10323,7 +10323,7 @@
         <v>44609</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10396,7 +10396,7 @@
         <v>46093</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10474,7 +10474,7 @@
         <v>46093</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10552,7 +10552,7 @@
         <v>45609</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10630,7 +10630,7 @@
         <v>45971</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10708,7 +10708,7 @@
         <v>45819</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10786,7 +10786,7 @@
         <v>45819</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10864,7 +10864,7 @@
         <v>45979</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10937,7 +10937,7 @@
         <v>45233</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11010,7 +11010,7 @@
         <v>45621</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11088,7 +11088,7 @@
         <v>45735</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11166,7 +11166,7 @@
         <v>44719</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11239,7 +11239,7 @@
         <v>46129</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11317,7 +11317,7 @@
         <v>45996</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11390,7 +11390,7 @@
         <v>45996</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         <v>46127</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11536,7 +11536,7 @@
         <v>45160</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11609,7 +11609,7 @@
         <v>46132</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11682,7 +11682,7 @@
         <v>45369</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11760,7 +11760,7 @@
         <v>45645</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11838,7 +11838,7 @@
         <v>44552</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11911,7 +11911,7 @@
         <v>45645</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11989,7 +11989,7 @@
         <v>45645</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12067,7 +12067,7 @@
         <v>45219</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12140,7 +12140,7 @@
         <v>45841</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12213,7 +12213,7 @@
         <v>45639</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12286,7 +12286,7 @@
         <v>45629</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12364,7 +12364,7 @@
         <v>45616</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12437,7 +12437,7 @@
         <v>45912</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12510,7 +12510,7 @@
         <v>45351</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12588,7 +12588,7 @@
         <v>46140</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12666,7 +12666,7 @@
         <v>46140</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12744,7 +12744,7 @@
         <v>46140</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12822,7 +12822,7 @@
         <v>45443</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12900,7 +12900,7 @@
         <v>45272</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12973,7 +12973,7 @@
         <v>46148</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13051,7 +13051,7 @@
         <v>46148</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13124,7 +13124,7 @@
         <v>46148</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13202,7 +13202,7 @@
         <v>46148</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13275,7 +13275,7 @@
         <v>45729</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13353,7 +13353,7 @@
         <v>45222</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13431,7 +13431,7 @@
         <v>45190</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13509,7 +13509,7 @@
         <v>45581</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13587,7 +13587,7 @@
         <v>45057</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13665,7 +13665,7 @@
         <v>45581</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13743,7 +13743,7 @@
         <v>45192</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13816,7 +13816,7 @@
         <v>45338</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13894,7 +13894,7 @@
         <v>46162</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13972,7 +13972,7 @@
         <v>46162</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14050,7 +14050,7 @@
         <v>45742</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14128,7 +14128,7 @@
         <v>45876</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14201,7 +14201,7 @@
         <v>46167</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14279,7 +14279,7 @@
         <v>45876</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14352,7 +14352,7 @@
         <v>45337</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14425,7 +14425,7 @@
         <v>45338</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14503,7 +14503,7 @@
         <v>46170</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14576,7 +14576,7 @@
         <v>46170</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14649,7 +14649,7 @@
         <v>45747</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14722,7 +14722,7 @@
         <v>44986</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14795,7 +14795,7 @@
         <v>46171</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14873,7 +14873,7 @@
         <v>45887</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>46185</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15029,7 +15029,7 @@
         <v>46185</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15107,7 +15107,7 @@
         <v>46185</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15185,7 +15185,7 @@
         <v>45330</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15258,7 +15258,7 @@
         <v>45601</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15336,7 +15336,7 @@
         <v>45116</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15409,7 +15409,7 @@
         <v>46189</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15487,7 +15487,7 @@
         <v>46195</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15560,7 +15560,7 @@
         <v>46191</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15638,7 +15638,7 @@
         <v>46191</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15716,7 +15716,7 @@
         <v>45190</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15794,7 +15794,7 @@
         <v>46198</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15872,7 +15872,7 @@
         <v>46198</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15950,7 +15950,7 @@
         <v>45222</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16028,7 +16028,7 @@
         <v>46198</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16106,7 +16106,7 @@
         <v>46202</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16184,7 +16184,7 @@
         <v>46199</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16257,7 +16257,7 @@
         <v>46202</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16335,7 +16335,7 @@
         <v>44839</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16408,7 +16408,7 @@
         <v>44781</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16481,7 +16481,7 @@
         <v>45387</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16554,7 +16554,7 @@
         <v>45384</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16632,7 +16632,7 @@
         <v>46260</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16710,7 +16710,7 @@
         <v>46268</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16783,7 +16783,7 @@
         <v>46268</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16856,7 +16856,7 @@
         <v>46268</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16929,7 +16929,7 @@
         <v>46230</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17002,7 +17002,7 @@
         <v>46231</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17080,7 +17080,7 @@
         <v>46231</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17158,7 +17158,7 @@
         <v>46231</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17236,7 +17236,7 @@
         <v>46279</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17309,7 +17309,7 @@
         <v>46281</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17387,7 +17387,7 @@
         <v>44509</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17465,7 +17465,7 @@
         <v>44816</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17543,7 +17543,7 @@
         <v>46239</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17621,7 +17621,7 @@
         <v>46283</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17699,7 +17699,7 @@
         <v>46282</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17772,7 +17772,7 @@
         <v>46239</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17850,7 +17850,7 @@
         <v>45589</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17928,7 +17928,7 @@
         <v>46283</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18006,7 +18006,7 @@
         <v>45601</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18084,7 +18084,7 @@
         <v>45351</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18162,7 +18162,7 @@
         <v>46241</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18235,7 +18235,7 @@
         <v>45106</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18308,7 +18308,7 @@
         <v>44904</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18386,7 +18386,7 @@
         <v>45763</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18459,7 +18459,7 @@
         <v>44986</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18532,7 +18532,7 @@
         <v>44989</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18605,7 +18605,7 @@
         <v>44986</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18678,7 +18678,7 @@
         <v>45602</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18756,7 +18756,7 @@
         <v>45520</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18829,7 +18829,7 @@
         <v>45195</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18907,7 +18907,7 @@
         <v>45569</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18980,7 +18980,7 @@
         <v>44816</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19058,7 +19058,7 @@
         <v>46204</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19136,7 +19136,7 @@
         <v>44501</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19214,7 +19214,7 @@
         <v>45705</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19292,7 +19292,7 @@
         <v>45600</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19365,7 +19365,7 @@
         <v>45600</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19438,7 +19438,7 @@
         <v>45376</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19511,7 +19511,7 @@
         <v>45764</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19589,7 +19589,7 @@
         <v>45119</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19662,7 +19662,7 @@
         <v>45474</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19735,7 +19735,7 @@
         <v>45581</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19813,7 +19813,7 @@
         <v>45223</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19891,7 +19891,7 @@
         <v>45635</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19969,7 +19969,7 @@
         <v>44587</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20042,7 +20042,7 @@
         <v>45805</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20120,7 +20120,7 @@
         <v>45805</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20198,7 +20198,7 @@
         <v>45729</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20276,7 +20276,7 @@
         <v>45729</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20354,7 +20354,7 @@
         <v>45742</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20432,7 +20432,7 @@
         <v>45742</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20510,7 +20510,7 @@
         <v>45916</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>

--- a/Översikt DEGERFORS.xlsx
+++ b/Översikt DEGERFORS.xlsx
@@ -601,7 +601,7 @@
         <v>46160</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>46051</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
         <v>46160</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>46107</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>46190</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>46190</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>46161</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>45175</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>45089</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>46160</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>45384</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
         <v>45384</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>45163</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>44550</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>46204</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>45175</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         <v>45163</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>45205</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
         <v>45932</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2897,7 +2897,7 @@
         <v>45866</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
         <v>45351</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>45559</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>45384</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>45931</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>46190</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>45558</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>45163</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3813,7 +3813,7 @@
         <v>45163</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         <v>46045</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         <v>45931</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         <v>45163</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>46199</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>44487</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>45163</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
         <v>45116</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
         <v>45163</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         <v>45096</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>45938</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
         <v>46099</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5146,7 +5146,7 @@
         <v>45931</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5255,7 +5255,7 @@
         <v>45205</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5369,7 +5369,7 @@
         <v>44651</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5474,7 +5474,7 @@
         <v>46186</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5584,7 +5584,7 @@
         <v>46186</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
         <v>45589</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5808,7 +5808,7 @@
         <v>46185</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5913,7 +5913,7 @@
         <v>45589</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6023,7 +6023,7 @@
         <v>45614</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6132,7 +6132,7 @@
         <v>44578</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6241,7 +6241,7 @@
         <v>44805</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6314,7 +6314,7 @@
         <v>44805</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6387,7 +6387,7 @@
         <v>44861</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6460,7 +6460,7 @@
         <v>44607</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>44692</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6611,7 +6611,7 @@
         <v>44609</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6684,7 +6684,7 @@
         <v>44497</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6757,7 +6757,7 @@
         <v>44594</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
         <v>44853</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
         <v>44515</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6976,7 +6976,7 @@
         <v>44643</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7049,7 +7049,7 @@
         <v>44529</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7127,7 +7127,7 @@
         <v>44509</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7205,7 +7205,7 @@
         <v>44525</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7278,7 +7278,7 @@
         <v>44505</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7356,7 +7356,7 @@
         <v>45707</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7434,7 +7434,7 @@
         <v>44754</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7512,7 +7512,7 @@
         <v>45541</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7590,7 +7590,7 @@
         <v>45763</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7663,7 +7663,7 @@
         <v>45215</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7741,7 +7741,7 @@
         <v>45163</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7819,7 +7819,7 @@
         <v>45272</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7892,7 +7892,7 @@
         <v>45624</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7965,7 +7965,7 @@
         <v>45205</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         <v>45887</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8121,7 +8121,7 @@
         <v>45443</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8199,7 +8199,7 @@
         <v>45351</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         <v>44986</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8350,7 +8350,7 @@
         <v>46027</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8423,7 +8423,7 @@
         <v>45535</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8496,7 +8496,7 @@
         <v>45163</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
         <v>45902</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8652,7 +8652,7 @@
         <v>45902</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8730,7 +8730,7 @@
         <v>45453</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8803,7 +8803,7 @@
         <v>45912</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         <v>45912</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8959,7 +8959,7 @@
         <v>45912</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9037,7 +9037,7 @@
         <v>45798</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9110,7 +9110,7 @@
         <v>45330</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9188,7 +9188,7 @@
         <v>45810</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9261,7 +9261,7 @@
         <v>44579</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>45936</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9407,7 +9407,7 @@
         <v>45810</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9480,7 +9480,7 @@
         <v>45947</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9558,7 +9558,7 @@
         <v>45261</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9636,7 +9636,7 @@
         <v>45952</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9709,7 +9709,7 @@
         <v>46070</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9782,7 +9782,7 @@
         <v>46086</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9860,7 +9860,7 @@
         <v>46086</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9938,7 +9938,7 @@
         <v>45468</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10016,7 +10016,7 @@
         <v>44582</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10089,7 +10089,7 @@
         <v>46092</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10167,7 +10167,7 @@
         <v>45602</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10245,7 +10245,7 @@
         <v>46094</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10323,7 +10323,7 @@
         <v>44609</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10396,7 +10396,7 @@
         <v>46093</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10474,7 +10474,7 @@
         <v>46093</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10552,7 +10552,7 @@
         <v>45609</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10630,7 +10630,7 @@
         <v>45971</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10708,7 +10708,7 @@
         <v>45819</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10786,7 +10786,7 @@
         <v>45819</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10864,7 +10864,7 @@
         <v>45979</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10937,7 +10937,7 @@
         <v>45233</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11010,7 +11010,7 @@
         <v>45621</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11088,7 +11088,7 @@
         <v>45735</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11166,7 +11166,7 @@
         <v>44719</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11239,7 +11239,7 @@
         <v>46129</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11317,7 +11317,7 @@
         <v>45996</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11390,7 +11390,7 @@
         <v>45996</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         <v>46127</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11536,7 +11536,7 @@
         <v>45160</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11609,7 +11609,7 @@
         <v>46132</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11682,7 +11682,7 @@
         <v>45369</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11760,7 +11760,7 @@
         <v>45645</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11838,7 +11838,7 @@
         <v>44552</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11911,7 +11911,7 @@
         <v>45645</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11989,7 +11989,7 @@
         <v>45645</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12067,7 +12067,7 @@
         <v>45219</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12140,7 +12140,7 @@
         <v>45841</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12213,7 +12213,7 @@
         <v>45639</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12286,7 +12286,7 @@
         <v>45629</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12364,7 +12364,7 @@
         <v>45616</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12437,7 +12437,7 @@
         <v>45912</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12510,7 +12510,7 @@
         <v>45351</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12588,7 +12588,7 @@
         <v>46140</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12666,7 +12666,7 @@
         <v>46140</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12744,7 +12744,7 @@
         <v>46140</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12822,7 +12822,7 @@
         <v>45443</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12900,7 +12900,7 @@
         <v>45272</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12973,7 +12973,7 @@
         <v>46148</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13051,7 +13051,7 @@
         <v>46148</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13124,7 +13124,7 @@
         <v>46148</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13202,7 +13202,7 @@
         <v>46148</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13275,7 +13275,7 @@
         <v>45729</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13353,7 +13353,7 @@
         <v>45222</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13431,7 +13431,7 @@
         <v>45190</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13509,7 +13509,7 @@
         <v>45581</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13587,7 +13587,7 @@
         <v>45057</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13665,7 +13665,7 @@
         <v>45581</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13743,7 +13743,7 @@
         <v>45192</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13816,7 +13816,7 @@
         <v>45338</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13894,7 +13894,7 @@
         <v>46162</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13972,7 +13972,7 @@
         <v>46162</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14050,7 +14050,7 @@
         <v>45742</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14128,7 +14128,7 @@
         <v>45876</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14201,7 +14201,7 @@
         <v>46167</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14279,7 +14279,7 @@
         <v>45876</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14352,7 +14352,7 @@
         <v>45337</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14425,7 +14425,7 @@
         <v>45338</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14503,7 +14503,7 @@
         <v>46170</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14576,7 +14576,7 @@
         <v>46170</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14649,7 +14649,7 @@
         <v>45747</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14722,7 +14722,7 @@
         <v>44986</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14795,7 +14795,7 @@
         <v>46171</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14873,7 +14873,7 @@
         <v>45887</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>46185</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15029,7 +15029,7 @@
         <v>46185</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15107,7 +15107,7 @@
         <v>46185</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15185,7 +15185,7 @@
         <v>45330</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15258,7 +15258,7 @@
         <v>45601</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15336,7 +15336,7 @@
         <v>45116</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15409,7 +15409,7 @@
         <v>46189</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15487,7 +15487,7 @@
         <v>46195</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15560,7 +15560,7 @@
         <v>46191</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15638,7 +15638,7 @@
         <v>46191</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15716,7 +15716,7 @@
         <v>45190</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15794,7 +15794,7 @@
         <v>46198</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15872,7 +15872,7 @@
         <v>46198</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15950,7 +15950,7 @@
         <v>45222</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16028,7 +16028,7 @@
         <v>46198</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16106,7 +16106,7 @@
         <v>46202</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16184,7 +16184,7 @@
         <v>46199</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16257,7 +16257,7 @@
         <v>46202</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16335,7 +16335,7 @@
         <v>44839</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16408,7 +16408,7 @@
         <v>44781</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16481,7 +16481,7 @@
         <v>45387</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16554,7 +16554,7 @@
         <v>45384</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16632,7 +16632,7 @@
         <v>46260</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16710,7 +16710,7 @@
         <v>46268</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16783,7 +16783,7 @@
         <v>46268</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16856,7 +16856,7 @@
         <v>46268</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16929,7 +16929,7 @@
         <v>46230</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17002,7 +17002,7 @@
         <v>46231</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17080,7 +17080,7 @@
         <v>46231</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17158,7 +17158,7 @@
         <v>46231</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17236,7 +17236,7 @@
         <v>46279</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17309,7 +17309,7 @@
         <v>46281</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17387,7 +17387,7 @@
         <v>44509</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17465,7 +17465,7 @@
         <v>44816</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17543,7 +17543,7 @@
         <v>46239</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17621,7 +17621,7 @@
         <v>46283</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17699,7 +17699,7 @@
         <v>46282</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17772,7 +17772,7 @@
         <v>46239</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17850,7 +17850,7 @@
         <v>45589</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17928,7 +17928,7 @@
         <v>46283</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18006,7 +18006,7 @@
         <v>45601</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18084,7 +18084,7 @@
         <v>45351</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18162,7 +18162,7 @@
         <v>46241</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18235,7 +18235,7 @@
         <v>45106</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18308,7 +18308,7 @@
         <v>44904</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18386,7 +18386,7 @@
         <v>45763</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18459,7 +18459,7 @@
         <v>44986</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18532,7 +18532,7 @@
         <v>44989</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18605,7 +18605,7 @@
         <v>44986</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18678,7 +18678,7 @@
         <v>45602</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18756,7 +18756,7 @@
         <v>45520</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18829,7 +18829,7 @@
         <v>45195</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18907,7 +18907,7 @@
         <v>45569</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18980,7 +18980,7 @@
         <v>44816</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19058,7 +19058,7 @@
         <v>46204</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19136,7 +19136,7 @@
         <v>44501</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19214,7 +19214,7 @@
         <v>45705</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19292,7 +19292,7 @@
         <v>45600</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19365,7 +19365,7 @@
         <v>45600</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19438,7 +19438,7 @@
         <v>45376</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19511,7 +19511,7 @@
         <v>45764</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19589,7 +19589,7 @@
         <v>45119</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19662,7 +19662,7 @@
         <v>45474</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19735,7 +19735,7 @@
         <v>45581</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19813,7 +19813,7 @@
         <v>45223</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19891,7 +19891,7 @@
         <v>45635</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19969,7 +19969,7 @@
         <v>44587</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20042,7 +20042,7 @@
         <v>45805</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20120,7 +20120,7 @@
         <v>45805</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20198,7 +20198,7 @@
         <v>45729</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20276,7 +20276,7 @@
         <v>45729</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20354,7 +20354,7 @@
         <v>45742</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20432,7 +20432,7 @@
         <v>45742</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20510,7 +20510,7 @@
         <v>45916</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>

--- a/Översikt DEGERFORS.xlsx
+++ b/Översikt DEGERFORS.xlsx
@@ -601,7 +601,7 @@
         <v>46160</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>46051</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 15809-2026</t>
+          <t>A 22871-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -850,10 +850,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46107</v>
+        <v>46160</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -871,13 +871,13 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>9.5</v>
+        <v>3.2</v>
       </c>
       <c r="J4" t="n">
         <v>11</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
         <v>6</v>
@@ -904,12 +904,138 @@
         <v>13</v>
       </c>
       <c r="T4" t="n">
+        <v>35</v>
+      </c>
+      <c r="U4" t="n">
+        <v>35</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Tornseglare
+Brunlångöra
+Dropptaggsvamp
+Duvhök
+Nordfladdermus
+Talltita
+Tretåig hackspett
+Grönpyrola
+Nattskärra
+Spillkråka
+Tofsmes
+Dvärgpipistrell
+Havsörn</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 22871-2026 artfynd.xlsx", "A 22871-2026")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 22871-2026 karta.png", "A 22871-2026")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 22871-2026 georefererad karta.tif", "A 22871-2026")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 22871-2026 FSC-klagomål.docx", "A 22871-2026")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 22871-2026 FSC-klagomål mail.docx", "A 22871-2026")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 22871-2026 tillsynsbegäran.docx", "A 22871-2026")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 22871-2026 tillsynsbegäran mail.docx", "A 22871-2026")</f>
+        <v/>
+      </c>
+      <c r="AE4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 22871-2026 prioriterade fågelarter.docx", "A 22871-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 15809-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>46107</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>DEGERFORS</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J5" t="n">
+        <v>11</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>6</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>7</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>13</v>
+      </c>
+      <c r="T5" t="n">
         <v>21</v>
       </c>
-      <c r="U4" t="n">
+      <c r="U5" t="n">
         <v>20</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Tornseglare
 Dropptaggsvamp
@@ -926,162 +1052,36 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 15809-2026 artfynd.xlsx", "A 15809-2026")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 15809-2026 karta.png", "A 15809-2026")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 15809-2026 georefererad karta.tif", "A 15809-2026")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 15809-2026 FSC-klagomål.docx", "A 15809-2026")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 15809-2026 FSC-klagomål mail.docx", "A 15809-2026")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 15809-2026 tillsynsbegäran.docx", "A 15809-2026")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 15809-2026 tillsynsbegäran mail.docx", "A 15809-2026")</f>
         <v/>
       </c>
-      <c r="AE4">
+      <c r="AE5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 15809-2026 prioriterade fågelarter.docx", "A 15809-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 22871-2026</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>46160</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>DEGERFORS</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>6</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>7</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" t="n">
-        <v>13</v>
-      </c>
-      <c r="T5" t="n">
-        <v>35</v>
-      </c>
-      <c r="U5" t="n">
-        <v>35</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Tornseglare
-Brunlångöra
-Dropptaggsvamp
-Duvhök
-Nordfladdermus
-Talltita
-Tretåig hackspett
-Grönpyrola
-Nattskärra
-Spillkråka
-Tofsmes
-Dvärgpipistrell
-Havsörn</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 22871-2026 artfynd.xlsx", "A 22871-2026")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 22871-2026 karta.png", "A 22871-2026")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 22871-2026 georefererad karta.tif", "A 22871-2026")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 22871-2026 FSC-klagomål.docx", "A 22871-2026")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 22871-2026 FSC-klagomål mail.docx", "A 22871-2026")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 22871-2026 tillsynsbegäran.docx", "A 22871-2026")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 22871-2026 tillsynsbegäran mail.docx", "A 22871-2026")</f>
-        <v/>
-      </c>
-      <c r="AE5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 22871-2026 prioriterade fågelarter.docx", "A 22871-2026")</f>
         <v/>
       </c>
     </row>
@@ -1105,7 +1105,7 @@
         <v>46190</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>46190</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>46161</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>45089</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>45175</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>46160</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>45384</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
         <v>45384</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 73321-2021</t>
+          <t>A 38916-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44550</v>
+        <v>45163</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2089,46 +2089,284 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>17</v>
+        <v>4.3</v>
       </c>
       <c r="J14" t="n">
         <v>3</v>
       </c>
       <c r="K14" t="n">
+        <v>3</v>
+      </c>
+      <c r="L14" t="n">
         <v>1</v>
       </c>
-      <c r="L14" t="n">
-        <v>3</v>
-      </c>
       <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
         <v>1</v>
       </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>4</v>
-      </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>6</v>
       </c>
       <c r="T14" t="n">
+        <v>27</v>
+      </c>
+      <c r="U14" t="n">
+        <v>27</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett
+Grönpyrola
+Thomsons trägnagare
+Vågbandad barkbock
+Spillkråka
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 38916-2023 artfynd.xlsx", "A 38916-2023")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 38916-2023 karta.png", "A 38916-2023")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 38916-2023 georefererad karta.tif", "A 38916-2023")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 38916-2023 FSC-klagomål.docx", "A 38916-2023")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 38916-2023 FSC-klagomål mail.docx", "A 38916-2023")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 38916-2023 tillsynsbegäran.docx", "A 38916-2023")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 38916-2023 tillsynsbegäran mail.docx", "A 38916-2023")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 38916-2023 prioriterade fågelarter.docx", "A 38916-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 29553-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>DEGERFORS</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>4</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>5</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1</v>
+      </c>
+      <c r="S15" t="n">
+        <v>6</v>
+      </c>
+      <c r="T15" t="n">
+        <v>6</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Garnlav
+Skuggblåslav
+Talltita
+Ullticka
+Vedskivlav
+Tofsmes</t>
+        </is>
+      </c>
+      <c r="W15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 29553-2026 artfynd.xlsx", "A 29553-2026")</f>
+        <v/>
+      </c>
+      <c r="X15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 29553-2026 karta.png", "A 29553-2026")</f>
+        <v/>
+      </c>
+      <c r="Y15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 29553-2026 georefererad karta.tif", "A 29553-2026")</f>
+        <v/>
+      </c>
+      <c r="AA15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 29553-2026 FSC-klagomål.docx", "A 29553-2026")</f>
+        <v/>
+      </c>
+      <c r="AB15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 29553-2026 FSC-klagomål mail.docx", "A 29553-2026")</f>
+        <v/>
+      </c>
+      <c r="AC15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 29553-2026 tillsynsbegäran.docx", "A 29553-2026")</f>
+        <v/>
+      </c>
+      <c r="AD15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 29553-2026 tillsynsbegäran mail.docx", "A 29553-2026")</f>
+        <v/>
+      </c>
+      <c r="AE15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 29553-2026 prioriterade fågelarter.docx", "A 29553-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A 73321-2021</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>44550</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>DEGERFORS</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>17</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" t="n">
+        <v>3</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>4</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1</v>
+      </c>
+      <c r="S16" t="n">
+        <v>6</v>
+      </c>
+      <c r="T16" t="n">
         <v>8</v>
       </c>
-      <c r="U14" t="n">
+      <c r="U16" t="n">
         <v>8</v>
       </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Grynig filtlav
@@ -2138,278 +2376,40 @@
 Spillkråka</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 73321-2021 artfynd.xlsx", "A 73321-2021")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 73321-2021 karta.png", "A 73321-2021")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 73321-2021 georefererad karta.tif", "A 73321-2021")</f>
         <v/>
       </c>
-      <c r="Z14">
+      <c r="Z16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/knärot/A 73321-2021 karta knärot.png", "A 73321-2021")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 73321-2021 FSC-klagomål.docx", "A 73321-2021")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 73321-2021 FSC-klagomål mail.docx", "A 73321-2021")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 73321-2021 tillsynsbegäran.docx", "A 73321-2021")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 73321-2021 tillsynsbegäran mail.docx", "A 73321-2021")</f>
         <v/>
       </c>
-      <c r="AE14">
+      <c r="AE16">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 73321-2021 prioriterade fågelarter.docx", "A 73321-2021")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 38916-2023</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>45163</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>DEGERFORS</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J15" t="n">
-        <v>3</v>
-      </c>
-      <c r="K15" t="n">
-        <v>3</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>6</v>
-      </c>
-      <c r="T15" t="n">
-        <v>27</v>
-      </c>
-      <c r="U15" t="n">
-        <v>27</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett
-Grönpyrola
-Thomsons trägnagare
-Vågbandad barkbock
-Spillkråka
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 38916-2023 artfynd.xlsx", "A 38916-2023")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 38916-2023 karta.png", "A 38916-2023")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 38916-2023 georefererad karta.tif", "A 38916-2023")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 38916-2023 FSC-klagomål.docx", "A 38916-2023")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 38916-2023 FSC-klagomål mail.docx", "A 38916-2023")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 38916-2023 tillsynsbegäran.docx", "A 38916-2023")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 38916-2023 tillsynsbegäran mail.docx", "A 38916-2023")</f>
-        <v/>
-      </c>
-      <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 38916-2023 prioriterade fågelarter.docx", "A 38916-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A 29553-2026</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>46204</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>DEGERFORS</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="J16" t="n">
-        <v>2</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>4</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>5</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1</v>
-      </c>
-      <c r="S16" t="n">
-        <v>6</v>
-      </c>
-      <c r="T16" t="n">
-        <v>6</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2</v>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Garnlav
-Skuggblåslav
-Talltita
-Ullticka
-Vedskivlav
-Tofsmes</t>
-        </is>
-      </c>
-      <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 29553-2026 artfynd.xlsx", "A 29553-2026")</f>
-        <v/>
-      </c>
-      <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 29553-2026 karta.png", "A 29553-2026")</f>
-        <v/>
-      </c>
-      <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 29553-2026 georefererad karta.tif", "A 29553-2026")</f>
-        <v/>
-      </c>
-      <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 29553-2026 FSC-klagomål.docx", "A 29553-2026")</f>
-        <v/>
-      </c>
-      <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 29553-2026 FSC-klagomål mail.docx", "A 29553-2026")</f>
-        <v/>
-      </c>
-      <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 29553-2026 tillsynsbegäran.docx", "A 29553-2026")</f>
-        <v/>
-      </c>
-      <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 29553-2026 tillsynsbegäran mail.docx", "A 29553-2026")</f>
-        <v/>
-      </c>
-      <c r="AE16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 29553-2026 prioriterade fågelarter.docx", "A 29553-2026")</f>
         <v/>
       </c>
     </row>
@@ -2433,7 +2433,7 @@
         <v>45175</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         <v>45866</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>45932</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         <v>45163</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         <v>45205</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
         <v>45351</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>45559</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>45931</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>45384</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>46190</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>46045</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>45931</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 38910-2023</t>
+          <t>A 40870-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3796,10 +3796,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45163</v>
+        <v>45558</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
       <c r="J29" t="n">
         <v>2</v>
@@ -3826,7 +3826,7 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -3841,7 +3841,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -3850,162 +3850,162 @@
         <v>2</v>
       </c>
       <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 40870-2024 artfynd.xlsx", "A 40870-2024")</f>
+        <v/>
+      </c>
+      <c r="X29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 40870-2024 karta.png", "A 40870-2024")</f>
+        <v/>
+      </c>
+      <c r="Y29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 40870-2024 georefererad karta.tif", "A 40870-2024")</f>
+        <v/>
+      </c>
+      <c r="AA29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 40870-2024 FSC-klagomål.docx", "A 40870-2024")</f>
+        <v/>
+      </c>
+      <c r="AB29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 40870-2024 FSC-klagomål mail.docx", "A 40870-2024")</f>
+        <v/>
+      </c>
+      <c r="AC29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 40870-2024 tillsynsbegäran.docx", "A 40870-2024")</f>
+        <v/>
+      </c>
+      <c r="AD29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 40870-2024 tillsynsbegäran mail.docx", "A 40870-2024")</f>
+        <v/>
+      </c>
+      <c r="AE29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 40870-2024 prioriterade fågelarter.docx", "A 40870-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>A 38910-2023</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D30" s="1" t="n">
+        <v>45163</v>
+      </c>
+      <c r="E30" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>DEGERFORS</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2</v>
+      </c>
+      <c r="T30" t="n">
         <v>3</v>
       </c>
-      <c r="U29" t="n">
+      <c r="U30" t="n">
         <v>3</v>
       </c>
-      <c r="V29" s="2" t="inlineStr">
+      <c r="V30" s="2" t="inlineStr">
         <is>
           <t>Tjäder
 Fläcknycklar</t>
         </is>
       </c>
-      <c r="W29">
+      <c r="W30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 38910-2023 artfynd.xlsx", "A 38910-2023")</f>
         <v/>
       </c>
-      <c r="X29">
+      <c r="X30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 38910-2023 karta.png", "A 38910-2023")</f>
         <v/>
       </c>
-      <c r="Y29">
+      <c r="Y30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 38910-2023 georefererad karta.tif", "A 38910-2023")</f>
         <v/>
       </c>
-      <c r="AA29">
+      <c r="AA30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 38910-2023 FSC-klagomål.docx", "A 38910-2023")</f>
         <v/>
       </c>
-      <c r="AB29">
+      <c r="AB30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 38910-2023 FSC-klagomål mail.docx", "A 38910-2023")</f>
         <v/>
       </c>
-      <c r="AC29">
+      <c r="AC30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 38910-2023 tillsynsbegäran.docx", "A 38910-2023")</f>
         <v/>
       </c>
-      <c r="AD29">
+      <c r="AD30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 38910-2023 tillsynsbegäran mail.docx", "A 38910-2023")</f>
         <v/>
       </c>
-      <c r="AE29">
+      <c r="AE30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 38910-2023 prioriterade fågelarter.docx", "A 38910-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>A 40870-2024</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D30" s="1" t="n">
-        <v>45558</v>
-      </c>
-      <c r="E30" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>DEGERFORS</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J30" t="n">
-        <v>2</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>1</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>1</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2</v>
-      </c>
-      <c r="U30" t="n">
-        <v>2</v>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 40870-2024 artfynd.xlsx", "A 40870-2024")</f>
-        <v/>
-      </c>
-      <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 40870-2024 karta.png", "A 40870-2024")</f>
-        <v/>
-      </c>
-      <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 40870-2024 georefererad karta.tif", "A 40870-2024")</f>
-        <v/>
-      </c>
-      <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 40870-2024 FSC-klagomål.docx", "A 40870-2024")</f>
-        <v/>
-      </c>
-      <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 40870-2024 FSC-klagomål mail.docx", "A 40870-2024")</f>
-        <v/>
-      </c>
-      <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 40870-2024 tillsynsbegäran.docx", "A 40870-2024")</f>
-        <v/>
-      </c>
-      <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 40870-2024 tillsynsbegäran mail.docx", "A 40870-2024")</f>
-        <v/>
-      </c>
-      <c r="AE30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 40870-2024 prioriterade fågelarter.docx", "A 40870-2024")</f>
         <v/>
       </c>
     </row>
@@ -4029,7 +4029,7 @@
         <v>45163</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4144,7 +4144,7 @@
         <v>45163</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>46199</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>44487</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4467,7 +4467,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 47915-2024</t>
+          <t>A 33297-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4481,10 +4481,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45589</v>
+        <v>45116</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4496,26 +4496,21 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
         <v>1</v>
       </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
       <c r="N35" t="n">
         <v>0</v>
       </c>
@@ -4526,10 +4521,10 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4538,46 +4533,46 @@
         <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 47915-2024 artfynd.xlsx", "A 47915-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 33297-2023 artfynd.xlsx", "A 33297-2023")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 47915-2024 karta.png", "A 47915-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 33297-2023 karta.png", "A 33297-2023")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 47915-2024 georefererad karta.tif", "A 47915-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 33297-2023 georefererad karta.tif", "A 33297-2023")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 47915-2024 FSC-klagomål.docx", "A 47915-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 33297-2023 FSC-klagomål.docx", "A 33297-2023")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 47915-2024 FSC-klagomål mail.docx", "A 47915-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 33297-2023 FSC-klagomål mail.docx", "A 33297-2023")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 47915-2024 tillsynsbegäran.docx", "A 47915-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 33297-2023 tillsynsbegäran.docx", "A 33297-2023")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 47915-2024 tillsynsbegäran mail.docx", "A 47915-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 33297-2023 tillsynsbegäran mail.docx", "A 33297-2023")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 49306-2025</t>
+          <t>A 38904-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4591,10 +4586,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45938</v>
+        <v>45163</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4606,14 +4601,19 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>5.8</v>
+        <v>2.9</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -4643,46 +4643,50 @@
         <v>1</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 49306-2025 artfynd.xlsx", "A 49306-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 38904-2023 artfynd.xlsx", "A 38904-2023")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 49306-2025 karta.png", "A 49306-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 38904-2023 karta.png", "A 38904-2023")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 49306-2025 georefererad karta.tif", "A 49306-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 38904-2023 georefererad karta.tif", "A 38904-2023")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 49306-2025 FSC-klagomål.docx", "A 49306-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 38904-2023 FSC-klagomål.docx", "A 38904-2023")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 49306-2025 FSC-klagomål mail.docx", "A 49306-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 38904-2023 FSC-klagomål mail.docx", "A 38904-2023")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 49306-2025 tillsynsbegäran.docx", "A 49306-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 38904-2023 tillsynsbegäran.docx", "A 38904-2023")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 49306-2025 tillsynsbegäran mail.docx", "A 49306-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 38904-2023 tillsynsbegäran mail.docx", "A 38904-2023")</f>
+        <v/>
+      </c>
+      <c r="AE36">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 38904-2023 prioriterade fågelarter.docx", "A 38904-2023")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 38904-2023</t>
+          <t>A 27093-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4696,10 +4700,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45163</v>
+        <v>45096</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4717,7 +4721,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.9</v>
+        <v>5.9</v>
       </c>
       <c r="J37" t="n">
         <v>1</v>
@@ -4761,42 +4765,42 @@
         </is>
       </c>
       <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 38904-2023 artfynd.xlsx", "A 38904-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 27093-2023 artfynd.xlsx", "A 27093-2023")</f>
         <v/>
       </c>
       <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 38904-2023 karta.png", "A 38904-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 27093-2023 karta.png", "A 27093-2023")</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 38904-2023 georefererad karta.tif", "A 38904-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 27093-2023 georefererad karta.tif", "A 27093-2023")</f>
         <v/>
       </c>
       <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 38904-2023 FSC-klagomål.docx", "A 38904-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 27093-2023 FSC-klagomål.docx", "A 27093-2023")</f>
         <v/>
       </c>
       <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 38904-2023 FSC-klagomål mail.docx", "A 38904-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 27093-2023 FSC-klagomål mail.docx", "A 27093-2023")</f>
         <v/>
       </c>
       <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 38904-2023 tillsynsbegäran.docx", "A 38904-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 27093-2023 tillsynsbegäran.docx", "A 27093-2023")</f>
         <v/>
       </c>
       <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 38904-2023 tillsynsbegäran mail.docx", "A 38904-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 27093-2023 tillsynsbegäran mail.docx", "A 27093-2023")</f>
         <v/>
       </c>
       <c r="AE37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 38904-2023 prioriterade fågelarter.docx", "A 38904-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 27093-2023 prioriterade fågelarter.docx", "A 27093-2023")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 48285-2023</t>
+          <t>A 49306-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4810,10 +4814,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45205</v>
+        <v>45938</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4825,19 +4829,14 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>1.1</v>
+        <v>5.8</v>
       </c>
       <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
         <v>1</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -4867,43 +4866,39 @@
         <v>1</v>
       </c>
       <c r="U38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 48285-2023 artfynd.xlsx", "A 48285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 49306-2025 artfynd.xlsx", "A 49306-2025")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 48285-2023 karta.png", "A 48285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 49306-2025 karta.png", "A 49306-2025")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 48285-2023 georefererad karta.tif", "A 48285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 49306-2025 georefererad karta.tif", "A 49306-2025")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 48285-2023 FSC-klagomål.docx", "A 48285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 49306-2025 FSC-klagomål.docx", "A 49306-2025")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 48285-2023 FSC-klagomål mail.docx", "A 48285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 49306-2025 FSC-klagomål mail.docx", "A 49306-2025")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 48285-2023 tillsynsbegäran.docx", "A 48285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 49306-2025 tillsynsbegäran.docx", "A 49306-2025")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 48285-2023 tillsynsbegäran mail.docx", "A 48285-2023")</f>
-        <v/>
-      </c>
-      <c r="AE38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 48285-2023 prioriterade fågelarter.docx", "A 48285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 49306-2025 tillsynsbegäran mail.docx", "A 49306-2025")</f>
         <v/>
       </c>
     </row>
@@ -4927,7 +4922,7 @@
         <v>46099</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5037,7 +5032,7 @@
         <v>45931</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5146,7 +5141,7 @@
         <v>45163</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5243,7 +5238,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 27093-2023</t>
+          <t>A 14121-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5257,10 +5252,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45096</v>
+        <v>44651</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5272,13 +5267,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>5.9</v>
+        <v>4.4</v>
       </c>
       <c r="J42" t="n">
         <v>1</v>
@@ -5318,46 +5308,42 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Hårklomossa</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 27093-2023 artfynd.xlsx", "A 27093-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 14121-2022 artfynd.xlsx", "A 14121-2022")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 27093-2023 karta.png", "A 27093-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 14121-2022 karta.png", "A 14121-2022")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 27093-2023 georefererad karta.tif", "A 27093-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 14121-2022 georefererad karta.tif", "A 14121-2022")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 27093-2023 FSC-klagomål.docx", "A 27093-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 14121-2022 FSC-klagomål.docx", "A 14121-2022")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 27093-2023 FSC-klagomål mail.docx", "A 27093-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 14121-2022 FSC-klagomål mail.docx", "A 14121-2022")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 27093-2023 tillsynsbegäran.docx", "A 27093-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 14121-2022 tillsynsbegäran.docx", "A 14121-2022")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 27093-2023 tillsynsbegäran mail.docx", "A 27093-2023")</f>
-        <v/>
-      </c>
-      <c r="AE42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 27093-2023 prioriterade fågelarter.docx", "A 27093-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 14121-2022 tillsynsbegäran mail.docx", "A 14121-2022")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 47941-2024</t>
+          <t>A 48285-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5371,10 +5357,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45589</v>
+        <v>45205</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5392,10 +5378,10 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -5404,7 +5390,7 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
@@ -5416,10 +5402,10 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -5428,46 +5414,50 @@
         <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Brunfläckig pärlemorfjäril</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 47941-2024 artfynd.xlsx", "A 47941-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 48285-2023 artfynd.xlsx", "A 48285-2023")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 47941-2024 karta.png", "A 47941-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 48285-2023 karta.png", "A 48285-2023")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 47941-2024 georefererad karta.tif", "A 47941-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 48285-2023 georefererad karta.tif", "A 48285-2023")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 47941-2024 FSC-klagomål.docx", "A 47941-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 48285-2023 FSC-klagomål.docx", "A 48285-2023")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 47941-2024 FSC-klagomål mail.docx", "A 47941-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 48285-2023 FSC-klagomål mail.docx", "A 48285-2023")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 47941-2024 tillsynsbegäran.docx", "A 47941-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 48285-2023 tillsynsbegäran.docx", "A 48285-2023")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 47941-2024 tillsynsbegäran mail.docx", "A 47941-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 48285-2023 tillsynsbegäran mail.docx", "A 48285-2023")</f>
+        <v/>
+      </c>
+      <c r="AE43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 48285-2023 prioriterade fågelarter.docx", "A 48285-2023")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 14121-2022</t>
+          <t>A 27071-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5481,10 +5471,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44651</v>
+        <v>46186</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5496,14 +5486,19 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>4.4</v>
+        <v>9.9</v>
       </c>
       <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
         <v>1</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
@@ -5533,46 +5528,46 @@
         <v>1</v>
       </c>
       <c r="U44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Hårklomossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 14121-2022 artfynd.xlsx", "A 14121-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 27071-2026 artfynd.xlsx", "A 27071-2026")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 14121-2022 karta.png", "A 14121-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 27071-2026 karta.png", "A 27071-2026")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 14121-2022 georefererad karta.tif", "A 14121-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 27071-2026 georefererad karta.tif", "A 27071-2026")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 14121-2022 FSC-klagomål.docx", "A 14121-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 27071-2026 FSC-klagomål.docx", "A 27071-2026")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 14121-2022 FSC-klagomål mail.docx", "A 14121-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 27071-2026 FSC-klagomål mail.docx", "A 27071-2026")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 14121-2022 tillsynsbegäran.docx", "A 14121-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 27071-2026 tillsynsbegäran.docx", "A 27071-2026")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 14121-2022 tillsynsbegäran mail.docx", "A 14121-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 27071-2026 tillsynsbegäran mail.docx", "A 27071-2026")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 27071-2026</t>
+          <t>A 27072-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5589,7 +5584,7 @@
         <v>46186</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5607,13 +5602,13 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>9.9</v>
+        <v>7.6</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -5643,46 +5638,50 @@
         <v>1</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 27071-2026 artfynd.xlsx", "A 27071-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 27072-2026 artfynd.xlsx", "A 27072-2026")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 27071-2026 karta.png", "A 27071-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 27072-2026 karta.png", "A 27072-2026")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 27071-2026 georefererad karta.tif", "A 27071-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 27072-2026 georefererad karta.tif", "A 27072-2026")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 27071-2026 FSC-klagomål.docx", "A 27071-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 27072-2026 FSC-klagomål.docx", "A 27072-2026")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 27071-2026 FSC-klagomål mail.docx", "A 27071-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 27072-2026 FSC-klagomål mail.docx", "A 27072-2026")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 27071-2026 tillsynsbegäran.docx", "A 27071-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 27072-2026 tillsynsbegäran.docx", "A 27072-2026")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 27071-2026 tillsynsbegäran mail.docx", "A 27071-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 27072-2026 tillsynsbegäran mail.docx", "A 27072-2026")</f>
+        <v/>
+      </c>
+      <c r="AE45">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 27072-2026 prioriterade fågelarter.docx", "A 27072-2026")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 27072-2026</t>
+          <t>A 26971-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5696,10 +5695,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46186</v>
+        <v>46185</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5711,19 +5710,14 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I46" t="n">
-        <v>7.6</v>
+        <v>2.1</v>
       </c>
       <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
         <v>1</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -5753,50 +5747,46 @@
         <v>1</v>
       </c>
       <c r="U46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 27072-2026 artfynd.xlsx", "A 27072-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 26971-2026 artfynd.xlsx", "A 26971-2026")</f>
         <v/>
       </c>
       <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 27072-2026 karta.png", "A 27072-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 26971-2026 karta.png", "A 26971-2026")</f>
         <v/>
       </c>
       <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 27072-2026 georefererad karta.tif", "A 27072-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 26971-2026 georefererad karta.tif", "A 26971-2026")</f>
         <v/>
       </c>
       <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 27072-2026 FSC-klagomål.docx", "A 27072-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 26971-2026 FSC-klagomål.docx", "A 26971-2026")</f>
         <v/>
       </c>
       <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 27072-2026 FSC-klagomål mail.docx", "A 27072-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 26971-2026 FSC-klagomål mail.docx", "A 26971-2026")</f>
         <v/>
       </c>
       <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 27072-2026 tillsynsbegäran.docx", "A 27072-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 26971-2026 tillsynsbegäran.docx", "A 26971-2026")</f>
         <v/>
       </c>
       <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 27072-2026 tillsynsbegäran mail.docx", "A 27072-2026")</f>
-        <v/>
-      </c>
-      <c r="AE46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 27072-2026 prioriterade fågelarter.docx", "A 27072-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 26971-2026 tillsynsbegäran mail.docx", "A 26971-2026")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 33297-2023</t>
+          <t>A 47941-2024</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5810,10 +5800,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45116</v>
+        <v>45589</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5825,8 +5815,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>7.2</v>
+        <v>1.4</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -5862,46 +5857,46 @@
         <v>1</v>
       </c>
       <c r="U47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Brunfläckig pärlemorfjäril</t>
         </is>
       </c>
       <c r="W47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 33297-2023 artfynd.xlsx", "A 33297-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 47941-2024 artfynd.xlsx", "A 47941-2024")</f>
         <v/>
       </c>
       <c r="X47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 33297-2023 karta.png", "A 33297-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 47941-2024 karta.png", "A 47941-2024")</f>
         <v/>
       </c>
       <c r="Y47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 33297-2023 georefererad karta.tif", "A 33297-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 47941-2024 georefererad karta.tif", "A 47941-2024")</f>
         <v/>
       </c>
       <c r="AA47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 33297-2023 FSC-klagomål.docx", "A 33297-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 47941-2024 FSC-klagomål.docx", "A 47941-2024")</f>
         <v/>
       </c>
       <c r="AB47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 33297-2023 FSC-klagomål mail.docx", "A 33297-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 47941-2024 FSC-klagomål mail.docx", "A 47941-2024")</f>
         <v/>
       </c>
       <c r="AC47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 33297-2023 tillsynsbegäran.docx", "A 33297-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 47941-2024 tillsynsbegäran.docx", "A 47941-2024")</f>
         <v/>
       </c>
       <c r="AD47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 33297-2023 tillsynsbegäran mail.docx", "A 33297-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 47941-2024 tillsynsbegäran mail.docx", "A 47941-2024")</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 26971-2026</t>
+          <t>A 47915-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5915,10 +5910,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46185</v>
+        <v>45589</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5930,14 +5925,19 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>2.1</v>
+        <v>5.8</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
@@ -5971,42 +5971,42 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 26971-2026 artfynd.xlsx", "A 26971-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 47915-2024 artfynd.xlsx", "A 47915-2024")</f>
         <v/>
       </c>
       <c r="X48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 26971-2026 karta.png", "A 26971-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 47915-2024 karta.png", "A 47915-2024")</f>
         <v/>
       </c>
       <c r="Y48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 26971-2026 georefererad karta.tif", "A 26971-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 47915-2024 georefererad karta.tif", "A 47915-2024")</f>
         <v/>
       </c>
       <c r="AA48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 26971-2026 FSC-klagomål.docx", "A 26971-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 47915-2024 FSC-klagomål.docx", "A 47915-2024")</f>
         <v/>
       </c>
       <c r="AB48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 26971-2026 FSC-klagomål mail.docx", "A 26971-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 47915-2024 FSC-klagomål mail.docx", "A 47915-2024")</f>
         <v/>
       </c>
       <c r="AC48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 26971-2026 tillsynsbegäran.docx", "A 26971-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 47915-2024 tillsynsbegäran.docx", "A 47915-2024")</f>
         <v/>
       </c>
       <c r="AD48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 26971-2026 tillsynsbegäran mail.docx", "A 26971-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 47915-2024 tillsynsbegäran mail.docx", "A 47915-2024")</f>
         <v/>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 2357-2022</t>
+          <t>A 53838-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6020,10 +6020,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44578</v>
+        <v>45614</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6036,7 +6036,7 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="J49" t="n">
         <v>1</v>
@@ -6080,42 +6080,42 @@
         </is>
       </c>
       <c r="W49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 2357-2022 artfynd.xlsx", "A 2357-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 53838-2024 artfynd.xlsx", "A 53838-2024")</f>
         <v/>
       </c>
       <c r="X49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 2357-2022 karta.png", "A 2357-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 53838-2024 karta.png", "A 53838-2024")</f>
         <v/>
       </c>
       <c r="Y49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 2357-2022 georefererad karta.tif", "A 2357-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 53838-2024 georefererad karta.tif", "A 53838-2024")</f>
         <v/>
       </c>
       <c r="AA49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 2357-2022 FSC-klagomål.docx", "A 2357-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 53838-2024 FSC-klagomål.docx", "A 53838-2024")</f>
         <v/>
       </c>
       <c r="AB49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 2357-2022 FSC-klagomål mail.docx", "A 2357-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 53838-2024 FSC-klagomål mail.docx", "A 53838-2024")</f>
         <v/>
       </c>
       <c r="AC49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 2357-2022 tillsynsbegäran.docx", "A 2357-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 53838-2024 tillsynsbegäran.docx", "A 53838-2024")</f>
         <v/>
       </c>
       <c r="AD49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 2357-2022 tillsynsbegäran mail.docx", "A 2357-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 53838-2024 tillsynsbegäran mail.docx", "A 53838-2024")</f>
         <v/>
       </c>
       <c r="AE49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 2357-2022 prioriterade fågelarter.docx", "A 2357-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 53838-2024 prioriterade fågelarter.docx", "A 53838-2024")</f>
         <v/>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 53838-2024</t>
+          <t>A 2357-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6129,10 +6129,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45614</v>
+        <v>44578</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="J50" t="n">
         <v>1</v>
@@ -6189,35 +6189,35 @@
         </is>
       </c>
       <c r="W50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 53838-2024 artfynd.xlsx", "A 53838-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 2357-2022 artfynd.xlsx", "A 2357-2022")</f>
         <v/>
       </c>
       <c r="X50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 53838-2024 karta.png", "A 53838-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 2357-2022 karta.png", "A 2357-2022")</f>
         <v/>
       </c>
       <c r="Y50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 53838-2024 georefererad karta.tif", "A 53838-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 2357-2022 georefererad karta.tif", "A 2357-2022")</f>
         <v/>
       </c>
       <c r="AA50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 53838-2024 FSC-klagomål.docx", "A 53838-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 2357-2022 FSC-klagomål.docx", "A 2357-2022")</f>
         <v/>
       </c>
       <c r="AB50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 53838-2024 FSC-klagomål mail.docx", "A 53838-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 2357-2022 FSC-klagomål mail.docx", "A 2357-2022")</f>
         <v/>
       </c>
       <c r="AC50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 53838-2024 tillsynsbegäran.docx", "A 53838-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 2357-2022 tillsynsbegäran.docx", "A 2357-2022")</f>
         <v/>
       </c>
       <c r="AD50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 53838-2024 tillsynsbegäran mail.docx", "A 53838-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 2357-2022 tillsynsbegäran mail.docx", "A 2357-2022")</f>
         <v/>
       </c>
       <c r="AE50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 53838-2024 prioriterade fågelarter.docx", "A 53838-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 2357-2022 prioriterade fågelarter.docx", "A 2357-2022")</f>
         <v/>
       </c>
     </row>
@@ -6241,7 +6241,7 @@
         <v>44805</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6314,7 +6314,7 @@
         <v>44805</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6387,7 +6387,7 @@
         <v>44861</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6460,7 +6460,7 @@
         <v>44607</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>44692</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6611,7 +6611,7 @@
         <v>44609</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6684,7 +6684,7 @@
         <v>44497</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6757,7 +6757,7 @@
         <v>44594</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
         <v>44853</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
         <v>44515</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6976,7 +6976,7 @@
         <v>44643</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7049,7 +7049,7 @@
         <v>44529</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7127,7 +7127,7 @@
         <v>44525</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7200,7 +7200,7 @@
         <v>44509</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7278,7 +7278,7 @@
         <v>44505</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7339,7 +7339,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 6394-2024</t>
+          <t>A 18675-2025</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7349,14 +7349,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45338</v>
+        <v>45763</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7368,13 +7368,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>0.9</v>
+        <v>6</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -7417,7 +7412,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 45861-2023</t>
+          <t>A 7975-2025</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7427,14 +7422,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45195</v>
+        <v>45707</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7452,7 +7447,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.7</v>
+        <v>5.3</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -7495,7 +7490,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 18675-2025</t>
+          <t>A 37672-2024</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7505,14 +7500,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45763</v>
+        <v>45541</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7524,8 +7519,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I68" t="n">
-        <v>6</v>
+        <v>0.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7568,7 +7568,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 38743-2022</t>
+          <t>A 29607-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7582,10 +7582,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>44816</v>
+        <v>44754</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7646,7 +7646,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 13405-2024</t>
+          <t>A 56478-2024</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7660,10 +7660,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45387</v>
+        <v>45624</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7676,7 +7676,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7719,7 +7719,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 26176-2024</t>
+          <t>A 8062-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7733,10 +7733,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45468</v>
+        <v>45351</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7754,7 +7754,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7797,7 +7797,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 3177-2022</t>
+          <t>A 10321-2023</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7811,10 +7811,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44582</v>
+        <v>44986</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7827,7 +7827,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.7</v>
+        <v>1.3</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7870,7 +7870,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 50378-2024</t>
+          <t>A 36437-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7884,10 +7884,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45601</v>
+        <v>45535</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7899,13 +7899,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I73" t="n">
-        <v>4.9</v>
+        <v>2.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7948,7 +7943,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 10321-2023</t>
+          <t>A 38921-2023</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7962,10 +7957,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>44986</v>
+        <v>45163</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7977,8 +7972,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I74" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -8021,7 +8021,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 57234-2024</t>
+          <t>A 5218-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -8035,10 +8035,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>45629</v>
+        <v>45330</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8056,7 +8056,7 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0.9</v>
+        <v>3.3</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 6387-2024</t>
+          <t>A 38874-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -8109,14 +8109,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45338</v>
+        <v>45887</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8134,7 +8134,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -8177,7 +8177,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 26783-2025</t>
+          <t>A 2565-2022</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8191,10 +8191,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45810</v>
+        <v>44579</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -8267,7 +8267,7 @@
         <v>45810</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8323,7 +8323,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 59158-2022</t>
+          <t>A 26783-2025</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -8333,14 +8333,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44904</v>
+        <v>45810</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8352,13 +8352,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I79" t="n">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -8401,7 +8396,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 38874-2025</t>
+          <t>A 41767-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8415,10 +8410,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45887</v>
+        <v>45902</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8436,7 +8431,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>8.300000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8479,7 +8474,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 38875-2025</t>
+          <t>A 41766-2025</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8493,10 +8488,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45887</v>
+        <v>45902</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8514,7 +8509,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.9</v>
+        <v>3.2</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8574,7 +8569,7 @@
         <v>45819</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8652,7 +8647,7 @@
         <v>45819</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8713,7 +8708,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 23066-2022</t>
+          <t>A 60907-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8723,14 +8718,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>44719</v>
+        <v>45261</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8742,8 +8737,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8786,7 +8786,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 5277-2024</t>
+          <t>A 43694-2025</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8800,10 +8800,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45330</v>
+        <v>45912</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8815,8 +8815,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>0.5</v>
+        <v>6.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8859,7 +8864,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 43768-2024</t>
+          <t>A 43691-2025</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8873,10 +8878,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45569</v>
+        <v>45912</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8888,8 +8893,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>7</v>
+        <v>2.7</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8932,7 +8942,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 41766-2025</t>
+          <t>A 43689-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8946,10 +8956,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45902</v>
+        <v>45912</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8967,7 +8977,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>3.2</v>
+        <v>1.4</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -9010,7 +9020,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 41767-2025</t>
+          <t>A 26176-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -9024,10 +9034,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45902</v>
+        <v>45468</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9045,7 +9055,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -9088,7 +9098,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 33404-2025</t>
+          <t>A 3177-2022</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -9102,10 +9112,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45841</v>
+        <v>44582</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9118,7 +9128,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.5</v>
+        <v>3.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -9161,7 +9171,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 59863-2024</t>
+          <t>A 23066-2022</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -9175,10 +9185,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45639</v>
+        <v>44719</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9191,7 +9201,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -9234,7 +9244,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 43691-2025</t>
+          <t>A 9273-2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -9248,10 +9258,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45912</v>
+        <v>46070</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9263,13 +9273,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -9312,7 +9317,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 43689-2025</t>
+          <t>A 12159-2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -9326,10 +9331,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45912</v>
+        <v>46086</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9347,7 +9352,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -9390,7 +9395,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 47935-2024</t>
+          <t>A 12160-2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -9404,10 +9409,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45589</v>
+        <v>46086</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9425,7 +9430,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -9468,7 +9473,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 43694-2025</t>
+          <t>A 50766-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -9482,10 +9487,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45912</v>
+        <v>45602</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9503,7 +9508,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>6.6</v>
+        <v>2.1</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -9546,7 +9551,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 21952-2024</t>
+          <t>A 8184-2022</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9556,14 +9561,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45443</v>
+        <v>44609</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9575,13 +9580,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I95" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -9624,7 +9624,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 52566-2023</t>
+          <t>A 52523-2024</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9638,10 +9638,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45219</v>
+        <v>45609</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9653,8 +9653,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I96" t="n">
-        <v>1.5</v>
+        <v>4.4</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9697,7 +9702,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 62972-2023</t>
+          <t>A 12936-2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9711,10 +9716,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45272</v>
+        <v>46092</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9726,8 +9731,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I97" t="n">
-        <v>0.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9770,7 +9780,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 50377-2024</t>
+          <t>A 13293-2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9784,10 +9794,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45601</v>
+        <v>46094</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9805,7 +9815,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9848,7 +9858,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 37333-2025</t>
+          <t>A 13040-2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9858,14 +9868,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45876</v>
+        <v>46093</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9877,8 +9887,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I99" t="n">
-        <v>0.7</v>
+        <v>7.1</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9921,7 +9936,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 37265-2025</t>
+          <t>A 13039-2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9935,10 +9950,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45876</v>
+        <v>46093</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9950,8 +9965,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I100" t="n">
-        <v>1.3</v>
+        <v>5.1</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -9994,7 +10014,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 15594-2025</t>
+          <t>A 48625-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -10008,10 +10028,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45747</v>
+        <v>45936</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10024,7 +10044,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -10067,7 +10087,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 48625-2025</t>
+          <t>A 33404-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -10081,10 +10101,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45936</v>
+        <v>45841</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10097,7 +10117,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -10140,7 +10160,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 11085-2023</t>
+          <t>A 54515-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -10154,10 +10174,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44986</v>
+        <v>45233</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10170,7 +10190,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -10213,7 +10233,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 51040-2025</t>
+          <t>A 54994-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -10227,10 +10247,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45947</v>
+        <v>45621</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10248,7 +10268,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -10291,7 +10311,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 50764-2024</t>
+          <t>A 51040-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -10305,10 +10325,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45602</v>
+        <v>45947</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10326,7 +10346,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -10369,7 +10389,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 52099-2025</t>
+          <t>A 59863-2024</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -10383,10 +10403,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45952</v>
+        <v>45639</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10399,7 +10419,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -10442,7 +10462,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 38921-2023</t>
+          <t>A 52099-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -10456,10 +10476,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45163</v>
+        <v>45952</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10471,13 +10491,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I107" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -10520,7 +10535,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 9273-2026</t>
+          <t>A 13236-2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10534,10 +10549,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>46070</v>
+        <v>45735</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10549,8 +10564,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I108" t="n">
-        <v>2.3</v>
+        <v>18.5</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -10593,7 +10613,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 12159-2026</t>
+          <t>A 18913-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10607,10 +10627,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>46086</v>
+        <v>46129</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10628,7 +10648,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -10671,7 +10691,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 12160-2026</t>
+          <t>A 37333-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10681,14 +10701,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>46086</v>
+        <v>45876</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10700,13 +10720,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I110" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10749,7 +10764,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 13039-2026</t>
+          <t>A 37265-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10763,10 +10778,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46093</v>
+        <v>45876</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10778,13 +10793,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I111" t="n">
-        <v>5.1</v>
+        <v>1.3</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10827,7 +10837,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 13040-2026</t>
+          <t>A 15594-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10841,10 +10851,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>46093</v>
+        <v>45747</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10856,13 +10866,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I112" t="n">
-        <v>7.1</v>
+        <v>1.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10905,7 +10910,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 12936-2026</t>
+          <t>A 18506-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10919,10 +10924,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>46092</v>
+        <v>46127</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10934,13 +10939,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I113" t="n">
-        <v>8.800000000000001</v>
+        <v>1.6</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10983,7 +10983,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 13293-2026</t>
+          <t>A 19227-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10997,10 +10997,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46094</v>
+        <v>46132</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11012,13 +11012,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I114" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -11078,7 +11073,7 @@
         <v>45971</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11139,7 +11134,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 63905-2021</t>
+          <t>A 38875-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -11153,10 +11148,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>44509</v>
+        <v>45887</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11174,7 +11169,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>3.7</v>
+        <v>1.9</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -11217,7 +11212,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 57086-2025</t>
+          <t>A 38233-2023</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -11231,10 +11226,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45979</v>
+        <v>45160</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11247,7 +11242,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>6.1</v>
+        <v>0.6</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -11290,7 +11285,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 18506-2026</t>
+          <t>A 10674-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -11300,14 +11295,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46127</v>
+        <v>45369</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11319,8 +11314,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I118" t="n">
-        <v>1.6</v>
+        <v>0.3</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -11363,7 +11363,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 20577-2023</t>
+          <t>A 60933-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -11373,14 +11373,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45057</v>
+        <v>45645</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11398,7 +11398,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -11441,7 +11441,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 10797-2023</t>
+          <t>A 57086-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -11451,14 +11451,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44989</v>
+        <v>45979</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11471,7 +11471,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>9.5</v>
+        <v>6.1</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -11514,7 +11514,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 44457-2022</t>
+          <t>A 73693-2021</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -11528,10 +11528,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>44839</v>
+        <v>44552</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11544,7 +11544,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>6.8</v>
+        <v>3.6</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -11587,7 +11587,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 19227-2026</t>
+          <t>A 60937-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -11601,10 +11601,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46132</v>
+        <v>45645</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11616,8 +11616,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I122" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -11660,7 +11665,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 29482-2023</t>
+          <t>A 60940-2024</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11674,10 +11679,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45106</v>
+        <v>45645</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11689,8 +11694,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I123" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -11733,7 +11743,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 18913-2026</t>
+          <t>A 54082-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11747,10 +11757,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46129</v>
+        <v>45616</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11762,13 +11772,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I124" t="n">
-        <v>8.300000000000001</v>
+        <v>6.3</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -11811,7 +11816,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 60708-2025</t>
+          <t>A 60736-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11828,7 +11833,7 @@
         <v>45996</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11841,7 +11846,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.9</v>
+        <v>5.8</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11884,7 +11889,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 60736-2025</t>
+          <t>A 43752-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11898,10 +11903,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45996</v>
+        <v>45912</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11914,7 +11919,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>5.8</v>
+        <v>3.1</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11957,7 +11962,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 48118-2023</t>
+          <t>A 60708-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11971,10 +11976,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45205</v>
+        <v>45996</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11986,13 +11991,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I127" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -12052,7 +12052,7 @@
         <v>45163</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12113,7 +12113,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 13236-2025</t>
+          <t>A 48118-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -12127,10 +12127,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45735</v>
+        <v>45205</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12148,7 +12148,7 @@
         </is>
       </c>
       <c r="I129" t="n">
-        <v>18.5</v>
+        <v>1.6</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -12191,7 +12191,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 11084-2023</t>
+          <t>A 20567-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -12205,10 +12205,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44986</v>
+        <v>46140</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12220,8 +12220,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I130" t="n">
-        <v>2.7</v>
+        <v>7.8</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -12264,7 +12269,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 56478-2024</t>
+          <t>A 20568-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -12278,10 +12283,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45624</v>
+        <v>46140</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12293,8 +12298,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I131" t="n">
-        <v>1.4</v>
+        <v>6.3</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -12337,7 +12347,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 770-2026</t>
+          <t>A 20478-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -12351,10 +12361,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46027</v>
+        <v>46140</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12366,8 +12376,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I132" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -12410,7 +12425,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 43752-2025</t>
+          <t>A 770-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -12424,10 +12439,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45912</v>
+        <v>46027</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12440,7 +12455,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -12483,7 +12498,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 60933-2024</t>
+          <t>A 21440-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -12497,10 +12512,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45645</v>
+        <v>46148</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12518,7 +12533,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>1.9</v>
+        <v>6.5</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -12561,7 +12576,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 61750-2021</t>
+          <t>A 21402-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -12575,10 +12590,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>44501</v>
+        <v>46148</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12590,13 +12605,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I135" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -12639,7 +12649,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 29607-2022</t>
+          <t>A 21442-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12653,10 +12663,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44754</v>
+        <v>46148</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12674,7 +12684,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>2.1</v>
+        <v>4.1</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -12717,7 +12727,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 6240-2024</t>
+          <t>A 21401-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12731,10 +12741,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45337</v>
+        <v>46148</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12747,7 +12757,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.9</v>
+        <v>3.5</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -12790,7 +12800,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 54082-2024</t>
+          <t>A 44841-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12804,10 +12814,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45616</v>
+        <v>45190</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12819,8 +12829,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I138" t="n">
-        <v>6.3</v>
+        <v>1.5</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -12863,7 +12878,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 20478-2026</t>
+          <t>A 46222-2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12877,10 +12892,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46140</v>
+        <v>45581</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12898,7 +12913,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12941,7 +12956,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 33658-2024</t>
+          <t>A 46219-2024</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12955,10 +12970,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45520</v>
+        <v>45581</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12970,8 +12985,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I140" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -13014,7 +13034,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 38233-2023</t>
+          <t>A 52566-2023</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -13024,14 +13044,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45160</v>
+        <v>45219</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13044,7 +13064,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -13087,7 +13107,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 20567-2026</t>
+          <t>A 23230-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -13101,10 +13121,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>46140</v>
+        <v>46162</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13122,7 +13142,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>7.8</v>
+        <v>0.9</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -13165,7 +13185,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 20568-2026</t>
+          <t>A 23229-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -13179,10 +13199,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>46140</v>
+        <v>46162</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13200,7 +13220,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>6.3</v>
+        <v>2.9</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -13243,7 +13263,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 50766-2024</t>
+          <t>A 14678-2025</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -13253,14 +13273,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45602</v>
+        <v>45742</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13278,7 +13298,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -13321,7 +13341,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 21402-2026</t>
+          <t>A 23854-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -13335,10 +13355,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46148</v>
+        <v>46167</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13350,8 +13370,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I145" t="n">
-        <v>1.4</v>
+        <v>20.9</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -13394,7 +13419,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 21440-2026</t>
+          <t>A 24460-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -13408,10 +13433,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>46148</v>
+        <v>46170</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13423,13 +13448,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I146" t="n">
-        <v>6.5</v>
+        <v>1.1</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -13472,7 +13492,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 21442-2026</t>
+          <t>A 24462-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -13486,10 +13506,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46148</v>
+        <v>46170</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13501,13 +13521,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I147" t="n">
-        <v>4.1</v>
+        <v>0.8</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -13550,7 +13565,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 21401-2026</t>
+          <t>A 24689-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -13564,10 +13579,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46148</v>
+        <v>46171</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13579,8 +13594,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I148" t="n">
-        <v>3.5</v>
+        <v>15.5</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -13623,7 +13643,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 50207-2024</t>
+          <t>A 57234-2024</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -13637,10 +13657,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45600</v>
+        <v>45629</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13652,8 +13672,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I149" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -13696,7 +13721,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 50208-2024</t>
+          <t>A 26857-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -13710,10 +13735,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45600</v>
+        <v>46185</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13725,8 +13750,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I150" t="n">
-        <v>0.4</v>
+        <v>15.1</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -13769,7 +13799,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 44841-2023</t>
+          <t>A 26946-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -13783,10 +13813,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45190</v>
+        <v>46185</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13804,7 +13834,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -13847,7 +13877,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 46222-2024</t>
+          <t>A 26947-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13861,10 +13891,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45581</v>
+        <v>46185</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13882,7 +13912,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -13925,7 +13955,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 46219-2024</t>
+          <t>A 27411-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13939,10 +13969,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45581</v>
+        <v>46189</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13960,7 +13990,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -14003,7 +14033,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 14678-2025</t>
+          <t>A 28789-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -14013,14 +14043,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45742</v>
+        <v>46195</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14032,13 +14062,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I154" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -14081,7 +14106,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 23230-2026</t>
+          <t>A 27745-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -14095,10 +14120,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46162</v>
+        <v>46191</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14116,7 +14141,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -14159,7 +14184,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 23229-2026</t>
+          <t>A 27746-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -14173,10 +14198,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46162</v>
+        <v>46191</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14194,7 +14219,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>2.9</v>
+        <v>1</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -14237,7 +14262,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 23854-2026</t>
+          <t>A 8074-2024</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -14251,10 +14276,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46167</v>
+        <v>45351</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14272,7 +14297,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>20.9</v>
+        <v>0.7</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -14315,7 +14340,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 12143-2025</t>
+          <t>A 21952-2024</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -14329,10 +14354,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45729</v>
+        <v>45443</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14350,7 +14375,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -14393,7 +14418,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 52523-2024</t>
+          <t>A 28696-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -14407,10 +14432,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45609</v>
+        <v>46198</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14428,7 +14453,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>4.4</v>
+        <v>2.5</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -14471,7 +14496,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 24462-2026</t>
+          <t>A 28708-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -14485,10 +14510,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46170</v>
+        <v>46198</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14500,8 +14525,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I160" t="n">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -14544,7 +14574,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 24689-2026</t>
+          <t>A 28695-2026</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -14558,10 +14588,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46171</v>
+        <v>46198</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14579,7 +14609,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>15.5</v>
+        <v>2.7</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -14622,7 +14652,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 8184-2022</t>
+          <t>A 29130-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -14636,10 +14666,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>44609</v>
+        <v>46202</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14651,8 +14681,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I162" t="n">
-        <v>1.7</v>
+        <v>10.3</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -14695,7 +14730,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 24460-2026</t>
+          <t>A 28930-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -14709,10 +14744,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46170</v>
+        <v>46199</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14725,7 +14760,7 @@
         </is>
       </c>
       <c r="I163" t="n">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -14768,7 +14803,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 60937-2024</t>
+          <t>A 62972-2023</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -14782,10 +14817,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45645</v>
+        <v>45272</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14797,13 +14832,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I164" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -14846,7 +14876,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 60940-2024</t>
+          <t>A 29132-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -14860,10 +14890,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45645</v>
+        <v>46202</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14881,7 +14911,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.2</v>
+        <v>11.9</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -14924,7 +14954,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 44807-2023</t>
+          <t>A 12143-2025</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -14934,14 +14964,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45190</v>
+        <v>45729</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14959,7 +14989,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>5.4</v>
+        <v>1.3</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -15002,7 +15032,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 51652-2023</t>
+          <t>A 51653-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -15019,7 +15049,7 @@
         <v>45222</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15037,7 +15067,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1.7</v>
+        <v>3.9</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -15080,7 +15110,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 26857-2026</t>
+          <t>A 20577-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -15090,14 +15120,14 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46185</v>
+        <v>45057</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15115,7 +15145,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>15.1</v>
+        <v>1.8</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -15158,7 +15188,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 33293-2023</t>
+          <t>A 45365-2023</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -15172,10 +15202,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>45116</v>
+        <v>45192</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15188,7 +15218,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>17.2</v>
+        <v>5</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -15231,7 +15261,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 26947-2026</t>
+          <t>A 6387-2024</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -15241,14 +15271,14 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46185</v>
+        <v>45338</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15266,7 +15296,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -15309,7 +15339,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 26946-2026</t>
+          <t>A 6240-2024</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -15323,10 +15353,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46185</v>
+        <v>45337</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15338,13 +15368,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I171" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -15387,7 +15412,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 32154-2023</t>
+          <t>A 6394-2024</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -15397,14 +15422,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45119</v>
+        <v>45338</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15416,8 +15441,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I172" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -15460,7 +15490,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 27411-2026</t>
+          <t>A 35213-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -15474,10 +15504,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46189</v>
+        <v>46260</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15495,7 +15525,7 @@
         </is>
       </c>
       <c r="I173" t="n">
-        <v>1.4</v>
+        <v>9.5</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -15538,7 +15568,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 27745-2026</t>
+          <t>A 11085-2023</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -15552,10 +15582,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46191</v>
+        <v>44986</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15567,13 +15597,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I174" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -15616,7 +15641,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 27746-2026</t>
+          <t>A 36339-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -15630,10 +15655,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46191</v>
+        <v>46268</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15645,13 +15670,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I175" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -15694,7 +15714,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 28789-2026</t>
+          <t>A 36345-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -15708,10 +15728,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46195</v>
+        <v>46268</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15724,7 +15744,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>2.7</v>
+        <v>0.3</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -15767,7 +15787,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 8062-2024</t>
+          <t>A 5277-2024</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -15781,10 +15801,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>45351</v>
+        <v>45330</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15796,13 +15816,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I177" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -15845,7 +15860,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 8074-2024</t>
+          <t>A 50378-2024</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -15859,10 +15874,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45351</v>
+        <v>45601</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15880,7 +15895,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>0.7</v>
+        <v>4.9</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -15923,7 +15938,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 60907-2023</t>
+          <t>A 33293-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -15933,14 +15948,14 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45261</v>
+        <v>45116</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15952,13 +15967,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H179" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I179" t="n">
-        <v>0.6</v>
+        <v>17.2</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -16001,7 +16011,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 28696-2026</t>
+          <t>A 36336-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -16015,10 +16025,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46198</v>
+        <v>46268</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16030,13 +16040,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I180" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -16079,7 +16084,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 28708-2026</t>
+          <t>A 44807-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -16093,10 +16098,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46198</v>
+        <v>45190</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16114,7 +16119,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>2.8</v>
+        <v>5.4</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -16157,7 +16162,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 28930-2026</t>
+          <t>A 51652-2023</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -16171,10 +16176,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46199</v>
+        <v>45222</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16186,8 +16191,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I182" t="n">
-        <v>2.7</v>
+        <v>1.7</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -16230,7 +16240,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 28695-2026</t>
+          <t>A 44457-2022</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -16244,10 +16254,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46198</v>
+        <v>44839</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16259,13 +16269,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I183" t="n">
-        <v>2.7</v>
+        <v>6.8</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -16308,7 +16313,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 29130-2026</t>
+          <t>A 31813-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -16322,10 +16327,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46202</v>
+        <v>46230</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16337,13 +16342,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I184" t="n">
-        <v>10.3</v>
+        <v>1.8</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -16386,7 +16386,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 29132-2026</t>
+          <t>A 32211-2022</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -16400,10 +16400,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46202</v>
+        <v>44781</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16415,13 +16415,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I185" t="n">
-        <v>11.9</v>
+        <v>2.3</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -16464,7 +16459,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 32211-2022</t>
+          <t>A 13405-2024</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -16478,10 +16473,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>44781</v>
+        <v>45387</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16494,7 +16489,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -16537,7 +16532,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 73693-2021</t>
+          <t>A 31870-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -16551,10 +16546,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>44552</v>
+        <v>46231</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16566,8 +16561,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I187" t="n">
-        <v>3.6</v>
+        <v>1.5</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -16610,7 +16610,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 35213-2026</t>
+          <t>A 31871-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -16624,10 +16624,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46260</v>
+        <v>46231</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16645,7 +16645,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>9.5</v>
+        <v>1.9</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -16688,7 +16688,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 36437-2024</t>
+          <t>A 12729-2024</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -16702,10 +16702,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45535</v>
+        <v>45384</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16717,8 +16717,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I189" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -16761,7 +16766,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 45365-2023</t>
+          <t>A 37809-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -16775,10 +16780,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45192</v>
+        <v>46279</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16791,7 +16796,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>5</v>
+        <v>2.9</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -16834,7 +16839,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 37672-2024</t>
+          <t>A 38126-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -16844,14 +16849,14 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45541</v>
+        <v>46281</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16869,7 +16874,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>0.6</v>
+        <v>5.5</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -16912,7 +16917,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 36339-2026</t>
+          <t>A 32506-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -16926,10 +16931,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46268</v>
+        <v>46239</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16941,8 +16946,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I192" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -16985,7 +16995,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 36336-2026</t>
+          <t>A 38651-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -16999,10 +17009,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46268</v>
+        <v>46283</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17014,8 +17024,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I193" t="n">
-        <v>1.1</v>
+        <v>11.3</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -17058,7 +17073,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 36345-2026</t>
+          <t>A 38463-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -17072,10 +17087,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46268</v>
+        <v>46282</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17088,7 +17103,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>0.3</v>
+        <v>3.4</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -17131,7 +17146,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 2565-2022</t>
+          <t>A 32508-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -17145,10 +17160,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>44579</v>
+        <v>46239</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17160,8 +17175,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I195" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -17204,7 +17224,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 31813-2026</t>
+          <t>A 38659-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -17218,10 +17238,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46230</v>
+        <v>46283</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17233,8 +17253,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I196" t="n">
-        <v>1.8</v>
+        <v>4.6</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -17277,7 +17302,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 31870-2026</t>
+          <t>A 32810-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -17291,10 +17316,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46231</v>
+        <v>46241</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17306,13 +17331,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I197" t="n">
-        <v>1.5</v>
+        <v>6.1</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -17355,7 +17375,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 31871-2026</t>
+          <t>A 63905-2021</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -17369,10 +17389,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46231</v>
+        <v>44509</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17390,7 +17410,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>1.9</v>
+        <v>3.7</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -17433,7 +17453,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 31872-2026</t>
+          <t>A 38743-2022</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -17447,10 +17467,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46231</v>
+        <v>44816</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17468,7 +17488,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>5.2</v>
+        <v>1.6</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -17511,7 +17531,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 10674-2024</t>
+          <t>A 47935-2024</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -17521,14 +17541,14 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45369</v>
+        <v>45589</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17546,7 +17566,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>0.3</v>
+        <v>2.2</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -17589,7 +17609,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 18773-2025</t>
+          <t>A 50377-2024</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -17603,10 +17623,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45763</v>
+        <v>45601</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17618,8 +17638,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I201" t="n">
-        <v>13</v>
+        <v>0.7</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -17662,7 +17687,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 51653-2023</t>
+          <t>A 8059-2024</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -17676,10 +17701,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45222</v>
+        <v>45351</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17697,7 +17722,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>3.9</v>
+        <v>1.6</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -17740,7 +17765,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 12108-2024</t>
+          <t>A 29482-2023</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -17754,10 +17779,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45376</v>
+        <v>45106</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17770,7 +17795,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>7.7</v>
+        <v>0.7</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -17813,7 +17838,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 37809-2026</t>
+          <t>A 59158-2022</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -17823,14 +17848,14 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>46279</v>
+        <v>44904</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17842,8 +17867,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I204" t="n">
-        <v>2.9</v>
+        <v>3.7</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -17886,7 +17916,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 54994-2024</t>
+          <t>A 18773-2025</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -17900,10 +17930,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45621</v>
+        <v>45763</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17915,13 +17945,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H205" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I205" t="n">
-        <v>0.5</v>
+        <v>13</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -17964,7 +17989,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 38126-2026</t>
+          <t>A 10320-2023</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -17978,10 +18003,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>46281</v>
+        <v>44986</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17993,13 +18018,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H206" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I206" t="n">
-        <v>5.5</v>
+        <v>2.6</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -18042,7 +18062,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 38463-2026</t>
+          <t>A 10797-2023</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -18056,10 +18076,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>46282</v>
+        <v>44989</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18072,7 +18092,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>3.4</v>
+        <v>9.5</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -18115,7 +18135,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 32508-2026</t>
+          <t>A 11084-2023</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -18129,10 +18149,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>46239</v>
+        <v>44986</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18144,13 +18164,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H208" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I208" t="n">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -18193,7 +18208,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 32506-2026</t>
+          <t>A 50764-2024</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -18207,10 +18222,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>46239</v>
+        <v>45602</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18228,7 +18243,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -18271,7 +18286,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 38659-2026</t>
+          <t>A 33658-2024</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -18285,10 +18300,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>46283</v>
+        <v>45520</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18300,13 +18315,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H210" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I210" t="n">
-        <v>4.6</v>
+        <v>2.2</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -18349,7 +18359,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 32810-2026</t>
+          <t>A 29552-2026</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -18363,10 +18373,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>46241</v>
+        <v>46204</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18378,8 +18388,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I211" t="n">
-        <v>6.1</v>
+        <v>2.3</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -18422,7 +18437,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 38651-2026</t>
+          <t>A 45861-2023</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -18432,14 +18447,14 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>46283</v>
+        <v>45195</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18457,7 +18472,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>11.3</v>
+        <v>0.7</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -18500,7 +18515,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 8059-2024</t>
+          <t>A 31872-2026</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -18514,10 +18529,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45351</v>
+        <v>46231</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18535,7 +18550,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>1.6</v>
+        <v>5.2</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -18578,7 +18593,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 54515-2023</t>
+          <t>A 43768-2024</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -18592,10 +18607,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45233</v>
+        <v>45569</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18608,7 +18623,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -18668,7 +18683,7 @@
         <v>44816</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18729,7 +18744,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 12729-2024</t>
+          <t>A 61750-2021</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -18743,10 +18758,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45384</v>
+        <v>44501</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18764,7 +18779,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -18807,7 +18822,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 10320-2023</t>
+          <t>A 7472-2025</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -18821,10 +18836,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>44986</v>
+        <v>45705</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18834,6 +18849,11 @@
       <c r="G217" t="inlineStr">
         <is>
           <t>DEGERFORS</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I217" t="n">
@@ -18880,7 +18900,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 7472-2025</t>
+          <t>A 50207-2024</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -18894,10 +18914,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45705</v>
+        <v>45600</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18909,13 +18929,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H218" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I218" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -18958,7 +18973,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 7975-2025</t>
+          <t>A 50208-2024</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -18972,10 +18987,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45707</v>
+        <v>45600</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18987,13 +19002,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H219" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I219" t="n">
-        <v>5.3</v>
+        <v>0.4</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -19036,7 +19046,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 18831-2025</t>
+          <t>A 12108-2024</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -19050,10 +19060,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45764</v>
+        <v>45376</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19065,13 +19075,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H220" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I220" t="n">
-        <v>4.2</v>
+        <v>7.7</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -19114,7 +19119,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 58629-2024</t>
+          <t>A 18831-2025</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -19128,10 +19133,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45635</v>
+        <v>45764</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19149,7 +19154,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>1.4</v>
+        <v>4.2</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -19192,7 +19197,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 27438-2024</t>
+          <t>A 32154-2023</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -19206,10 +19211,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45474</v>
+        <v>45119</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19222,7 +19227,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -19265,7 +19270,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 50102-2023</t>
+          <t>A 27438-2024</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -19279,10 +19284,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45215</v>
+        <v>45474</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19294,13 +19299,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H223" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I223" t="n">
-        <v>3.9</v>
+        <v>2.6</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -19343,7 +19343,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 51996-2023</t>
+          <t>A 46288-2024</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -19357,10 +19357,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45223</v>
+        <v>45581</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19378,7 +19378,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -19421,7 +19421,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 62982-2023</t>
+          <t>A 51996-2023</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -19435,10 +19435,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45272</v>
+        <v>45223</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19450,8 +19450,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I225" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -19494,7 +19499,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 46288-2024</t>
+          <t>A 58629-2024</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -19508,10 +19513,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45581</v>
+        <v>45635</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19529,7 +19534,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>3.7</v>
+        <v>1.4</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -19572,7 +19577,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 21935-2024</t>
+          <t>A 50102-2023</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -19586,10 +19591,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45443</v>
+        <v>45215</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19607,7 +19612,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>1.8</v>
+        <v>3.9</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -19650,7 +19655,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 29552-2026</t>
+          <t>A 62982-2023</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -19664,10 +19669,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>46204</v>
+        <v>45272</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19679,13 +19684,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H228" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I228" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -19728,7 +19728,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 23460-2024</t>
+          <t>A 21935-2024</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -19742,10 +19742,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>45453</v>
+        <v>45443</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19757,8 +19757,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I229" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -19801,7 +19806,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 5218-2024</t>
+          <t>A 23460-2024</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -19815,10 +19820,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45330</v>
+        <v>45453</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19830,13 +19835,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H230" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I230" t="n">
-        <v>3.3</v>
+        <v>0.7</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -19896,7 +19896,7 @@
         <v>45798</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19969,7 +19969,7 @@
         <v>44587</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20042,7 +20042,7 @@
         <v>45805</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20120,7 +20120,7 @@
         <v>45805</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20198,7 +20198,7 @@
         <v>45729</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20276,7 +20276,7 @@
         <v>45729</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20354,7 +20354,7 @@
         <v>45742</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20432,7 +20432,7 @@
         <v>45742</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20510,7 +20510,7 @@
         <v>45916</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>

--- a/Översikt DEGERFORS.xlsx
+++ b/Översikt DEGERFORS.xlsx
@@ -601,7 +601,7 @@
         <v>46160</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>46051</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 22871-2026</t>
+          <t>A 15809-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -850,10 +850,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46160</v>
+        <v>46107</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -871,13 +871,13 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>3.2</v>
+        <v>9.5</v>
       </c>
       <c r="J4" t="n">
         <v>11</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>6</v>
@@ -904,12 +904,138 @@
         <v>13</v>
       </c>
       <c r="T4" t="n">
+        <v>21</v>
+      </c>
+      <c r="U4" t="n">
+        <v>20</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Tornseglare
+Dropptaggsvamp
+Duvhök
+Järnsparv
+Nordfladdermus
+Orange taggsvamp
+Talltita
+Spillkråka
+Tjäder
+Tofsmes
+Dvärgpipistrell
+Vattenfladdermus
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 15809-2026 artfynd.xlsx", "A 15809-2026")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 15809-2026 karta.png", "A 15809-2026")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 15809-2026 georefererad karta.tif", "A 15809-2026")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 15809-2026 FSC-klagomål.docx", "A 15809-2026")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 15809-2026 FSC-klagomål mail.docx", "A 15809-2026")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 15809-2026 tillsynsbegäran.docx", "A 15809-2026")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 15809-2026 tillsynsbegäran mail.docx", "A 15809-2026")</f>
+        <v/>
+      </c>
+      <c r="AE4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 15809-2026 prioriterade fågelarter.docx", "A 15809-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 22871-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>46160</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>DEGERFORS</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J5" t="n">
+        <v>11</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>6</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>7</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>13</v>
+      </c>
+      <c r="T5" t="n">
         <v>35</v>
       </c>
-      <c r="U4" t="n">
+      <c r="U5" t="n">
         <v>35</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Tornseglare
 Brunlångöra
@@ -926,162 +1052,36 @@
 Havsörn</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 22871-2026 artfynd.xlsx", "A 22871-2026")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 22871-2026 karta.png", "A 22871-2026")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 22871-2026 georefererad karta.tif", "A 22871-2026")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 22871-2026 FSC-klagomål.docx", "A 22871-2026")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 22871-2026 FSC-klagomål mail.docx", "A 22871-2026")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 22871-2026 tillsynsbegäran.docx", "A 22871-2026")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 22871-2026 tillsynsbegäran mail.docx", "A 22871-2026")</f>
         <v/>
       </c>
-      <c r="AE4">
+      <c r="AE5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 22871-2026 prioriterade fågelarter.docx", "A 22871-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 15809-2026</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>46107</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>DEGERFORS</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="J5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>6</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>7</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" t="n">
-        <v>13</v>
-      </c>
-      <c r="T5" t="n">
-        <v>21</v>
-      </c>
-      <c r="U5" t="n">
-        <v>20</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Tornseglare
-Dropptaggsvamp
-Duvhök
-Järnsparv
-Nordfladdermus
-Orange taggsvamp
-Talltita
-Spillkråka
-Tjäder
-Tofsmes
-Dvärgpipistrell
-Vattenfladdermus
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 15809-2026 artfynd.xlsx", "A 15809-2026")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 15809-2026 karta.png", "A 15809-2026")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 15809-2026 georefererad karta.tif", "A 15809-2026")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 15809-2026 FSC-klagomål.docx", "A 15809-2026")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 15809-2026 FSC-klagomål mail.docx", "A 15809-2026")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 15809-2026 tillsynsbegäran.docx", "A 15809-2026")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 15809-2026 tillsynsbegäran mail.docx", "A 15809-2026")</f>
-        <v/>
-      </c>
-      <c r="AE5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 15809-2026 prioriterade fågelarter.docx", "A 15809-2026")</f>
         <v/>
       </c>
     </row>
@@ -1105,7 +1105,7 @@
         <v>46190</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>46190</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>46161</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>45089</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>45175</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>46160</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>45384</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
         <v>45384</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 38916-2023</t>
+          <t>A 73321-2021</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45163</v>
+        <v>44550</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2089,26 +2089,21 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>4.3</v>
+        <v>17</v>
       </c>
       <c r="J14" t="n">
         <v>3</v>
       </c>
       <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
         <v>3</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>1</v>
       </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
@@ -2119,21 +2114,144 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
+        <v>4</v>
+      </c>
+      <c r="R14" t="n">
         <v>1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>6</v>
       </c>
       <c r="T14" t="n">
+        <v>8</v>
+      </c>
+      <c r="U14" t="n">
+        <v>8</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Grynig filtlav
+Gulsparv
+Rynkskinn
+Vedticka
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 73321-2021 artfynd.xlsx", "A 73321-2021")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 73321-2021 karta.png", "A 73321-2021")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 73321-2021 georefererad karta.tif", "A 73321-2021")</f>
+        <v/>
+      </c>
+      <c r="Z14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/knärot/A 73321-2021 karta knärot.png", "A 73321-2021")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 73321-2021 FSC-klagomål.docx", "A 73321-2021")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 73321-2021 FSC-klagomål mail.docx", "A 73321-2021")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 73321-2021 tillsynsbegäran.docx", "A 73321-2021")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 73321-2021 tillsynsbegäran mail.docx", "A 73321-2021")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 73321-2021 prioriterade fågelarter.docx", "A 73321-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 38916-2023</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45163</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>DEGERFORS</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>6</v>
+      </c>
+      <c r="T15" t="n">
         <v>27</v>
       </c>
-      <c r="U14" t="n">
+      <c r="U15" t="n">
         <v>27</v>
       </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Tretåig hackspett
 Grönpyrola
@@ -2143,154 +2261,36 @@
 Tjäder</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 38916-2023 artfynd.xlsx", "A 38916-2023")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 38916-2023 karta.png", "A 38916-2023")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 38916-2023 georefererad karta.tif", "A 38916-2023")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 38916-2023 FSC-klagomål.docx", "A 38916-2023")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 38916-2023 FSC-klagomål mail.docx", "A 38916-2023")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 38916-2023 tillsynsbegäran.docx", "A 38916-2023")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 38916-2023 tillsynsbegäran mail.docx", "A 38916-2023")</f>
         <v/>
       </c>
-      <c r="AE14">
+      <c r="AE15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 38916-2023 prioriterade fågelarter.docx", "A 38916-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 73321-2021</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>44550</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>DEGERFORS</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>17</v>
-      </c>
-      <c r="J15" t="n">
-        <v>3</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" t="n">
-        <v>3</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>4</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1</v>
-      </c>
-      <c r="S15" t="n">
-        <v>6</v>
-      </c>
-      <c r="T15" t="n">
-        <v>8</v>
-      </c>
-      <c r="U15" t="n">
-        <v>8</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Grynig filtlav
-Gulsparv
-Rynkskinn
-Vedticka
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 73321-2021 artfynd.xlsx", "A 73321-2021")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 73321-2021 karta.png", "A 73321-2021")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 73321-2021 georefererad karta.tif", "A 73321-2021")</f>
-        <v/>
-      </c>
-      <c r="Z15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/knärot/A 73321-2021 karta knärot.png", "A 73321-2021")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 73321-2021 FSC-klagomål.docx", "A 73321-2021")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 73321-2021 FSC-klagomål mail.docx", "A 73321-2021")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 73321-2021 tillsynsbegäran.docx", "A 73321-2021")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 73321-2021 tillsynsbegäran mail.docx", "A 73321-2021")</f>
-        <v/>
-      </c>
-      <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 73321-2021 prioriterade fågelarter.docx", "A 73321-2021")</f>
         <v/>
       </c>
     </row>
@@ -2314,7 +2314,7 @@
         <v>46204</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>45175</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 36081-2025</t>
+          <t>A 8063-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2548,10 +2548,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45866</v>
+        <v>45351</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v>4</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
@@ -2616,31 +2616,31 @@
         </is>
       </c>
       <c r="W18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 36081-2025 artfynd.xlsx", "A 36081-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 8063-2024 artfynd.xlsx", "A 8063-2024")</f>
         <v/>
       </c>
       <c r="X18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 36081-2025 karta.png", "A 36081-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 8063-2024 karta.png", "A 8063-2024")</f>
         <v/>
       </c>
       <c r="Y18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 36081-2025 georefererad karta.tif", "A 36081-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 8063-2024 georefererad karta.tif", "A 8063-2024")</f>
         <v/>
       </c>
       <c r="AA18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 36081-2025 FSC-klagomål.docx", "A 36081-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 8063-2024 FSC-klagomål.docx", "A 8063-2024")</f>
         <v/>
       </c>
       <c r="AB18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 36081-2025 FSC-klagomål mail.docx", "A 36081-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 8063-2024 FSC-klagomål mail.docx", "A 8063-2024")</f>
         <v/>
       </c>
       <c r="AC18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 36081-2025 tillsynsbegäran.docx", "A 36081-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 8063-2024 tillsynsbegäran.docx", "A 8063-2024")</f>
         <v/>
       </c>
       <c r="AD18">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 36081-2025 tillsynsbegäran mail.docx", "A 36081-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 8063-2024 tillsynsbegäran mail.docx", "A 8063-2024")</f>
         <v/>
       </c>
     </row>
@@ -2664,7 +2664,7 @@
         <v>45932</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2759,7 +2759,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 38915-2023</t>
+          <t>A 36081-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2773,10 +2773,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45163</v>
+        <v>45866</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2794,16 +2794,16 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>4.5</v>
+        <v>1.5</v>
       </c>
       <c r="J20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -2818,7 +2818,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2827,12 +2827,125 @@
         <v>4</v>
       </c>
       <c r="T20" t="n">
+        <v>4</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Jungfrulin
+Skogsklocka
+Svinrot
+Springkorn</t>
+        </is>
+      </c>
+      <c r="W20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 36081-2025 artfynd.xlsx", "A 36081-2025")</f>
+        <v/>
+      </c>
+      <c r="X20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 36081-2025 karta.png", "A 36081-2025")</f>
+        <v/>
+      </c>
+      <c r="Y20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 36081-2025 georefererad karta.tif", "A 36081-2025")</f>
+        <v/>
+      </c>
+      <c r="AA20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 36081-2025 FSC-klagomål.docx", "A 36081-2025")</f>
+        <v/>
+      </c>
+      <c r="AB20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 36081-2025 FSC-klagomål mail.docx", "A 36081-2025")</f>
+        <v/>
+      </c>
+      <c r="AC20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 36081-2025 tillsynsbegäran.docx", "A 36081-2025")</f>
+        <v/>
+      </c>
+      <c r="AD20">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 36081-2025 tillsynsbegäran mail.docx", "A 36081-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A 38915-2023</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>45163</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>DEGERFORS</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J21" t="n">
+        <v>4</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>4</v>
+      </c>
+      <c r="T21" t="n">
         <v>9</v>
       </c>
-      <c r="U20" t="n">
+      <c r="U21" t="n">
         <v>9</v>
       </c>
-      <c r="V20" s="2" t="inlineStr">
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>Tretåig hackspett
 Mattlummer
@@ -2840,116 +2953,116 @@
 Sångsvan</t>
         </is>
       </c>
-      <c r="W20">
+      <c r="W21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 38915-2023 artfynd.xlsx", "A 38915-2023")</f>
         <v/>
       </c>
-      <c r="X20">
+      <c r="X21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 38915-2023 karta.png", "A 38915-2023")</f>
         <v/>
       </c>
-      <c r="Y20">
+      <c r="Y21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 38915-2023 georefererad karta.tif", "A 38915-2023")</f>
         <v/>
       </c>
-      <c r="AA20">
+      <c r="AA21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 38915-2023 FSC-klagomål.docx", "A 38915-2023")</f>
         <v/>
       </c>
-      <c r="AB20">
+      <c r="AB21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 38915-2023 FSC-klagomål mail.docx", "A 38915-2023")</f>
         <v/>
       </c>
-      <c r="AC20">
+      <c r="AC21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 38915-2023 tillsynsbegäran.docx", "A 38915-2023")</f>
         <v/>
       </c>
-      <c r="AD20">
+      <c r="AD21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 38915-2023 tillsynsbegäran mail.docx", "A 38915-2023")</f>
         <v/>
       </c>
-      <c r="AE20">
+      <c r="AE21">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 38915-2023 prioriterade fågelarter.docx", "A 38915-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" t="inlineStr">
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
         <is>
           <t>A 48284-2023</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="n">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
         <v>45205</v>
       </c>
-      <c r="E21" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>DEGERFORS</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
+      <c r="E22" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>DEGERFORS</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I21" t="n">
+      <c r="I22" t="n">
         <v>6.7</v>
       </c>
-      <c r="J21" t="n">
+      <c r="J22" t="n">
         <v>4</v>
       </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
         <v>1</v>
       </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
         <v>1</v>
       </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
         <v>4</v>
       </c>
-      <c r="T21" t="n">
+      <c r="T22" t="n">
         <v>9</v>
       </c>
-      <c r="U21" t="n">
+      <c r="U22" t="n">
         <v>9</v>
       </c>
-      <c r="V21" s="2" t="inlineStr">
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Tretåig hackspett
 Spillkråka
@@ -2957,149 +3070,36 @@
 Revlummer</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 48284-2023 artfynd.xlsx", "A 48284-2023")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 48284-2023 karta.png", "A 48284-2023")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 48284-2023 georefererad karta.tif", "A 48284-2023")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 48284-2023 FSC-klagomål.docx", "A 48284-2023")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 48284-2023 FSC-klagomål mail.docx", "A 48284-2023")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 48284-2023 tillsynsbegäran.docx", "A 48284-2023")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 48284-2023 tillsynsbegäran mail.docx", "A 48284-2023")</f>
         <v/>
       </c>
-      <c r="AE21">
+      <c r="AE22">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 48284-2023 prioriterade fågelarter.docx", "A 48284-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 8063-2024</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>45351</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>DEGERFORS</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" t="n">
-        <v>3</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>3</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>4</v>
-      </c>
-      <c r="T22" t="n">
-        <v>4</v>
-      </c>
-      <c r="U22" t="n">
-        <v>4</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Jungfrulin
-Skogsklocka
-Svinrot
-Springkorn</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 8063-2024 artfynd.xlsx", "A 8063-2024")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 8063-2024 karta.png", "A 8063-2024")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 8063-2024 georefererad karta.tif", "A 8063-2024")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 8063-2024 FSC-klagomål.docx", "A 8063-2024")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 8063-2024 FSC-klagomål mail.docx", "A 8063-2024")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 8063-2024 tillsynsbegäran.docx", "A 8063-2024")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 8063-2024 tillsynsbegäran mail.docx", "A 8063-2024")</f>
         <v/>
       </c>
     </row>
@@ -3123,7 +3123,7 @@
         <v>45559</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>45931</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>45384</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>46190</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 38914-2023</t>
+          <t>A 47785-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3580,10 +3580,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45163</v>
+        <v>45931</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3595,13 +3595,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>5.4</v>
+        <v>2</v>
       </c>
       <c r="J27" t="n">
         <v>2</v>
@@ -3610,7 +3605,7 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -3625,7 +3620,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -3641,157 +3636,162 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
+          <t>Spillkråka
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 47785-2025 artfynd.xlsx", "A 47785-2025")</f>
+        <v/>
+      </c>
+      <c r="X27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 47785-2025 karta.png", "A 47785-2025")</f>
+        <v/>
+      </c>
+      <c r="Y27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 47785-2025 georefererad karta.tif", "A 47785-2025")</f>
+        <v/>
+      </c>
+      <c r="AA27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 47785-2025 FSC-klagomål.docx", "A 47785-2025")</f>
+        <v/>
+      </c>
+      <c r="AB27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 47785-2025 FSC-klagomål mail.docx", "A 47785-2025")</f>
+        <v/>
+      </c>
+      <c r="AC27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 47785-2025 tillsynsbegäran.docx", "A 47785-2025")</f>
+        <v/>
+      </c>
+      <c r="AD27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 47785-2025 tillsynsbegäran mail.docx", "A 47785-2025")</f>
+        <v/>
+      </c>
+      <c r="AE27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 47785-2025 prioriterade fågelarter.docx", "A 47785-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>A 38914-2023</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>45163</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>DEGERFORS</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
           <t>Tretåig hackspett
 Tjäder</t>
         </is>
       </c>
-      <c r="W27">
+      <c r="W28">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 38914-2023 artfynd.xlsx", "A 38914-2023")</f>
         <v/>
       </c>
-      <c r="X27">
+      <c r="X28">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 38914-2023 karta.png", "A 38914-2023")</f>
         <v/>
       </c>
-      <c r="Y27">
+      <c r="Y28">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 38914-2023 georefererad karta.tif", "A 38914-2023")</f>
         <v/>
       </c>
-      <c r="AA27">
+      <c r="AA28">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 38914-2023 FSC-klagomål.docx", "A 38914-2023")</f>
         <v/>
       </c>
-      <c r="AB27">
+      <c r="AB28">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 38914-2023 FSC-klagomål mail.docx", "A 38914-2023")</f>
         <v/>
       </c>
-      <c r="AC27">
+      <c r="AC28">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 38914-2023 tillsynsbegäran.docx", "A 38914-2023")</f>
         <v/>
       </c>
-      <c r="AD27">
+      <c r="AD28">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 38914-2023 tillsynsbegäran mail.docx", "A 38914-2023")</f>
         <v/>
       </c>
-      <c r="AE27">
+      <c r="AE28">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 38914-2023 prioriterade fågelarter.docx", "A 38914-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>A 47785-2025</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D28" s="1" t="n">
-        <v>45931</v>
-      </c>
-      <c r="E28" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>DEGERFORS</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>2</v>
-      </c>
-      <c r="J28" t="n">
-        <v>2</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2</v>
-      </c>
-      <c r="U28" t="n">
-        <v>2</v>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 47785-2025 artfynd.xlsx", "A 47785-2025")</f>
-        <v/>
-      </c>
-      <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 47785-2025 karta.png", "A 47785-2025")</f>
-        <v/>
-      </c>
-      <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 47785-2025 georefererad karta.tif", "A 47785-2025")</f>
-        <v/>
-      </c>
-      <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 47785-2025 FSC-klagomål.docx", "A 47785-2025")</f>
-        <v/>
-      </c>
-      <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 47785-2025 FSC-klagomål mail.docx", "A 47785-2025")</f>
-        <v/>
-      </c>
-      <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 47785-2025 tillsynsbegäran.docx", "A 47785-2025")</f>
-        <v/>
-      </c>
-      <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 47785-2025 tillsynsbegäran mail.docx", "A 47785-2025")</f>
-        <v/>
-      </c>
-      <c r="AE28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 47785-2025 prioriterade fågelarter.docx", "A 47785-2025")</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 40870-2024</t>
+          <t>A 38910-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3805,10 +3805,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45558</v>
+        <v>45163</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="J29" t="n">
         <v>2</v>
@@ -3835,7 +3835,7 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -3850,7 +3850,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -3859,162 +3859,162 @@
         <v>2</v>
       </c>
       <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>3</v>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>Tjäder
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 38910-2023 artfynd.xlsx", "A 38910-2023")</f>
+        <v/>
+      </c>
+      <c r="X29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 38910-2023 karta.png", "A 38910-2023")</f>
+        <v/>
+      </c>
+      <c r="Y29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 38910-2023 georefererad karta.tif", "A 38910-2023")</f>
+        <v/>
+      </c>
+      <c r="AA29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 38910-2023 FSC-klagomål.docx", "A 38910-2023")</f>
+        <v/>
+      </c>
+      <c r="AB29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 38910-2023 FSC-klagomål mail.docx", "A 38910-2023")</f>
+        <v/>
+      </c>
+      <c r="AC29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 38910-2023 tillsynsbegäran.docx", "A 38910-2023")</f>
+        <v/>
+      </c>
+      <c r="AD29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 38910-2023 tillsynsbegäran mail.docx", "A 38910-2023")</f>
+        <v/>
+      </c>
+      <c r="AE29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 38910-2023 prioriterade fågelarter.docx", "A 38910-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>A 40870-2024</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D30" s="1" t="n">
+        <v>45558</v>
+      </c>
+      <c r="E30" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>DEGERFORS</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J30" t="n">
         <v>2</v>
       </c>
-      <c r="U29" t="n">
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
         <v>2</v>
       </c>
-      <c r="V29" s="2" t="inlineStr">
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
         <is>
           <t>Tretåig hackspett
 Spillkråka</t>
         </is>
       </c>
-      <c r="W29">
+      <c r="W30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 40870-2024 artfynd.xlsx", "A 40870-2024")</f>
         <v/>
       </c>
-      <c r="X29">
+      <c r="X30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 40870-2024 karta.png", "A 40870-2024")</f>
         <v/>
       </c>
-      <c r="Y29">
+      <c r="Y30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 40870-2024 georefererad karta.tif", "A 40870-2024")</f>
         <v/>
       </c>
-      <c r="AA29">
+      <c r="AA30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 40870-2024 FSC-klagomål.docx", "A 40870-2024")</f>
         <v/>
       </c>
-      <c r="AB29">
+      <c r="AB30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 40870-2024 FSC-klagomål mail.docx", "A 40870-2024")</f>
         <v/>
       </c>
-      <c r="AC29">
+      <c r="AC30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 40870-2024 tillsynsbegäran.docx", "A 40870-2024")</f>
         <v/>
       </c>
-      <c r="AD29">
+      <c r="AD30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 40870-2024 tillsynsbegäran mail.docx", "A 40870-2024")</f>
         <v/>
       </c>
-      <c r="AE29">
+      <c r="AE30">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 40870-2024 prioriterade fågelarter.docx", "A 40870-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>A 38910-2023</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D30" s="1" t="n">
-        <v>45163</v>
-      </c>
-      <c r="E30" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>DEGERFORS</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J30" t="n">
-        <v>2</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2</v>
-      </c>
-      <c r="T30" t="n">
-        <v>3</v>
-      </c>
-      <c r="U30" t="n">
-        <v>3</v>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>Tjäder
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 38910-2023 artfynd.xlsx", "A 38910-2023")</f>
-        <v/>
-      </c>
-      <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 38910-2023 karta.png", "A 38910-2023")</f>
-        <v/>
-      </c>
-      <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 38910-2023 georefererad karta.tif", "A 38910-2023")</f>
-        <v/>
-      </c>
-      <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 38910-2023 FSC-klagomål.docx", "A 38910-2023")</f>
-        <v/>
-      </c>
-      <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 38910-2023 FSC-klagomål mail.docx", "A 38910-2023")</f>
-        <v/>
-      </c>
-      <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 38910-2023 tillsynsbegäran.docx", "A 38910-2023")</f>
-        <v/>
-      </c>
-      <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 38910-2023 tillsynsbegäran mail.docx", "A 38910-2023")</f>
-        <v/>
-      </c>
-      <c r="AE30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 38910-2023 prioriterade fågelarter.docx", "A 38910-2023")</f>
         <v/>
       </c>
     </row>
@@ -4038,7 +4038,7 @@
         <v>45163</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>46045</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>46199</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>44487</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4467,7 +4467,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 33297-2023</t>
+          <t>A 27093-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4481,10 +4481,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45116</v>
+        <v>45096</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4496,11 +4496,16 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>7.2</v>
+        <v>5.9</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -4509,7 +4514,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -4521,10 +4526,10 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4537,42 +4542,46 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 33297-2023 artfynd.xlsx", "A 33297-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 27093-2023 artfynd.xlsx", "A 27093-2023")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 33297-2023 karta.png", "A 33297-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 27093-2023 karta.png", "A 27093-2023")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 33297-2023 georefererad karta.tif", "A 33297-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 27093-2023 georefererad karta.tif", "A 27093-2023")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 33297-2023 FSC-klagomål.docx", "A 33297-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 27093-2023 FSC-klagomål.docx", "A 27093-2023")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 33297-2023 FSC-klagomål mail.docx", "A 33297-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 27093-2023 FSC-klagomål mail.docx", "A 27093-2023")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 33297-2023 tillsynsbegäran.docx", "A 33297-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 27093-2023 tillsynsbegäran.docx", "A 27093-2023")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 33297-2023 tillsynsbegäran mail.docx", "A 33297-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 27093-2023 tillsynsbegäran mail.docx", "A 27093-2023")</f>
+        <v/>
+      </c>
+      <c r="AE35">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 27093-2023 prioriterade fågelarter.docx", "A 27093-2023")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 38904-2023</t>
+          <t>A 47941-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4586,10 +4595,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45163</v>
+        <v>45589</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4607,20 +4616,20 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
         <v>1</v>
       </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
       <c r="N36" t="n">
         <v>0</v>
       </c>
@@ -4631,10 +4640,10 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4643,50 +4652,46 @@
         <v>1</v>
       </c>
       <c r="U36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Brunfläckig pärlemorfjäril</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 38904-2023 artfynd.xlsx", "A 38904-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 47941-2024 artfynd.xlsx", "A 47941-2024")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 38904-2023 karta.png", "A 38904-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 47941-2024 karta.png", "A 47941-2024")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 38904-2023 georefererad karta.tif", "A 38904-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 47941-2024 georefererad karta.tif", "A 47941-2024")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 38904-2023 FSC-klagomål.docx", "A 38904-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 47941-2024 FSC-klagomål.docx", "A 47941-2024")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 38904-2023 FSC-klagomål mail.docx", "A 38904-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 47941-2024 FSC-klagomål mail.docx", "A 47941-2024")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 38904-2023 tillsynsbegäran.docx", "A 38904-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 47941-2024 tillsynsbegäran.docx", "A 47941-2024")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 38904-2023 tillsynsbegäran mail.docx", "A 38904-2023")</f>
-        <v/>
-      </c>
-      <c r="AE36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 38904-2023 prioriterade fågelarter.docx", "A 38904-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 47941-2024 tillsynsbegäran mail.docx", "A 47941-2024")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 27093-2023</t>
+          <t>A 2357-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4700,10 +4705,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45096</v>
+        <v>44578</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4715,13 +4720,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>5.9</v>
+        <v>4.5</v>
       </c>
       <c r="J37" t="n">
         <v>1</v>
@@ -4761,46 +4761,46 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 27093-2023 artfynd.xlsx", "A 27093-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 2357-2022 artfynd.xlsx", "A 2357-2022")</f>
         <v/>
       </c>
       <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 27093-2023 karta.png", "A 27093-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 2357-2022 karta.png", "A 2357-2022")</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 27093-2023 georefererad karta.tif", "A 27093-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 2357-2022 georefererad karta.tif", "A 2357-2022")</f>
         <v/>
       </c>
       <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 27093-2023 FSC-klagomål.docx", "A 27093-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 2357-2022 FSC-klagomål.docx", "A 2357-2022")</f>
         <v/>
       </c>
       <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 27093-2023 FSC-klagomål mail.docx", "A 27093-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 2357-2022 FSC-klagomål mail.docx", "A 2357-2022")</f>
         <v/>
       </c>
       <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 27093-2023 tillsynsbegäran.docx", "A 27093-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 2357-2022 tillsynsbegäran.docx", "A 2357-2022")</f>
         <v/>
       </c>
       <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 27093-2023 tillsynsbegäran mail.docx", "A 27093-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 2357-2022 tillsynsbegäran mail.docx", "A 2357-2022")</f>
         <v/>
       </c>
       <c r="AE37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 27093-2023 prioriterade fågelarter.docx", "A 27093-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 2357-2022 prioriterade fågelarter.docx", "A 2357-2022")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 14177-2026</t>
+          <t>A 53838-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4814,10 +4814,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46099</v>
+        <v>45614</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4829,22 +4829,17 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>2.2</v>
+        <v>4.3</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -4859,7 +4854,7 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -4871,39 +4866,43 @@
         <v>1</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 14177-2026 artfynd.xlsx", "A 14177-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 53838-2024 artfynd.xlsx", "A 53838-2024")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 14177-2026 karta.png", "A 14177-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 53838-2024 karta.png", "A 53838-2024")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 14177-2026 georefererad karta.tif", "A 14177-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 53838-2024 georefererad karta.tif", "A 53838-2024")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 14177-2026 FSC-klagomål.docx", "A 14177-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 53838-2024 FSC-klagomål.docx", "A 53838-2024")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 14177-2026 FSC-klagomål mail.docx", "A 14177-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 53838-2024 FSC-klagomål mail.docx", "A 53838-2024")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 14177-2026 tillsynsbegäran.docx", "A 14177-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 53838-2024 tillsynsbegäran.docx", "A 53838-2024")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 14177-2026 tillsynsbegäran mail.docx", "A 14177-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 53838-2024 tillsynsbegäran mail.docx", "A 53838-2024")</f>
+        <v/>
+      </c>
+      <c r="AE38">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 53838-2024 prioriterade fågelarter.docx", "A 53838-2024")</f>
         <v/>
       </c>
     </row>
@@ -4927,7 +4926,7 @@
         <v>45938</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5015,7 +5014,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 48285-2023</t>
+          <t>A 47915-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5029,10 +5028,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45205</v>
+        <v>45589</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5050,7 +5049,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.1</v>
+        <v>5.8</v>
       </c>
       <c r="J40" t="n">
         <v>1</v>
@@ -5086,50 +5085,46 @@
         <v>1</v>
       </c>
       <c r="U40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 48285-2023 artfynd.xlsx", "A 48285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 47915-2024 artfynd.xlsx", "A 47915-2024")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 48285-2023 karta.png", "A 48285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 47915-2024 karta.png", "A 47915-2024")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 48285-2023 georefererad karta.tif", "A 48285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 47915-2024 georefererad karta.tif", "A 47915-2024")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 48285-2023 FSC-klagomål.docx", "A 48285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 47915-2024 FSC-klagomål.docx", "A 47915-2024")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 48285-2023 FSC-klagomål mail.docx", "A 48285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 47915-2024 FSC-klagomål mail.docx", "A 47915-2024")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 48285-2023 tillsynsbegäran.docx", "A 48285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 47915-2024 tillsynsbegäran.docx", "A 47915-2024")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 48285-2023 tillsynsbegäran mail.docx", "A 48285-2023")</f>
-        <v/>
-      </c>
-      <c r="AE40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 48285-2023 prioriterade fågelarter.docx", "A 48285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 47915-2024 tillsynsbegäran mail.docx", "A 47915-2024")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 47787-2025</t>
+          <t>A 33297-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5143,10 +5138,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45931</v>
+        <v>45116</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5159,19 +5154,19 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>4.1</v>
+        <v>7.2</v>
       </c>
       <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
         <v>1</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" t="n">
-        <v>1</v>
-      </c>
-      <c r="M41" t="n">
-        <v>0</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -5186,59 +5181,55 @@
         <v>1</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
       </c>
       <c r="T41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 47787-2025 artfynd.xlsx", "A 47787-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 33297-2023 artfynd.xlsx", "A 33297-2023")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 47787-2025 karta.png", "A 47787-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 33297-2023 karta.png", "A 33297-2023")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 47787-2025 georefererad karta.tif", "A 47787-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 33297-2023 georefererad karta.tif", "A 33297-2023")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 47787-2025 FSC-klagomål.docx", "A 47787-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 33297-2023 FSC-klagomål.docx", "A 33297-2023")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 47787-2025 FSC-klagomål mail.docx", "A 47787-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 33297-2023 FSC-klagomål mail.docx", "A 33297-2023")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 47787-2025 tillsynsbegäran.docx", "A 47787-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 33297-2023 tillsynsbegäran.docx", "A 33297-2023")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 47787-2025 tillsynsbegäran mail.docx", "A 47787-2025")</f>
-        <v/>
-      </c>
-      <c r="AE41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 47787-2025 prioriterade fågelarter.docx", "A 47787-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 33297-2023 tillsynsbegäran mail.docx", "A 33297-2023")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 38907-2023</t>
+          <t>A 47787-2025</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5252,10 +5243,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45163</v>
+        <v>45931</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5267,13 +5258,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>2.9</v>
+        <v>4.1</v>
       </c>
       <c r="J42" t="n">
         <v>1</v>
@@ -5282,7 +5268,7 @@
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -5297,7 +5283,7 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -5306,53 +5292,53 @@
         <v>1</v>
       </c>
       <c r="T42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 38907-2023 artfynd.xlsx", "A 38907-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 47787-2025 artfynd.xlsx", "A 47787-2025")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 38907-2023 karta.png", "A 38907-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 47787-2025 karta.png", "A 47787-2025")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 38907-2023 georefererad karta.tif", "A 38907-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 47787-2025 georefererad karta.tif", "A 47787-2025")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 38907-2023 FSC-klagomål.docx", "A 38907-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 47787-2025 FSC-klagomål.docx", "A 47787-2025")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 38907-2023 FSC-klagomål mail.docx", "A 38907-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 47787-2025 FSC-klagomål mail.docx", "A 47787-2025")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 38907-2023 tillsynsbegäran.docx", "A 38907-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 47787-2025 tillsynsbegäran.docx", "A 47787-2025")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 38907-2023 tillsynsbegäran mail.docx", "A 38907-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 47787-2025 tillsynsbegäran mail.docx", "A 47787-2025")</f>
         <v/>
       </c>
       <c r="AE42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 38907-2023 prioriterade fågelarter.docx", "A 38907-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 47787-2025 prioriterade fågelarter.docx", "A 47787-2025")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 47941-2024</t>
+          <t>A 38904-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5366,10 +5352,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45589</v>
+        <v>45163</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5387,10 +5373,10 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -5399,7 +5385,7 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
@@ -5411,10 +5397,10 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -5423,46 +5409,50 @@
         <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Brunfläckig pärlemorfjäril</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 47941-2024 artfynd.xlsx", "A 47941-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 38904-2023 artfynd.xlsx", "A 38904-2023")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 47941-2024 karta.png", "A 47941-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 38904-2023 karta.png", "A 38904-2023")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 47941-2024 georefererad karta.tif", "A 47941-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 38904-2023 georefererad karta.tif", "A 38904-2023")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 47941-2024 FSC-klagomål.docx", "A 47941-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 38904-2023 FSC-klagomål.docx", "A 38904-2023")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 47941-2024 FSC-klagomål mail.docx", "A 47941-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 38904-2023 FSC-klagomål mail.docx", "A 38904-2023")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 47941-2024 tillsynsbegäran.docx", "A 47941-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 38904-2023 tillsynsbegäran.docx", "A 38904-2023")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 47941-2024 tillsynsbegäran mail.docx", "A 47941-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 38904-2023 tillsynsbegäran mail.docx", "A 38904-2023")</f>
+        <v/>
+      </c>
+      <c r="AE43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 38904-2023 prioriterade fågelarter.docx", "A 38904-2023")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 14121-2022</t>
+          <t>A 48285-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5476,10 +5466,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44651</v>
+        <v>45205</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5491,8 +5481,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>4.4</v>
+        <v>1.1</v>
       </c>
       <c r="J44" t="n">
         <v>1</v>
@@ -5532,42 +5527,46 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Hårklomossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 14121-2022 artfynd.xlsx", "A 14121-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 48285-2023 artfynd.xlsx", "A 48285-2023")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 14121-2022 karta.png", "A 14121-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 48285-2023 karta.png", "A 48285-2023")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 14121-2022 georefererad karta.tif", "A 14121-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 48285-2023 georefererad karta.tif", "A 48285-2023")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 14121-2022 FSC-klagomål.docx", "A 14121-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 48285-2023 FSC-klagomål.docx", "A 48285-2023")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 14121-2022 FSC-klagomål mail.docx", "A 14121-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 48285-2023 FSC-klagomål mail.docx", "A 48285-2023")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 14121-2022 tillsynsbegäran.docx", "A 14121-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 48285-2023 tillsynsbegäran.docx", "A 48285-2023")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 14121-2022 tillsynsbegäran mail.docx", "A 14121-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 48285-2023 tillsynsbegäran mail.docx", "A 48285-2023")</f>
+        <v/>
+      </c>
+      <c r="AE44">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 48285-2023 prioriterade fågelarter.docx", "A 48285-2023")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 47915-2024</t>
+          <t>A 14177-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5581,10 +5580,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45589</v>
+        <v>46099</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5602,17 +5601,17 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>5.8</v>
+        <v>2.2</v>
       </c>
       <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
         <v>1</v>
       </c>
-      <c r="K45" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" t="n">
-        <v>0</v>
-      </c>
       <c r="M45" t="n">
         <v>0</v>
       </c>
@@ -5626,7 +5625,7 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
@@ -5642,42 +5641,42 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 47915-2024 artfynd.xlsx", "A 47915-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 14177-2026 artfynd.xlsx", "A 14177-2026")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 47915-2024 karta.png", "A 47915-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 14177-2026 karta.png", "A 14177-2026")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 47915-2024 georefererad karta.tif", "A 47915-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 14177-2026 georefererad karta.tif", "A 14177-2026")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 47915-2024 FSC-klagomål.docx", "A 47915-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 14177-2026 FSC-klagomål.docx", "A 14177-2026")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 47915-2024 FSC-klagomål mail.docx", "A 47915-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 14177-2026 FSC-klagomål mail.docx", "A 14177-2026")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 47915-2024 tillsynsbegäran.docx", "A 47915-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 14177-2026 tillsynsbegäran.docx", "A 14177-2026")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 47915-2024 tillsynsbegäran mail.docx", "A 47915-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 14177-2026 tillsynsbegäran mail.docx", "A 14177-2026")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 27071-2026</t>
+          <t>A 38907-2023</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5691,10 +5690,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46186</v>
+        <v>45163</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5712,13 +5711,13 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>9.9</v>
+        <v>2.9</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -5748,46 +5747,50 @@
         <v>1</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 27071-2026 artfynd.xlsx", "A 27071-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 38907-2023 artfynd.xlsx", "A 38907-2023")</f>
         <v/>
       </c>
       <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 27071-2026 karta.png", "A 27071-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 38907-2023 karta.png", "A 38907-2023")</f>
         <v/>
       </c>
       <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 27071-2026 georefererad karta.tif", "A 27071-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 38907-2023 georefererad karta.tif", "A 38907-2023")</f>
         <v/>
       </c>
       <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 27071-2026 FSC-klagomål.docx", "A 27071-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 38907-2023 FSC-klagomål.docx", "A 38907-2023")</f>
         <v/>
       </c>
       <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 27071-2026 FSC-klagomål mail.docx", "A 27071-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 38907-2023 FSC-klagomål mail.docx", "A 38907-2023")</f>
         <v/>
       </c>
       <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 27071-2026 tillsynsbegäran.docx", "A 27071-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 38907-2023 tillsynsbegäran.docx", "A 38907-2023")</f>
         <v/>
       </c>
       <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 27071-2026 tillsynsbegäran mail.docx", "A 27071-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 38907-2023 tillsynsbegäran mail.docx", "A 38907-2023")</f>
+        <v/>
+      </c>
+      <c r="AE46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 38907-2023 prioriterade fågelarter.docx", "A 38907-2023")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 27072-2026</t>
+          <t>A 14121-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5801,10 +5804,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46186</v>
+        <v>44651</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5816,13 +5819,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>7.6</v>
+        <v>4.4</v>
       </c>
       <c r="J47" t="n">
         <v>1</v>
@@ -5862,46 +5860,42 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Hårklomossa</t>
         </is>
       </c>
       <c r="W47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 27072-2026 artfynd.xlsx", "A 27072-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 14121-2022 artfynd.xlsx", "A 14121-2022")</f>
         <v/>
       </c>
       <c r="X47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 27072-2026 karta.png", "A 27072-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 14121-2022 karta.png", "A 14121-2022")</f>
         <v/>
       </c>
       <c r="Y47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 27072-2026 georefererad karta.tif", "A 27072-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 14121-2022 georefererad karta.tif", "A 14121-2022")</f>
         <v/>
       </c>
       <c r="AA47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 27072-2026 FSC-klagomål.docx", "A 27072-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 14121-2022 FSC-klagomål.docx", "A 14121-2022")</f>
         <v/>
       </c>
       <c r="AB47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 27072-2026 FSC-klagomål mail.docx", "A 27072-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 14121-2022 FSC-klagomål mail.docx", "A 14121-2022")</f>
         <v/>
       </c>
       <c r="AC47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 27072-2026 tillsynsbegäran.docx", "A 27072-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 14121-2022 tillsynsbegäran.docx", "A 14121-2022")</f>
         <v/>
       </c>
       <c r="AD47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 27072-2026 tillsynsbegäran mail.docx", "A 27072-2026")</f>
-        <v/>
-      </c>
-      <c r="AE47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 27072-2026 prioriterade fågelarter.docx", "A 27072-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 14121-2022 tillsynsbegäran mail.docx", "A 14121-2022")</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 26971-2026</t>
+          <t>A 27071-2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5915,10 +5909,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46185</v>
+        <v>46186</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5930,8 +5924,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>2.1</v>
+        <v>9.9</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -5971,42 +5970,42 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="W48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 26971-2026 artfynd.xlsx", "A 26971-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 27071-2026 artfynd.xlsx", "A 27071-2026")</f>
         <v/>
       </c>
       <c r="X48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 26971-2026 karta.png", "A 26971-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 27071-2026 karta.png", "A 27071-2026")</f>
         <v/>
       </c>
       <c r="Y48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 26971-2026 georefererad karta.tif", "A 26971-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 27071-2026 georefererad karta.tif", "A 27071-2026")</f>
         <v/>
       </c>
       <c r="AA48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 26971-2026 FSC-klagomål.docx", "A 26971-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 27071-2026 FSC-klagomål.docx", "A 27071-2026")</f>
         <v/>
       </c>
       <c r="AB48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 26971-2026 FSC-klagomål mail.docx", "A 26971-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 27071-2026 FSC-klagomål mail.docx", "A 27071-2026")</f>
         <v/>
       </c>
       <c r="AC48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 26971-2026 tillsynsbegäran.docx", "A 26971-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 27071-2026 tillsynsbegäran.docx", "A 27071-2026")</f>
         <v/>
       </c>
       <c r="AD48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 26971-2026 tillsynsbegäran mail.docx", "A 26971-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 27071-2026 tillsynsbegäran mail.docx", "A 27071-2026")</f>
         <v/>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 53838-2024</t>
+          <t>A 27072-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6020,10 +6019,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45614</v>
+        <v>46186</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6035,8 +6034,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>4.3</v>
+        <v>7.6</v>
       </c>
       <c r="J49" t="n">
         <v>1</v>
@@ -6080,42 +6084,42 @@
         </is>
       </c>
       <c r="W49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 53838-2024 artfynd.xlsx", "A 53838-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 27072-2026 artfynd.xlsx", "A 27072-2026")</f>
         <v/>
       </c>
       <c r="X49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 53838-2024 karta.png", "A 53838-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 27072-2026 karta.png", "A 27072-2026")</f>
         <v/>
       </c>
       <c r="Y49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 53838-2024 georefererad karta.tif", "A 53838-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 27072-2026 georefererad karta.tif", "A 27072-2026")</f>
         <v/>
       </c>
       <c r="AA49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 53838-2024 FSC-klagomål.docx", "A 53838-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 27072-2026 FSC-klagomål.docx", "A 27072-2026")</f>
         <v/>
       </c>
       <c r="AB49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 53838-2024 FSC-klagomål mail.docx", "A 53838-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 27072-2026 FSC-klagomål mail.docx", "A 27072-2026")</f>
         <v/>
       </c>
       <c r="AC49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 53838-2024 tillsynsbegäran.docx", "A 53838-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 27072-2026 tillsynsbegäran.docx", "A 27072-2026")</f>
         <v/>
       </c>
       <c r="AD49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 53838-2024 tillsynsbegäran mail.docx", "A 53838-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 27072-2026 tillsynsbegäran mail.docx", "A 27072-2026")</f>
         <v/>
       </c>
       <c r="AE49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 53838-2024 prioriterade fågelarter.docx", "A 53838-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 27072-2026 prioriterade fågelarter.docx", "A 27072-2026")</f>
         <v/>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 2357-2022</t>
+          <t>A 26971-2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6129,10 +6133,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>44578</v>
+        <v>46185</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6145,13 +6149,13 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>4.5</v>
+        <v>2.1</v>
       </c>
       <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="n">
         <v>1</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
@@ -6181,43 +6185,39 @@
         <v>1</v>
       </c>
       <c r="U50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="W50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 2357-2022 artfynd.xlsx", "A 2357-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 26971-2026 artfynd.xlsx", "A 26971-2026")</f>
         <v/>
       </c>
       <c r="X50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 2357-2022 karta.png", "A 2357-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 26971-2026 karta.png", "A 26971-2026")</f>
         <v/>
       </c>
       <c r="Y50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 2357-2022 georefererad karta.tif", "A 2357-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 26971-2026 georefererad karta.tif", "A 26971-2026")</f>
         <v/>
       </c>
       <c r="AA50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 2357-2022 FSC-klagomål.docx", "A 2357-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 26971-2026 FSC-klagomål.docx", "A 26971-2026")</f>
         <v/>
       </c>
       <c r="AB50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 2357-2022 FSC-klagomål mail.docx", "A 2357-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 26971-2026 FSC-klagomål mail.docx", "A 26971-2026")</f>
         <v/>
       </c>
       <c r="AC50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 2357-2022 tillsynsbegäran.docx", "A 2357-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 26971-2026 tillsynsbegäran.docx", "A 26971-2026")</f>
         <v/>
       </c>
       <c r="AD50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 2357-2022 tillsynsbegäran mail.docx", "A 2357-2022")</f>
-        <v/>
-      </c>
-      <c r="AE50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 2357-2022 prioriterade fågelarter.docx", "A 2357-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 26971-2026 tillsynsbegäran mail.docx", "A 26971-2026")</f>
         <v/>
       </c>
     </row>
@@ -6241,7 +6241,7 @@
         <v>44805</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6314,7 +6314,7 @@
         <v>44805</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6387,7 +6387,7 @@
         <v>44861</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6460,7 +6460,7 @@
         <v>44607</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>44692</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6611,7 +6611,7 @@
         <v>44609</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6667,7 +6667,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 60889-2021</t>
+          <t>A 5319-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6681,10 +6681,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44497</v>
+        <v>44594</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 5319-2022</t>
+          <t>A 47569-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6754,10 +6754,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44594</v>
+        <v>44853</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6770,7 +6770,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6813,7 +6813,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 47569-2022</t>
+          <t>A 12977-2022</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6827,10 +6827,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44853</v>
+        <v>44643</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6843,7 +6843,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6886,7 +6886,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 65456-2021</t>
+          <t>A 60889-2021</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6900,10 +6900,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44515</v>
+        <v>44497</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6916,7 +6916,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6959,7 +6959,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 12977-2022</t>
+          <t>A 68578-2021</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6973,10 +6973,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44643</v>
+        <v>44529</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6988,8 +6988,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -7032,7 +7037,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 68578-2021</t>
+          <t>A 67998-2021</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -7046,10 +7051,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44529</v>
+        <v>44525</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7061,13 +7066,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -7110,7 +7110,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 67998-2021</t>
+          <t>A 65456-2021</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -7124,10 +7124,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44525</v>
+        <v>44515</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>2.9</v>
+        <v>0.8</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -7200,7 +7200,7 @@
         <v>44509</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7261,7 +7261,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 63008-2021</t>
+          <t>A 6394-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7271,14 +7271,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44505</v>
+        <v>45338</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7296,7 +7296,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -7339,7 +7339,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 7975-2025</t>
+          <t>A 63008-2021</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7353,10 +7353,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45707</v>
+        <v>44505</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>5.3</v>
+        <v>1.5</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -7434,7 +7434,7 @@
         <v>45763</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7490,7 +7490,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 29607-2022</t>
+          <t>A 13236-2025</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7504,10 +7504,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44754</v>
+        <v>45735</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7525,7 +7525,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.1</v>
+        <v>18.5</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7568,7 +7568,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 37672-2024</t>
+          <t>A 38743-2022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7578,14 +7578,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45541</v>
+        <v>44816</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7646,7 +7646,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 56478-2024</t>
+          <t>A 11084-2023</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7660,10 +7660,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45624</v>
+        <v>44986</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7676,7 +7676,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7719,7 +7719,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 8062-2024</t>
+          <t>A 56478-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7733,10 +7733,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45351</v>
+        <v>45624</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7748,13 +7748,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I71" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7797,7 +7792,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 10321-2023</t>
+          <t>A 13405-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7811,10 +7806,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44986</v>
+        <v>45387</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7827,7 +7822,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7870,7 +7865,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 36437-2024</t>
+          <t>A 26176-2024</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7884,10 +7879,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45535</v>
+        <v>45468</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7899,8 +7894,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I73" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7943,7 +7943,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 38921-2023</t>
+          <t>A 8059-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7957,10 +7957,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45163</v>
+        <v>45351</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -8021,7 +8021,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 2565-2022</t>
+          <t>A 45861-2023</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -8031,14 +8031,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44579</v>
+        <v>45195</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8050,8 +8050,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -8094,7 +8099,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 12159-2026</t>
+          <t>A 60933-2024</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -8108,10 +8113,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46086</v>
+        <v>45645</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8129,7 +8134,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -8172,7 +8177,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 12160-2026</t>
+          <t>A 61750-2021</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8186,10 +8191,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>46086</v>
+        <v>44501</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8207,7 +8212,7 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -8250,7 +8255,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 60907-2023</t>
+          <t>A 54515-2023</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8260,14 +8265,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45261</v>
+        <v>45233</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8279,13 +8284,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I78" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -8328,7 +8328,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 38874-2025</t>
+          <t>A 38738-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -8342,10 +8342,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45887</v>
+        <v>44816</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8363,7 +8363,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>8.300000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -8406,7 +8406,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 33404-2025</t>
+          <t>A 38874-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8420,10 +8420,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45841</v>
+        <v>45887</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8435,8 +8435,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I80" t="n">
-        <v>1.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8479,7 +8484,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 26176-2024</t>
+          <t>A 3177-2022</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8493,10 +8498,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45468</v>
+        <v>44582</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8508,13 +8513,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>0.7</v>
+        <v>3.7</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8557,7 +8557,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 59863-2024</t>
+          <t>A 38875-2025</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8571,10 +8571,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45639</v>
+        <v>45887</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8586,8 +8586,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I82" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8630,7 +8635,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 3177-2022</t>
+          <t>A 50378-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8644,10 +8649,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44582</v>
+        <v>45601</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8659,8 +8664,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>3.7</v>
+        <v>4.9</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8703,7 +8713,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 50766-2024</t>
+          <t>A 29607-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8717,10 +8727,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45602</v>
+        <v>44754</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8781,7 +8791,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 8184-2022</t>
+          <t>A 6240-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8795,10 +8805,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44609</v>
+        <v>45337</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8811,7 +8821,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8854,7 +8864,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 52523-2024</t>
+          <t>A 12729-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8868,10 +8878,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45609</v>
+        <v>45384</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8889,7 +8899,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>4.4</v>
+        <v>2.5</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8932,7 +8942,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 12936-2026</t>
+          <t>A 10320-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8946,10 +8956,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>46092</v>
+        <v>44986</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8961,13 +8971,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I87" t="n">
-        <v>8.800000000000001</v>
+        <v>2.6</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -9010,7 +9015,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 13293-2026</t>
+          <t>A 41766-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -9024,10 +9029,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>46094</v>
+        <v>45902</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9045,7 +9050,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1.1</v>
+        <v>3.2</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -9088,7 +9093,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 37333-2025</t>
+          <t>A 41767-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -9098,14 +9103,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45876</v>
+        <v>45902</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9117,8 +9122,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -9161,7 +9171,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 37265-2025</t>
+          <t>A 7472-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -9175,10 +9185,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45876</v>
+        <v>45705</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9190,8 +9200,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I90" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -9234,7 +9249,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 13040-2026</t>
+          <t>A 10321-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -9248,10 +9263,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46093</v>
+        <v>44986</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9263,13 +9278,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I91" t="n">
-        <v>7.1</v>
+        <v>1.3</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -9312,7 +9322,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 54515-2023</t>
+          <t>A 7975-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -9326,10 +9336,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45233</v>
+        <v>45707</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9341,8 +9351,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I92" t="n">
-        <v>1</v>
+        <v>5.3</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -9385,7 +9400,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 15594-2025</t>
+          <t>A 57234-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -9399,10 +9414,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45747</v>
+        <v>45629</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9414,8 +9429,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I93" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -9458,7 +9478,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 41767-2025</t>
+          <t>A 18831-2025</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -9472,10 +9492,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45902</v>
+        <v>45764</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9493,7 +9513,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.1</v>
+        <v>4.2</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -9536,7 +9556,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 41766-2025</t>
+          <t>A 33658-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9550,10 +9570,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45902</v>
+        <v>45520</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9565,13 +9585,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I95" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -9614,7 +9629,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 13039-2026</t>
+          <t>A 38233-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9624,14 +9639,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>46093</v>
+        <v>45160</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9643,13 +9658,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I96" t="n">
-        <v>5.1</v>
+        <v>0.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9692,7 +9702,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 54994-2024</t>
+          <t>A 6387-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9702,14 +9712,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45621</v>
+        <v>45338</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9727,7 +9737,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9770,7 +9780,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 43694-2025</t>
+          <t>A 43691-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9787,7 +9797,7 @@
         <v>45912</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9805,7 +9815,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>6.6</v>
+        <v>2.7</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9848,7 +9858,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 43691-2025</t>
+          <t>A 43689-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9865,7 +9875,7 @@
         <v>45912</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9883,7 +9893,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.7</v>
+        <v>1.4</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9926,7 +9936,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 38875-2025</t>
+          <t>A 43694-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9940,10 +9950,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45887</v>
+        <v>45912</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9961,7 +9971,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1.9</v>
+        <v>6.6</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -10004,7 +10014,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 43689-2025</t>
+          <t>A 58629-2024</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -10018,10 +10028,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45912</v>
+        <v>45635</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10082,7 +10092,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 13236-2025</t>
+          <t>A 27438-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -10096,10 +10106,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45735</v>
+        <v>45474</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10111,13 +10121,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>18.5</v>
+        <v>2.6</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -10160,7 +10165,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 38233-2023</t>
+          <t>A 50102-2023</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -10170,14 +10175,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45160</v>
+        <v>45215</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10189,8 +10194,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I103" t="n">
-        <v>0.6</v>
+        <v>3.9</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -10233,7 +10243,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 10674-2024</t>
+          <t>A 50766-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -10243,14 +10253,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45369</v>
+        <v>45602</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10268,7 +10278,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.3</v>
+        <v>2.1</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -10311,7 +10321,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 60933-2024</t>
+          <t>A 59158-2022</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -10321,14 +10331,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45645</v>
+        <v>44904</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10346,7 +10356,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>1.9</v>
+        <v>3.7</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -10389,7 +10399,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 73693-2021</t>
+          <t>A 51996-2023</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -10403,10 +10413,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>44552</v>
+        <v>45223</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10418,8 +10428,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I106" t="n">
-        <v>3.6</v>
+        <v>2</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -10462,7 +10477,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 48625-2025</t>
+          <t>A 62982-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -10476,10 +10491,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45936</v>
+        <v>45272</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10492,7 +10507,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -10535,7 +10550,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 60937-2024</t>
+          <t>A 46288-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10549,10 +10564,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45645</v>
+        <v>45581</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10570,7 +10585,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0.6</v>
+        <v>3.7</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -10613,7 +10628,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 60940-2024</t>
+          <t>A 5277-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10627,10 +10642,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45645</v>
+        <v>45330</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10642,13 +10657,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I109" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -10691,7 +10701,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 52566-2023</t>
+          <t>A 50207-2024</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10705,10 +10715,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45219</v>
+        <v>45600</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10721,7 +10731,7 @@
         </is>
       </c>
       <c r="I110" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10764,7 +10774,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 51040-2025</t>
+          <t>A 50208-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10778,10 +10788,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45947</v>
+        <v>45600</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10793,13 +10803,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I111" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10842,7 +10847,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 57234-2024</t>
+          <t>A 21935-2024</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10856,10 +10861,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45629</v>
+        <v>45443</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10877,7 +10882,7 @@
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10920,7 +10925,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 52099-2025</t>
+          <t>A 43768-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10934,10 +10939,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45952</v>
+        <v>45569</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10950,7 +10955,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>2.6</v>
+        <v>7</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10993,7 +10998,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 18913-2026</t>
+          <t>A 23460-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -11007,10 +11012,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>46129</v>
+        <v>45453</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11022,13 +11027,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I114" t="n">
-        <v>8.300000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -11071,7 +11071,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 55341-2025</t>
+          <t>A 5218-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -11085,10 +11085,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45971</v>
+        <v>45330</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11106,7 +11106,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -11149,7 +11149,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 8074-2024</t>
+          <t>A 24707-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -11163,10 +11163,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45351</v>
+        <v>45798</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11178,13 +11178,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I116" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -11227,7 +11222,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 18506-2026</t>
+          <t>A 48625-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -11241,10 +11236,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46127</v>
+        <v>45936</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11300,7 +11295,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 57086-2025</t>
+          <t>A 47935-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -11310,14 +11305,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45979</v>
+        <v>45589</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11329,8 +11324,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I118" t="n">
-        <v>6.1</v>
+        <v>2.2</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -11373,7 +11373,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 19227-2026</t>
+          <t>A 21952-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -11383,14 +11383,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46132</v>
+        <v>45443</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11402,8 +11402,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I119" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -11446,7 +11451,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 21952-2024</t>
+          <t>A 12143-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -11460,10 +11465,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45443</v>
+        <v>45729</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11481,7 +11486,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -11524,7 +11529,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 62972-2023</t>
+          <t>A 52566-2023</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -11538,10 +11543,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45272</v>
+        <v>45219</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11554,7 +11559,7 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -11597,7 +11602,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 12143-2025</t>
+          <t>A 52523-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -11607,14 +11612,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45729</v>
+        <v>45609</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11632,7 +11637,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.3</v>
+        <v>4.4</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -11675,7 +11680,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 51653-2023</t>
+          <t>A 8184-2022</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11689,10 +11694,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45222</v>
+        <v>44609</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11704,13 +11709,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I123" t="n">
-        <v>3.9</v>
+        <v>1.7</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -11753,7 +11753,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 60736-2025</t>
+          <t>A 26783-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11767,10 +11767,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45996</v>
+        <v>45810</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11783,7 +11783,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>5.8</v>
+        <v>2.5</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -11826,7 +11826,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 60708-2025</t>
+          <t>A 60937-2024</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11840,10 +11840,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45996</v>
+        <v>45645</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11855,8 +11855,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I125" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11899,7 +11904,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 38917-2023</t>
+          <t>A 60940-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11913,10 +11918,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45163</v>
+        <v>45645</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11934,7 +11939,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>2.2</v>
+        <v>1.2</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11977,7 +11982,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 20577-2023</t>
+          <t>A 62972-2023</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11987,14 +11992,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45057</v>
+        <v>45272</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12006,13 +12011,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I127" t="n">
-        <v>1.8</v>
+        <v>0.3</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -12055,7 +12055,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 48118-2023</t>
+          <t>A 26820-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -12069,10 +12069,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45205</v>
+        <v>45810</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12084,13 +12084,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I128" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -12133,7 +12128,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 45365-2023</t>
+          <t>A 50377-2024</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -12147,10 +12142,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45192</v>
+        <v>45601</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12162,8 +12157,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I129" t="n">
-        <v>5</v>
+        <v>0.7</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -12206,7 +12206,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 6387-2024</t>
+          <t>A 51040-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -12216,14 +12216,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45338</v>
+        <v>45947</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12241,7 +12241,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -12284,7 +12284,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 770-2026</t>
+          <t>A 28367-2025</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -12298,10 +12298,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46027</v>
+        <v>45819</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12313,8 +12313,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I131" t="n">
-        <v>2.2</v>
+        <v>6.1</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -12357,7 +12362,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 6240-2024</t>
+          <t>A 28368-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -12371,10 +12376,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45337</v>
+        <v>45819</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12386,8 +12391,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I132" t="n">
-        <v>1.9</v>
+        <v>8.1</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -12430,7 +12440,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 54082-2024</t>
+          <t>A 44807-2023</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -12444,10 +12454,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45616</v>
+        <v>45190</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12459,8 +12469,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I133" t="n">
-        <v>6.3</v>
+        <v>5.4</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -12503,7 +12518,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 6394-2024</t>
+          <t>A 23066-2022</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -12513,14 +12528,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45338</v>
+        <v>44719</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12532,13 +12547,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I134" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -12581,7 +12591,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 43752-2025</t>
+          <t>A 51652-2023</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -12595,10 +12605,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45912</v>
+        <v>45222</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12610,8 +12620,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I135" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -12654,7 +12669,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 11085-2023</t>
+          <t>A 52099-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12668,10 +12683,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44986</v>
+        <v>45952</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12684,7 +12699,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>0.8</v>
+        <v>2.6</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -12727,7 +12742,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 20567-2026</t>
+          <t>A 11085-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12741,10 +12756,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46140</v>
+        <v>44986</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12756,13 +12771,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I137" t="n">
-        <v>7.8</v>
+        <v>0.8</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -12805,7 +12815,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 20568-2026</t>
+          <t>A 33293-2023</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12819,10 +12829,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46140</v>
+        <v>45116</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12834,13 +12844,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I138" t="n">
-        <v>6.3</v>
+        <v>17.2</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -12883,7 +12888,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 20478-2026</t>
+          <t>A 50764-2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12897,10 +12902,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46140</v>
+        <v>45602</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12918,7 +12923,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12961,7 +12966,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 5277-2024</t>
+          <t>A 32154-2023</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12975,10 +12980,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45330</v>
+        <v>45119</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12991,7 +12996,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -13034,7 +13039,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 50378-2024</t>
+          <t>A 33404-2025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -13048,10 +13053,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45601</v>
+        <v>45841</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13063,13 +13068,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I141" t="n">
-        <v>4.9</v>
+        <v>1.5</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -13112,7 +13112,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 33293-2023</t>
+          <t>A 55341-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -13126,10 +13126,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45116</v>
+        <v>45971</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13141,8 +13141,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I142" t="n">
-        <v>17.2</v>
+        <v>3.4</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -13185,7 +13190,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 44807-2023</t>
+          <t>A 38921-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -13199,10 +13204,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45190</v>
+        <v>45163</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13220,7 +13225,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>5.4</v>
+        <v>2.2</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -13263,7 +13268,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 51652-2023</t>
+          <t>A 59863-2024</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -13277,10 +13282,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>45222</v>
+        <v>45639</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13292,13 +13297,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I144" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -13341,7 +13341,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 9273-2026</t>
+          <t>A 8062-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -13355,10 +13355,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>46070</v>
+        <v>45351</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13370,8 +13370,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I145" t="n">
-        <v>2.3</v>
+        <v>0.8</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -13414,7 +13419,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 44457-2022</t>
+          <t>A 8074-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -13428,10 +13433,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>44839</v>
+        <v>45351</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13443,8 +13448,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I146" t="n">
-        <v>6.8</v>
+        <v>0.7</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -13487,7 +13497,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 21440-2026</t>
+          <t>A 60907-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -13497,14 +13507,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46148</v>
+        <v>45261</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13522,7 +13532,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>6.5</v>
+        <v>0.6</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -13565,7 +13575,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 32211-2022</t>
+          <t>A 63905-2021</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -13579,10 +13589,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>44781</v>
+        <v>44509</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13594,8 +13604,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I148" t="n">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -13638,7 +13653,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 21402-2026</t>
+          <t>A 57086-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -13648,14 +13663,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>46148</v>
+        <v>45979</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13668,7 +13683,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>1.4</v>
+        <v>6.1</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -13711,7 +13726,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 13405-2024</t>
+          <t>A 37333-2025</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -13721,14 +13736,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45387</v>
+        <v>45876</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13741,7 +13756,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -13784,7 +13799,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 21442-2026</t>
+          <t>A 37265-2025</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -13798,10 +13813,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46148</v>
+        <v>45876</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13813,13 +13828,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I151" t="n">
-        <v>4.1</v>
+        <v>1.3</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -13862,7 +13872,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 21401-2026</t>
+          <t>A 32211-2022</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13876,10 +13886,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46148</v>
+        <v>44781</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13892,7 +13902,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -13935,7 +13945,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 12729-2024</t>
+          <t>A 15594-2025</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13949,10 +13959,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45384</v>
+        <v>45747</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13964,13 +13974,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I153" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -14013,7 +14018,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 44841-2023</t>
+          <t>A 13293-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -14027,10 +14032,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45190</v>
+        <v>46094</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14048,7 +14053,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -14091,7 +14096,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 46222-2024</t>
+          <t>A 20577-2023</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -14101,14 +14106,14 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45581</v>
+        <v>45057</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14126,7 +14131,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -14169,7 +14174,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 46219-2024</t>
+          <t>A 10797-2023</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -14183,10 +14188,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45581</v>
+        <v>44989</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14198,13 +14203,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I156" t="n">
-        <v>2.4</v>
+        <v>9.5</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -14247,7 +14247,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 23230-2026</t>
+          <t>A 44457-2022</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -14261,10 +14261,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46162</v>
+        <v>44839</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14276,13 +14276,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I157" t="n">
-        <v>0.9</v>
+        <v>6.8</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -14325,7 +14320,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 23229-2026</t>
+          <t>A 29482-2023</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -14339,10 +14334,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46162</v>
+        <v>45106</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14354,13 +14349,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I158" t="n">
-        <v>2.9</v>
+        <v>0.7</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -14403,7 +14393,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 14678-2025</t>
+          <t>A 73693-2021</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -14413,14 +14403,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45742</v>
+        <v>44552</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14432,13 +14422,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I159" t="n">
-        <v>1.9</v>
+        <v>3.6</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -14481,7 +14466,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 23854-2026</t>
+          <t>A 18506-2026</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -14495,10 +14480,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46167</v>
+        <v>46127</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14510,13 +14495,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I160" t="n">
-        <v>20.9</v>
+        <v>1.6</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -14559,7 +14539,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 24460-2026</t>
+          <t>A 60708-2025</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -14573,10 +14553,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46170</v>
+        <v>45996</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14589,7 +14569,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1.1</v>
+        <v>1.9</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -14632,7 +14612,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 24462-2026</t>
+          <t>A 60736-2025</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -14646,10 +14626,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46170</v>
+        <v>45996</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14662,7 +14642,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>0.8</v>
+        <v>5.8</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -14705,7 +14685,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 24689-2026</t>
+          <t>A 36437-2024</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -14719,10 +14699,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46171</v>
+        <v>45535</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14734,13 +14714,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I163" t="n">
-        <v>15.5</v>
+        <v>2.3</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -14783,7 +14758,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 63905-2021</t>
+          <t>A 19227-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -14797,10 +14772,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>44509</v>
+        <v>46132</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14812,13 +14787,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I164" t="n">
-        <v>3.7</v>
+        <v>2.4</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -14861,7 +14831,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 38743-2022</t>
+          <t>A 18913-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -14875,10 +14845,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>44816</v>
+        <v>46129</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14896,7 +14866,7 @@
         </is>
       </c>
       <c r="I165" t="n">
-        <v>1.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -14939,7 +14909,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 47935-2024</t>
+          <t>A 48118-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -14953,10 +14923,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45589</v>
+        <v>45205</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14974,7 +14944,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -15017,7 +14987,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 50377-2024</t>
+          <t>A 38917-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -15031,10 +15001,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45601</v>
+        <v>45163</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15052,7 +15022,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -15095,7 +15065,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 8059-2024</t>
+          <t>A 45365-2023</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -15109,10 +15079,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45351</v>
+        <v>45192</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15124,13 +15094,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I168" t="n">
-        <v>1.6</v>
+        <v>5</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -15173,7 +15138,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 26857-2026</t>
+          <t>A 37672-2024</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -15183,14 +15148,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46185</v>
+        <v>45541</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15208,7 +15173,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>15.1</v>
+        <v>0.6</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -15251,7 +15216,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 26946-2026</t>
+          <t>A 43752-2025</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -15265,10 +15230,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46185</v>
+        <v>45912</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15280,13 +15245,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H170" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I170" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -15329,7 +15289,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 26947-2026</t>
+          <t>A 770-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -15343,10 +15303,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46185</v>
+        <v>46027</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15358,13 +15318,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I171" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -15407,7 +15362,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 29482-2023</t>
+          <t>A 2565-2022</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -15421,10 +15376,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45106</v>
+        <v>44579</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15437,7 +15392,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -15480,7 +15435,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 59158-2022</t>
+          <t>A 54082-2024</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -15490,14 +15445,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>44904</v>
+        <v>45616</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15509,13 +15464,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I173" t="n">
-        <v>3.7</v>
+        <v>6.3</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -15558,7 +15508,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 27411-2026</t>
+          <t>A 20478-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -15572,10 +15522,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>46189</v>
+        <v>46140</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15593,7 +15543,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -15636,7 +15586,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 18773-2025</t>
+          <t>A 10674-2024</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -15646,14 +15596,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45763</v>
+        <v>45369</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15665,8 +15615,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I175" t="n">
-        <v>13</v>
+        <v>0.3</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -15709,7 +15664,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 10320-2023</t>
+          <t>A 20567-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -15723,10 +15678,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>44986</v>
+        <v>46140</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15738,8 +15693,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I176" t="n">
-        <v>2.6</v>
+        <v>7.8</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -15782,7 +15742,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 28789-2026</t>
+          <t>A 20568-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -15796,10 +15756,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46195</v>
+        <v>46140</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15811,8 +15771,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I177" t="n">
-        <v>2.7</v>
+        <v>6.3</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -15855,7 +15820,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 27745-2026</t>
+          <t>A 18773-2025</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -15869,10 +15834,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46191</v>
+        <v>45763</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15884,13 +15849,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I178" t="n">
-        <v>1.7</v>
+        <v>13</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -15933,7 +15893,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 27746-2026</t>
+          <t>A 51653-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -15947,10 +15907,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46191</v>
+        <v>45222</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15968,7 +15928,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>1</v>
+        <v>3.9</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -16011,7 +15971,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 28696-2026</t>
+          <t>A 12108-2024</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -16025,10 +15985,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46198</v>
+        <v>45376</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16040,13 +16000,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I180" t="n">
-        <v>2.5</v>
+        <v>7.7</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -16089,7 +16044,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 28708-2026</t>
+          <t>A 54994-2024</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -16103,10 +16058,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46198</v>
+        <v>45621</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16124,7 +16079,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>2.8</v>
+        <v>0.5</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -16167,7 +16122,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 10797-2023</t>
+          <t>A 21402-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -16181,10 +16136,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>44989</v>
+        <v>46148</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16197,7 +16152,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>9.5</v>
+        <v>1.4</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -16240,7 +16195,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 11084-2023</t>
+          <t>A 21440-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -16254,10 +16209,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>44986</v>
+        <v>46148</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16269,8 +16224,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I183" t="n">
-        <v>2.7</v>
+        <v>6.5</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -16313,7 +16273,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 50764-2024</t>
+          <t>A 21442-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -16327,10 +16287,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45602</v>
+        <v>46148</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16348,7 +16308,7 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>2.4</v>
+        <v>4.1</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -16391,7 +16351,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 28695-2026</t>
+          <t>A 21401-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -16405,10 +16365,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46198</v>
+        <v>46148</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16420,13 +16380,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I185" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -16469,7 +16424,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 33658-2024</t>
+          <t>A 44841-2023</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -16483,10 +16438,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45520</v>
+        <v>45190</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16498,8 +16453,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I186" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -16542,7 +16502,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 29130-2026</t>
+          <t>A 9273-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -16556,10 +16516,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46202</v>
+        <v>46070</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16571,13 +16531,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I187" t="n">
-        <v>10.3</v>
+        <v>2.3</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -16620,7 +16575,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 28930-2026</t>
+          <t>A 46222-2024</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -16634,10 +16589,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46199</v>
+        <v>45581</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16649,8 +16604,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I188" t="n">
-        <v>2.7</v>
+        <v>0.9</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -16693,7 +16653,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 29132-2026</t>
+          <t>A 46219-2024</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -16707,10 +16667,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>46202</v>
+        <v>45581</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16728,7 +16688,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>11.9</v>
+        <v>2.4</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -16771,7 +16731,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 45861-2023</t>
+          <t>A 12159-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -16781,14 +16741,14 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45195</v>
+        <v>46086</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16806,7 +16766,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -16849,7 +16809,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 43768-2024</t>
+          <t>A 12160-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -16863,10 +16823,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45569</v>
+        <v>46086</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16878,8 +16838,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I191" t="n">
-        <v>7</v>
+        <v>0.9</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -16922,7 +16887,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 38738-2022</t>
+          <t>A 13039-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -16936,10 +16901,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>44816</v>
+        <v>46093</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16957,7 +16922,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>0.9</v>
+        <v>5.1</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -17000,7 +16965,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 36339-2026</t>
+          <t>A 13040-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -17014,10 +16979,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46268</v>
+        <v>46093</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17029,8 +16994,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I193" t="n">
-        <v>0.4</v>
+        <v>7.1</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -17073,7 +17043,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 36345-2026</t>
+          <t>A 14678-2025</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -17083,14 +17053,14 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46268</v>
+        <v>45742</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17102,8 +17072,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I194" t="n">
-        <v>0.3</v>
+        <v>1.9</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -17146,7 +17121,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 61750-2021</t>
+          <t>A 12936-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -17160,10 +17135,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>44501</v>
+        <v>46092</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17181,7 +17156,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>1.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -17224,7 +17199,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 36336-2026</t>
+          <t>A 23230-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -17238,10 +17213,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46268</v>
+        <v>46162</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17253,8 +17228,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I196" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -17297,7 +17277,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 7472-2025</t>
+          <t>A 23229-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -17311,10 +17291,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45705</v>
+        <v>46162</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17332,7 +17312,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -17375,7 +17355,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 31813-2026</t>
+          <t>A 23854-2026</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -17389,10 +17369,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46230</v>
+        <v>46167</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17404,8 +17384,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I198" t="n">
-        <v>1.8</v>
+        <v>20.9</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -17448,7 +17433,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 50207-2024</t>
+          <t>A 24462-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -17462,10 +17447,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45600</v>
+        <v>46170</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17478,7 +17463,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -17521,7 +17506,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 50208-2024</t>
+          <t>A 24689-2026</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -17535,10 +17520,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45600</v>
+        <v>46171</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17550,8 +17535,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I200" t="n">
-        <v>0.4</v>
+        <v>15.5</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -17594,7 +17584,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 31870-2026</t>
+          <t>A 24460-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -17608,10 +17598,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46231</v>
+        <v>46170</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17623,13 +17613,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H201" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I201" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -17672,7 +17657,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 31871-2026</t>
+          <t>A 26857-2026</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -17686,10 +17671,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>46231</v>
+        <v>46185</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17707,7 +17692,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>1.9</v>
+        <v>15.1</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -17750,7 +17735,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 12108-2024</t>
+          <t>A 26947-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -17764,10 +17749,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45376</v>
+        <v>46185</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17779,8 +17764,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I203" t="n">
-        <v>7.7</v>
+        <v>2</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -17823,7 +17813,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 18831-2025</t>
+          <t>A 26946-2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -17837,10 +17827,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45764</v>
+        <v>46185</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17858,7 +17848,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>4.2</v>
+        <v>1.8</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -17901,7 +17891,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 37809-2026</t>
+          <t>A 27411-2026</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -17915,10 +17905,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46279</v>
+        <v>46189</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17930,8 +17920,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I205" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -17974,7 +17969,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 32154-2023</t>
+          <t>A 27745-2026</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -17988,10 +17983,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45119</v>
+        <v>46191</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18003,8 +17998,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I206" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -18047,7 +18047,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 38126-2026</t>
+          <t>A 27746-2026</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -18061,10 +18061,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>46281</v>
+        <v>46191</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18082,7 +18082,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>5.5</v>
+        <v>1</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -18125,7 +18125,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 27438-2024</t>
+          <t>A 28696-2026</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -18139,10 +18139,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45474</v>
+        <v>46198</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18154,8 +18154,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I208" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -18198,7 +18203,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 46288-2024</t>
+          <t>A 28708-2026</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -18212,10 +18217,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45581</v>
+        <v>46198</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18233,7 +18238,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -18276,7 +18281,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 32506-2026</t>
+          <t>A 28930-2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -18290,10 +18295,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>46239</v>
+        <v>46199</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18305,13 +18310,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H210" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I210" t="n">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -18354,7 +18354,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 51996-2023</t>
+          <t>A 28695-2026</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -18368,10 +18368,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45223</v>
+        <v>46198</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18389,7 +18389,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -18432,7 +18432,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 38651-2026</t>
+          <t>A 29130-2026</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -18446,10 +18446,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>46283</v>
+        <v>46202</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18467,7 +18467,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>11.3</v>
+        <v>10.3</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -18510,7 +18510,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 58629-2024</t>
+          <t>A 36339-2026</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -18524,10 +18524,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45635</v>
+        <v>46268</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18539,13 +18539,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H213" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I213" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -18588,7 +18583,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 38463-2026</t>
+          <t>A 36336-2026</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -18602,10 +18597,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>46282</v>
+        <v>46268</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18618,7 +18613,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -18661,7 +18656,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 32508-2026</t>
+          <t>A 36345-2026</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -18675,10 +18670,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>46239</v>
+        <v>46268</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18690,13 +18685,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H215" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I215" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -18739,7 +18729,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 38659-2026</t>
+          <t>A 31813-2026</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -18753,10 +18743,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>46283</v>
+        <v>46230</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18768,13 +18758,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I216" t="n">
-        <v>4.6</v>
+        <v>1.8</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -18817,7 +18802,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 50102-2023</t>
+          <t>A 31870-2026</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -18831,10 +18816,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45215</v>
+        <v>46231</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18852,7 +18837,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>3.9</v>
+        <v>1.5</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -18895,7 +18880,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 62982-2023</t>
+          <t>A 31871-2026</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -18909,10 +18894,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45272</v>
+        <v>46231</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18924,8 +18909,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I218" t="n">
-        <v>3.5</v>
+        <v>1.9</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -18968,7 +18958,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 21935-2024</t>
+          <t>A 37809-2026</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -18982,10 +18972,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45443</v>
+        <v>46279</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18997,13 +18987,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H219" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I219" t="n">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -19046,7 +19031,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 32810-2026</t>
+          <t>A 38126-2026</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -19060,10 +19045,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>46241</v>
+        <v>46281</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19075,8 +19060,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I220" t="n">
-        <v>6.1</v>
+        <v>5.5</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -19119,7 +19109,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 23460-2024</t>
+          <t>A 38463-2026</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -19133,10 +19123,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45453</v>
+        <v>46282</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19149,7 +19139,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -19192,7 +19182,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 24707-2025</t>
+          <t>A 32508-2026</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -19206,10 +19196,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45798</v>
+        <v>46239</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19221,8 +19211,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I222" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -19265,7 +19260,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 5218-2024</t>
+          <t>A 32506-2026</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -19279,10 +19274,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45330</v>
+        <v>46239</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19300,7 +19295,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -19343,7 +19338,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 26820-2025</t>
+          <t>A 38659-2026</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -19357,10 +19352,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45810</v>
+        <v>46283</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19372,8 +19367,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I224" t="n">
-        <v>0.7</v>
+        <v>4.6</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -19416,7 +19416,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 26783-2025</t>
+          <t>A 32810-2026</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -19430,10 +19430,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45810</v>
+        <v>46241</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19446,7 +19446,7 @@
         </is>
       </c>
       <c r="I225" t="n">
-        <v>2.5</v>
+        <v>6.1</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -19489,7 +19489,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 28367-2025</t>
+          <t>A 38651-2026</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -19503,10 +19503,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45819</v>
+        <v>46283</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19524,7 +19524,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>6.1</v>
+        <v>11.3</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -19567,7 +19567,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 28368-2025</t>
+          <t>A 31872-2026</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -19581,10 +19581,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45819</v>
+        <v>46231</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19602,7 +19602,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>8.1</v>
+        <v>5.2</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -19645,7 +19645,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 23066-2022</t>
+          <t>A 41889-2026</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -19659,10 +19659,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>44719</v>
+        <v>46303</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19674,8 +19674,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I228" t="n">
-        <v>2.4</v>
+        <v>5.6</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -19718,7 +19723,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 31872-2026</t>
+          <t>A 29552-2026</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -19732,10 +19737,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>46231</v>
+        <v>46204</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19753,7 +19758,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>5.2</v>
+        <v>2.3</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -19796,7 +19801,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 29552-2026</t>
+          <t>A 41890-2026</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -19810,10 +19815,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>46204</v>
+        <v>46303</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19831,7 +19836,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>2.3</v>
+        <v>6.3</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -19874,7 +19879,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 41890-2026</t>
+          <t>A 35213-2026</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -19888,10 +19893,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>46303</v>
+        <v>46260</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19909,7 +19914,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>6.3</v>
+        <v>9.5</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -19952,7 +19957,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 35213-2026</t>
+          <t>A 28789-2026</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -19966,10 +19971,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>46260</v>
+        <v>46195</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19981,13 +19986,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H232" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I232" t="n">
-        <v>9.5</v>
+        <v>2.7</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -20030,7 +20030,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 41889-2026</t>
+          <t>A 29132-2026</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -20044,10 +20044,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>46303</v>
+        <v>46202</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20065,7 +20065,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>5.6</v>
+        <v>11.9</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -20125,7 +20125,7 @@
         <v>44587</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20198,7 +20198,7 @@
         <v>45805</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20276,7 +20276,7 @@
         <v>45805</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20354,7 +20354,7 @@
         <v>45729</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20432,7 +20432,7 @@
         <v>45729</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20510,7 +20510,7 @@
         <v>45742</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20588,7 +20588,7 @@
         <v>45742</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20666,7 +20666,7 @@
         <v>45916</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>

--- a/Översikt DEGERFORS.xlsx
+++ b/Översikt DEGERFORS.xlsx
@@ -601,7 +601,7 @@
         <v>46160</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>46051</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
         <v>46107</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>46160</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>46190</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>46190</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>46161</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>45089</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>45175</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>46160</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>45384</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
         <v>45384</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>44550</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>45163</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>46204</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>45175</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         <v>45351</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>45932</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         <v>45866</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         <v>45163</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>45205</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>45559</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>45931</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>45384</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>46190</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>45931</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>45163</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>45163</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>45558</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4038,7 +4038,7 @@
         <v>45163</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>46045</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>46199</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>44487</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>45096</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
         <v>45589</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4708,7 +4708,7 @@
         <v>44578</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         <v>45614</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>45938</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
         <v>45589</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5141,7 +5141,7 @@
         <v>45116</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5246,7 +5246,7 @@
         <v>45931</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
         <v>45163</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
         <v>45205</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         <v>46099</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5693,7 +5693,7 @@
         <v>45163</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5807,7 +5807,7 @@
         <v>44651</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5912,7 +5912,7 @@
         <v>46186</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
         <v>46186</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6136,7 +6136,7 @@
         <v>46185</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6241,7 +6241,7 @@
         <v>44805</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6314,7 +6314,7 @@
         <v>44805</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6387,7 +6387,7 @@
         <v>44861</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6460,7 +6460,7 @@
         <v>44607</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>44692</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6611,7 +6611,7 @@
         <v>44609</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6684,7 +6684,7 @@
         <v>44594</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6757,7 +6757,7 @@
         <v>44853</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
         <v>44643</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
         <v>44497</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6976,7 +6976,7 @@
         <v>44529</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         <v>44525</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7127,7 +7127,7 @@
         <v>44515</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7200,7 +7200,7 @@
         <v>44509</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7278,7 +7278,7 @@
         <v>45338</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7356,7 +7356,7 @@
         <v>44505</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7434,7 +7434,7 @@
         <v>45763</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         <v>45735</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7585,7 +7585,7 @@
         <v>44816</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7663,7 +7663,7 @@
         <v>44986</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7736,7 +7736,7 @@
         <v>45624</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         <v>45387</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         <v>45468</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7960,7 +7960,7 @@
         <v>45351</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8038,7 +8038,7 @@
         <v>45195</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8116,7 +8116,7 @@
         <v>45645</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8194,7 +8194,7 @@
         <v>44501</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8272,7 +8272,7 @@
         <v>45233</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8345,7 +8345,7 @@
         <v>44816</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8423,7 +8423,7 @@
         <v>45887</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8501,7 +8501,7 @@
         <v>44582</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
         <v>45887</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8652,7 +8652,7 @@
         <v>45601</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8730,7 +8730,7 @@
         <v>44754</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8808,7 +8808,7 @@
         <v>45337</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         <v>45384</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8959,7 +8959,7 @@
         <v>44986</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9032,7 +9032,7 @@
         <v>45902</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9110,7 +9110,7 @@
         <v>45902</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9188,7 +9188,7 @@
         <v>45705</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9266,7 +9266,7 @@
         <v>44986</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9339,7 +9339,7 @@
         <v>45707</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9417,7 +9417,7 @@
         <v>45629</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9495,7 +9495,7 @@
         <v>45764</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9573,7 +9573,7 @@
         <v>45520</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9646,7 +9646,7 @@
         <v>45160</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9719,7 +9719,7 @@
         <v>45338</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9797,7 +9797,7 @@
         <v>45912</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9875,7 +9875,7 @@
         <v>45912</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9953,7 +9953,7 @@
         <v>45912</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10031,7 +10031,7 @@
         <v>45635</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10109,7 +10109,7 @@
         <v>45474</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10182,7 +10182,7 @@
         <v>45215</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10260,7 +10260,7 @@
         <v>45602</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10338,7 +10338,7 @@
         <v>44904</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10416,7 +10416,7 @@
         <v>45223</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10494,7 +10494,7 @@
         <v>45272</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10567,7 +10567,7 @@
         <v>45581</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10645,7 +10645,7 @@
         <v>45330</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10718,7 +10718,7 @@
         <v>45600</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10791,7 +10791,7 @@
         <v>45600</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10864,7 +10864,7 @@
         <v>45443</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10942,7 +10942,7 @@
         <v>45569</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11015,7 +11015,7 @@
         <v>45453</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11088,7 +11088,7 @@
         <v>45330</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11166,7 +11166,7 @@
         <v>45798</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11239,7 +11239,7 @@
         <v>45936</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11312,7 +11312,7 @@
         <v>45589</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11390,7 +11390,7 @@
         <v>45443</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11468,7 +11468,7 @@
         <v>45729</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11546,7 +11546,7 @@
         <v>45219</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
         <v>45609</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
         <v>44609</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11770,7 +11770,7 @@
         <v>45810</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11843,7 +11843,7 @@
         <v>45645</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11921,7 +11921,7 @@
         <v>45645</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11999,7 +11999,7 @@
         <v>45272</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12072,7 +12072,7 @@
         <v>45810</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12145,7 +12145,7 @@
         <v>45601</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12223,7 +12223,7 @@
         <v>45947</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12301,7 +12301,7 @@
         <v>45819</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12379,7 +12379,7 @@
         <v>45819</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12457,7 +12457,7 @@
         <v>45190</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12535,7 +12535,7 @@
         <v>44719</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12608,7 +12608,7 @@
         <v>45222</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12686,7 +12686,7 @@
         <v>45952</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12759,7 +12759,7 @@
         <v>44986</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12832,7 +12832,7 @@
         <v>45116</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12905,7 +12905,7 @@
         <v>45602</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12983,7 +12983,7 @@
         <v>45119</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13056,7 +13056,7 @@
         <v>45841</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13129,7 +13129,7 @@
         <v>45971</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13207,7 +13207,7 @@
         <v>45163</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13285,7 +13285,7 @@
         <v>45639</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13358,7 +13358,7 @@
         <v>45351</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13436,7 +13436,7 @@
         <v>45351</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13514,7 +13514,7 @@
         <v>45261</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13592,7 +13592,7 @@
         <v>44509</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13670,7 +13670,7 @@
         <v>45979</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13743,7 +13743,7 @@
         <v>45876</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13816,7 +13816,7 @@
         <v>45876</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13889,7 +13889,7 @@
         <v>44781</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13962,7 +13962,7 @@
         <v>45747</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14035,7 +14035,7 @@
         <v>46094</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14113,7 +14113,7 @@
         <v>45057</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14191,7 +14191,7 @@
         <v>44989</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14264,7 +14264,7 @@
         <v>44839</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14337,7 +14337,7 @@
         <v>45106</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14410,7 +14410,7 @@
         <v>44552</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14483,7 +14483,7 @@
         <v>46127</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14556,7 +14556,7 @@
         <v>45996</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14629,7 +14629,7 @@
         <v>45996</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14702,7 +14702,7 @@
         <v>45535</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14775,7 +14775,7 @@
         <v>46132</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14848,7 +14848,7 @@
         <v>46129</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14926,7 +14926,7 @@
         <v>45205</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15004,7 +15004,7 @@
         <v>45163</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15082,7 +15082,7 @@
         <v>45192</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15155,7 +15155,7 @@
         <v>45541</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15233,7 +15233,7 @@
         <v>45912</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15306,7 +15306,7 @@
         <v>46027</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15379,7 +15379,7 @@
         <v>44579</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15452,7 +15452,7 @@
         <v>45616</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15525,7 +15525,7 @@
         <v>46140</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15603,7 +15603,7 @@
         <v>45369</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15681,7 +15681,7 @@
         <v>46140</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15759,7 +15759,7 @@
         <v>46140</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15837,7 +15837,7 @@
         <v>45763</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15910,7 +15910,7 @@
         <v>45222</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15988,7 +15988,7 @@
         <v>45376</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16061,7 +16061,7 @@
         <v>45621</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16139,7 +16139,7 @@
         <v>46148</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16212,7 +16212,7 @@
         <v>46148</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16290,7 +16290,7 @@
         <v>46148</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16368,7 +16368,7 @@
         <v>46148</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16441,7 +16441,7 @@
         <v>45190</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16519,7 +16519,7 @@
         <v>46070</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16592,7 +16592,7 @@
         <v>45581</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16670,7 +16670,7 @@
         <v>45581</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16748,7 +16748,7 @@
         <v>46086</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16826,7 +16826,7 @@
         <v>46086</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16904,7 +16904,7 @@
         <v>46093</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16982,7 +16982,7 @@
         <v>46093</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17060,7 +17060,7 @@
         <v>45742</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17138,7 +17138,7 @@
         <v>46092</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17216,7 +17216,7 @@
         <v>46162</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17294,7 +17294,7 @@
         <v>46162</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17372,7 +17372,7 @@
         <v>46167</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17450,7 +17450,7 @@
         <v>46170</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17523,7 +17523,7 @@
         <v>46171</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17601,7 +17601,7 @@
         <v>46170</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17674,7 +17674,7 @@
         <v>46185</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17752,7 +17752,7 @@
         <v>46185</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17830,7 +17830,7 @@
         <v>46185</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17908,7 +17908,7 @@
         <v>46189</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17986,7 +17986,7 @@
         <v>46191</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18064,7 +18064,7 @@
         <v>46191</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18142,7 +18142,7 @@
         <v>46198</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18220,7 +18220,7 @@
         <v>46198</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18298,7 +18298,7 @@
         <v>46199</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18371,7 +18371,7 @@
         <v>46198</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18449,7 +18449,7 @@
         <v>46202</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18527,7 +18527,7 @@
         <v>46268</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18600,7 +18600,7 @@
         <v>46268</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18673,7 +18673,7 @@
         <v>46268</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18746,7 +18746,7 @@
         <v>46230</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18819,7 +18819,7 @@
         <v>46231</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18897,7 +18897,7 @@
         <v>46231</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18975,7 +18975,7 @@
         <v>46279</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19048,7 +19048,7 @@
         <v>46281</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19126,7 +19126,7 @@
         <v>46282</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19199,7 +19199,7 @@
         <v>46239</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19277,7 +19277,7 @@
         <v>46239</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19355,7 +19355,7 @@
         <v>46283</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19433,7 +19433,7 @@
         <v>46241</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19506,7 +19506,7 @@
         <v>46283</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19584,7 +19584,7 @@
         <v>46231</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19662,7 +19662,7 @@
         <v>46303</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19740,7 +19740,7 @@
         <v>46204</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19818,7 +19818,7 @@
         <v>46303</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19896,7 +19896,7 @@
         <v>46260</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19974,7 +19974,7 @@
         <v>46195</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20047,7 +20047,7 @@
         <v>46202</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20125,7 +20125,7 @@
         <v>44587</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20198,7 +20198,7 @@
         <v>45805</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20276,7 +20276,7 @@
         <v>45805</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20354,7 +20354,7 @@
         <v>45729</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20432,7 +20432,7 @@
         <v>45729</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20510,7 +20510,7 @@
         <v>45742</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20588,7 +20588,7 @@
         <v>45742</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20666,7 +20666,7 @@
         <v>45916</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>

--- a/Översikt DEGERFORS.xlsx
+++ b/Översikt DEGERFORS.xlsx
@@ -601,7 +601,7 @@
         <v>46160</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>46051</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
         <v>46107</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>46160</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>46190</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>46190</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>46161</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>45089</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>45175</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>46160</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>45384</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
         <v>45384</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>44550</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>45163</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>46204</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>45175</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         <v>45351</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>45932</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         <v>45866</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         <v>45163</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>45205</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>45559</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>45931</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>45384</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>46190</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>45931</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3693,7 +3693,7 @@
         <v>45163</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3808,7 +3808,7 @@
         <v>45163</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>45558</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4038,7 +4038,7 @@
         <v>45163</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         <v>46045</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>46199</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>44487</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         <v>45096</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4598,7 +4598,7 @@
         <v>45589</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4708,7 +4708,7 @@
         <v>44578</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         <v>45614</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         <v>45938</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
         <v>45589</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5141,7 +5141,7 @@
         <v>45116</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5246,7 +5246,7 @@
         <v>45931</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
         <v>45163</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
         <v>45205</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         <v>46099</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5693,7 +5693,7 @@
         <v>45163</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5807,7 +5807,7 @@
         <v>44651</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5912,7 +5912,7 @@
         <v>46186</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
         <v>46186</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6136,7 +6136,7 @@
         <v>46185</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6241,7 +6241,7 @@
         <v>44805</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6314,7 +6314,7 @@
         <v>44805</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6387,7 +6387,7 @@
         <v>44861</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6460,7 +6460,7 @@
         <v>44607</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         <v>44692</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6611,7 +6611,7 @@
         <v>44609</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6684,7 +6684,7 @@
         <v>44594</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6757,7 +6757,7 @@
         <v>44853</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
         <v>44643</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
         <v>44497</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6976,7 +6976,7 @@
         <v>44529</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         <v>44525</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7127,7 +7127,7 @@
         <v>44515</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7200,7 +7200,7 @@
         <v>44509</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7278,7 +7278,7 @@
         <v>45338</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7356,7 +7356,7 @@
         <v>44505</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7434,7 +7434,7 @@
         <v>45763</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         <v>45735</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7585,7 +7585,7 @@
         <v>44816</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7663,7 +7663,7 @@
         <v>44986</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7736,7 +7736,7 @@
         <v>45624</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         <v>45387</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         <v>45468</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7960,7 +7960,7 @@
         <v>45351</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8038,7 +8038,7 @@
         <v>45195</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8116,7 +8116,7 @@
         <v>45645</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8194,7 +8194,7 @@
         <v>44501</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8272,7 +8272,7 @@
         <v>45233</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8345,7 +8345,7 @@
         <v>44816</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8423,7 +8423,7 @@
         <v>45887</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8501,7 +8501,7 @@
         <v>44582</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
         <v>45887</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8652,7 +8652,7 @@
         <v>45601</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8730,7 +8730,7 @@
         <v>44754</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8808,7 +8808,7 @@
         <v>45337</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         <v>45384</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8959,7 +8959,7 @@
         <v>44986</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9032,7 +9032,7 @@
         <v>45902</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9110,7 +9110,7 @@
         <v>45902</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9188,7 +9188,7 @@
         <v>45705</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9266,7 +9266,7 @@
         <v>44986</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9339,7 +9339,7 @@
         <v>45707</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9417,7 +9417,7 @@
         <v>45629</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9495,7 +9495,7 @@
         <v>45764</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9573,7 +9573,7 @@
         <v>45520</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9646,7 +9646,7 @@
         <v>45160</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9719,7 +9719,7 @@
         <v>45338</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9797,7 +9797,7 @@
         <v>45912</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9875,7 +9875,7 @@
         <v>45912</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9953,7 +9953,7 @@
         <v>45912</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10031,7 +10031,7 @@
         <v>45635</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10109,7 +10109,7 @@
         <v>45474</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10182,7 +10182,7 @@
         <v>45215</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10260,7 +10260,7 @@
         <v>45602</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10338,7 +10338,7 @@
         <v>44904</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10416,7 +10416,7 @@
         <v>45223</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10494,7 +10494,7 @@
         <v>45272</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10567,7 +10567,7 @@
         <v>45581</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10645,7 +10645,7 @@
         <v>45330</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10718,7 +10718,7 @@
         <v>45600</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10791,7 +10791,7 @@
         <v>45600</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10864,7 +10864,7 @@
         <v>45443</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10942,7 +10942,7 @@
         <v>45569</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11015,7 +11015,7 @@
         <v>45453</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11088,7 +11088,7 @@
         <v>45330</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11166,7 +11166,7 @@
         <v>45798</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11239,7 +11239,7 @@
         <v>45936</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11312,7 +11312,7 @@
         <v>45589</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11390,7 +11390,7 @@
         <v>45443</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11468,7 +11468,7 @@
         <v>45729</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11546,7 +11546,7 @@
         <v>45219</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
         <v>45609</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11697,7 +11697,7 @@
         <v>44609</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11770,7 +11770,7 @@
         <v>45810</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11843,7 +11843,7 @@
         <v>45645</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11921,7 +11921,7 @@
         <v>45645</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11999,7 +11999,7 @@
         <v>45272</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12072,7 +12072,7 @@
         <v>45810</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12145,7 +12145,7 @@
         <v>45601</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12223,7 +12223,7 @@
         <v>45947</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12301,7 +12301,7 @@
         <v>45819</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12379,7 +12379,7 @@
         <v>45819</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12457,7 +12457,7 @@
         <v>45190</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12535,7 +12535,7 @@
         <v>44719</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12608,7 +12608,7 @@
         <v>45222</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12686,7 +12686,7 @@
         <v>45952</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12759,7 +12759,7 @@
         <v>44986</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12832,7 +12832,7 @@
         <v>45116</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12905,7 +12905,7 @@
         <v>45602</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12983,7 +12983,7 @@
         <v>45119</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13056,7 +13056,7 @@
         <v>45841</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13129,7 +13129,7 @@
         <v>45971</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13207,7 +13207,7 @@
         <v>45163</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13285,7 +13285,7 @@
         <v>45639</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13358,7 +13358,7 @@
         <v>45351</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13436,7 +13436,7 @@
         <v>45351</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13514,7 +13514,7 @@
         <v>45261</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13592,7 +13592,7 @@
         <v>44509</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13670,7 +13670,7 @@
         <v>45979</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13743,7 +13743,7 @@
         <v>45876</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13816,7 +13816,7 @@
         <v>45876</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13889,7 +13889,7 @@
         <v>44781</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13962,7 +13962,7 @@
         <v>45747</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14035,7 +14035,7 @@
         <v>46094</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14113,7 +14113,7 @@
         <v>45057</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14191,7 +14191,7 @@
         <v>44989</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14264,7 +14264,7 @@
         <v>44839</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14337,7 +14337,7 @@
         <v>45106</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14410,7 +14410,7 @@
         <v>44552</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14483,7 +14483,7 @@
         <v>46127</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14556,7 +14556,7 @@
         <v>45996</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14629,7 +14629,7 @@
         <v>45996</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14702,7 +14702,7 @@
         <v>45535</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14775,7 +14775,7 @@
         <v>46132</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14848,7 +14848,7 @@
         <v>46129</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14926,7 +14926,7 @@
         <v>45205</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15004,7 +15004,7 @@
         <v>45163</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15082,7 +15082,7 @@
         <v>45192</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15155,7 +15155,7 @@
         <v>45541</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15233,7 +15233,7 @@
         <v>45912</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15306,7 +15306,7 @@
         <v>46027</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15379,7 +15379,7 @@
         <v>44579</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15452,7 +15452,7 @@
         <v>45616</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15525,7 +15525,7 @@
         <v>46140</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15603,7 +15603,7 @@
         <v>45369</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15681,7 +15681,7 @@
         <v>46140</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15759,7 +15759,7 @@
         <v>46140</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15837,7 +15837,7 @@
         <v>45763</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15910,7 +15910,7 @@
         <v>45222</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15988,7 +15988,7 @@
         <v>45376</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16061,7 +16061,7 @@
         <v>45621</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16139,7 +16139,7 @@
         <v>46148</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16212,7 +16212,7 @@
         <v>46148</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16290,7 +16290,7 @@
         <v>46148</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16368,7 +16368,7 @@
         <v>46148</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16441,7 +16441,7 @@
         <v>45190</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16519,7 +16519,7 @@
         <v>46070</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16592,7 +16592,7 @@
         <v>45581</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16670,7 +16670,7 @@
         <v>45581</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16748,7 +16748,7 @@
         <v>46086</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16826,7 +16826,7 @@
         <v>46086</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16904,7 +16904,7 @@
         <v>46093</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16982,7 +16982,7 @@
         <v>46093</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17060,7 +17060,7 @@
         <v>45742</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17138,7 +17138,7 @@
         <v>46092</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17216,7 +17216,7 @@
         <v>46162</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17294,7 +17294,7 @@
         <v>46162</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17372,7 +17372,7 @@
         <v>46167</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17450,7 +17450,7 @@
         <v>46170</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17523,7 +17523,7 @@
         <v>46171</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17601,7 +17601,7 @@
         <v>46170</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17674,7 +17674,7 @@
         <v>46185</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17752,7 +17752,7 @@
         <v>46185</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17830,7 +17830,7 @@
         <v>46185</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17908,7 +17908,7 @@
         <v>46189</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17986,7 +17986,7 @@
         <v>46191</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18064,7 +18064,7 @@
         <v>46191</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18142,7 +18142,7 @@
         <v>46198</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18220,7 +18220,7 @@
         <v>46198</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18298,7 +18298,7 @@
         <v>46199</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18371,7 +18371,7 @@
         <v>46198</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18449,7 +18449,7 @@
         <v>46202</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18527,7 +18527,7 @@
         <v>46268</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18600,7 +18600,7 @@
         <v>46268</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18673,7 +18673,7 @@
         <v>46268</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18746,7 +18746,7 @@
         <v>46230</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18819,7 +18819,7 @@
         <v>46231</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18897,7 +18897,7 @@
         <v>46231</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18975,7 +18975,7 @@
         <v>46279</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19048,7 +19048,7 @@
         <v>46281</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19126,7 +19126,7 @@
         <v>46282</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19199,7 +19199,7 @@
         <v>46239</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19277,7 +19277,7 @@
         <v>46239</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19355,7 +19355,7 @@
         <v>46283</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19433,7 +19433,7 @@
         <v>46241</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19506,7 +19506,7 @@
         <v>46283</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19584,7 +19584,7 @@
         <v>46231</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19662,7 +19662,7 @@
         <v>46303</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19740,7 +19740,7 @@
         <v>46204</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19818,7 +19818,7 @@
         <v>46303</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19896,7 +19896,7 @@
         <v>46260</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19974,7 +19974,7 @@
         <v>46195</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20047,7 +20047,7 @@
         <v>46202</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20125,7 +20125,7 @@
         <v>44587</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20198,7 +20198,7 @@
         <v>45805</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20276,7 +20276,7 @@
         <v>45805</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20354,7 +20354,7 @@
         <v>45729</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20432,7 +20432,7 @@
         <v>45729</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20510,7 +20510,7 @@
         <v>45742</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20588,7 +20588,7 @@
         <v>45742</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20666,7 +20666,7 @@
         <v>45916</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>

--- a/Översikt DEGERFORS.xlsx
+++ b/Översikt DEGERFORS.xlsx
@@ -601,7 +601,7 @@
         <v>46160</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>46051</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
         <v>46160</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>46107</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>46190</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>46190</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>46161</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>45089</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>45175</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>46160</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>45384</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1957,7 +1957,7 @@
         <v>45384</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>45163</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>44550</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>46204</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>45175</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         <v>45866</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>45932</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
         <v>45163</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         <v>45205</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
         <v>45351</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         <v>45559</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         <v>45931</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>45384</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>46190</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 4256-2026</t>
+          <t>A 47785-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3580,10 +3580,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46045</v>
+        <v>45931</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3596,16 +3596,16 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K27" t="n">
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -3620,7 +3620,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -3632,610 +3632,610 @@
         <v>2</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>Spillkråka
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 47785-2025 artfynd.xlsx", "A 47785-2025")</f>
+        <v/>
+      </c>
+      <c r="X27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 47785-2025 karta.png", "A 47785-2025")</f>
+        <v/>
+      </c>
+      <c r="Y27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 47785-2025 georefererad karta.tif", "A 47785-2025")</f>
+        <v/>
+      </c>
+      <c r="AA27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 47785-2025 FSC-klagomål.docx", "A 47785-2025")</f>
+        <v/>
+      </c>
+      <c r="AB27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 47785-2025 FSC-klagomål mail.docx", "A 47785-2025")</f>
+        <v/>
+      </c>
+      <c r="AC27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 47785-2025 tillsynsbegäran.docx", "A 47785-2025")</f>
+        <v/>
+      </c>
+      <c r="AD27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 47785-2025 tillsynsbegäran mail.docx", "A 47785-2025")</f>
+        <v/>
+      </c>
+      <c r="AE27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 47785-2025 prioriterade fågelarter.docx", "A 47785-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>A 40870-2024</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>45558</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>DEGERFORS</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 40870-2024 artfynd.xlsx", "A 40870-2024")</f>
+        <v/>
+      </c>
+      <c r="X28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 40870-2024 karta.png", "A 40870-2024")</f>
+        <v/>
+      </c>
+      <c r="Y28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 40870-2024 georefererad karta.tif", "A 40870-2024")</f>
+        <v/>
+      </c>
+      <c r="AA28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 40870-2024 FSC-klagomål.docx", "A 40870-2024")</f>
+        <v/>
+      </c>
+      <c r="AB28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 40870-2024 FSC-klagomål mail.docx", "A 40870-2024")</f>
+        <v/>
+      </c>
+      <c r="AC28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 40870-2024 tillsynsbegäran.docx", "A 40870-2024")</f>
+        <v/>
+      </c>
+      <c r="AD28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 40870-2024 tillsynsbegäran mail.docx", "A 40870-2024")</f>
+        <v/>
+      </c>
+      <c r="AE28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 40870-2024 prioriterade fågelarter.docx", "A 40870-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>A 38910-2023</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="n">
+        <v>45163</v>
+      </c>
+      <c r="E29" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>DEGERFORS</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>3</v>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>Tjäder
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 38910-2023 artfynd.xlsx", "A 38910-2023")</f>
+        <v/>
+      </c>
+      <c r="X29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 38910-2023 karta.png", "A 38910-2023")</f>
+        <v/>
+      </c>
+      <c r="Y29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 38910-2023 georefererad karta.tif", "A 38910-2023")</f>
+        <v/>
+      </c>
+      <c r="AA29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 38910-2023 FSC-klagomål.docx", "A 38910-2023")</f>
+        <v/>
+      </c>
+      <c r="AB29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 38910-2023 FSC-klagomål mail.docx", "A 38910-2023")</f>
+        <v/>
+      </c>
+      <c r="AC29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 38910-2023 tillsynsbegäran.docx", "A 38910-2023")</f>
+        <v/>
+      </c>
+      <c r="AD29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 38910-2023 tillsynsbegäran mail.docx", "A 38910-2023")</f>
+        <v/>
+      </c>
+      <c r="AE29">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 38910-2023 prioriterade fågelarter.docx", "A 38910-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>A 38912-2023</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D30" s="1" t="n">
+        <v>45163</v>
+      </c>
+      <c r="E30" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>DEGERFORS</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 38912-2023 artfynd.xlsx", "A 38912-2023")</f>
+        <v/>
+      </c>
+      <c r="X30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 38912-2023 karta.png", "A 38912-2023")</f>
+        <v/>
+      </c>
+      <c r="Y30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 38912-2023 georefererad karta.tif", "A 38912-2023")</f>
+        <v/>
+      </c>
+      <c r="AA30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 38912-2023 FSC-klagomål.docx", "A 38912-2023")</f>
+        <v/>
+      </c>
+      <c r="AB30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 38912-2023 FSC-klagomål mail.docx", "A 38912-2023")</f>
+        <v/>
+      </c>
+      <c r="AC30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 38912-2023 tillsynsbegäran.docx", "A 38912-2023")</f>
+        <v/>
+      </c>
+      <c r="AD30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 38912-2023 tillsynsbegäran mail.docx", "A 38912-2023")</f>
+        <v/>
+      </c>
+      <c r="AE30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 38912-2023 prioriterade fågelarter.docx", "A 38912-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>A 38914-2023</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D31" s="1" t="n">
+        <v>45163</v>
+      </c>
+      <c r="E31" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>DEGERFORS</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett
+Tjäder</t>
+        </is>
+      </c>
+      <c r="W31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 38914-2023 artfynd.xlsx", "A 38914-2023")</f>
+        <v/>
+      </c>
+      <c r="X31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 38914-2023 karta.png", "A 38914-2023")</f>
+        <v/>
+      </c>
+      <c r="Y31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 38914-2023 georefererad karta.tif", "A 38914-2023")</f>
+        <v/>
+      </c>
+      <c r="AA31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 38914-2023 FSC-klagomål.docx", "A 38914-2023")</f>
+        <v/>
+      </c>
+      <c r="AB31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 38914-2023 FSC-klagomål mail.docx", "A 38914-2023")</f>
+        <v/>
+      </c>
+      <c r="AC31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 38914-2023 tillsynsbegäran.docx", "A 38914-2023")</f>
+        <v/>
+      </c>
+      <c r="AD31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 38914-2023 tillsynsbegäran mail.docx", "A 38914-2023")</f>
+        <v/>
+      </c>
+      <c r="AE31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 38914-2023 prioriterade fågelarter.docx", "A 38914-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>A 4256-2026</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D32" s="1" t="n">
+        <v>46045</v>
+      </c>
+      <c r="E32" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>DEGERFORS</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>2</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>2</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
         <is>
           <t>Skogsklocka
 Slåtterfibbla</t>
         </is>
       </c>
-      <c r="W27">
+      <c r="W32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 4256-2026 artfynd.xlsx", "A 4256-2026")</f>
         <v/>
       </c>
-      <c r="X27">
+      <c r="X32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 4256-2026 karta.png", "A 4256-2026")</f>
         <v/>
       </c>
-      <c r="Y27">
+      <c r="Y32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 4256-2026 georefererad karta.tif", "A 4256-2026")</f>
         <v/>
       </c>
-      <c r="AA27">
+      <c r="AA32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 4256-2026 FSC-klagomål.docx", "A 4256-2026")</f>
         <v/>
       </c>
-      <c r="AB27">
+      <c r="AB32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 4256-2026 FSC-klagomål mail.docx", "A 4256-2026")</f>
         <v/>
       </c>
-      <c r="AC27">
+      <c r="AC32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 4256-2026 tillsynsbegäran.docx", "A 4256-2026")</f>
         <v/>
       </c>
-      <c r="AD27">
+      <c r="AD32">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 4256-2026 tillsynsbegäran mail.docx", "A 4256-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>A 47785-2025</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D28" s="1" t="n">
-        <v>45931</v>
-      </c>
-      <c r="E28" s="1" t="n">
-        <v>46309</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>DEGERFORS</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>2</v>
-      </c>
-      <c r="J28" t="n">
-        <v>2</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2</v>
-      </c>
-      <c r="U28" t="n">
-        <v>2</v>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 47785-2025 artfynd.xlsx", "A 47785-2025")</f>
-        <v/>
-      </c>
-      <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 47785-2025 karta.png", "A 47785-2025")</f>
-        <v/>
-      </c>
-      <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 47785-2025 georefererad karta.tif", "A 47785-2025")</f>
-        <v/>
-      </c>
-      <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 47785-2025 FSC-klagomål.docx", "A 47785-2025")</f>
-        <v/>
-      </c>
-      <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 47785-2025 FSC-klagomål mail.docx", "A 47785-2025")</f>
-        <v/>
-      </c>
-      <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 47785-2025 tillsynsbegäran.docx", "A 47785-2025")</f>
-        <v/>
-      </c>
-      <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 47785-2025 tillsynsbegäran mail.docx", "A 47785-2025")</f>
-        <v/>
-      </c>
-      <c r="AE28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 47785-2025 prioriterade fågelarter.docx", "A 47785-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>A 38910-2023</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D29" s="1" t="n">
-        <v>45163</v>
-      </c>
-      <c r="E29" s="1" t="n">
-        <v>46309</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>DEGERFORS</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J29" t="n">
-        <v>2</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T29" t="n">
-        <v>3</v>
-      </c>
-      <c r="U29" t="n">
-        <v>3</v>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>Tjäder
-Fläcknycklar</t>
-        </is>
-      </c>
-      <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 38910-2023 artfynd.xlsx", "A 38910-2023")</f>
-        <v/>
-      </c>
-      <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 38910-2023 karta.png", "A 38910-2023")</f>
-        <v/>
-      </c>
-      <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 38910-2023 georefererad karta.tif", "A 38910-2023")</f>
-        <v/>
-      </c>
-      <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 38910-2023 FSC-klagomål.docx", "A 38910-2023")</f>
-        <v/>
-      </c>
-      <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 38910-2023 FSC-klagomål mail.docx", "A 38910-2023")</f>
-        <v/>
-      </c>
-      <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 38910-2023 tillsynsbegäran.docx", "A 38910-2023")</f>
-        <v/>
-      </c>
-      <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 38910-2023 tillsynsbegäran mail.docx", "A 38910-2023")</f>
-        <v/>
-      </c>
-      <c r="AE29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 38910-2023 prioriterade fågelarter.docx", "A 38910-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>A 40870-2024</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D30" s="1" t="n">
-        <v>45558</v>
-      </c>
-      <c r="E30" s="1" t="n">
-        <v>46309</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>DEGERFORS</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J30" t="n">
-        <v>2</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>1</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>1</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2</v>
-      </c>
-      <c r="U30" t="n">
-        <v>2</v>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 40870-2024 artfynd.xlsx", "A 40870-2024")</f>
-        <v/>
-      </c>
-      <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 40870-2024 karta.png", "A 40870-2024")</f>
-        <v/>
-      </c>
-      <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 40870-2024 georefererad karta.tif", "A 40870-2024")</f>
-        <v/>
-      </c>
-      <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 40870-2024 FSC-klagomål.docx", "A 40870-2024")</f>
-        <v/>
-      </c>
-      <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 40870-2024 FSC-klagomål mail.docx", "A 40870-2024")</f>
-        <v/>
-      </c>
-      <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 40870-2024 tillsynsbegäran.docx", "A 40870-2024")</f>
-        <v/>
-      </c>
-      <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 40870-2024 tillsynsbegäran mail.docx", "A 40870-2024")</f>
-        <v/>
-      </c>
-      <c r="AE30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 40870-2024 prioriterade fågelarter.docx", "A 40870-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>A 38912-2023</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D31" s="1" t="n">
-        <v>45163</v>
-      </c>
-      <c r="E31" s="1" t="n">
-        <v>46309</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>DEGERFORS</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I31" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="J31" t="n">
-        <v>2</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>1</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2</v>
-      </c>
-      <c r="U31" t="n">
-        <v>2</v>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 38912-2023 artfynd.xlsx", "A 38912-2023")</f>
-        <v/>
-      </c>
-      <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 38912-2023 karta.png", "A 38912-2023")</f>
-        <v/>
-      </c>
-      <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 38912-2023 georefererad karta.tif", "A 38912-2023")</f>
-        <v/>
-      </c>
-      <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 38912-2023 FSC-klagomål.docx", "A 38912-2023")</f>
-        <v/>
-      </c>
-      <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 38912-2023 FSC-klagomål mail.docx", "A 38912-2023")</f>
-        <v/>
-      </c>
-      <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 38912-2023 tillsynsbegäran.docx", "A 38912-2023")</f>
-        <v/>
-      </c>
-      <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 38912-2023 tillsynsbegäran mail.docx", "A 38912-2023")</f>
-        <v/>
-      </c>
-      <c r="AE31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 38912-2023 prioriterade fågelarter.docx", "A 38912-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="15" customHeight="1">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>A 38914-2023</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D32" s="1" t="n">
-        <v>45163</v>
-      </c>
-      <c r="E32" s="1" t="n">
-        <v>46309</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>DEGERFORS</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I32" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="J32" t="n">
-        <v>2</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>1</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>1</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2</v>
-      </c>
-      <c r="U32" t="n">
-        <v>2</v>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett
-Tjäder</t>
-        </is>
-      </c>
-      <c r="W32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 38914-2023 artfynd.xlsx", "A 38914-2023")</f>
-        <v/>
-      </c>
-      <c r="X32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 38914-2023 karta.png", "A 38914-2023")</f>
-        <v/>
-      </c>
-      <c r="Y32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 38914-2023 georefererad karta.tif", "A 38914-2023")</f>
-        <v/>
-      </c>
-      <c r="AA32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 38914-2023 FSC-klagomål.docx", "A 38914-2023")</f>
-        <v/>
-      </c>
-      <c r="AB32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 38914-2023 FSC-klagomål mail.docx", "A 38914-2023")</f>
-        <v/>
-      </c>
-      <c r="AC32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 38914-2023 tillsynsbegäran.docx", "A 38914-2023")</f>
-        <v/>
-      </c>
-      <c r="AD32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 38914-2023 tillsynsbegäran mail.docx", "A 38914-2023")</f>
-        <v/>
-      </c>
-      <c r="AE32">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 38914-2023 prioriterade fågelarter.docx", "A 38914-2023")</f>
         <v/>
       </c>
     </row>
@@ -4259,7 +4259,7 @@
         <v>46199</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4374,7 +4374,7 @@
         <v>44487</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4467,7 +4467,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 49306-2025</t>
+          <t>A 33297-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4481,10 +4481,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45938</v>
+        <v>45116</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4497,20 +4497,20 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
         <v>1</v>
       </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
       <c r="N35" t="n">
         <v>0</v>
       </c>
@@ -4521,10 +4521,10 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4533,46 +4533,46 @@
         <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 49306-2025 artfynd.xlsx", "A 49306-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 33297-2023 artfynd.xlsx", "A 33297-2023")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 49306-2025 karta.png", "A 49306-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 33297-2023 karta.png", "A 33297-2023")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 49306-2025 georefererad karta.tif", "A 49306-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 33297-2023 georefererad karta.tif", "A 33297-2023")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 49306-2025 FSC-klagomål.docx", "A 49306-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 33297-2023 FSC-klagomål.docx", "A 33297-2023")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 49306-2025 FSC-klagomål mail.docx", "A 49306-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 33297-2023 FSC-klagomål mail.docx", "A 33297-2023")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 49306-2025 tillsynsbegäran.docx", "A 49306-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 33297-2023 tillsynsbegäran.docx", "A 33297-2023")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 49306-2025 tillsynsbegäran mail.docx", "A 49306-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 33297-2023 tillsynsbegäran mail.docx", "A 33297-2023")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 47787-2025</t>
+          <t>A 38904-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4586,10 +4586,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45931</v>
+        <v>45163</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4601,8 +4601,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>4.1</v>
+        <v>2.9</v>
       </c>
       <c r="J36" t="n">
         <v>1</v>
@@ -4611,7 +4616,7 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -4626,7 +4631,7 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -4635,53 +4640,53 @@
         <v>1</v>
       </c>
       <c r="T36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 47787-2025 artfynd.xlsx", "A 47787-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 38904-2023 artfynd.xlsx", "A 38904-2023")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 47787-2025 karta.png", "A 47787-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 38904-2023 karta.png", "A 38904-2023")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 47787-2025 georefererad karta.tif", "A 47787-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 38904-2023 georefererad karta.tif", "A 38904-2023")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 47787-2025 FSC-klagomål.docx", "A 47787-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 38904-2023 FSC-klagomål.docx", "A 38904-2023")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 47787-2025 FSC-klagomål mail.docx", "A 47787-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 38904-2023 FSC-klagomål mail.docx", "A 38904-2023")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 47787-2025 tillsynsbegäran.docx", "A 47787-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 38904-2023 tillsynsbegäran.docx", "A 38904-2023")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 47787-2025 tillsynsbegäran mail.docx", "A 47787-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 38904-2023 tillsynsbegäran mail.docx", "A 38904-2023")</f>
         <v/>
       </c>
       <c r="AE36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 47787-2025 prioriterade fågelarter.docx", "A 47787-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 38904-2023 prioriterade fågelarter.docx", "A 38904-2023")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 47915-2024</t>
+          <t>A 49306-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4695,10 +4700,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45589</v>
+        <v>45938</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4708,21 +4713,16 @@
       <c r="G37" t="inlineStr">
         <is>
           <t>DEGERFORS</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I37" t="n">
         <v>5.8</v>
       </c>
       <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
         <v>1</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -4756,42 +4756,42 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 47915-2024 artfynd.xlsx", "A 47915-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 49306-2025 artfynd.xlsx", "A 49306-2025")</f>
         <v/>
       </c>
       <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 47915-2024 karta.png", "A 47915-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 49306-2025 karta.png", "A 49306-2025")</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 47915-2024 georefererad karta.tif", "A 47915-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 49306-2025 georefererad karta.tif", "A 49306-2025")</f>
         <v/>
       </c>
       <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 47915-2024 FSC-klagomål.docx", "A 47915-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 49306-2025 FSC-klagomål.docx", "A 49306-2025")</f>
         <v/>
       </c>
       <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 47915-2024 FSC-klagomål mail.docx", "A 47915-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 49306-2025 FSC-klagomål mail.docx", "A 49306-2025")</f>
         <v/>
       </c>
       <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 47915-2024 tillsynsbegäran.docx", "A 47915-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 49306-2025 tillsynsbegäran.docx", "A 49306-2025")</f>
         <v/>
       </c>
       <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 47915-2024 tillsynsbegäran mail.docx", "A 47915-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 49306-2025 tillsynsbegäran mail.docx", "A 49306-2025")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 38907-2023</t>
+          <t>A 27093-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4805,10 +4805,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45163</v>
+        <v>45096</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4826,7 +4826,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.9</v>
+        <v>5.9</v>
       </c>
       <c r="J38" t="n">
         <v>1</v>
@@ -4870,42 +4870,42 @@
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 38907-2023 artfynd.xlsx", "A 38907-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 27093-2023 artfynd.xlsx", "A 27093-2023")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 38907-2023 karta.png", "A 38907-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 27093-2023 karta.png", "A 27093-2023")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 38907-2023 georefererad karta.tif", "A 38907-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 27093-2023 georefererad karta.tif", "A 27093-2023")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 38907-2023 FSC-klagomål.docx", "A 38907-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 27093-2023 FSC-klagomål.docx", "A 27093-2023")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 38907-2023 FSC-klagomål mail.docx", "A 38907-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 27093-2023 FSC-klagomål mail.docx", "A 27093-2023")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 38907-2023 tillsynsbegäran.docx", "A 38907-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 27093-2023 tillsynsbegäran.docx", "A 27093-2023")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 38907-2023 tillsynsbegäran mail.docx", "A 38907-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 27093-2023 tillsynsbegäran mail.docx", "A 27093-2023")</f>
         <v/>
       </c>
       <c r="AE38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 38907-2023 prioriterade fågelarter.docx", "A 38907-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 27093-2023 prioriterade fågelarter.docx", "A 27093-2023")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 38904-2023</t>
+          <t>A 14177-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4919,10 +4919,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45163</v>
+        <v>46099</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4940,17 +4940,17 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
         <v>1</v>
       </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
       <c r="M39" t="n">
         <v>0</v>
       </c>
@@ -4964,7 +4964,7 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -4976,50 +4976,46 @@
         <v>1</v>
       </c>
       <c r="U39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 38904-2023 artfynd.xlsx", "A 38904-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 14177-2026 artfynd.xlsx", "A 14177-2026")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 38904-2023 karta.png", "A 38904-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 14177-2026 karta.png", "A 14177-2026")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 38904-2023 georefererad karta.tif", "A 38904-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 14177-2026 georefererad karta.tif", "A 14177-2026")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 38904-2023 FSC-klagomål.docx", "A 38904-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 14177-2026 FSC-klagomål.docx", "A 14177-2026")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 38904-2023 FSC-klagomål mail.docx", "A 38904-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 14177-2026 FSC-klagomål mail.docx", "A 14177-2026")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 38904-2023 tillsynsbegäran.docx", "A 38904-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 14177-2026 tillsynsbegäran.docx", "A 14177-2026")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 38904-2023 tillsynsbegäran mail.docx", "A 38904-2023")</f>
-        <v/>
-      </c>
-      <c r="AE39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 38904-2023 prioriterade fågelarter.docx", "A 38904-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 14177-2026 tillsynsbegäran mail.docx", "A 14177-2026")</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 48285-2023</t>
+          <t>A 47787-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5033,10 +5029,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45205</v>
+        <v>45931</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5048,13 +5044,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>1.1</v>
+        <v>4.1</v>
       </c>
       <c r="J40" t="n">
         <v>1</v>
@@ -5063,7 +5054,7 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
@@ -5078,7 +5069,7 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
@@ -5087,53 +5078,53 @@
         <v>1</v>
       </c>
       <c r="T40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 48285-2023 artfynd.xlsx", "A 48285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 47787-2025 artfynd.xlsx", "A 47787-2025")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 48285-2023 karta.png", "A 48285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 47787-2025 karta.png", "A 47787-2025")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 48285-2023 georefererad karta.tif", "A 48285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 47787-2025 georefererad karta.tif", "A 47787-2025")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 48285-2023 FSC-klagomål.docx", "A 48285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 47787-2025 FSC-klagomål.docx", "A 47787-2025")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 48285-2023 FSC-klagomål mail.docx", "A 48285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 47787-2025 FSC-klagomål mail.docx", "A 47787-2025")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 48285-2023 tillsynsbegäran.docx", "A 48285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 47787-2025 tillsynsbegäran.docx", "A 47787-2025")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 48285-2023 tillsynsbegäran mail.docx", "A 48285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 47787-2025 tillsynsbegäran mail.docx", "A 47787-2025")</f>
         <v/>
       </c>
       <c r="AE40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 48285-2023 prioriterade fågelarter.docx", "A 48285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 47787-2025 prioriterade fågelarter.docx", "A 47787-2025")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 14177-2026</t>
+          <t>A 38907-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5147,10 +5138,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46099</v>
+        <v>45163</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5168,16 +5159,16 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
         <v>0</v>
@@ -5192,7 +5183,7 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -5204,46 +5195,50 @@
         <v>1</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 14177-2026 artfynd.xlsx", "A 14177-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 38907-2023 artfynd.xlsx", "A 38907-2023")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 14177-2026 karta.png", "A 14177-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 38907-2023 karta.png", "A 38907-2023")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 14177-2026 georefererad karta.tif", "A 14177-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 38907-2023 georefererad karta.tif", "A 38907-2023")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 14177-2026 FSC-klagomål.docx", "A 14177-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 38907-2023 FSC-klagomål.docx", "A 38907-2023")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 14177-2026 FSC-klagomål mail.docx", "A 14177-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 38907-2023 FSC-klagomål mail.docx", "A 38907-2023")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 14177-2026 tillsynsbegäran.docx", "A 14177-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 38907-2023 tillsynsbegäran.docx", "A 38907-2023")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 14177-2026 tillsynsbegäran mail.docx", "A 14177-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 38907-2023 tillsynsbegäran mail.docx", "A 38907-2023")</f>
+        <v/>
+      </c>
+      <c r="AE41">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 38907-2023 prioriterade fågelarter.docx", "A 38907-2023")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 27093-2023</t>
+          <t>A 48285-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5257,10 +5252,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45096</v>
+        <v>45205</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5278,7 +5273,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>5.9</v>
+        <v>1.1</v>
       </c>
       <c r="J42" t="n">
         <v>1</v>
@@ -5322,42 +5317,42 @@
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 27093-2023 artfynd.xlsx", "A 27093-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 48285-2023 artfynd.xlsx", "A 48285-2023")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 27093-2023 karta.png", "A 27093-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 48285-2023 karta.png", "A 48285-2023")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 27093-2023 georefererad karta.tif", "A 27093-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 48285-2023 georefererad karta.tif", "A 48285-2023")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 27093-2023 FSC-klagomål.docx", "A 27093-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 48285-2023 FSC-klagomål.docx", "A 48285-2023")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 27093-2023 FSC-klagomål mail.docx", "A 27093-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 48285-2023 FSC-klagomål mail.docx", "A 48285-2023")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 27093-2023 tillsynsbegäran.docx", "A 27093-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 48285-2023 tillsynsbegäran.docx", "A 48285-2023")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 27093-2023 tillsynsbegäran mail.docx", "A 27093-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 48285-2023 tillsynsbegäran mail.docx", "A 48285-2023")</f>
         <v/>
       </c>
       <c r="AE42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 27093-2023 prioriterade fågelarter.docx", "A 27093-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 48285-2023 prioriterade fågelarter.docx", "A 48285-2023")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 47941-2024</t>
+          <t>A 14121-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5371,10 +5366,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45589</v>
+        <v>44651</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5386,16 +5381,11 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>1.4</v>
+        <v>4.4</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -5404,7 +5394,7 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
         <v>0</v>
@@ -5416,10 +5406,10 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>1</v>
@@ -5428,46 +5418,46 @@
         <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Brunfläckig pärlemorfjäril</t>
+          <t>Hårklomossa</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 47941-2024 artfynd.xlsx", "A 47941-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 14121-2022 artfynd.xlsx", "A 14121-2022")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 47941-2024 karta.png", "A 47941-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 14121-2022 karta.png", "A 14121-2022")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 47941-2024 georefererad karta.tif", "A 47941-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 14121-2022 georefererad karta.tif", "A 14121-2022")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 47941-2024 FSC-klagomål.docx", "A 47941-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 14121-2022 FSC-klagomål.docx", "A 14121-2022")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 47941-2024 FSC-klagomål mail.docx", "A 47941-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 14121-2022 FSC-klagomål mail.docx", "A 14121-2022")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 47941-2024 tillsynsbegäran.docx", "A 47941-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 14121-2022 tillsynsbegäran.docx", "A 14121-2022")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 47941-2024 tillsynsbegäran mail.docx", "A 47941-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 14121-2022 tillsynsbegäran mail.docx", "A 14121-2022")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 14121-2022</t>
+          <t>A 47941-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5481,10 +5471,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44651</v>
+        <v>45589</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5496,21 +5486,26 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>4.4</v>
+        <v>1.4</v>
       </c>
       <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
         <v>1</v>
       </c>
-      <c r="K44" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" t="n">
-        <v>0</v>
-      </c>
       <c r="N44" t="n">
         <v>0</v>
       </c>
@@ -5521,10 +5516,10 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>
@@ -5533,46 +5528,46 @@
         <v>1</v>
       </c>
       <c r="U44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Hårklomossa</t>
+          <t>Brunfläckig pärlemorfjäril</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 14121-2022 artfynd.xlsx", "A 14121-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 47941-2024 artfynd.xlsx", "A 47941-2024")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 14121-2022 karta.png", "A 14121-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 47941-2024 karta.png", "A 47941-2024")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 14121-2022 georefererad karta.tif", "A 14121-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 47941-2024 georefererad karta.tif", "A 47941-2024")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 14121-2022 FSC-klagomål.docx", "A 14121-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 47941-2024 FSC-klagomål.docx", "A 47941-2024")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 14121-2022 FSC-klagomål mail.docx", "A 14121-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 47941-2024 FSC-klagomål mail.docx", "A 47941-2024")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 14121-2022 tillsynsbegäran.docx", "A 14121-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 47941-2024 tillsynsbegäran.docx", "A 47941-2024")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 14121-2022 tillsynsbegäran mail.docx", "A 14121-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 47941-2024 tillsynsbegäran mail.docx", "A 47941-2024")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 33297-2023</t>
+          <t>A 27071-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5586,10 +5581,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45116</v>
+        <v>46186</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5601,20 +5596,25 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>7.2</v>
+        <v>9.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
         <v>0</v>
@@ -5626,10 +5626,10 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>1</v>
@@ -5638,46 +5638,46 @@
         <v>1</v>
       </c>
       <c r="U45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 33297-2023 artfynd.xlsx", "A 33297-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 27071-2026 artfynd.xlsx", "A 27071-2026")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 33297-2023 karta.png", "A 33297-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 27071-2026 karta.png", "A 27071-2026")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 33297-2023 georefererad karta.tif", "A 33297-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 27071-2026 georefererad karta.tif", "A 27071-2026")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 33297-2023 FSC-klagomål.docx", "A 33297-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 27071-2026 FSC-klagomål.docx", "A 27071-2026")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 33297-2023 FSC-klagomål mail.docx", "A 33297-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 27071-2026 FSC-klagomål mail.docx", "A 27071-2026")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 33297-2023 tillsynsbegäran.docx", "A 33297-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 27071-2026 tillsynsbegäran.docx", "A 27071-2026")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 33297-2023 tillsynsbegäran mail.docx", "A 33297-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 27071-2026 tillsynsbegäran mail.docx", "A 27071-2026")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 27071-2026</t>
+          <t>A 27072-2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5694,7 +5694,7 @@
         <v>46186</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5712,13 +5712,13 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>9.9</v>
+        <v>7.6</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -5748,46 +5748,50 @@
         <v>1</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 27071-2026 artfynd.xlsx", "A 27071-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 27072-2026 artfynd.xlsx", "A 27072-2026")</f>
         <v/>
       </c>
       <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 27071-2026 karta.png", "A 27071-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 27072-2026 karta.png", "A 27072-2026")</f>
         <v/>
       </c>
       <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 27071-2026 georefererad karta.tif", "A 27071-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 27072-2026 georefererad karta.tif", "A 27072-2026")</f>
         <v/>
       </c>
       <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 27071-2026 FSC-klagomål.docx", "A 27071-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 27072-2026 FSC-klagomål.docx", "A 27072-2026")</f>
         <v/>
       </c>
       <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 27071-2026 FSC-klagomål mail.docx", "A 27071-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 27072-2026 FSC-klagomål mail.docx", "A 27072-2026")</f>
         <v/>
       </c>
       <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 27071-2026 tillsynsbegäran.docx", "A 27071-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 27072-2026 tillsynsbegäran.docx", "A 27072-2026")</f>
         <v/>
       </c>
       <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 27071-2026 tillsynsbegäran mail.docx", "A 27071-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 27072-2026 tillsynsbegäran mail.docx", "A 27072-2026")</f>
+        <v/>
+      </c>
+      <c r="AE46">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 27072-2026 prioriterade fågelarter.docx", "A 27072-2026")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 27072-2026</t>
+          <t>A 26971-2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5801,10 +5805,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46186</v>
+        <v>46185</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5816,19 +5820,14 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>7.6</v>
+        <v>2.1</v>
       </c>
       <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
         <v>1</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
@@ -5858,50 +5857,46 @@
         <v>1</v>
       </c>
       <c r="U47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="W47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 27072-2026 artfynd.xlsx", "A 27072-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 26971-2026 artfynd.xlsx", "A 26971-2026")</f>
         <v/>
       </c>
       <c r="X47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 27072-2026 karta.png", "A 27072-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 26971-2026 karta.png", "A 26971-2026")</f>
         <v/>
       </c>
       <c r="Y47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 27072-2026 georefererad karta.tif", "A 27072-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 26971-2026 georefererad karta.tif", "A 26971-2026")</f>
         <v/>
       </c>
       <c r="AA47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 27072-2026 FSC-klagomål.docx", "A 27072-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 26971-2026 FSC-klagomål.docx", "A 26971-2026")</f>
         <v/>
       </c>
       <c r="AB47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 27072-2026 FSC-klagomål mail.docx", "A 27072-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 26971-2026 FSC-klagomål mail.docx", "A 26971-2026")</f>
         <v/>
       </c>
       <c r="AC47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 27072-2026 tillsynsbegäran.docx", "A 27072-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 26971-2026 tillsynsbegäran.docx", "A 26971-2026")</f>
         <v/>
       </c>
       <c r="AD47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 27072-2026 tillsynsbegäran mail.docx", "A 27072-2026")</f>
-        <v/>
-      </c>
-      <c r="AE47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 27072-2026 prioriterade fågelarter.docx", "A 27072-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 26971-2026 tillsynsbegäran mail.docx", "A 26971-2026")</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 26971-2026</t>
+          <t>A 47915-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5915,10 +5910,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46185</v>
+        <v>45589</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5930,14 +5925,19 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>2.1</v>
+        <v>5.8</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
@@ -5971,42 +5971,42 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 26971-2026 artfynd.xlsx", "A 26971-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 47915-2024 artfynd.xlsx", "A 47915-2024")</f>
         <v/>
       </c>
       <c r="X48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 26971-2026 karta.png", "A 26971-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 47915-2024 karta.png", "A 47915-2024")</f>
         <v/>
       </c>
       <c r="Y48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 26971-2026 georefererad karta.tif", "A 26971-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 47915-2024 georefererad karta.tif", "A 47915-2024")</f>
         <v/>
       </c>
       <c r="AA48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 26971-2026 FSC-klagomål.docx", "A 26971-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 47915-2024 FSC-klagomål.docx", "A 47915-2024")</f>
         <v/>
       </c>
       <c r="AB48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 26971-2026 FSC-klagomål mail.docx", "A 26971-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 47915-2024 FSC-klagomål mail.docx", "A 47915-2024")</f>
         <v/>
       </c>
       <c r="AC48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 26971-2026 tillsynsbegäran.docx", "A 26971-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 47915-2024 tillsynsbegäran.docx", "A 47915-2024")</f>
         <v/>
       </c>
       <c r="AD48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 26971-2026 tillsynsbegäran mail.docx", "A 26971-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 47915-2024 tillsynsbegäran mail.docx", "A 47915-2024")</f>
         <v/>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 2357-2022</t>
+          <t>A 42337-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6020,10 +6020,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44578</v>
+        <v>46307</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6035,8 +6035,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="J49" t="n">
         <v>1</v>
@@ -6072,43 +6077,39 @@
         <v>1</v>
       </c>
       <c r="U49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 2357-2022 artfynd.xlsx", "A 2357-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 42337-2026 artfynd.xlsx", "A 42337-2026")</f>
         <v/>
       </c>
       <c r="X49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 2357-2022 karta.png", "A 2357-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 42337-2026 karta.png", "A 42337-2026")</f>
         <v/>
       </c>
       <c r="Y49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 2357-2022 georefererad karta.tif", "A 2357-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 42337-2026 georefererad karta.tif", "A 42337-2026")</f>
         <v/>
       </c>
       <c r="AA49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 2357-2022 FSC-klagomål.docx", "A 2357-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 42337-2026 FSC-klagomål.docx", "A 42337-2026")</f>
         <v/>
       </c>
       <c r="AB49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 2357-2022 FSC-klagomål mail.docx", "A 2357-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 42337-2026 FSC-klagomål mail.docx", "A 42337-2026")</f>
         <v/>
       </c>
       <c r="AC49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 2357-2022 tillsynsbegäran.docx", "A 2357-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 42337-2026 tillsynsbegäran.docx", "A 42337-2026")</f>
         <v/>
       </c>
       <c r="AD49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 2357-2022 tillsynsbegäran mail.docx", "A 2357-2022")</f>
-        <v/>
-      </c>
-      <c r="AE49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 2357-2022 prioriterade fågelarter.docx", "A 2357-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 42337-2026 tillsynsbegäran mail.docx", "A 42337-2026")</f>
         <v/>
       </c>
     </row>
@@ -6132,7 +6133,7 @@
         <v>45614</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6224,7 +6225,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 42337-2026</t>
+          <t>A 2357-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6238,10 +6239,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46307</v>
+        <v>44578</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6253,13 +6254,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I51" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="J51" t="n">
         <v>1</v>
@@ -6295,39 +6291,43 @@
         <v>1</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 42337-2026 artfynd.xlsx", "A 42337-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 2357-2022 artfynd.xlsx", "A 2357-2022")</f>
         <v/>
       </c>
       <c r="X51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 42337-2026 karta.png", "A 42337-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 2357-2022 karta.png", "A 2357-2022")</f>
         <v/>
       </c>
       <c r="Y51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 42337-2026 georefererad karta.tif", "A 42337-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 2357-2022 georefererad karta.tif", "A 2357-2022")</f>
         <v/>
       </c>
       <c r="AA51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 42337-2026 FSC-klagomål.docx", "A 42337-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 2357-2022 FSC-klagomål.docx", "A 2357-2022")</f>
         <v/>
       </c>
       <c r="AB51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 42337-2026 FSC-klagomål mail.docx", "A 42337-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 2357-2022 FSC-klagomål mail.docx", "A 2357-2022")</f>
         <v/>
       </c>
       <c r="AC51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 42337-2026 tillsynsbegäran.docx", "A 42337-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 2357-2022 tillsynsbegäran.docx", "A 2357-2022")</f>
         <v/>
       </c>
       <c r="AD51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 42337-2026 tillsynsbegäran mail.docx", "A 42337-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 2357-2022 tillsynsbegäran mail.docx", "A 2357-2022")</f>
+        <v/>
+      </c>
+      <c r="AE51">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 2357-2022 prioriterade fågelarter.docx", "A 2357-2022")</f>
         <v/>
       </c>
     </row>
@@ -6351,7 +6351,7 @@
         <v>44805</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6424,7 +6424,7 @@
         <v>44805</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         <v>44861</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         <v>44607</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6648,7 +6648,7 @@
         <v>44692</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6721,7 +6721,7 @@
         <v>44609</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6794,7 +6794,7 @@
         <v>44497</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6867,7 +6867,7 @@
         <v>44594</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6940,7 +6940,7 @@
         <v>44853</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 65456-2021</t>
+          <t>A 23460-2024</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -7010,10 +7010,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44515</v>
+        <v>45453</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -7069,7 +7069,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 12977-2022</t>
+          <t>A 65456-2021</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -7083,10 +7083,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44643</v>
+        <v>44515</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7099,7 +7099,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -7142,7 +7142,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 68578-2021</t>
+          <t>A 24707-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -7156,10 +7156,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44529</v>
+        <v>45798</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7171,13 +7171,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -7220,7 +7215,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 67998-2021</t>
+          <t>A 63008-2021</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7234,10 +7229,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44525</v>
+        <v>44505</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7249,8 +7244,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I64" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -7293,7 +7293,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 63906-2021</t>
+          <t>A 5218-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7307,10 +7307,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44509</v>
+        <v>45330</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7328,7 +7328,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.6</v>
+        <v>3.3</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -7371,7 +7371,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 63008-2021</t>
+          <t>A 12977-2022</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7385,10 +7385,10 @@
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>44505</v>
+        <v>44643</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7400,13 +7400,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I66" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -7449,7 +7444,7 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>A 45861-2023</t>
+          <t>A 68578-2021</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -7459,14 +7454,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>45195</v>
+        <v>44529</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7484,7 +7479,7 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -7527,7 +7522,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 6394-2024</t>
+          <t>A 67998-2021</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7537,14 +7532,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>45338</v>
+        <v>44525</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7556,13 +7551,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I68" t="n">
-        <v>0.9</v>
+        <v>2.9</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7605,7 +7595,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 18675-2025</t>
+          <t>A 63906-2021</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7619,10 +7609,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45763</v>
+        <v>44509</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7634,8 +7624,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I69" t="n">
-        <v>6</v>
+        <v>1.6</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7678,7 +7673,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 38743-2022</t>
+          <t>A 26820-2025</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7692,10 +7687,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>44816</v>
+        <v>45810</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7707,13 +7702,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I70" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7756,7 +7746,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 13405-2024</t>
+          <t>A 26783-2025</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7770,10 +7760,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45387</v>
+        <v>45810</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7786,7 +7776,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7829,7 +7819,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 26176-2024</t>
+          <t>A 28367-2025</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7843,10 +7833,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>45468</v>
+        <v>45819</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7864,7 +7854,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0.7</v>
+        <v>6.1</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7907,7 +7897,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 21935-2024</t>
+          <t>A 28368-2025</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7921,10 +7911,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45443</v>
+        <v>45819</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7942,7 +7932,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>1.8</v>
+        <v>8.1</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7985,7 +7975,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 23460-2024</t>
+          <t>A 23066-2022</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7999,10 +7989,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45453</v>
+        <v>44719</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8015,7 +8005,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -8058,7 +8048,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 770-2026</t>
+          <t>A 38874-2025</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -8072,10 +8062,10 @@
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46027</v>
+        <v>45887</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8087,8 +8077,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>2.2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -8131,7 +8126,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 5218-2024</t>
+          <t>A 18675-2025</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -8145,10 +8140,10 @@
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45330</v>
+        <v>45763</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8160,13 +8155,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I76" t="n">
-        <v>3.3</v>
+        <v>6</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -8209,7 +8199,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 3177-2022</t>
+          <t>A 8074-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8223,10 +8213,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>44582</v>
+        <v>45351</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8238,8 +8228,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I77" t="n">
-        <v>3.7</v>
+        <v>0.7</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -8282,7 +8277,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 50378-2024</t>
+          <t>A 7975-2025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8296,10 +8291,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45601</v>
+        <v>45707</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8317,7 +8312,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -8360,7 +8355,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 38874-2025</t>
+          <t>A 29607-2022</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -8374,10 +8369,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>45887</v>
+        <v>44754</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8395,7 +8390,7 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>8.300000000000001</v>
+        <v>2.1</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -8438,7 +8433,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 24707-2025</t>
+          <t>A 33404-2025</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8452,10 +8447,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45798</v>
+        <v>45841</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8468,7 +8463,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8511,7 +8506,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 38875-2025</t>
+          <t>A 37672-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8521,14 +8516,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45887</v>
+        <v>45541</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8546,7 +8541,7 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8589,7 +8584,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 26783-2025</t>
+          <t>A 59863-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8603,10 +8598,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45810</v>
+        <v>45639</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8619,7 +8614,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8662,7 +8657,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 10321-2023</t>
+          <t>A 56478-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8676,10 +8671,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>44986</v>
+        <v>45624</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8692,7 +8687,7 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8735,7 +8730,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 26820-2025</t>
+          <t>A 41767-2025</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8749,10 +8744,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45810</v>
+        <v>45902</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8764,8 +8759,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I84" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8825,7 +8825,7 @@
         <v>45902</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8886,7 +8886,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 41767-2025</t>
+          <t>A 8062-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8900,10 +8900,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45902</v>
+        <v>45351</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8921,7 +8921,7 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8964,7 +8964,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 57234-2024</t>
+          <t>A 21952-2024</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8974,14 +8974,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45629</v>
+        <v>45443</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8999,7 +8999,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -9042,7 +9042,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 43691-2025</t>
+          <t>A 43694-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -9059,7 +9059,7 @@
         <v>45912</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9077,7 +9077,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.7</v>
+        <v>6.6</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -9120,7 +9120,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 43689-2025</t>
+          <t>A 43691-2025</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -9137,7 +9137,7 @@
         <v>45912</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9155,7 +9155,7 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -9198,7 +9198,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 43694-2025</t>
+          <t>A 10321-2023</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -9212,10 +9212,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45912</v>
+        <v>44986</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9227,13 +9227,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>6.6</v>
+        <v>1.3</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -9276,7 +9271,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 28367-2025</t>
+          <t>A 43689-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -9290,10 +9285,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45819</v>
+        <v>45912</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9311,7 +9306,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>6.1</v>
+        <v>1.4</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -9354,7 +9349,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 28368-2025</t>
+          <t>A 37333-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -9364,14 +9359,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45819</v>
+        <v>45876</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9383,13 +9378,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I92" t="n">
-        <v>8.1</v>
+        <v>0.7</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -9432,7 +9422,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 6387-2024</t>
+          <t>A 37265-2025</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -9442,14 +9432,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45338</v>
+        <v>45876</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9461,13 +9451,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I93" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -9510,7 +9495,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 23066-2022</t>
+          <t>A 36437-2024</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -9524,10 +9509,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44719</v>
+        <v>45535</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9540,7 +9525,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -9583,7 +9568,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 59158-2022</t>
+          <t>A 15594-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9593,14 +9578,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>44904</v>
+        <v>45747</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9612,13 +9597,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I95" t="n">
-        <v>3.7</v>
+        <v>1.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -9661,7 +9641,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 5277-2024</t>
+          <t>A 38921-2023</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9675,10 +9655,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45330</v>
+        <v>45163</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9690,8 +9670,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I96" t="n">
-        <v>0.5</v>
+        <v>2.2</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9734,7 +9719,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 33404-2025</t>
+          <t>A 62972-2023</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9748,10 +9733,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45841</v>
+        <v>45272</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9764,7 +9749,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9807,7 +9792,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 48625-2025</t>
+          <t>A 38875-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9821,10 +9806,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45936</v>
+        <v>45887</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9836,8 +9821,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I98" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9880,7 +9870,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 59863-2024</t>
+          <t>A 48625-2025</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9894,10 +9884,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45639</v>
+        <v>45936</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9953,7 +9943,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 43768-2024</t>
+          <t>A 2565-2022</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9967,10 +9957,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45569</v>
+        <v>44579</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9983,7 +9973,7 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>7</v>
+        <v>1.4</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -10043,7 +10033,7 @@
         <v>45947</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10104,7 +10094,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 52099-2025</t>
+          <t>A 12143-2025</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -10114,14 +10104,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45952</v>
+        <v>45729</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10133,8 +10123,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I102" t="n">
-        <v>2.6</v>
+        <v>1.3</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -10177,7 +10172,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 37333-2025</t>
+          <t>A 9273-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -10187,14 +10182,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45876</v>
+        <v>46070</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10207,7 +10202,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -10250,7 +10245,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 37265-2025</t>
+          <t>A 12159-2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -10264,10 +10259,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45876</v>
+        <v>46086</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10279,8 +10274,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I104" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -10323,7 +10323,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 47935-2024</t>
+          <t>A 12160-2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -10337,10 +10337,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45589</v>
+        <v>46086</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10358,7 +10358,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -10401,7 +10401,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 21952-2024</t>
+          <t>A 52099-2025</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -10411,14 +10411,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45443</v>
+        <v>45952</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10430,13 +10430,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I106" t="n">
-        <v>0.7</v>
+        <v>2.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -10479,7 +10474,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 15594-2025</t>
+          <t>A 51653-2023</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -10493,10 +10488,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45747</v>
+        <v>45222</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10508,8 +10503,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I107" t="n">
-        <v>1.5</v>
+        <v>3.9</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -10552,7 +10552,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 52566-2023</t>
+          <t>A 12936-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10566,10 +10566,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45219</v>
+        <v>46092</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10581,8 +10581,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I108" t="n">
-        <v>1.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -10625,7 +10630,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 55341-2025</t>
+          <t>A 13293-2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10639,10 +10644,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45971</v>
+        <v>46094</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10660,7 +10665,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -10703,7 +10708,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 62972-2023</t>
+          <t>A 13040-2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10717,10 +10722,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45272</v>
+        <v>46093</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10732,8 +10737,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I110" t="n">
-        <v>0.3</v>
+        <v>7.1</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10776,7 +10786,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 50377-2024</t>
+          <t>A 13039-2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10790,10 +10800,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45601</v>
+        <v>46093</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10811,7 +10821,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0.7</v>
+        <v>5.1</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10854,7 +10864,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 57086-2025</t>
+          <t>A 20577-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10868,10 +10878,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45979</v>
+        <v>45057</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10883,8 +10893,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I112" t="n">
-        <v>6.1</v>
+        <v>1.8</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10927,7 +10942,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 60708-2025</t>
+          <t>A 55341-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10941,10 +10956,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45996</v>
+        <v>45971</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10956,8 +10971,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I113" t="n">
-        <v>1.9</v>
+        <v>3.4</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -11000,7 +11020,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 11085-2023</t>
+          <t>A 60907-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -11010,14 +11030,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>44986</v>
+        <v>45261</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11029,8 +11049,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I114" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -11073,7 +11098,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 60736-2025</t>
+          <t>A 45365-2023</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -11087,10 +11112,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45996</v>
+        <v>45192</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11103,7 +11128,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -11146,7 +11171,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 48118-2023</t>
+          <t>A 57086-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -11156,14 +11181,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45205</v>
+        <v>45979</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11175,13 +11200,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I116" t="n">
-        <v>1.6</v>
+        <v>6.1</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -11224,7 +11244,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 38917-2023</t>
+          <t>A 6387-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -11234,14 +11254,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45163</v>
+        <v>45338</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11259,7 +11279,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -11302,7 +11322,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 50764-2024</t>
+          <t>A 26176-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -11316,10 +11336,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>45602</v>
+        <v>45468</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11337,7 +11357,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>2.4</v>
+        <v>0.7</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -11380,7 +11400,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 9273-2026</t>
+          <t>A 3177-2022</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -11394,10 +11414,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46070</v>
+        <v>44582</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11410,7 +11430,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>2.3</v>
+        <v>3.7</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -11453,7 +11473,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 38921-2023</t>
+          <t>A 50766-2024</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -11467,10 +11487,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>45163</v>
+        <v>45602</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11488,7 +11508,7 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -11531,7 +11551,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 12159-2026</t>
+          <t>A 8184-2022</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -11545,10 +11565,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46086</v>
+        <v>44609</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11560,13 +11580,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I121" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -11609,7 +11624,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 12160-2026</t>
+          <t>A 52523-2024</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -11623,10 +11638,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46086</v>
+        <v>45609</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11644,7 +11659,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0.9</v>
+        <v>4.4</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -11687,7 +11702,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 13039-2026</t>
+          <t>A 18913-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11701,10 +11716,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46093</v>
+        <v>46129</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11722,7 +11737,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>5.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -11765,7 +11780,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 13040-2026</t>
+          <t>A 18506-2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11779,10 +11794,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46093</v>
+        <v>46127</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11794,13 +11809,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I124" t="n">
-        <v>7.1</v>
+        <v>1.6</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -11843,7 +11853,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 12936-2026</t>
+          <t>A 60736-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11857,10 +11867,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>46092</v>
+        <v>45996</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11872,13 +11882,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I125" t="n">
-        <v>8.800000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11921,7 +11926,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 13293-2026</t>
+          <t>A 19227-2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11935,10 +11940,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46094</v>
+        <v>46132</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11950,13 +11955,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I126" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11999,7 +11999,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 63905-2021</t>
+          <t>A 60708-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -12013,10 +12013,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>44509</v>
+        <v>45996</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12028,13 +12028,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I127" t="n">
-        <v>3.7</v>
+        <v>1.9</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -12077,7 +12072,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 20577-2023</t>
+          <t>A 54515-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -12087,14 +12082,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45057</v>
+        <v>45233</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12106,13 +12101,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I128" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -12155,7 +12145,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 10797-2023</t>
+          <t>A 38917-2023</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -12169,10 +12159,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>44989</v>
+        <v>45163</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12184,8 +12174,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I129" t="n">
-        <v>9.5</v>
+        <v>2.2</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -12228,7 +12223,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 44457-2022</t>
+          <t>A 54994-2024</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -12242,10 +12237,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44839</v>
+        <v>45621</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12257,8 +12252,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I130" t="n">
-        <v>6.8</v>
+        <v>0.5</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -12301,7 +12301,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 29482-2023</t>
+          <t>A 48118-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -12315,10 +12315,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45106</v>
+        <v>45205</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12330,8 +12330,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I131" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -12374,7 +12379,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 18506-2026</t>
+          <t>A 13236-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -12388,10 +12393,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>46127</v>
+        <v>45735</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12403,8 +12408,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I132" t="n">
-        <v>1.6</v>
+        <v>18.5</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -12447,7 +12457,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 19227-2026</t>
+          <t>A 770-2026</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -12461,10 +12471,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46132</v>
+        <v>46027</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12477,7 +12487,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -12520,7 +12530,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 18913-2026</t>
+          <t>A 38233-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -12530,14 +12540,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>46129</v>
+        <v>45160</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12549,13 +12559,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I134" t="n">
-        <v>8.300000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -12598,7 +12603,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 13236-2025</t>
+          <t>A 10674-2024</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -12608,14 +12613,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45735</v>
+        <v>45369</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12633,7 +12638,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>18.5</v>
+        <v>0.3</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -12676,7 +12681,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 11084-2023</t>
+          <t>A 60933-2024</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12690,10 +12695,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44986</v>
+        <v>45645</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12705,8 +12710,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I136" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -12749,7 +12759,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 56478-2024</t>
+          <t>A 73693-2021</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12763,10 +12773,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45624</v>
+        <v>44552</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12779,7 +12789,7 @@
         </is>
       </c>
       <c r="I137" t="n">
-        <v>1.4</v>
+        <v>3.6</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -12822,7 +12832,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 43752-2025</t>
+          <t>A 54082-2024</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12836,10 +12846,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45912</v>
+        <v>45616</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12852,7 +12862,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>3.1</v>
+        <v>6.3</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -12895,7 +12905,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 60933-2024</t>
+          <t>A 60937-2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12912,7 +12922,7 @@
         <v>45645</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12930,7 +12940,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12973,7 +12983,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 61750-2021</t>
+          <t>A 60940-2024</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12987,10 +12997,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>44501</v>
+        <v>45645</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13008,7 +13018,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -13051,7 +13061,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 29607-2022</t>
+          <t>A 43752-2025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -13065,10 +13075,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>44754</v>
+        <v>45912</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13080,13 +13090,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I141" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -13129,7 +13134,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 6240-2024</t>
+          <t>A 52566-2023</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -13143,10 +13148,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45337</v>
+        <v>45219</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13159,7 +13164,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -13202,7 +13207,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 54082-2024</t>
+          <t>A 20567-2026</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -13216,10 +13221,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45616</v>
+        <v>46140</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13231,8 +13236,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I143" t="n">
-        <v>6.3</v>
+        <v>7.8</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -13275,7 +13285,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 20478-2026</t>
+          <t>A 20568-2026</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -13292,7 +13302,7 @@
         <v>46140</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13310,7 +13320,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1.1</v>
+        <v>6.3</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -13353,7 +13363,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 33658-2024</t>
+          <t>A 20478-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -13367,10 +13377,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45520</v>
+        <v>46140</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13382,8 +13392,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I145" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -13426,7 +13441,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 38233-2023</t>
+          <t>A 57234-2024</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -13436,14 +13451,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45160</v>
+        <v>45629</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13455,8 +13470,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I146" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -13499,7 +13519,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 20567-2026</t>
+          <t>A 6240-2024</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -13513,10 +13533,10 @@
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>46140</v>
+        <v>45337</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13528,13 +13548,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I147" t="n">
-        <v>7.8</v>
+        <v>1.9</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -13577,7 +13592,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 20568-2026</t>
+          <t>A 21440-2026</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -13591,10 +13606,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46140</v>
+        <v>46148</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13612,7 +13627,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -13655,7 +13670,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 50766-2024</t>
+          <t>A 21442-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -13669,10 +13684,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45602</v>
+        <v>46148</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13690,7 +13705,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>2.1</v>
+        <v>4.1</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -13733,7 +13748,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 21440-2026</t>
+          <t>A 21401-2026</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -13750,7 +13765,7 @@
         <v>46148</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13762,13 +13777,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I150" t="n">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -13811,7 +13821,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 21442-2026</t>
+          <t>A 6394-2024</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -13821,14 +13831,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46148</v>
+        <v>45338</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13846,7 +13856,7 @@
         </is>
       </c>
       <c r="I151" t="n">
-        <v>4.1</v>
+        <v>0.9</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -13889,7 +13899,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 50207-2024</t>
+          <t>A 44841-2023</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13903,10 +13913,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45600</v>
+        <v>45190</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13918,8 +13928,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I152" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -13962,7 +13977,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 50208-2024</t>
+          <t>A 11085-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13976,10 +13991,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45600</v>
+        <v>44986</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13992,7 +14007,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -14035,7 +14050,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 21401-2026</t>
+          <t>A 46222-2024</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -14049,10 +14064,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46148</v>
+        <v>45581</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14064,8 +14079,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I154" t="n">
-        <v>3.5</v>
+        <v>0.9</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -14108,7 +14128,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 44841-2023</t>
+          <t>A 46219-2024</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -14122,10 +14142,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45190</v>
+        <v>45581</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14143,7 +14163,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -14186,7 +14206,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 46222-2024</t>
+          <t>A 23230-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -14200,10 +14220,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45581</v>
+        <v>46162</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14264,7 +14284,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 46219-2024</t>
+          <t>A 23229-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -14278,10 +14298,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>45581</v>
+        <v>46162</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14299,7 +14319,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -14359,7 +14379,7 @@
         <v>45742</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14420,7 +14440,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 12143-2025</t>
+          <t>A 23854-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -14430,14 +14450,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>45729</v>
+        <v>46167</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14455,7 +14475,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1.3</v>
+        <v>20.9</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -14498,7 +14518,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 52523-2024</t>
+          <t>A 5277-2024</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -14512,10 +14532,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45609</v>
+        <v>45330</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14527,13 +14547,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I160" t="n">
-        <v>4.4</v>
+        <v>0.5</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -14576,7 +14591,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 23230-2026</t>
+          <t>A 50378-2024</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -14590,10 +14605,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46162</v>
+        <v>45601</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14611,7 +14626,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>0.9</v>
+        <v>4.9</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -14654,7 +14669,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 23229-2026</t>
+          <t>A 33293-2023</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -14668,10 +14683,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46162</v>
+        <v>45116</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14683,13 +14698,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I162" t="n">
-        <v>2.9</v>
+        <v>17.2</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -14732,7 +14742,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 8184-2022</t>
+          <t>A 44807-2023</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -14746,10 +14756,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>44609</v>
+        <v>45190</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14761,8 +14771,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I163" t="n">
-        <v>1.7</v>
+        <v>5.4</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -14805,7 +14820,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 60937-2024</t>
+          <t>A 24460-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -14819,10 +14834,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>45645</v>
+        <v>46170</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14834,13 +14849,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I164" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -14883,7 +14893,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 60940-2024</t>
+          <t>A 24462-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -14897,10 +14907,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45645</v>
+        <v>46170</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14912,13 +14922,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I165" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -14961,7 +14966,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 23854-2026</t>
+          <t>A 51652-2023</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -14975,10 +14980,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46167</v>
+        <v>45222</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14996,7 +15001,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>20.9</v>
+        <v>1.7</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -15039,7 +15044,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 44807-2023</t>
+          <t>A 24689-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -15053,10 +15058,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45190</v>
+        <v>46171</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15074,7 +15079,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>5.4</v>
+        <v>15.5</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -15117,7 +15122,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 24462-2026</t>
+          <t>A 44457-2022</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -15131,10 +15136,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46170</v>
+        <v>44839</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15147,7 +15152,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>0.8</v>
+        <v>6.8</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -15190,7 +15195,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 24689-2026</t>
+          <t>A 32211-2022</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -15204,10 +15209,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46171</v>
+        <v>44781</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15219,13 +15224,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I169" t="n">
-        <v>15.5</v>
+        <v>2.3</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -15268,7 +15268,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 24460-2026</t>
+          <t>A 13405-2024</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -15282,10 +15282,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46170</v>
+        <v>45387</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15298,7 +15298,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -15341,7 +15341,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 51652-2023</t>
+          <t>A 12729-2024</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -15355,10 +15355,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45222</v>
+        <v>45384</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15376,7 +15376,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -15419,7 +15419,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 33293-2023</t>
+          <t>A 26857-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -15433,10 +15433,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45116</v>
+        <v>46185</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15448,8 +15448,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I172" t="n">
-        <v>17.2</v>
+        <v>15.1</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -15492,7 +15497,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 32154-2023</t>
+          <t>A 26946-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -15506,10 +15511,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45119</v>
+        <v>46185</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15521,8 +15526,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I173" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -15565,7 +15575,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 26857-2026</t>
+          <t>A 26947-2026</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -15582,7 +15592,7 @@
         <v>46185</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15600,7 +15610,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>15.1</v>
+        <v>2</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -15643,7 +15653,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 26947-2026</t>
+          <t>A 27411-2026</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -15657,10 +15667,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46185</v>
+        <v>46189</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15678,7 +15688,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -15721,7 +15731,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 26946-2026</t>
+          <t>A 27745-2026</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -15735,10 +15745,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46185</v>
+        <v>46191</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15756,7 +15766,7 @@
         </is>
       </c>
       <c r="I176" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -15799,7 +15809,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 27411-2026</t>
+          <t>A 27746-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -15813,10 +15823,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15834,7 +15844,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -15877,7 +15887,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 8062-2024</t>
+          <t>A 28696-2026</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -15891,10 +15901,10 @@
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>45351</v>
+        <v>46198</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15912,7 +15922,7 @@
         </is>
       </c>
       <c r="I178" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -15955,7 +15965,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 8074-2024</t>
+          <t>A 28708-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -15969,10 +15979,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>45351</v>
+        <v>46198</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15990,7 +16000,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>0.7</v>
+        <v>2.8</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -16033,7 +16043,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 60907-2023</t>
+          <t>A 28695-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -16043,14 +16053,14 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>45261</v>
+        <v>46198</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16068,7 +16078,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>0.6</v>
+        <v>2.7</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -16111,7 +16121,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 27745-2026</t>
+          <t>A 29130-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -16125,10 +16135,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>46191</v>
+        <v>46202</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16146,7 +16156,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>1.7</v>
+        <v>10.3</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -16189,7 +16199,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 27746-2026</t>
+          <t>A 28930-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -16203,10 +16213,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46191</v>
+        <v>46199</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16218,13 +16228,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I182" t="n">
-        <v>1</v>
+        <v>2.7</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -16267,7 +16272,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 32211-2022</t>
+          <t>A 36339-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -16281,10 +16286,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>44781</v>
+        <v>46268</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16297,7 +16302,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>2.3</v>
+        <v>0.4</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -16340,7 +16345,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 28696-2026</t>
+          <t>A 36345-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -16354,10 +16359,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46198</v>
+        <v>46268</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16369,13 +16374,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I184" t="n">
-        <v>2.5</v>
+        <v>0.3</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -16418,7 +16418,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 28708-2026</t>
+          <t>A 36336-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -16432,10 +16432,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>46198</v>
+        <v>46268</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16447,13 +16447,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I185" t="n">
-        <v>2.8</v>
+        <v>1.1</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -16496,7 +16491,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 28930-2026</t>
+          <t>A 63905-2021</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -16510,10 +16505,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46199</v>
+        <v>44509</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16525,8 +16520,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I186" t="n">
-        <v>2.7</v>
+        <v>3.7</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -16569,7 +16569,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 28695-2026</t>
+          <t>A 38743-2022</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -16583,10 +16583,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46198</v>
+        <v>44816</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16604,7 +16604,7 @@
         </is>
       </c>
       <c r="I187" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -16647,7 +16647,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 29130-2026</t>
+          <t>A 31813-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -16661,10 +16661,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46202</v>
+        <v>46230</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16676,13 +16676,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I188" t="n">
-        <v>10.3</v>
+        <v>1.8</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -16725,7 +16720,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 73693-2021</t>
+          <t>A 47935-2024</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -16739,10 +16734,10 @@
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>44552</v>
+        <v>45589</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16754,8 +16749,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I189" t="n">
-        <v>3.6</v>
+        <v>2.2</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -16798,7 +16798,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 36437-2024</t>
+          <t>A 50377-2024</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -16812,10 +16812,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45535</v>
+        <v>45601</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16827,8 +16827,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I190" t="n">
-        <v>2.3</v>
+        <v>0.7</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -16871,7 +16876,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 45365-2023</t>
+          <t>A 31870-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -16885,10 +16890,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>45192</v>
+        <v>46231</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16900,8 +16905,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I191" t="n">
-        <v>5</v>
+        <v>1.5</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -16944,7 +16954,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 37672-2024</t>
+          <t>A 31871-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -16954,14 +16964,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45541</v>
+        <v>46231</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16979,7 +16989,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -17022,7 +17032,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 36339-2026</t>
+          <t>A 8059-2024</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -17036,10 +17046,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46268</v>
+        <v>45351</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17051,8 +17061,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I193" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -17095,7 +17110,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 36336-2026</t>
+          <t>A 29482-2023</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -17109,10 +17124,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46268</v>
+        <v>45106</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17125,7 +17140,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -17168,7 +17183,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 36345-2026</t>
+          <t>A 37809-2026</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -17182,10 +17197,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>46268</v>
+        <v>46279</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17198,7 +17213,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>0.3</v>
+        <v>2.9</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -17241,7 +17256,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 2565-2022</t>
+          <t>A 59158-2022</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -17251,14 +17266,14 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>44579</v>
+        <v>44904</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17270,8 +17285,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I196" t="n">
-        <v>1.4</v>
+        <v>3.7</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -17314,7 +17334,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 31813-2026</t>
+          <t>A 38126-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -17328,10 +17348,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46230</v>
+        <v>46281</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17343,8 +17363,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I197" t="n">
-        <v>1.8</v>
+        <v>5.5</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -17387,7 +17412,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 31870-2026</t>
+          <t>A 18773-2025</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -17401,10 +17426,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46231</v>
+        <v>45763</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17416,13 +17441,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I198" t="n">
-        <v>1.5</v>
+        <v>13</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -17465,7 +17485,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 31871-2026</t>
+          <t>A 32506-2026</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -17479,10 +17499,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46231</v>
+        <v>46239</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17500,7 +17520,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -17543,7 +17563,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 10674-2024</t>
+          <t>A 38651-2026</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -17553,14 +17573,14 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45369</v>
+        <v>46283</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17578,7 +17598,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>0.3</v>
+        <v>11.3</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -17621,7 +17641,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 18773-2025</t>
+          <t>A 38463-2026</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -17635,10 +17655,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>45763</v>
+        <v>46282</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17651,7 +17671,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>13</v>
+        <v>3.4</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -17694,7 +17714,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 51653-2023</t>
+          <t>A 10320-2023</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -17708,10 +17728,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>45222</v>
+        <v>44986</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17723,13 +17743,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I202" t="n">
-        <v>3.9</v>
+        <v>2.6</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -17772,7 +17787,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 12108-2024</t>
+          <t>A 32508-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -17786,10 +17801,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45376</v>
+        <v>46239</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17801,8 +17816,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I203" t="n">
-        <v>7.7</v>
+        <v>1.1</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -17845,7 +17865,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 54994-2024</t>
+          <t>A 38659-2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -17859,10 +17879,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45621</v>
+        <v>46283</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17880,7 +17900,7 @@
         </is>
       </c>
       <c r="I204" t="n">
-        <v>0.5</v>
+        <v>4.6</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -17923,7 +17943,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 37809-2026</t>
+          <t>A 10797-2023</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -17937,10 +17957,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46279</v>
+        <v>44989</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17953,7 +17973,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>2.9</v>
+        <v>9.5</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -17996,7 +18016,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 38126-2026</t>
+          <t>A 11084-2023</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -18010,10 +18030,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>46281</v>
+        <v>44986</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18025,13 +18045,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H206" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I206" t="n">
-        <v>5.5</v>
+        <v>2.7</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -18074,7 +18089,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 38463-2026</t>
+          <t>A 50764-2024</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -18088,10 +18103,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>46282</v>
+        <v>45602</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18103,8 +18118,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I207" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -18147,7 +18167,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 32508-2026</t>
+          <t>A 33658-2024</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -18161,10 +18181,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>46239</v>
+        <v>45520</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18176,13 +18196,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H208" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I208" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -18225,7 +18240,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 32506-2026</t>
+          <t>A 45861-2023</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -18235,14 +18250,14 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>46239</v>
+        <v>45195</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18260,7 +18275,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -18303,7 +18318,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 38659-2026</t>
+          <t>A 43768-2024</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -18317,10 +18332,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>46283</v>
+        <v>45569</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18332,13 +18347,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H210" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I210" t="n">
-        <v>4.6</v>
+        <v>7</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -18398,7 +18408,7 @@
         <v>46241</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18454,7 +18464,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 38651-2026</t>
+          <t>A 38738-2022</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -18468,10 +18478,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>46283</v>
+        <v>44816</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18489,7 +18499,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>11.3</v>
+        <v>0.9</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -18532,7 +18542,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 8059-2024</t>
+          <t>A 61750-2021</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -18546,10 +18556,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45351</v>
+        <v>44501</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18567,7 +18577,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -18610,7 +18620,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 54515-2023</t>
+          <t>A 7472-2025</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -18624,10 +18634,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>45233</v>
+        <v>45705</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18639,8 +18649,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I214" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -18683,7 +18698,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 38738-2022</t>
+          <t>A 31872-2026</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -18697,10 +18712,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>44816</v>
+        <v>46231</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18718,7 +18733,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>0.9</v>
+        <v>5.2</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -18761,7 +18776,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 12729-2024</t>
+          <t>A 50207-2024</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -18775,10 +18790,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45384</v>
+        <v>45600</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18790,13 +18805,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I216" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -18839,7 +18849,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 10320-2023</t>
+          <t>A 50208-2024</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -18853,10 +18863,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>44986</v>
+        <v>45600</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18869,7 +18879,7 @@
         </is>
       </c>
       <c r="I217" t="n">
-        <v>2.6</v>
+        <v>0.4</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -18912,7 +18922,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 7472-2025</t>
+          <t>A 29552-2026</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -18926,10 +18936,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45705</v>
+        <v>46204</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18947,7 +18957,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -18990,7 +19000,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 7975-2025</t>
+          <t>A 12108-2024</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -19004,10 +19014,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45707</v>
+        <v>45376</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19019,13 +19029,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H219" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I219" t="n">
-        <v>5.3</v>
+        <v>7.7</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -19068,7 +19073,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 18831-2025</t>
+          <t>A 41890-2026</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -19082,10 +19087,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>45764</v>
+        <v>46303</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19103,7 +19108,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>4.2</v>
+        <v>6.3</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -19146,7 +19151,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 58629-2024</t>
+          <t>A 18831-2025</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -19160,10 +19165,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45635</v>
+        <v>45764</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19181,7 +19186,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>1.4</v>
+        <v>4.2</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -19224,7 +19229,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 27438-2024</t>
+          <t>A 35213-2026</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -19238,10 +19243,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45474</v>
+        <v>46260</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19253,8 +19258,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I222" t="n">
-        <v>2.6</v>
+        <v>9.5</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -19297,7 +19307,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 50102-2023</t>
+          <t>A 32154-2023</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -19311,10 +19321,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>45215</v>
+        <v>45119</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19326,13 +19336,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H223" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I223" t="n">
-        <v>3.9</v>
+        <v>2.3</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -19375,7 +19380,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 51996-2023</t>
+          <t>A 27438-2024</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -19389,10 +19394,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>45223</v>
+        <v>45474</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19404,13 +19409,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H224" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I224" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -19453,7 +19453,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 62982-2023</t>
+          <t>A 42336-2026</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -19467,10 +19467,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>45272</v>
+        <v>46307</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19482,8 +19482,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I225" t="n">
-        <v>3.5</v>
+        <v>7.1</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -19543,7 +19548,7 @@
         <v>45581</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19604,7 +19609,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 31872-2026</t>
+          <t>A 28789-2026</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -19618,10 +19623,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>46231</v>
+        <v>46195</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19633,13 +19638,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H227" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I227" t="n">
-        <v>5.2</v>
+        <v>2.7</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -19682,7 +19682,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 41889-2026</t>
+          <t>A 51996-2023</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -19696,10 +19696,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>46303</v>
+        <v>45223</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19717,7 +19717,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>5.6</v>
+        <v>2</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -19760,7 +19760,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 29552-2026</t>
+          <t>A 58629-2024</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -19774,10 +19774,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>46204</v>
+        <v>45635</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19795,7 +19795,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -19838,7 +19838,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 41890-2026</t>
+          <t>A 41889-2026</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -19855,7 +19855,7 @@
         <v>46303</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19873,7 +19873,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>6.3</v>
+        <v>5.6</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -19916,7 +19916,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 35213-2026</t>
+          <t>A 50102-2023</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -19930,10 +19930,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>46260</v>
+        <v>45215</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19951,7 +19951,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>9.5</v>
+        <v>3.9</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -19994,7 +19994,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 28789-2026</t>
+          <t>A 62982-2023</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -20008,10 +20008,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>46195</v>
+        <v>45272</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20024,7 +20024,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -20067,7 +20067,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 42336-2026</t>
+          <t>A 21935-2024</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -20081,10 +20081,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>46307</v>
+        <v>45443</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20102,7 +20102,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>7.1</v>
+        <v>1.8</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -20162,7 +20162,7 @@
         <v>44587</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20235,7 +20235,7 @@
         <v>45805</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20313,7 +20313,7 @@
         <v>45805</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20391,7 +20391,7 @@
         <v>45729</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20469,7 +20469,7 @@
         <v>45729</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20547,7 +20547,7 @@
         <v>45742</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20625,7 +20625,7 @@
         <v>45742</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20703,7 +20703,7 @@
         <v>45916</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>

--- a/Översikt DEGERFORS.xlsx
+++ b/Översikt DEGERFORS.xlsx
@@ -601,7 +601,7 @@
         <v>46160</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>46051</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
         <v>46160</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>46107</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>46190</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>46190</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>46161</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>45089</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>45175</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>45384</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>46160</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>45384</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>45163</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>44550</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>45175</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>45932</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>45163</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2662,7 +2662,7 @@
         <v>45205</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>45384</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>45351</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         <v>45866</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         <v>45559</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>45931</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3350,7 +3350,7 @@
         <v>46190</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>45163</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         <v>45931</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>45558</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3806,7 +3806,7 @@
         <v>45163</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         <v>45163</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         <v>46045</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         <v>46199</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         <v>44487</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>45116</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         <v>45163</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>45096</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         <v>45205</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         <v>45938</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4919,7 +4919,7 @@
         <v>45931</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
         <v>44651</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5133,7 +5133,7 @@
         <v>45163</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>45589</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
         <v>46186</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5467,7 +5467,7 @@
         <v>46186</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         <v>46099</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         <v>46185</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         <v>45589</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5906,7 +5906,7 @@
         <v>45614</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6015,7 +6015,7 @@
         <v>44578</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         <v>46307</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6234,7 +6234,7 @@
         <v>44805</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         <v>44805</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6380,7 +6380,7 @@
         <v>44861</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>44607</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6531,7 +6531,7 @@
         <v>44692</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6604,7 +6604,7 @@
         <v>44609</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6677,7 +6677,7 @@
         <v>44497</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6750,7 +6750,7 @@
         <v>44594</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         <v>44853</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6896,7 +6896,7 @@
         <v>44515</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6969,7 +6969,7 @@
         <v>44643</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7042,7 +7042,7 @@
         <v>44529</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7120,7 +7120,7 @@
         <v>44525</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7193,7 +7193,7 @@
         <v>44509</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7271,7 +7271,7 @@
         <v>44505</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7349,7 +7349,7 @@
         <v>45707</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7427,7 +7427,7 @@
         <v>45763</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7500,7 +7500,7 @@
         <v>44754</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7578,7 +7578,7 @@
         <v>45541</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7656,7 +7656,7 @@
         <v>45624</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7729,7 +7729,7 @@
         <v>45351</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7807,7 +7807,7 @@
         <v>44986</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7880,7 +7880,7 @@
         <v>45535</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7953,7 +7953,7 @@
         <v>45163</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
         <v>44579</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8104,7 +8104,7 @@
         <v>45261</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8182,7 +8182,7 @@
         <v>45468</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8260,7 +8260,7 @@
         <v>44582</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8333,7 +8333,7 @@
         <v>44609</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8406,7 +8406,7 @@
         <v>45602</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8484,7 +8484,7 @@
         <v>45609</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8562,7 +8562,7 @@
         <v>45621</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>45233</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8713,7 +8713,7 @@
         <v>45887</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8791,7 +8791,7 @@
         <v>45735</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         <v>45887</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         <v>45160</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9020,7 +9020,7 @@
         <v>45616</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9093,7 +9093,7 @@
         <v>45912</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9166,7 +9166,7 @@
         <v>46140</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9244,7 +9244,7 @@
         <v>46140</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9322,7 +9322,7 @@
         <v>45369</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9400,7 +9400,7 @@
         <v>46140</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9478,7 +9478,7 @@
         <v>45645</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         <v>45902</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9634,7 +9634,7 @@
         <v>45902</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9712,7 +9712,7 @@
         <v>44552</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9785,7 +9785,7 @@
         <v>45645</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9863,7 +9863,7 @@
         <v>45645</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9941,7 +9941,7 @@
         <v>45912</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10019,7 +10019,7 @@
         <v>45912</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10097,7 +10097,7 @@
         <v>45912</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10175,7 +10175,7 @@
         <v>45219</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10248,7 +10248,7 @@
         <v>46148</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10326,7 +10326,7 @@
         <v>45629</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10404,7 +10404,7 @@
         <v>46148</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10482,7 +10482,7 @@
         <v>46148</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10555,7 +10555,7 @@
         <v>45936</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10628,7 +10628,7 @@
         <v>45190</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10706,7 +10706,7 @@
         <v>45947</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10784,7 +10784,7 @@
         <v>45581</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10862,7 +10862,7 @@
         <v>45952</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10935,7 +10935,7 @@
         <v>45581</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11013,7 +11013,7 @@
         <v>45351</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11091,7 +11091,7 @@
         <v>45443</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11169,7 +11169,7 @@
         <v>45971</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11247,7 +11247,7 @@
         <v>46162</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11325,7 +11325,7 @@
         <v>46162</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11403,7 +11403,7 @@
         <v>45272</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11476,7 +11476,7 @@
         <v>45742</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11554,7 +11554,7 @@
         <v>45979</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11627,7 +11627,7 @@
         <v>45729</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11705,7 +11705,7 @@
         <v>45222</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11783,7 +11783,7 @@
         <v>46167</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11861,7 +11861,7 @@
         <v>45057</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11939,7 +11939,7 @@
         <v>45192</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12012,7 +12012,7 @@
         <v>45338</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12090,7 +12090,7 @@
         <v>45996</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>45996</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12236,7 +12236,7 @@
         <v>45337</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12309,7 +12309,7 @@
         <v>46170</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12382,7 +12382,7 @@
         <v>45163</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         <v>46170</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12533,7 +12533,7 @@
         <v>45205</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12611,7 +12611,7 @@
         <v>45338</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12689,7 +12689,7 @@
         <v>44986</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12762,7 +12762,7 @@
         <v>46171</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12840,7 +12840,7 @@
         <v>46027</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12913,7 +12913,7 @@
         <v>45330</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12986,7 +12986,7 @@
         <v>45601</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13064,7 +13064,7 @@
         <v>45116</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13137,7 +13137,7 @@
         <v>45190</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13215,7 +13215,7 @@
         <v>45222</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13293,7 +13293,7 @@
         <v>46185</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13371,7 +13371,7 @@
         <v>46185</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13449,7 +13449,7 @@
         <v>44839</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13522,7 +13522,7 @@
         <v>46185</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13600,7 +13600,7 @@
         <v>44781</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13673,7 +13673,7 @@
         <v>45387</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13746,7 +13746,7 @@
         <v>45384</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13824,7 +13824,7 @@
         <v>46070</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13897,7 +13897,7 @@
         <v>46086</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13975,7 +13975,7 @@
         <v>46086</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14053,7 +14053,7 @@
         <v>46189</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14131,7 +14131,7 @@
         <v>46092</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14209,7 +14209,7 @@
         <v>46094</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14287,7 +14287,7 @@
         <v>46093</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14365,7 +14365,7 @@
         <v>46093</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14443,7 +14443,7 @@
         <v>46191</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14521,7 +14521,7 @@
         <v>46191</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14599,7 +14599,7 @@
         <v>46198</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14677,7 +14677,7 @@
         <v>46198</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14755,7 +14755,7 @@
         <v>46198</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14833,7 +14833,7 @@
         <v>46202</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14911,7 +14911,7 @@
         <v>46199</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14984,7 +14984,7 @@
         <v>46129</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15062,7 +15062,7 @@
         <v>46127</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15135,7 +15135,7 @@
         <v>46132</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15208,7 +15208,7 @@
         <v>44509</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15286,7 +15286,7 @@
         <v>44816</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15364,7 +15364,7 @@
         <v>45589</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15442,7 +15442,7 @@
         <v>45601</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15520,7 +15520,7 @@
         <v>45351</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15598,7 +15598,7 @@
         <v>45106</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15671,7 +15671,7 @@
         <v>44904</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15749,7 +15749,7 @@
         <v>45763</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15822,7 +15822,7 @@
         <v>44986</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15895,7 +15895,7 @@
         <v>46230</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15968,7 +15968,7 @@
         <v>44989</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16041,7 +16041,7 @@
         <v>44986</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16114,7 +16114,7 @@
         <v>45602</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16192,7 +16192,7 @@
         <v>45520</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16265,7 +16265,7 @@
         <v>46231</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16343,7 +16343,7 @@
         <v>46231</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16421,7 +16421,7 @@
         <v>45195</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16499,7 +16499,7 @@
         <v>45569</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16572,7 +16572,7 @@
         <v>46279</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16645,7 +16645,7 @@
         <v>46281</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16723,7 +16723,7 @@
         <v>46239</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16801,7 +16801,7 @@
         <v>46283</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16879,7 +16879,7 @@
         <v>46282</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16952,7 +16952,7 @@
         <v>46239</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17030,7 +17030,7 @@
         <v>46283</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17108,7 +17108,7 @@
         <v>44816</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17186,7 +17186,7 @@
         <v>46241</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17259,7 +17259,7 @@
         <v>44501</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17337,7 +17337,7 @@
         <v>45705</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17415,7 +17415,7 @@
         <v>45600</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17488,7 +17488,7 @@
         <v>45600</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17561,7 +17561,7 @@
         <v>45376</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17634,7 +17634,7 @@
         <v>45764</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17712,7 +17712,7 @@
         <v>46231</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17790,7 +17790,7 @@
         <v>45119</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17863,7 +17863,7 @@
         <v>45474</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17936,7 +17936,7 @@
         <v>45581</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18014,7 +18014,7 @@
         <v>45223</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18092,7 +18092,7 @@
         <v>45635</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18170,7 +18170,7 @@
         <v>45215</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18248,7 +18248,7 @@
         <v>46303</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18326,7 +18326,7 @@
         <v>45272</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18399,7 +18399,7 @@
         <v>46260</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18477,7 +18477,7 @@
         <v>45443</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18555,7 +18555,7 @@
         <v>45453</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18628,7 +18628,7 @@
         <v>46307</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18706,7 +18706,7 @@
         <v>45798</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18779,7 +18779,7 @@
         <v>45330</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18857,7 +18857,7 @@
         <v>46195</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18930,7 +18930,7 @@
         <v>45810</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19003,7 +19003,7 @@
         <v>45810</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19076,7 +19076,7 @@
         <v>46268</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19149,7 +19149,7 @@
         <v>45819</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19227,7 +19227,7 @@
         <v>45819</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19305,7 +19305,7 @@
         <v>46268</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19378,7 +19378,7 @@
         <v>46268</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19451,7 +19451,7 @@
         <v>46303</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19529,7 +19529,7 @@
         <v>44719</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19602,7 +19602,7 @@
         <v>45841</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19675,7 +19675,7 @@
         <v>45639</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19748,7 +19748,7 @@
         <v>45876</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19821,7 +19821,7 @@
         <v>45876</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19894,7 +19894,7 @@
         <v>45747</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19967,7 +19967,7 @@
         <v>44587</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20040,7 +20040,7 @@
         <v>45805</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20118,7 +20118,7 @@
         <v>45805</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20196,7 +20196,7 @@
         <v>45729</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20274,7 +20274,7 @@
         <v>45729</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20352,7 +20352,7 @@
         <v>45742</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20430,7 +20430,7 @@
         <v>45742</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20508,7 +20508,7 @@
         <v>45916</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>

--- a/Översikt DEGERFORS.xlsx
+++ b/Översikt DEGERFORS.xlsx
@@ -601,7 +601,7 @@
         <v>46160</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>46051</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -853,7 +853,7 @@
         <v>46160</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>46107</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>46190</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>46190</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>46161</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>45089</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>45175</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>45384</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>46160</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>45384</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         <v>45163</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2197,7 +2197,7 @@
         <v>44550</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>45175</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>45932</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>45163</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2662,7 +2662,7 @@
         <v>45205</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>45384</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>45351</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         <v>45866</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         <v>45559</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>45931</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3350,7 +3350,7 @@
         <v>46190</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>45163</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3581,7 +3581,7 @@
         <v>45931</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>45558</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3806,7 +3806,7 @@
         <v>45163</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         <v>45163</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
         <v>46045</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
         <v>46199</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4257,7 +4257,7 @@
         <v>44487</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>45116</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         <v>45163</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>45096</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         <v>45205</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         <v>45938</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4919,7 +4919,7 @@
         <v>45931</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
         <v>44651</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5133,7 +5133,7 @@
         <v>45163</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>45589</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5357,7 +5357,7 @@
         <v>46186</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5467,7 +5467,7 @@
         <v>46186</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         <v>46099</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         <v>46185</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         <v>45589</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5906,7 +5906,7 @@
         <v>45614</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6015,7 +6015,7 @@
         <v>44578</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         <v>46307</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6234,7 +6234,7 @@
         <v>44805</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         <v>44805</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6380,7 +6380,7 @@
         <v>44861</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>44607</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6531,7 +6531,7 @@
         <v>44692</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6604,7 +6604,7 @@
         <v>44609</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6677,7 +6677,7 @@
         <v>44497</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6750,7 +6750,7 @@
         <v>44594</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         <v>44853</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6896,7 +6896,7 @@
         <v>44515</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6969,7 +6969,7 @@
         <v>44643</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7042,7 +7042,7 @@
         <v>44529</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7120,7 +7120,7 @@
         <v>44525</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7193,7 +7193,7 @@
         <v>44509</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7271,7 +7271,7 @@
         <v>44505</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7349,7 +7349,7 @@
         <v>45707</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7427,7 +7427,7 @@
         <v>45763</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7500,7 +7500,7 @@
         <v>44754</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7578,7 +7578,7 @@
         <v>45541</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7656,7 +7656,7 @@
         <v>45624</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7729,7 +7729,7 @@
         <v>45351</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7807,7 +7807,7 @@
         <v>44986</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7880,7 +7880,7 @@
         <v>45535</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7953,7 +7953,7 @@
         <v>45163</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
         <v>44579</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8104,7 +8104,7 @@
         <v>45261</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8182,7 +8182,7 @@
         <v>45468</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8260,7 +8260,7 @@
         <v>44582</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8333,7 +8333,7 @@
         <v>44609</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8406,7 +8406,7 @@
         <v>45602</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8484,7 +8484,7 @@
         <v>45609</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8562,7 +8562,7 @@
         <v>45621</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>45233</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8713,7 +8713,7 @@
         <v>45887</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8791,7 +8791,7 @@
         <v>45735</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         <v>45887</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         <v>45160</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9020,7 +9020,7 @@
         <v>45616</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9093,7 +9093,7 @@
         <v>45912</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9166,7 +9166,7 @@
         <v>46140</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9244,7 +9244,7 @@
         <v>46140</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9322,7 +9322,7 @@
         <v>45369</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9400,7 +9400,7 @@
         <v>46140</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9478,7 +9478,7 @@
         <v>45645</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9556,7 +9556,7 @@
         <v>45902</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9634,7 +9634,7 @@
         <v>45902</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9712,7 +9712,7 @@
         <v>44552</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9785,7 +9785,7 @@
         <v>45645</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9863,7 +9863,7 @@
         <v>45645</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9941,7 +9941,7 @@
         <v>45912</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10019,7 +10019,7 @@
         <v>45912</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10097,7 +10097,7 @@
         <v>45912</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10175,7 +10175,7 @@
         <v>45219</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10248,7 +10248,7 @@
         <v>46148</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10326,7 +10326,7 @@
         <v>45629</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10404,7 +10404,7 @@
         <v>46148</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10482,7 +10482,7 @@
         <v>46148</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10555,7 +10555,7 @@
         <v>45936</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10628,7 +10628,7 @@
         <v>45190</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10706,7 +10706,7 @@
         <v>45947</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10784,7 +10784,7 @@
         <v>45581</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10862,7 +10862,7 @@
         <v>45952</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10935,7 +10935,7 @@
         <v>45581</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11013,7 +11013,7 @@
         <v>45351</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11091,7 +11091,7 @@
         <v>45443</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11169,7 +11169,7 @@
         <v>45971</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11247,7 +11247,7 @@
         <v>46162</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11325,7 +11325,7 @@
         <v>46162</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11403,7 +11403,7 @@
         <v>45272</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11476,7 +11476,7 @@
         <v>45742</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11554,7 +11554,7 @@
         <v>45979</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11627,7 +11627,7 @@
         <v>45729</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11705,7 +11705,7 @@
         <v>45222</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11783,7 +11783,7 @@
         <v>46167</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11861,7 +11861,7 @@
         <v>45057</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11939,7 +11939,7 @@
         <v>45192</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12012,7 +12012,7 @@
         <v>45338</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12090,7 +12090,7 @@
         <v>45996</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>45996</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12236,7 +12236,7 @@
         <v>45337</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12309,7 +12309,7 @@
         <v>46170</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12382,7 +12382,7 @@
         <v>45163</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         <v>46170</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12533,7 +12533,7 @@
         <v>45205</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12611,7 +12611,7 @@
         <v>45338</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12689,7 +12689,7 @@
         <v>44986</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12762,7 +12762,7 @@
         <v>46171</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12840,7 +12840,7 @@
         <v>46027</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12913,7 +12913,7 @@
         <v>45330</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12986,7 +12986,7 @@
         <v>45601</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13064,7 +13064,7 @@
         <v>45116</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13137,7 +13137,7 @@
         <v>45190</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13215,7 +13215,7 @@
         <v>45222</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13293,7 +13293,7 @@
         <v>46185</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13371,7 +13371,7 @@
         <v>46185</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13449,7 +13449,7 @@
         <v>44839</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13522,7 +13522,7 @@
         <v>46185</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13600,7 +13600,7 @@
         <v>44781</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13673,7 +13673,7 @@
         <v>45387</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13746,7 +13746,7 @@
         <v>45384</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13824,7 +13824,7 @@
         <v>46070</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13897,7 +13897,7 @@
         <v>46086</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13975,7 +13975,7 @@
         <v>46086</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14053,7 +14053,7 @@
         <v>46189</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14131,7 +14131,7 @@
         <v>46092</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14209,7 +14209,7 @@
         <v>46094</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14287,7 +14287,7 @@
         <v>46093</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14365,7 +14365,7 @@
         <v>46093</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14443,7 +14443,7 @@
         <v>46191</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14521,7 +14521,7 @@
         <v>46191</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14599,7 +14599,7 @@
         <v>46198</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14677,7 +14677,7 @@
         <v>46198</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14755,7 +14755,7 @@
         <v>46198</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14833,7 +14833,7 @@
         <v>46202</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14911,7 +14911,7 @@
         <v>46199</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14984,7 +14984,7 @@
         <v>46129</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15062,7 +15062,7 @@
         <v>46127</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15135,7 +15135,7 @@
         <v>46132</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15208,7 +15208,7 @@
         <v>44509</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15286,7 +15286,7 @@
         <v>44816</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15364,7 +15364,7 @@
         <v>45589</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15442,7 +15442,7 @@
         <v>45601</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15520,7 +15520,7 @@
         <v>45351</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15598,7 +15598,7 @@
         <v>45106</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15671,7 +15671,7 @@
         <v>44904</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15749,7 +15749,7 @@
         <v>45763</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15822,7 +15822,7 @@
         <v>44986</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15895,7 +15895,7 @@
         <v>46230</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15968,7 +15968,7 @@
         <v>44989</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16041,7 +16041,7 @@
         <v>44986</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16114,7 +16114,7 @@
         <v>45602</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16192,7 +16192,7 @@
         <v>45520</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16265,7 +16265,7 @@
         <v>46231</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16343,7 +16343,7 @@
         <v>46231</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16421,7 +16421,7 @@
         <v>45195</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16499,7 +16499,7 @@
         <v>45569</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16572,7 +16572,7 @@
         <v>46279</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16645,7 +16645,7 @@
         <v>46281</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16723,7 +16723,7 @@
         <v>46239</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16801,7 +16801,7 @@
         <v>46283</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16879,7 +16879,7 @@
         <v>46282</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16952,7 +16952,7 @@
         <v>46239</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17030,7 +17030,7 @@
         <v>46283</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17108,7 +17108,7 @@
         <v>44816</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17186,7 +17186,7 @@
         <v>46241</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17259,7 +17259,7 @@
         <v>44501</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17337,7 +17337,7 @@
         <v>45705</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17415,7 +17415,7 @@
         <v>45600</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17488,7 +17488,7 @@
         <v>45600</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17561,7 +17561,7 @@
         <v>45376</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17634,7 +17634,7 @@
         <v>45764</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17712,7 +17712,7 @@
         <v>46231</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17790,7 +17790,7 @@
         <v>45119</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17863,7 +17863,7 @@
         <v>45474</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17936,7 +17936,7 @@
         <v>45581</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18014,7 +18014,7 @@
         <v>45223</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18092,7 +18092,7 @@
         <v>45635</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18170,7 +18170,7 @@
         <v>45215</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18248,7 +18248,7 @@
         <v>46303</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18326,7 +18326,7 @@
         <v>45272</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18399,7 +18399,7 @@
         <v>46260</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18477,7 +18477,7 @@
         <v>45443</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18555,7 +18555,7 @@
         <v>45453</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18628,7 +18628,7 @@
         <v>46307</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18706,7 +18706,7 @@
         <v>45798</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18779,7 +18779,7 @@
         <v>45330</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18857,7 +18857,7 @@
         <v>46195</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18930,7 +18930,7 @@
         <v>45810</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19003,7 +19003,7 @@
         <v>45810</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19076,7 +19076,7 @@
         <v>46268</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19149,7 +19149,7 @@
         <v>45819</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19227,7 +19227,7 @@
         <v>45819</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19305,7 +19305,7 @@
         <v>46268</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19378,7 +19378,7 @@
         <v>46268</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19451,7 +19451,7 @@
         <v>46303</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19529,7 +19529,7 @@
         <v>44719</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19602,7 +19602,7 @@
         <v>45841</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19675,7 +19675,7 @@
         <v>45639</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19748,7 +19748,7 @@
         <v>45876</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19821,7 +19821,7 @@
         <v>45876</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19894,7 +19894,7 @@
         <v>45747</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19967,7 +19967,7 @@
         <v>44587</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20040,7 +20040,7 @@
         <v>45805</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20118,7 +20118,7 @@
         <v>45805</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20196,7 +20196,7 @@
         <v>45729</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20274,7 +20274,7 @@
         <v>45729</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20352,7 +20352,7 @@
         <v>45742</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20430,7 +20430,7 @@
         <v>45742</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20508,7 +20508,7 @@
         <v>45916</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>

--- a/Översikt DEGERFORS.xlsx
+++ b/Översikt DEGERFORS.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE239"/>
+  <dimension ref="A1:AE238"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>46160</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         <v>46051</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -836,7 +836,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 22871-2026</t>
+          <t>A 15809-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -850,10 +850,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46160</v>
+        <v>46107</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -871,13 +871,13 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>3.2</v>
+        <v>9.5</v>
       </c>
       <c r="J4" t="n">
         <v>11</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>6</v>
@@ -904,12 +904,138 @@
         <v>13</v>
       </c>
       <c r="T4" t="n">
+        <v>21</v>
+      </c>
+      <c r="U4" t="n">
+        <v>20</v>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Tornseglare
+Dropptaggsvamp
+Duvhök
+Järnsparv
+Nordfladdermus
+Orange taggsvamp
+Talltita
+Spillkråka
+Tjäder
+Tofsmes
+Dvärgpipistrell
+Vattenfladdermus
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 15809-2026 artfynd.xlsx", "A 15809-2026")</f>
+        <v/>
+      </c>
+      <c r="X4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 15809-2026 karta.png", "A 15809-2026")</f>
+        <v/>
+      </c>
+      <c r="Y4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 15809-2026 georefererad karta.tif", "A 15809-2026")</f>
+        <v/>
+      </c>
+      <c r="AA4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 15809-2026 FSC-klagomål.docx", "A 15809-2026")</f>
+        <v/>
+      </c>
+      <c r="AB4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 15809-2026 FSC-klagomål mail.docx", "A 15809-2026")</f>
+        <v/>
+      </c>
+      <c r="AC4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 15809-2026 tillsynsbegäran.docx", "A 15809-2026")</f>
+        <v/>
+      </c>
+      <c r="AD4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 15809-2026 tillsynsbegäran mail.docx", "A 15809-2026")</f>
+        <v/>
+      </c>
+      <c r="AE4">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 15809-2026 prioriterade fågelarter.docx", "A 15809-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A 22871-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>46160</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>DEGERFORS</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J5" t="n">
+        <v>11</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>6</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>7</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
+        <v>13</v>
+      </c>
+      <c r="T5" t="n">
         <v>35</v>
       </c>
-      <c r="U4" t="n">
+      <c r="U5" t="n">
         <v>35</v>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>Tornseglare
 Brunlångöra
@@ -926,162 +1052,36 @@
 Havsörn</t>
         </is>
       </c>
-      <c r="W4">
+      <c r="W5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 22871-2026 artfynd.xlsx", "A 22871-2026")</f>
         <v/>
       </c>
-      <c r="X4">
+      <c r="X5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 22871-2026 karta.png", "A 22871-2026")</f>
         <v/>
       </c>
-      <c r="Y4">
+      <c r="Y5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 22871-2026 georefererad karta.tif", "A 22871-2026")</f>
         <v/>
       </c>
-      <c r="AA4">
+      <c r="AA5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 22871-2026 FSC-klagomål.docx", "A 22871-2026")</f>
         <v/>
       </c>
-      <c r="AB4">
+      <c r="AB5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 22871-2026 FSC-klagomål mail.docx", "A 22871-2026")</f>
         <v/>
       </c>
-      <c r="AC4">
+      <c r="AC5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 22871-2026 tillsynsbegäran.docx", "A 22871-2026")</f>
         <v/>
       </c>
-      <c r="AD4">
+      <c r="AD5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 22871-2026 tillsynsbegäran mail.docx", "A 22871-2026")</f>
         <v/>
       </c>
-      <c r="AE4">
+      <c r="AE5">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 22871-2026 prioriterade fågelarter.docx", "A 22871-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A 15809-2026</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>46107</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46314</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>DEGERFORS</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="J5" t="n">
-        <v>11</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
-        <v>6</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>7</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" t="n">
-        <v>13</v>
-      </c>
-      <c r="T5" t="n">
-        <v>21</v>
-      </c>
-      <c r="U5" t="n">
-        <v>20</v>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>Tornseglare
-Dropptaggsvamp
-Duvhök
-Järnsparv
-Nordfladdermus
-Orange taggsvamp
-Talltita
-Spillkråka
-Tjäder
-Tofsmes
-Dvärgpipistrell
-Vattenfladdermus
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 15809-2026 artfynd.xlsx", "A 15809-2026")</f>
-        <v/>
-      </c>
-      <c r="X5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 15809-2026 karta.png", "A 15809-2026")</f>
-        <v/>
-      </c>
-      <c r="Y5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 15809-2026 georefererad karta.tif", "A 15809-2026")</f>
-        <v/>
-      </c>
-      <c r="AA5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 15809-2026 FSC-klagomål.docx", "A 15809-2026")</f>
-        <v/>
-      </c>
-      <c r="AB5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 15809-2026 FSC-klagomål mail.docx", "A 15809-2026")</f>
-        <v/>
-      </c>
-      <c r="AC5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 15809-2026 tillsynsbegäran.docx", "A 15809-2026")</f>
-        <v/>
-      </c>
-      <c r="AD5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 15809-2026 tillsynsbegäran mail.docx", "A 15809-2026")</f>
-        <v/>
-      </c>
-      <c r="AE5">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 15809-2026 prioriterade fågelarter.docx", "A 15809-2026")</f>
         <v/>
       </c>
     </row>
@@ -1105,7 +1105,7 @@
         <v>46190</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>46190</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>46161</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>45089</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>45175</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         <v>45384</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>46160</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>45384</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 38916-2023</t>
+          <t>A 73321-2021</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2075,10 +2075,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45163</v>
+        <v>44550</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2090,26 +2090,21 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>4.3</v>
+        <v>17</v>
       </c>
       <c r="J14" t="n">
         <v>3</v>
       </c>
       <c r="K14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L14" t="n">
         <v>3</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>1</v>
       </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
@@ -2120,21 +2115,144 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
+        <v>4</v>
+      </c>
+      <c r="R14" t="n">
         <v>1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>6</v>
       </c>
       <c r="T14" t="n">
+        <v>8</v>
+      </c>
+      <c r="U14" t="n">
+        <v>8</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Grynig filtlav
+Gulsparv
+Rynkskinn
+Vedticka
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 73321-2021 artfynd.xlsx", "A 73321-2021")</f>
+        <v/>
+      </c>
+      <c r="X14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 73321-2021 karta.png", "A 73321-2021")</f>
+        <v/>
+      </c>
+      <c r="Y14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 73321-2021 georefererad karta.tif", "A 73321-2021")</f>
+        <v/>
+      </c>
+      <c r="Z14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/knärot/A 73321-2021 karta knärot.png", "A 73321-2021")</f>
+        <v/>
+      </c>
+      <c r="AA14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 73321-2021 FSC-klagomål.docx", "A 73321-2021")</f>
+        <v/>
+      </c>
+      <c r="AB14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 73321-2021 FSC-klagomål mail.docx", "A 73321-2021")</f>
+        <v/>
+      </c>
+      <c r="AC14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 73321-2021 tillsynsbegäran.docx", "A 73321-2021")</f>
+        <v/>
+      </c>
+      <c r="AD14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 73321-2021 tillsynsbegäran mail.docx", "A 73321-2021")</f>
+        <v/>
+      </c>
+      <c r="AE14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 73321-2021 prioriterade fågelarter.docx", "A 73321-2021")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A 38916-2023</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>45163</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>DEGERFORS</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>6</v>
+      </c>
+      <c r="T15" t="n">
         <v>27</v>
       </c>
-      <c r="U14" t="n">
+      <c r="U15" t="n">
         <v>27</v>
       </c>
-      <c r="V14" s="2" t="inlineStr">
+      <c r="V15" s="2" t="inlineStr">
         <is>
           <t>Tretåig hackspett
 Grönpyrola
@@ -2144,154 +2262,36 @@
 Tjäder</t>
         </is>
       </c>
-      <c r="W14">
+      <c r="W15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 38916-2023 artfynd.xlsx", "A 38916-2023")</f>
         <v/>
       </c>
-      <c r="X14">
+      <c r="X15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 38916-2023 karta.png", "A 38916-2023")</f>
         <v/>
       </c>
-      <c r="Y14">
+      <c r="Y15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 38916-2023 georefererad karta.tif", "A 38916-2023")</f>
         <v/>
       </c>
-      <c r="AA14">
+      <c r="AA15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 38916-2023 FSC-klagomål.docx", "A 38916-2023")</f>
         <v/>
       </c>
-      <c r="AB14">
+      <c r="AB15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 38916-2023 FSC-klagomål mail.docx", "A 38916-2023")</f>
         <v/>
       </c>
-      <c r="AC14">
+      <c r="AC15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 38916-2023 tillsynsbegäran.docx", "A 38916-2023")</f>
         <v/>
       </c>
-      <c r="AD14">
+      <c r="AD15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 38916-2023 tillsynsbegäran mail.docx", "A 38916-2023")</f>
         <v/>
       </c>
-      <c r="AE14">
+      <c r="AE15">
         <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 38916-2023 prioriterade fågelarter.docx", "A 38916-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A 73321-2021</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>44550</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46314</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>DEGERFORS</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>17</v>
-      </c>
-      <c r="J15" t="n">
-        <v>3</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L15" t="n">
-        <v>3</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>4</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1</v>
-      </c>
-      <c r="S15" t="n">
-        <v>6</v>
-      </c>
-      <c r="T15" t="n">
-        <v>8</v>
-      </c>
-      <c r="U15" t="n">
-        <v>8</v>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Grynig filtlav
-Gulsparv
-Rynkskinn
-Vedticka
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 73321-2021 artfynd.xlsx", "A 73321-2021")</f>
-        <v/>
-      </c>
-      <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 73321-2021 karta.png", "A 73321-2021")</f>
-        <v/>
-      </c>
-      <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 73321-2021 georefererad karta.tif", "A 73321-2021")</f>
-        <v/>
-      </c>
-      <c r="Z15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/knärot/A 73321-2021 karta knärot.png", "A 73321-2021")</f>
-        <v/>
-      </c>
-      <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 73321-2021 FSC-klagomål.docx", "A 73321-2021")</f>
-        <v/>
-      </c>
-      <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 73321-2021 FSC-klagomål mail.docx", "A 73321-2021")</f>
-        <v/>
-      </c>
-      <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 73321-2021 tillsynsbegäran.docx", "A 73321-2021")</f>
-        <v/>
-      </c>
-      <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 73321-2021 tillsynsbegäran mail.docx", "A 73321-2021")</f>
-        <v/>
-      </c>
-      <c r="AE15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 73321-2021 prioriterade fågelarter.docx", "A 73321-2021")</f>
         <v/>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
         <v>45175</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>45932</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>45163</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2662,7 +2662,7 @@
         <v>45205</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2779,7 +2779,7 @@
         <v>45384</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>45351</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         <v>45866</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         <v>45559</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
         <v>45931</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3350,7 +3350,7 @@
         <v>46190</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 38914-2023</t>
+          <t>A 47785-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3463,10 +3463,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45163</v>
+        <v>45931</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3478,13 +3478,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>5.4</v>
+        <v>2</v>
       </c>
       <c r="J26" t="n">
         <v>2</v>
@@ -3493,7 +3488,7 @@
         <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -3508,7 +3503,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -3524,387 +3519,392 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
+          <t>Spillkråka
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 47785-2025 artfynd.xlsx", "A 47785-2025")</f>
+        <v/>
+      </c>
+      <c r="X26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 47785-2025 karta.png", "A 47785-2025")</f>
+        <v/>
+      </c>
+      <c r="Y26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 47785-2025 georefererad karta.tif", "A 47785-2025")</f>
+        <v/>
+      </c>
+      <c r="AA26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 47785-2025 FSC-klagomål.docx", "A 47785-2025")</f>
+        <v/>
+      </c>
+      <c r="AB26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 47785-2025 FSC-klagomål mail.docx", "A 47785-2025")</f>
+        <v/>
+      </c>
+      <c r="AC26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 47785-2025 tillsynsbegäran.docx", "A 47785-2025")</f>
+        <v/>
+      </c>
+      <c r="AD26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 47785-2025 tillsynsbegäran mail.docx", "A 47785-2025")</f>
+        <v/>
+      </c>
+      <c r="AE26">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 47785-2025 prioriterade fågelarter.docx", "A 47785-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>A 38910-2023</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>45163</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>DEGERFORS</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>3</v>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>Tjäder
+Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="W27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 38910-2023 artfynd.xlsx", "A 38910-2023")</f>
+        <v/>
+      </c>
+      <c r="X27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 38910-2023 karta.png", "A 38910-2023")</f>
+        <v/>
+      </c>
+      <c r="Y27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 38910-2023 georefererad karta.tif", "A 38910-2023")</f>
+        <v/>
+      </c>
+      <c r="AA27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 38910-2023 FSC-klagomål.docx", "A 38910-2023")</f>
+        <v/>
+      </c>
+      <c r="AB27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 38910-2023 FSC-klagomål mail.docx", "A 38910-2023")</f>
+        <v/>
+      </c>
+      <c r="AC27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 38910-2023 tillsynsbegäran.docx", "A 38910-2023")</f>
+        <v/>
+      </c>
+      <c r="AD27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 38910-2023 tillsynsbegäran mail.docx", "A 38910-2023")</f>
+        <v/>
+      </c>
+      <c r="AE27">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 38910-2023 prioriterade fågelarter.docx", "A 38910-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>A 40870-2024</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>45558</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>DEGERFORS</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 40870-2024 artfynd.xlsx", "A 40870-2024")</f>
+        <v/>
+      </c>
+      <c r="X28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 40870-2024 karta.png", "A 40870-2024")</f>
+        <v/>
+      </c>
+      <c r="Y28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 40870-2024 georefererad karta.tif", "A 40870-2024")</f>
+        <v/>
+      </c>
+      <c r="AA28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 40870-2024 FSC-klagomål.docx", "A 40870-2024")</f>
+        <v/>
+      </c>
+      <c r="AB28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 40870-2024 FSC-klagomål mail.docx", "A 40870-2024")</f>
+        <v/>
+      </c>
+      <c r="AC28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 40870-2024 tillsynsbegäran.docx", "A 40870-2024")</f>
+        <v/>
+      </c>
+      <c r="AD28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 40870-2024 tillsynsbegäran mail.docx", "A 40870-2024")</f>
+        <v/>
+      </c>
+      <c r="AE28">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 40870-2024 prioriterade fågelarter.docx", "A 40870-2024")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>A 38912-2023</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="n">
+        <v>45163</v>
+      </c>
+      <c r="E29" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>DEGERFORS</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
           <t>Tretåig hackspett
 Tjäder</t>
         </is>
       </c>
-      <c r="W26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 38914-2023 artfynd.xlsx", "A 38914-2023")</f>
-        <v/>
-      </c>
-      <c r="X26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 38914-2023 karta.png", "A 38914-2023")</f>
-        <v/>
-      </c>
-      <c r="Y26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 38914-2023 georefererad karta.tif", "A 38914-2023")</f>
-        <v/>
-      </c>
-      <c r="AA26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 38914-2023 FSC-klagomål.docx", "A 38914-2023")</f>
-        <v/>
-      </c>
-      <c r="AB26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 38914-2023 FSC-klagomål mail.docx", "A 38914-2023")</f>
-        <v/>
-      </c>
-      <c r="AC26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 38914-2023 tillsynsbegäran.docx", "A 38914-2023")</f>
-        <v/>
-      </c>
-      <c r="AD26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 38914-2023 tillsynsbegäran mail.docx", "A 38914-2023")</f>
-        <v/>
-      </c>
-      <c r="AE26">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 38914-2023 prioriterade fågelarter.docx", "A 38914-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>A 47785-2025</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="n">
-        <v>45931</v>
-      </c>
-      <c r="E27" s="1" t="n">
-        <v>46314</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>DEGERFORS</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>2</v>
-      </c>
-      <c r="J27" t="n">
-        <v>2</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2</v>
-      </c>
-      <c r="U27" t="n">
-        <v>2</v>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>Spillkråka
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 47785-2025 artfynd.xlsx", "A 47785-2025")</f>
-        <v/>
-      </c>
-      <c r="X27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 47785-2025 karta.png", "A 47785-2025")</f>
-        <v/>
-      </c>
-      <c r="Y27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 47785-2025 georefererad karta.tif", "A 47785-2025")</f>
-        <v/>
-      </c>
-      <c r="AA27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 47785-2025 FSC-klagomål.docx", "A 47785-2025")</f>
-        <v/>
-      </c>
-      <c r="AB27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 47785-2025 FSC-klagomål mail.docx", "A 47785-2025")</f>
-        <v/>
-      </c>
-      <c r="AC27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 47785-2025 tillsynsbegäran.docx", "A 47785-2025")</f>
-        <v/>
-      </c>
-      <c r="AD27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 47785-2025 tillsynsbegäran mail.docx", "A 47785-2025")</f>
-        <v/>
-      </c>
-      <c r="AE27">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 47785-2025 prioriterade fågelarter.docx", "A 47785-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>A 40870-2024</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D28" s="1" t="n">
-        <v>45558</v>
-      </c>
-      <c r="E28" s="1" t="n">
-        <v>46314</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>DEGERFORS</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J28" t="n">
-        <v>2</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
-        <v>1</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>1</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2</v>
-      </c>
-      <c r="U28" t="n">
-        <v>2</v>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 40870-2024 artfynd.xlsx", "A 40870-2024")</f>
-        <v/>
-      </c>
-      <c r="X28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 40870-2024 karta.png", "A 40870-2024")</f>
-        <v/>
-      </c>
-      <c r="Y28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 40870-2024 georefererad karta.tif", "A 40870-2024")</f>
-        <v/>
-      </c>
-      <c r="AA28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 40870-2024 FSC-klagomål.docx", "A 40870-2024")</f>
-        <v/>
-      </c>
-      <c r="AB28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 40870-2024 FSC-klagomål mail.docx", "A 40870-2024")</f>
-        <v/>
-      </c>
-      <c r="AC28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 40870-2024 tillsynsbegäran.docx", "A 40870-2024")</f>
-        <v/>
-      </c>
-      <c r="AD28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 40870-2024 tillsynsbegäran mail.docx", "A 40870-2024")</f>
-        <v/>
-      </c>
-      <c r="AE28">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 40870-2024 prioriterade fågelarter.docx", "A 40870-2024")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>A 38910-2023</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D29" s="1" t="n">
-        <v>45163</v>
-      </c>
-      <c r="E29" s="1" t="n">
-        <v>46314</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>DEGERFORS</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J29" t="n">
-        <v>2</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2</v>
-      </c>
-      <c r="T29" t="n">
-        <v>3</v>
-      </c>
-      <c r="U29" t="n">
-        <v>3</v>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>Tjäder
-Fläcknycklar</t>
-        </is>
-      </c>
       <c r="W29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 38910-2023 artfynd.xlsx", "A 38910-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 38912-2023 artfynd.xlsx", "A 38912-2023")</f>
         <v/>
       </c>
       <c r="X29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 38910-2023 karta.png", "A 38910-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 38912-2023 karta.png", "A 38912-2023")</f>
         <v/>
       </c>
       <c r="Y29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 38910-2023 georefererad karta.tif", "A 38910-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 38912-2023 georefererad karta.tif", "A 38912-2023")</f>
         <v/>
       </c>
       <c r="AA29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 38910-2023 FSC-klagomål.docx", "A 38910-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 38912-2023 FSC-klagomål.docx", "A 38912-2023")</f>
         <v/>
       </c>
       <c r="AB29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 38910-2023 FSC-klagomål mail.docx", "A 38910-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 38912-2023 FSC-klagomål mail.docx", "A 38912-2023")</f>
         <v/>
       </c>
       <c r="AC29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 38910-2023 tillsynsbegäran.docx", "A 38910-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 38912-2023 tillsynsbegäran.docx", "A 38912-2023")</f>
         <v/>
       </c>
       <c r="AD29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 38910-2023 tillsynsbegäran mail.docx", "A 38910-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 38912-2023 tillsynsbegäran mail.docx", "A 38912-2023")</f>
         <v/>
       </c>
       <c r="AE29">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 38910-2023 prioriterade fågelarter.docx", "A 38910-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 38912-2023 prioriterade fågelarter.docx", "A 38912-2023")</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 38912-2023</t>
+          <t>A 4256-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45163</v>
+        <v>46045</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3933,23 +3933,18 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>5.4</v>
+        <v>2.9</v>
       </c>
       <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
         <v>2</v>
       </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>1</v>
-      </c>
       <c r="M30" t="n">
         <v>0</v>
       </c>
@@ -3963,7 +3958,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -3975,150 +3970,155 @@
         <v>2</v>
       </c>
       <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>Skogsklocka
+Slåtterfibbla</t>
+        </is>
+      </c>
+      <c r="W30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 4256-2026 artfynd.xlsx", "A 4256-2026")</f>
+        <v/>
+      </c>
+      <c r="X30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 4256-2026 karta.png", "A 4256-2026")</f>
+        <v/>
+      </c>
+      <c r="Y30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 4256-2026 georefererad karta.tif", "A 4256-2026")</f>
+        <v/>
+      </c>
+      <c r="AA30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 4256-2026 FSC-klagomål.docx", "A 4256-2026")</f>
+        <v/>
+      </c>
+      <c r="AB30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 4256-2026 FSC-klagomål mail.docx", "A 4256-2026")</f>
+        <v/>
+      </c>
+      <c r="AC30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 4256-2026 tillsynsbegäran.docx", "A 4256-2026")</f>
+        <v/>
+      </c>
+      <c r="AD30">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 4256-2026 tillsynsbegäran mail.docx", "A 4256-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>A 38914-2023</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D31" s="1" t="n">
+        <v>45163</v>
+      </c>
+      <c r="E31" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>ÖREBRO LÄN</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>DEGERFORS</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J31" t="n">
         <v>2</v>
       </c>
-      <c r="V30" s="2" t="inlineStr">
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
         <is>
           <t>Tretåig hackspett
 Tjäder</t>
         </is>
       </c>
-      <c r="W30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 38912-2023 artfynd.xlsx", "A 38912-2023")</f>
-        <v/>
-      </c>
-      <c r="X30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 38912-2023 karta.png", "A 38912-2023")</f>
-        <v/>
-      </c>
-      <c r="Y30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 38912-2023 georefererad karta.tif", "A 38912-2023")</f>
-        <v/>
-      </c>
-      <c r="AA30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 38912-2023 FSC-klagomål.docx", "A 38912-2023")</f>
-        <v/>
-      </c>
-      <c r="AB30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 38912-2023 FSC-klagomål mail.docx", "A 38912-2023")</f>
-        <v/>
-      </c>
-      <c r="AC30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 38912-2023 tillsynsbegäran.docx", "A 38912-2023")</f>
-        <v/>
-      </c>
-      <c r="AD30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 38912-2023 tillsynsbegäran mail.docx", "A 38912-2023")</f>
-        <v/>
-      </c>
-      <c r="AE30">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 38912-2023 prioriterade fågelarter.docx", "A 38912-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>A 4256-2026</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D31" s="1" t="n">
-        <v>46045</v>
-      </c>
-      <c r="E31" s="1" t="n">
-        <v>46314</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>ÖREBRO LÄN</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>DEGERFORS</t>
-        </is>
-      </c>
-      <c r="I31" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>2</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>2</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>Skogsklocka
-Slåtterfibbla</t>
-        </is>
-      </c>
       <c r="W31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 4256-2026 artfynd.xlsx", "A 4256-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 38914-2023 artfynd.xlsx", "A 38914-2023")</f>
         <v/>
       </c>
       <c r="X31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 4256-2026 karta.png", "A 4256-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 38914-2023 karta.png", "A 38914-2023")</f>
         <v/>
       </c>
       <c r="Y31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 4256-2026 georefererad karta.tif", "A 4256-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 38914-2023 georefererad karta.tif", "A 38914-2023")</f>
         <v/>
       </c>
       <c r="AA31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 4256-2026 FSC-klagomål.docx", "A 4256-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 38914-2023 FSC-klagomål.docx", "A 38914-2023")</f>
         <v/>
       </c>
       <c r="AB31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 4256-2026 FSC-klagomål mail.docx", "A 4256-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 38914-2023 FSC-klagomål mail.docx", "A 38914-2023")</f>
         <v/>
       </c>
       <c r="AC31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 4256-2026 tillsynsbegäran.docx", "A 4256-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 38914-2023 tillsynsbegäran.docx", "A 38914-2023")</f>
         <v/>
       </c>
       <c r="AD31">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 4256-2026 tillsynsbegäran mail.docx", "A 4256-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 38914-2023 tillsynsbegäran mail.docx", "A 38914-2023")</f>
+        <v/>
+      </c>
+      <c r="AE31">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 38914-2023 prioriterade fågelarter.docx", "A 38914-2023")</f>
         <v/>
       </c>
     </row>
@@ -4142,7 +4142,7 @@
         <v>46199</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4240,7 +4240,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 58132-2021</t>
+          <t>A 47915-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4250,14 +4250,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44487</v>
+        <v>45589</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4275,7 +4275,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.2</v>
+        <v>5.8</v>
       </c>
       <c r="J33" t="n">
         <v>1</v>
@@ -4308,49 +4308,49 @@
         <v>1</v>
       </c>
       <c r="T33" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U33" t="n">
         <v>0</v>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>Hårklomossa</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 58132-2021 artfynd.xlsx", "A 58132-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 47915-2024 artfynd.xlsx", "A 47915-2024")</f>
         <v/>
       </c>
       <c r="X33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 58132-2021 karta.png", "A 58132-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 47915-2024 karta.png", "A 47915-2024")</f>
         <v/>
       </c>
       <c r="Y33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 58132-2021 georefererad karta.tif", "A 58132-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 47915-2024 georefererad karta.tif", "A 47915-2024")</f>
         <v/>
       </c>
       <c r="AA33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 58132-2021 FSC-klagomål.docx", "A 58132-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 47915-2024 FSC-klagomål.docx", "A 47915-2024")</f>
         <v/>
       </c>
       <c r="AB33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 58132-2021 FSC-klagomål mail.docx", "A 58132-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 47915-2024 FSC-klagomål mail.docx", "A 47915-2024")</f>
         <v/>
       </c>
       <c r="AC33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 58132-2021 tillsynsbegäran.docx", "A 58132-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 47915-2024 tillsynsbegäran.docx", "A 47915-2024")</f>
         <v/>
       </c>
       <c r="AD33">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 58132-2021 tillsynsbegäran mail.docx", "A 58132-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 47915-2024 tillsynsbegäran mail.docx", "A 47915-2024")</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 33297-2023</t>
+          <t>A 38904-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4364,10 +4364,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45116</v>
+        <v>45163</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4379,11 +4379,16 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>7.2</v>
+        <v>2.9</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" t="n">
         <v>0</v>
@@ -4392,7 +4397,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
@@ -4404,10 +4409,10 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4420,42 +4425,46 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>Igelkott</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 33297-2023 artfynd.xlsx", "A 33297-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 38904-2023 artfynd.xlsx", "A 38904-2023")</f>
         <v/>
       </c>
       <c r="X34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 33297-2023 karta.png", "A 33297-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 38904-2023 karta.png", "A 38904-2023")</f>
         <v/>
       </c>
       <c r="Y34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 33297-2023 georefererad karta.tif", "A 33297-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 38904-2023 georefererad karta.tif", "A 38904-2023")</f>
         <v/>
       </c>
       <c r="AA34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 33297-2023 FSC-klagomål.docx", "A 33297-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 38904-2023 FSC-klagomål.docx", "A 38904-2023")</f>
         <v/>
       </c>
       <c r="AB34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 33297-2023 FSC-klagomål mail.docx", "A 33297-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 38904-2023 FSC-klagomål mail.docx", "A 38904-2023")</f>
         <v/>
       </c>
       <c r="AC34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 33297-2023 tillsynsbegäran.docx", "A 33297-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 38904-2023 tillsynsbegäran.docx", "A 38904-2023")</f>
         <v/>
       </c>
       <c r="AD34">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 33297-2023 tillsynsbegäran mail.docx", "A 33297-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 38904-2023 tillsynsbegäran mail.docx", "A 38904-2023")</f>
+        <v/>
+      </c>
+      <c r="AE34">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 38904-2023 prioriterade fågelarter.docx", "A 38904-2023")</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 38904-2023</t>
+          <t>A 48285-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4469,10 +4478,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45163</v>
+        <v>45205</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4490,7 +4499,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J35" t="n">
         <v>1</v>
@@ -4534,42 +4543,42 @@
         </is>
       </c>
       <c r="W35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 38904-2023 artfynd.xlsx", "A 38904-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 48285-2023 artfynd.xlsx", "A 48285-2023")</f>
         <v/>
       </c>
       <c r="X35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 38904-2023 karta.png", "A 38904-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 48285-2023 karta.png", "A 48285-2023")</f>
         <v/>
       </c>
       <c r="Y35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 38904-2023 georefererad karta.tif", "A 38904-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 48285-2023 georefererad karta.tif", "A 48285-2023")</f>
         <v/>
       </c>
       <c r="AA35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 38904-2023 FSC-klagomål.docx", "A 38904-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 48285-2023 FSC-klagomål.docx", "A 48285-2023")</f>
         <v/>
       </c>
       <c r="AB35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 38904-2023 FSC-klagomål mail.docx", "A 38904-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 48285-2023 FSC-klagomål mail.docx", "A 48285-2023")</f>
         <v/>
       </c>
       <c r="AC35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 38904-2023 tillsynsbegäran.docx", "A 38904-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 48285-2023 tillsynsbegäran.docx", "A 48285-2023")</f>
         <v/>
       </c>
       <c r="AD35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 38904-2023 tillsynsbegäran mail.docx", "A 38904-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 48285-2023 tillsynsbegäran mail.docx", "A 48285-2023")</f>
         <v/>
       </c>
       <c r="AE35">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 38904-2023 prioriterade fågelarter.docx", "A 38904-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 48285-2023 prioriterade fågelarter.docx", "A 48285-2023")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 27093-2023</t>
+          <t>A 49306-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4583,10 +4592,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45096</v>
+        <v>45938</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4598,19 +4607,14 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
         <v>1</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -4640,50 +4644,46 @@
         <v>1</v>
       </c>
       <c r="U36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="W36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 27093-2023 artfynd.xlsx", "A 27093-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 49306-2025 artfynd.xlsx", "A 49306-2025")</f>
         <v/>
       </c>
       <c r="X36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 27093-2023 karta.png", "A 27093-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 49306-2025 karta.png", "A 49306-2025")</f>
         <v/>
       </c>
       <c r="Y36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 27093-2023 georefererad karta.tif", "A 27093-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 49306-2025 georefererad karta.tif", "A 49306-2025")</f>
         <v/>
       </c>
       <c r="AA36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 27093-2023 FSC-klagomål.docx", "A 27093-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 49306-2025 FSC-klagomål.docx", "A 49306-2025")</f>
         <v/>
       </c>
       <c r="AB36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 27093-2023 FSC-klagomål mail.docx", "A 27093-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 49306-2025 FSC-klagomål mail.docx", "A 49306-2025")</f>
         <v/>
       </c>
       <c r="AC36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 27093-2023 tillsynsbegäran.docx", "A 27093-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 49306-2025 tillsynsbegäran.docx", "A 49306-2025")</f>
         <v/>
       </c>
       <c r="AD36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 27093-2023 tillsynsbegäran mail.docx", "A 27093-2023")</f>
-        <v/>
-      </c>
-      <c r="AE36">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 27093-2023 prioriterade fågelarter.docx", "A 27093-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 49306-2025 tillsynsbegäran mail.docx", "A 49306-2025")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 48285-2023</t>
+          <t>A 27093-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4697,10 +4697,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45205</v>
+        <v>45096</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4718,7 +4718,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.1</v>
+        <v>5.9</v>
       </c>
       <c r="J37" t="n">
         <v>1</v>
@@ -4762,42 +4762,42 @@
         </is>
       </c>
       <c r="W37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 48285-2023 artfynd.xlsx", "A 48285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 27093-2023 artfynd.xlsx", "A 27093-2023")</f>
         <v/>
       </c>
       <c r="X37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 48285-2023 karta.png", "A 48285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 27093-2023 karta.png", "A 27093-2023")</f>
         <v/>
       </c>
       <c r="Y37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 48285-2023 georefererad karta.tif", "A 48285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 27093-2023 georefererad karta.tif", "A 27093-2023")</f>
         <v/>
       </c>
       <c r="AA37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 48285-2023 FSC-klagomål.docx", "A 48285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 27093-2023 FSC-klagomål.docx", "A 27093-2023")</f>
         <v/>
       </c>
       <c r="AB37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 48285-2023 FSC-klagomål mail.docx", "A 48285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 27093-2023 FSC-klagomål mail.docx", "A 27093-2023")</f>
         <v/>
       </c>
       <c r="AC37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 48285-2023 tillsynsbegäran.docx", "A 48285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 27093-2023 tillsynsbegäran.docx", "A 27093-2023")</f>
         <v/>
       </c>
       <c r="AD37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 48285-2023 tillsynsbegäran mail.docx", "A 48285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 27093-2023 tillsynsbegäran mail.docx", "A 27093-2023")</f>
         <v/>
       </c>
       <c r="AE37">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 48285-2023 prioriterade fågelarter.docx", "A 48285-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 27093-2023 prioriterade fågelarter.docx", "A 27093-2023")</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 49306-2025</t>
+          <t>A 47787-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4811,10 +4811,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45938</v>
+        <v>45931</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4827,17 +4827,17 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>5.8</v>
+        <v>4.1</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
         <v>1</v>
       </c>
-      <c r="L38" t="n">
-        <v>0</v>
-      </c>
       <c r="M38" t="n">
         <v>0</v>
       </c>
@@ -4851,7 +4851,7 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -4860,49 +4860,53 @@
         <v>1</v>
       </c>
       <c r="T38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="W38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 49306-2025 artfynd.xlsx", "A 49306-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 47787-2025 artfynd.xlsx", "A 47787-2025")</f>
         <v/>
       </c>
       <c r="X38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 49306-2025 karta.png", "A 49306-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 47787-2025 karta.png", "A 47787-2025")</f>
         <v/>
       </c>
       <c r="Y38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 49306-2025 georefererad karta.tif", "A 49306-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 47787-2025 georefererad karta.tif", "A 47787-2025")</f>
         <v/>
       </c>
       <c r="AA38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 49306-2025 FSC-klagomål.docx", "A 49306-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 47787-2025 FSC-klagomål.docx", "A 47787-2025")</f>
         <v/>
       </c>
       <c r="AB38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 49306-2025 FSC-klagomål mail.docx", "A 49306-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 47787-2025 FSC-klagomål mail.docx", "A 47787-2025")</f>
         <v/>
       </c>
       <c r="AC38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 49306-2025 tillsynsbegäran.docx", "A 49306-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 47787-2025 tillsynsbegäran.docx", "A 47787-2025")</f>
         <v/>
       </c>
       <c r="AD38">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 49306-2025 tillsynsbegäran mail.docx", "A 49306-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 47787-2025 tillsynsbegäran mail.docx", "A 47787-2025")</f>
+        <v/>
+      </c>
+      <c r="AE38">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 47787-2025 prioriterade fågelarter.docx", "A 47787-2025")</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 47787-2025</t>
+          <t>A 47941-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4916,10 +4920,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45931</v>
+        <v>45589</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4931,20 +4935,25 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>4.1</v>
+        <v>1.4</v>
       </c>
       <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
         <v>1</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" t="n">
-        <v>1</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0</v>
       </c>
       <c r="N39" t="n">
         <v>0</v>
@@ -4959,52 +4968,48 @@
         <v>1</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S39" t="n">
         <v>1</v>
       </c>
       <c r="T39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunfläckig pärlemorfjäril</t>
         </is>
       </c>
       <c r="W39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 47787-2025 artfynd.xlsx", "A 47787-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 47941-2024 artfynd.xlsx", "A 47941-2024")</f>
         <v/>
       </c>
       <c r="X39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 47787-2025 karta.png", "A 47787-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 47941-2024 karta.png", "A 47941-2024")</f>
         <v/>
       </c>
       <c r="Y39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 47787-2025 georefererad karta.tif", "A 47787-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 47941-2024 georefererad karta.tif", "A 47941-2024")</f>
         <v/>
       </c>
       <c r="AA39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 47787-2025 FSC-klagomål.docx", "A 47787-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 47941-2024 FSC-klagomål.docx", "A 47941-2024")</f>
         <v/>
       </c>
       <c r="AB39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 47787-2025 FSC-klagomål mail.docx", "A 47787-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 47941-2024 FSC-klagomål mail.docx", "A 47941-2024")</f>
         <v/>
       </c>
       <c r="AC39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 47787-2025 tillsynsbegäran.docx", "A 47787-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 47941-2024 tillsynsbegäran.docx", "A 47941-2024")</f>
         <v/>
       </c>
       <c r="AD39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 47787-2025 tillsynsbegäran mail.docx", "A 47787-2025")</f>
-        <v/>
-      </c>
-      <c r="AE39">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 47787-2025 prioriterade fågelarter.docx", "A 47787-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 47941-2024 tillsynsbegäran mail.docx", "A 47941-2024")</f>
         <v/>
       </c>
     </row>
@@ -5028,7 +5033,7 @@
         <v>44651</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5133,7 +5138,7 @@
         <v>45163</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5230,7 +5235,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 47941-2024</t>
+          <t>A 27071-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5244,10 +5249,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45589</v>
+        <v>46186</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5265,19 +5270,19 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.4</v>
+        <v>9.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
         <v>0</v>
@@ -5289,10 +5294,10 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>1</v>
@@ -5305,42 +5310,42 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Brunfläckig pärlemorfjäril</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 47941-2024 artfynd.xlsx", "A 47941-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 27071-2026 artfynd.xlsx", "A 27071-2026")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 47941-2024 karta.png", "A 47941-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 27071-2026 karta.png", "A 27071-2026")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 47941-2024 georefererad karta.tif", "A 47941-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 27071-2026 georefererad karta.tif", "A 27071-2026")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 47941-2024 FSC-klagomål.docx", "A 47941-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 27071-2026 FSC-klagomål.docx", "A 27071-2026")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 47941-2024 FSC-klagomål mail.docx", "A 47941-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 27071-2026 FSC-klagomål mail.docx", "A 27071-2026")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 47941-2024 tillsynsbegäran.docx", "A 47941-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 27071-2026 tillsynsbegäran.docx", "A 27071-2026")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 47941-2024 tillsynsbegäran mail.docx", "A 47941-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 27071-2026 tillsynsbegäran mail.docx", "A 27071-2026")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 27071-2026</t>
+          <t>A 27072-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5357,7 +5362,7 @@
         <v>46186</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5375,13 +5380,13 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>9.9</v>
+        <v>7.6</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -5411,46 +5416,50 @@
         <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 27071-2026 artfynd.xlsx", "A 27071-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 27072-2026 artfynd.xlsx", "A 27072-2026")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 27071-2026 karta.png", "A 27071-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 27072-2026 karta.png", "A 27072-2026")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 27071-2026 georefererad karta.tif", "A 27071-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 27072-2026 georefererad karta.tif", "A 27072-2026")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 27071-2026 FSC-klagomål.docx", "A 27071-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 27072-2026 FSC-klagomål.docx", "A 27072-2026")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 27071-2026 FSC-klagomål mail.docx", "A 27071-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 27072-2026 FSC-klagomål mail.docx", "A 27072-2026")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 27071-2026 tillsynsbegäran.docx", "A 27071-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 27072-2026 tillsynsbegäran.docx", "A 27072-2026")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 27071-2026 tillsynsbegäran mail.docx", "A 27071-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 27072-2026 tillsynsbegäran mail.docx", "A 27072-2026")</f>
+        <v/>
+      </c>
+      <c r="AE43">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 27072-2026 prioriterade fågelarter.docx", "A 27072-2026")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 27072-2026</t>
+          <t>A 33297-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5464,10 +5473,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46186</v>
+        <v>45116</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5479,26 +5488,21 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
         <v>1</v>
       </c>
-      <c r="K44" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" t="n">
-        <v>0</v>
-      </c>
       <c r="N44" t="n">
         <v>0</v>
       </c>
@@ -5509,10 +5513,10 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>
@@ -5525,39 +5529,35 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Igelkott</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 27072-2026 artfynd.xlsx", "A 27072-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 33297-2023 artfynd.xlsx", "A 33297-2023")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 27072-2026 karta.png", "A 27072-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 33297-2023 karta.png", "A 33297-2023")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 27072-2026 georefererad karta.tif", "A 27072-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 33297-2023 georefererad karta.tif", "A 33297-2023")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 27072-2026 FSC-klagomål.docx", "A 27072-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 33297-2023 FSC-klagomål.docx", "A 33297-2023")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 27072-2026 FSC-klagomål mail.docx", "A 27072-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 33297-2023 FSC-klagomål mail.docx", "A 33297-2023")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 27072-2026 tillsynsbegäran.docx", "A 27072-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 33297-2023 tillsynsbegäran.docx", "A 33297-2023")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 27072-2026 tillsynsbegäran mail.docx", "A 27072-2026")</f>
-        <v/>
-      </c>
-      <c r="AE44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 27072-2026 prioriterade fågelarter.docx", "A 27072-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 33297-2023 tillsynsbegäran mail.docx", "A 33297-2023")</f>
         <v/>
       </c>
     </row>
@@ -5581,7 +5581,7 @@
         <v>46099</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         <v>46185</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5779,7 +5779,7 @@
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 47915-2024</t>
+          <t>A 2357-2022</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5793,10 +5793,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45589</v>
+        <v>44578</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5808,13 +5808,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I47" t="n">
-        <v>5.8</v>
+        <v>4.5</v>
       </c>
       <c r="J47" t="n">
         <v>1</v>
@@ -5850,39 +5845,43 @@
         <v>1</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="W47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 47915-2024 artfynd.xlsx", "A 47915-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 2357-2022 artfynd.xlsx", "A 2357-2022")</f>
         <v/>
       </c>
       <c r="X47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 47915-2024 karta.png", "A 47915-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 2357-2022 karta.png", "A 2357-2022")</f>
         <v/>
       </c>
       <c r="Y47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 47915-2024 georefererad karta.tif", "A 47915-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 2357-2022 georefererad karta.tif", "A 2357-2022")</f>
         <v/>
       </c>
       <c r="AA47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 47915-2024 FSC-klagomål.docx", "A 47915-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 2357-2022 FSC-klagomål.docx", "A 2357-2022")</f>
         <v/>
       </c>
       <c r="AB47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 47915-2024 FSC-klagomål mail.docx", "A 47915-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 2357-2022 FSC-klagomål mail.docx", "A 2357-2022")</f>
         <v/>
       </c>
       <c r="AC47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 47915-2024 tillsynsbegäran.docx", "A 47915-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 2357-2022 tillsynsbegäran.docx", "A 2357-2022")</f>
         <v/>
       </c>
       <c r="AD47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 47915-2024 tillsynsbegäran mail.docx", "A 47915-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 2357-2022 tillsynsbegäran mail.docx", "A 2357-2022")</f>
+        <v/>
+      </c>
+      <c r="AE47">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 2357-2022 prioriterade fågelarter.docx", "A 2357-2022")</f>
         <v/>
       </c>
     </row>
@@ -5906,7 +5905,7 @@
         <v>45614</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5998,7 +5997,7 @@
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 2357-2022</t>
+          <t>A 42337-2026</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6012,10 +6011,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44578</v>
+        <v>46307</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6027,8 +6026,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I49" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="J49" t="n">
         <v>1</v>
@@ -6064,50 +6068,46 @@
         <v>1</v>
       </c>
       <c r="U49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 2357-2022 artfynd.xlsx", "A 2357-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 42337-2026 artfynd.xlsx", "A 42337-2026")</f>
         <v/>
       </c>
       <c r="X49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 2357-2022 karta.png", "A 2357-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 42337-2026 karta.png", "A 42337-2026")</f>
         <v/>
       </c>
       <c r="Y49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 2357-2022 georefererad karta.tif", "A 2357-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 42337-2026 georefererad karta.tif", "A 42337-2026")</f>
         <v/>
       </c>
       <c r="AA49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 2357-2022 FSC-klagomål.docx", "A 2357-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 42337-2026 FSC-klagomål.docx", "A 42337-2026")</f>
         <v/>
       </c>
       <c r="AB49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 2357-2022 FSC-klagomål mail.docx", "A 2357-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 42337-2026 FSC-klagomål mail.docx", "A 42337-2026")</f>
         <v/>
       </c>
       <c r="AC49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 2357-2022 tillsynsbegäran.docx", "A 2357-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 42337-2026 tillsynsbegäran.docx", "A 42337-2026")</f>
         <v/>
       </c>
       <c r="AD49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 2357-2022 tillsynsbegäran mail.docx", "A 2357-2022")</f>
-        <v/>
-      </c>
-      <c r="AE49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/fåglar/A 2357-2022 prioriterade fågelarter.docx", "A 2357-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 42337-2026 tillsynsbegäran mail.docx", "A 42337-2026")</f>
         <v/>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 42337-2026</t>
+          <t>A 36798-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6121,10 +6121,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46307</v>
+        <v>44805</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6136,16 +6136,11 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>4.7</v>
+        <v>1.1</v>
       </c>
       <c r="J50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
@@ -6172,52 +6167,20 @@
         <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U50" t="n">
         <v>0</v>
       </c>
-      <c r="V50" s="2" t="inlineStr">
-        <is>
-          <t>Mattlummer</t>
-        </is>
-      </c>
-      <c r="W50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/artfynd/A 42337-2026 artfynd.xlsx", "A 42337-2026")</f>
-        <v/>
-      </c>
-      <c r="X50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor/A 42337-2026 karta.png", "A 42337-2026")</f>
-        <v/>
-      </c>
-      <c r="Y50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/kartor_geotiff/A 42337-2026 georefererad karta.tif", "A 42337-2026")</f>
-        <v/>
-      </c>
-      <c r="AA50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomål/A 42337-2026 FSC-klagomål.docx", "A 42337-2026")</f>
-        <v/>
-      </c>
-      <c r="AB50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/klagomålsmail/A 42337-2026 FSC-klagomål mail.docx", "A 42337-2026")</f>
-        <v/>
-      </c>
-      <c r="AC50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsyn/A 42337-2026 tillsynsbegäran.docx", "A 42337-2026")</f>
-        <v/>
-      </c>
-      <c r="AD50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1862/tillsynsmail/A 42337-2026 tillsynsbegäran mail.docx", "A 42337-2026")</f>
-        <v/>
-      </c>
+      <c r="V50" s="2" t="inlineStr"/>
     </row>
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 36798-2022</t>
+          <t>A 36784-2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6234,7 +6197,7 @@
         <v>44805</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6247,7 +6210,7 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
@@ -6290,7 +6253,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 36784-2022</t>
+          <t>A 50599-2022</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6304,10 +6267,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>44805</v>
+        <v>44861</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6320,7 +6283,7 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -6363,7 +6326,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 50599-2022</t>
+          <t>A 7510-2022</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6373,14 +6336,14 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>44861</v>
+        <v>44607</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6392,8 +6355,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I53" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
@@ -6436,7 +6404,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 7510-2022</t>
+          <t>A 19371-2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6446,14 +6414,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>44607</v>
+        <v>44692</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6465,13 +6433,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I54" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -6514,7 +6477,7 @@
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 19371-2022</t>
+          <t>A 8186-2022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6528,10 +6491,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>44692</v>
+        <v>44609</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6544,7 +6507,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -6587,7 +6550,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 8186-2022</t>
+          <t>A 60889-2021</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6601,10 +6564,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>44609</v>
+        <v>44497</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6660,7 +6623,7 @@
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 60889-2021</t>
+          <t>A 5319-2022</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6674,10 +6637,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>44497</v>
+        <v>44594</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6733,7 +6696,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 5319-2022</t>
+          <t>A 47569-2022</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6747,10 +6710,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>44594</v>
+        <v>44853</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6763,7 +6726,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -6806,7 +6769,7 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 47569-2022</t>
+          <t>A 65456-2021</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6820,10 +6783,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44853</v>
+        <v>44515</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6836,7 +6799,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -6879,7 +6842,7 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>A 65456-2021</t>
+          <t>A 12977-2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6893,10 +6856,10 @@
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>44515</v>
+        <v>44643</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6909,7 +6872,7 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -6952,7 +6915,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 12977-2022</t>
+          <t>A 68578-2021</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6966,10 +6929,10 @@
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>44643</v>
+        <v>44529</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6981,8 +6944,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I61" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -7025,7 +6993,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 68578-2021</t>
+          <t>A 67998-2021</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -7039,10 +7007,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>44529</v>
+        <v>44525</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7054,13 +7022,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I62" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -7103,7 +7066,7 @@
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 67998-2021</t>
+          <t>A 63906-2021</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -7117,10 +7080,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>44525</v>
+        <v>44509</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7132,8 +7095,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I63" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -7176,7 +7144,7 @@
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 63906-2021</t>
+          <t>A 63008-2021</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7190,10 +7158,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>44509</v>
+        <v>44505</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7211,7 +7179,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -7254,7 +7222,7 @@
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 63008-2021</t>
+          <t>A 45861-2023</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7264,14 +7232,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>44505</v>
+        <v>45195</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7289,7 +7257,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>1.5</v>
+        <v>0.7</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
@@ -7332,7 +7300,7 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>A 7975-2025</t>
+          <t>A 6394-2024</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -7342,14 +7310,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>45707</v>
+        <v>45338</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7367,7 +7335,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>5.3</v>
+        <v>0.9</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -7427,7 +7395,7 @@
         <v>45763</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7483,7 +7451,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 29607-2022</t>
+          <t>A 38743-2022</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7497,10 +7465,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>44754</v>
+        <v>44816</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7518,7 +7486,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -7561,7 +7529,7 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 37672-2024</t>
+          <t>A 26176-2024</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -7571,14 +7539,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45541</v>
+        <v>45468</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7596,7 +7564,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -7639,7 +7607,7 @@
     <row r="70" ht="15" customHeight="1">
       <c r="A70" t="inlineStr">
         <is>
-          <t>A 56478-2024</t>
+          <t>A 3177-2022</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -7653,10 +7621,10 @@
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>45624</v>
+        <v>44582</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7669,7 +7637,7 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1.4</v>
+        <v>3.7</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
@@ -7712,7 +7680,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 8062-2024</t>
+          <t>A 50378-2024</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -7726,10 +7694,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>45351</v>
+        <v>45601</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7747,7 +7715,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0.8</v>
+        <v>4.9</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
@@ -7790,7 +7758,7 @@
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 10321-2023</t>
+          <t>A 13405-2024</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7804,10 +7772,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>44986</v>
+        <v>45387</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7820,7 +7788,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
@@ -7863,7 +7831,7 @@
     <row r="73" ht="15" customHeight="1">
       <c r="A73" t="inlineStr">
         <is>
-          <t>A 36437-2024</t>
+          <t>A 10321-2023</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7877,10 +7845,10 @@
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>45535</v>
+        <v>44986</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7893,7 +7861,7 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
@@ -7936,7 +7904,7 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>A 38921-2023</t>
+          <t>A 57234-2024</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7950,10 +7918,10 @@
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>45163</v>
+        <v>45629</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7971,7 +7939,7 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
@@ -8014,7 +7982,7 @@
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A 2565-2022</t>
+          <t>A 6387-2024</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -8024,14 +7992,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>44579</v>
+        <v>45338</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8043,8 +8011,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I75" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -8087,7 +8060,7 @@
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>A 60907-2023</t>
+          <t>A 59158-2022</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -8097,14 +8070,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>45261</v>
+        <v>44904</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8122,7 +8095,7 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0.6</v>
+        <v>3.7</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -8165,7 +8138,7 @@
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>A 26176-2024</t>
+          <t>A 5277-2024</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -8179,10 +8152,10 @@
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45468</v>
+        <v>45330</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8194,13 +8167,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I77" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
@@ -8243,7 +8211,7 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A 3177-2022</t>
+          <t>A 43768-2024</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -8257,10 +8225,10 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>44582</v>
+        <v>45569</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8273,7 +8241,7 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>3.7</v>
+        <v>7</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
@@ -8316,7 +8284,7 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>A 8184-2022</t>
+          <t>A 47935-2024</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -8330,10 +8298,10 @@
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>44609</v>
+        <v>45589</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8345,8 +8313,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I79" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -8389,7 +8362,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 50766-2024</t>
+          <t>A 21952-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -8399,14 +8372,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45602</v>
+        <v>45443</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8424,7 +8397,7 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>2.1</v>
+        <v>0.7</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -8467,7 +8440,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 52523-2024</t>
+          <t>A 52566-2023</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8481,10 +8454,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45609</v>
+        <v>45219</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8496,13 +8469,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>4.4</v>
+        <v>1.5</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -8545,7 +8513,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 54994-2024</t>
+          <t>A 62972-2023</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8559,10 +8527,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>45621</v>
+        <v>45272</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8574,13 +8542,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I82" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -8623,7 +8586,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 54515-2023</t>
+          <t>A 50377-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -8637,10 +8600,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45233</v>
+        <v>45601</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8652,8 +8615,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -8696,7 +8664,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 38874-2025</t>
+          <t>A 11085-2023</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -8710,10 +8678,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45887</v>
+        <v>44986</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8725,13 +8693,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I84" t="n">
-        <v>8.300000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -8774,7 +8737,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 13236-2025</t>
+          <t>A 50764-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -8788,10 +8751,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45735</v>
+        <v>45602</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8809,7 +8772,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>18.5</v>
+        <v>2.4</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -8852,7 +8815,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 38875-2025</t>
+          <t>A 54082-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -8866,10 +8829,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45887</v>
+        <v>45616</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8881,13 +8844,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>1.9</v>
+        <v>6.3</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -8930,7 +8888,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 38233-2023</t>
+          <t>A 38874-2025</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8940,14 +8898,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45160</v>
+        <v>45887</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8959,8 +8917,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I87" t="n">
-        <v>0.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -9003,7 +8966,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 54082-2024</t>
+          <t>A 38875-2025</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -9017,10 +8980,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45616</v>
+        <v>45887</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9032,8 +8995,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>6.3</v>
+        <v>1.9</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -9076,7 +9044,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 43752-2025</t>
+          <t>A 38921-2023</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -9090,10 +9058,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45912</v>
+        <v>45163</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9105,8 +9073,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -9149,7 +9122,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 20567-2026</t>
+          <t>A 20478-2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -9166,7 +9139,7 @@
         <v>46140</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9184,7 +9157,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>7.8</v>
+        <v>1.1</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -9227,7 +9200,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 20568-2026</t>
+          <t>A 41766-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -9241,10 +9214,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>46140</v>
+        <v>45902</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9262,7 +9235,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>6.3</v>
+        <v>3.2</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -9305,7 +9278,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 10674-2024</t>
+          <t>A 41767-2025</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -9315,14 +9288,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45369</v>
+        <v>45902</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9340,7 +9313,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>0.3</v>
+        <v>1.1</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -9383,7 +9356,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 20478-2026</t>
+          <t>A 63905-2021</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -9397,10 +9370,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>46140</v>
+        <v>44509</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9418,7 +9391,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>1.1</v>
+        <v>3.7</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -9461,7 +9434,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 60933-2024</t>
+          <t>A 20567-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -9475,10 +9448,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45645</v>
+        <v>46140</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9496,7 +9469,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>1.9</v>
+        <v>7.8</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -9539,7 +9512,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 41767-2025</t>
+          <t>A 20568-2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -9553,10 +9526,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45902</v>
+        <v>46140</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9574,7 +9547,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1.1</v>
+        <v>6.3</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -9617,7 +9590,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 41766-2025</t>
+          <t>A 43691-2025</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9631,10 +9604,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45902</v>
+        <v>45912</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9652,7 +9625,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -9695,7 +9668,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 73693-2021</t>
+          <t>A 43689-2025</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -9709,10 +9682,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>44552</v>
+        <v>45912</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9724,8 +9697,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I97" t="n">
-        <v>3.6</v>
+        <v>1.4</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -9768,7 +9746,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 60937-2024</t>
+          <t>A 43694-2025</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9782,10 +9760,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45645</v>
+        <v>45912</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9803,7 +9781,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0.6</v>
+        <v>6.6</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -9846,7 +9824,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 60940-2024</t>
+          <t>A 20577-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9856,14 +9834,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45645</v>
+        <v>45057</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9881,7 +9859,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -9924,7 +9902,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 43694-2025</t>
+          <t>A 10797-2023</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9938,10 +9916,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45912</v>
+        <v>44989</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9953,13 +9931,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I100" t="n">
-        <v>6.6</v>
+        <v>9.5</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -10002,7 +9975,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 43691-2025</t>
+          <t>A 44457-2022</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -10016,10 +9989,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>45912</v>
+        <v>44839</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10031,13 +10004,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I101" t="n">
-        <v>2.7</v>
+        <v>6.8</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -10080,7 +10048,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 43689-2025</t>
+          <t>A 29482-2023</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -10094,10 +10062,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45912</v>
+        <v>45106</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10109,13 +10077,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -10158,7 +10121,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 52566-2023</t>
+          <t>A 48625-2025</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -10172,10 +10135,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45219</v>
+        <v>45936</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10188,7 +10151,7 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -10248,7 +10211,7 @@
         <v>46148</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10309,7 +10272,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 57234-2024</t>
+          <t>A 13236-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -10323,10 +10286,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45629</v>
+        <v>45735</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10344,7 +10307,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0.9</v>
+        <v>18.5</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -10404,7 +10367,7 @@
         <v>46148</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10465,7 +10428,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 21401-2026</t>
+          <t>A 51040-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -10479,10 +10442,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>46148</v>
+        <v>45947</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10494,8 +10457,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I107" t="n">
-        <v>3.5</v>
+        <v>1.1</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -10538,7 +10506,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 48625-2025</t>
+          <t>A 21401-2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10552,10 +10520,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45936</v>
+        <v>46148</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10568,7 +10536,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.6</v>
+        <v>3.5</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -10611,7 +10579,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 44841-2023</t>
+          <t>A 52099-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10625,10 +10593,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45190</v>
+        <v>45952</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10640,13 +10608,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I109" t="n">
-        <v>1.5</v>
+        <v>2.6</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -10689,7 +10652,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 51040-2025</t>
+          <t>A 11084-2023</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10703,10 +10666,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45947</v>
+        <v>44986</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10718,13 +10681,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I110" t="n">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -10767,7 +10725,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 46222-2024</t>
+          <t>A 56478-2024</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10781,10 +10739,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45581</v>
+        <v>45624</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10796,13 +10754,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I111" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -10845,7 +10798,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 52099-2025</t>
+          <t>A 44841-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10859,10 +10812,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45952</v>
+        <v>45190</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10874,8 +10827,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I112" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -10918,7 +10876,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 46219-2024</t>
+          <t>A 46222-2024</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10935,7 +10893,7 @@
         <v>45581</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10953,7 +10911,7 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -10996,7 +10954,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 8074-2024</t>
+          <t>A 46219-2024</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -11010,10 +10968,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45351</v>
+        <v>45581</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11031,7 +10989,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.7</v>
+        <v>2.4</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -11074,7 +11032,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 21952-2024</t>
+          <t>A 60933-2024</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -11084,14 +11042,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45443</v>
+        <v>45645</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11109,7 +11067,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -11152,7 +11110,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 55341-2025</t>
+          <t>A 61750-2021</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -11166,10 +11124,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45971</v>
+        <v>44501</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11187,7 +11145,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -11230,7 +11188,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 23230-2026</t>
+          <t>A 55341-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -11244,10 +11202,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>46162</v>
+        <v>45971</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11265,7 +11223,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0.9</v>
+        <v>3.4</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -11308,7 +11266,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 23229-2026</t>
+          <t>A 29607-2022</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -11322,10 +11280,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46162</v>
+        <v>44754</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11343,7 +11301,7 @@
         </is>
       </c>
       <c r="I118" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -11386,7 +11344,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 62972-2023</t>
+          <t>A 6240-2024</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -11400,10 +11358,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45272</v>
+        <v>45337</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11416,7 +11374,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>0.3</v>
+        <v>1.9</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -11476,7 +11434,7 @@
         <v>45742</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11554,7 +11512,7 @@
         <v>45979</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11610,7 +11568,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 12143-2025</t>
+          <t>A 23230-2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -11620,14 +11578,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45729</v>
+        <v>46162</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11645,7 +11603,7 @@
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -11688,7 +11646,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 51653-2023</t>
+          <t>A 23229-2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11702,10 +11660,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45222</v>
+        <v>46162</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11723,7 +11681,7 @@
         </is>
       </c>
       <c r="I123" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -11766,7 +11724,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 23854-2026</t>
+          <t>A 33658-2024</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11780,10 +11738,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46167</v>
+        <v>45520</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11795,13 +11753,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I124" t="n">
-        <v>20.9</v>
+        <v>2.2</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -11844,7 +11797,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 20577-2023</t>
+          <t>A 38233-2023</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11858,10 +11811,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45057</v>
+        <v>45160</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11873,13 +11826,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I125" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -11922,7 +11870,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 45365-2023</t>
+          <t>A 60708-2025</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11936,10 +11884,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>45192</v>
+        <v>45996</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11952,7 +11900,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>5</v>
+        <v>1.9</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -11995,7 +11943,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 6387-2024</t>
+          <t>A 60736-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -12005,14 +11953,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45338</v>
+        <v>45996</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12024,13 +11972,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I127" t="n">
-        <v>1.8</v>
+        <v>5.8</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -12073,7 +12016,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 60736-2025</t>
+          <t>A 50766-2024</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -12087,10 +12030,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45996</v>
+        <v>45602</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12102,8 +12045,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I128" t="n">
-        <v>5.8</v>
+        <v>2.1</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -12146,7 +12094,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 60708-2025</t>
+          <t>A 23854-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -12160,10 +12108,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45996</v>
+        <v>46167</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12175,8 +12123,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I129" t="n">
-        <v>1.9</v>
+        <v>20.9</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -12219,7 +12172,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 6240-2024</t>
+          <t>A 48118-2023</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -12233,10 +12186,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45337</v>
+        <v>45205</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12248,8 +12201,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I130" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -12292,7 +12250,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 24460-2026</t>
+          <t>A 38917-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -12306,10 +12264,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>46170</v>
+        <v>45163</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12321,8 +12279,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I131" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -12365,7 +12328,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 38917-2023</t>
+          <t>A 24462-2026</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -12379,10 +12342,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45163</v>
+        <v>46170</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12394,13 +12357,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I132" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -12443,7 +12401,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 24462-2026</t>
+          <t>A 50207-2024</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -12457,10 +12415,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>46170</v>
+        <v>45600</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12473,7 +12431,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -12516,7 +12474,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 48118-2023</t>
+          <t>A 50208-2024</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -12530,10 +12488,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45205</v>
+        <v>45600</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12545,13 +12503,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I134" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -12594,7 +12547,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 6394-2024</t>
+          <t>A 24689-2026</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -12604,14 +12557,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45338</v>
+        <v>46171</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12629,7 +12582,7 @@
         </is>
       </c>
       <c r="I135" t="n">
-        <v>0.9</v>
+        <v>15.5</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -12672,7 +12625,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 11085-2023</t>
+          <t>A 24460-2026</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -12686,10 +12639,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>44986</v>
+        <v>46170</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12702,7 +12655,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -12745,7 +12698,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 24689-2026</t>
+          <t>A 770-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -12759,10 +12712,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>46171</v>
+        <v>46027</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12774,13 +12727,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I137" t="n">
-        <v>15.5</v>
+        <v>2.2</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -12823,7 +12771,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 770-2026</t>
+          <t>A 12143-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -12833,14 +12781,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>46027</v>
+        <v>45729</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12852,8 +12800,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I138" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -12896,7 +12849,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 5277-2024</t>
+          <t>A 52523-2024</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -12910,10 +12863,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45330</v>
+        <v>45609</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12925,8 +12878,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I139" t="n">
-        <v>0.5</v>
+        <v>4.4</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -12969,7 +12927,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 50378-2024</t>
+          <t>A 8184-2022</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -12983,10 +12941,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>45601</v>
+        <v>44609</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12998,13 +12956,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I140" t="n">
-        <v>4.9</v>
+        <v>1.7</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -13047,7 +13000,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 33293-2023</t>
+          <t>A 60937-2024</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -13061,10 +13014,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45116</v>
+        <v>45645</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13076,8 +13029,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I141" t="n">
-        <v>17.2</v>
+        <v>0.6</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -13120,7 +13078,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 44807-2023</t>
+          <t>A 60940-2024</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -13134,10 +13092,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45190</v>
+        <v>45645</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13155,7 +13113,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>5.4</v>
+        <v>1.2</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -13198,7 +13156,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 51652-2023</t>
+          <t>A 44807-2023</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -13212,10 +13170,10 @@
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45222</v>
+        <v>45190</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13233,7 +13191,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>1.7</v>
+        <v>5.4</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -13276,7 +13234,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 26857-2026</t>
+          <t>A 51652-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -13290,10 +13248,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46185</v>
+        <v>45222</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13311,7 +13269,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>15.1</v>
+        <v>1.7</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -13354,7 +13312,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 26946-2026</t>
+          <t>A 26857-2026</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -13371,7 +13329,7 @@
         <v>46185</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13389,7 +13347,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>1.8</v>
+        <v>15.1</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -13432,7 +13390,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 44457-2022</t>
+          <t>A 26947-2026</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -13446,10 +13404,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>44839</v>
+        <v>46185</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13461,8 +13419,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I146" t="n">
-        <v>6.8</v>
+        <v>2</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -13505,7 +13468,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 26947-2026</t>
+          <t>A 26946-2026</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -13522,7 +13485,7 @@
         <v>46185</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13540,7 +13503,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -13583,7 +13546,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 32211-2022</t>
+          <t>A 33293-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -13597,10 +13560,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>44781</v>
+        <v>45116</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13613,7 +13576,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>2.3</v>
+        <v>17.2</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -13656,7 +13619,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 13405-2024</t>
+          <t>A 9273-2026</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -13670,10 +13633,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45387</v>
+        <v>46070</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13686,7 +13649,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>0.9</v>
+        <v>2.3</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -13729,7 +13692,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 12729-2024</t>
+          <t>A 32154-2023</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -13743,10 +13706,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45384</v>
+        <v>45119</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13758,13 +13721,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I150" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -13807,7 +13765,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 9273-2026</t>
+          <t>A 12159-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -13821,10 +13779,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>46070</v>
+        <v>46086</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13836,8 +13794,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I151" t="n">
-        <v>2.3</v>
+        <v>0.9</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -13880,7 +13843,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 12159-2026</t>
+          <t>A 12160-2026</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -13897,7 +13860,7 @@
         <v>46086</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13958,7 +13921,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 12160-2026</t>
+          <t>A 27411-2026</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -13972,10 +13935,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>46086</v>
+        <v>46189</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13993,7 +13956,7 @@
         </is>
       </c>
       <c r="I153" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -14036,7 +13999,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 27411-2026</t>
+          <t>A 13039-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -14050,10 +14013,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46189</v>
+        <v>46093</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14071,7 +14034,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>1.4</v>
+        <v>5.1</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -14114,7 +14077,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 12936-2026</t>
+          <t>A 13040-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -14128,10 +14091,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14149,7 +14112,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>8.800000000000001</v>
+        <v>7.1</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -14192,7 +14155,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 13293-2026</t>
+          <t>A 12936-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -14206,10 +14169,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>46094</v>
+        <v>46092</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14227,7 +14190,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -14270,7 +14233,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 13040-2026</t>
+          <t>A 13293-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -14284,10 +14247,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14305,7 +14268,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>7.1</v>
+        <v>1.1</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -14348,7 +14311,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 13039-2026</t>
+          <t>A 27745-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -14362,10 +14325,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>46093</v>
+        <v>46191</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14383,7 +14346,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>5.1</v>
+        <v>1.7</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -14426,7 +14389,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 27745-2026</t>
+          <t>A 27746-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -14443,7 +14406,7 @@
         <v>46191</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14461,7 +14424,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -14504,7 +14467,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 27746-2026</t>
+          <t>A 8062-2024</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -14518,10 +14481,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>46191</v>
+        <v>45351</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14539,7 +14502,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -14582,7 +14545,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 28696-2026</t>
+          <t>A 8074-2024</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -14596,10 +14559,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>46198</v>
+        <v>45351</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14617,7 +14580,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -14660,7 +14623,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 28708-2026</t>
+          <t>A 60907-2023</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -14670,14 +14633,14 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46198</v>
+        <v>45261</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14695,7 +14658,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -14738,7 +14701,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 28695-2026</t>
+          <t>A 32211-2022</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -14752,10 +14715,10 @@
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46198</v>
+        <v>44781</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14767,13 +14730,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I163" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -14816,7 +14774,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 29130-2026</t>
+          <t>A 28696-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -14830,10 +14788,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46202</v>
+        <v>46198</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14851,7 +14809,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>10.3</v>
+        <v>2.5</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -14894,7 +14852,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 28930-2026</t>
+          <t>A 28708-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -14908,10 +14866,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46199</v>
+        <v>46198</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14923,8 +14881,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I165" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -14967,7 +14930,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 18913-2026</t>
+          <t>A 18506-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -14981,10 +14944,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>46129</v>
+        <v>46127</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14996,13 +14959,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I166" t="n">
-        <v>8.300000000000001</v>
+        <v>1.6</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -15045,7 +15003,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 18506-2026</t>
+          <t>A 19227-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -15059,10 +15017,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>46127</v>
+        <v>46132</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15075,7 +15033,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -15118,7 +15076,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 19227-2026</t>
+          <t>A 28930-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -15132,10 +15090,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46132</v>
+        <v>46199</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15148,7 +15106,7 @@
         </is>
       </c>
       <c r="I168" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -15191,7 +15149,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 63905-2021</t>
+          <t>A 28695-2026</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -15205,10 +15163,10 @@
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>44509</v>
+        <v>46198</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15226,7 +15184,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>3.7</v>
+        <v>2.7</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -15269,7 +15227,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 38743-2022</t>
+          <t>A 18913-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -15283,10 +15241,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>44816</v>
+        <v>46129</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15304,7 +15262,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>1.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -15347,7 +15305,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 47935-2024</t>
+          <t>A 29130-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -15361,10 +15319,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45589</v>
+        <v>46202</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15382,7 +15340,7 @@
         </is>
       </c>
       <c r="I171" t="n">
-        <v>2.2</v>
+        <v>10.3</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -15425,7 +15383,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 50377-2024</t>
+          <t>A 73693-2021</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -15439,10 +15397,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45601</v>
+        <v>44552</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15454,13 +15412,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H172" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I172" t="n">
-        <v>0.7</v>
+        <v>3.6</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -15503,7 +15456,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 8059-2024</t>
+          <t>A 36437-2024</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -15517,10 +15470,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>45351</v>
+        <v>45535</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15532,13 +15485,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I173" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -15581,7 +15529,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 29482-2023</t>
+          <t>A 43752-2025</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -15595,10 +15543,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45106</v>
+        <v>45912</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15611,7 +15559,7 @@
         </is>
       </c>
       <c r="I174" t="n">
-        <v>0.7</v>
+        <v>3.1</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -15654,7 +15602,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 59158-2022</t>
+          <t>A 45365-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -15664,14 +15612,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>44904</v>
+        <v>45192</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15683,13 +15631,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I175" t="n">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -15732,7 +15675,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 18773-2025</t>
+          <t>A 37672-2024</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -15742,14 +15685,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>45763</v>
+        <v>45541</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15761,8 +15704,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I176" t="n">
-        <v>13</v>
+        <v>0.6</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -15805,7 +15753,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 10320-2023</t>
+          <t>A 2565-2022</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -15819,10 +15767,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>44986</v>
+        <v>44579</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15835,7 +15783,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>2.6</v>
+        <v>1.4</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -15895,7 +15843,7 @@
         <v>46230</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15951,7 +15899,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 10797-2023</t>
+          <t>A 31870-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -15965,10 +15913,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>44989</v>
+        <v>46231</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15980,8 +15928,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I179" t="n">
-        <v>9.5</v>
+        <v>1.5</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -16024,7 +15977,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 11084-2023</t>
+          <t>A 31871-2026</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -16038,10 +15991,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>44986</v>
+        <v>46231</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16053,8 +16006,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I180" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -16097,7 +16055,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 50764-2024</t>
+          <t>A 10674-2024</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -16107,14 +16065,14 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45602</v>
+        <v>45369</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16132,7 +16090,7 @@
         </is>
       </c>
       <c r="I181" t="n">
-        <v>2.4</v>
+        <v>0.3</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -16175,7 +16133,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 33658-2024</t>
+          <t>A 18773-2025</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -16189,10 +16147,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45520</v>
+        <v>45763</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16205,7 +16163,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>2.2</v>
+        <v>13</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -16248,7 +16206,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 31870-2026</t>
+          <t>A 51653-2023</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -16262,10 +16220,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46231</v>
+        <v>45222</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16283,7 +16241,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>1.5</v>
+        <v>3.9</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -16326,7 +16284,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 31871-2026</t>
+          <t>A 12108-2024</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -16340,10 +16298,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46231</v>
+        <v>45376</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16355,13 +16313,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I184" t="n">
-        <v>1.9</v>
+        <v>7.7</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -16404,7 +16357,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 45861-2023</t>
+          <t>A 54994-2024</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -16414,14 +16367,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45195</v>
+        <v>45621</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16439,7 +16392,7 @@
         </is>
       </c>
       <c r="I185" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -16482,7 +16435,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 43768-2024</t>
+          <t>A 37809-2026</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -16496,10 +16449,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>45569</v>
+        <v>46279</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16512,7 +16465,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>7</v>
+        <v>2.9</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -16555,7 +16508,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 37809-2026</t>
+          <t>A 38126-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -16569,10 +16522,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46279</v>
+        <v>46281</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16584,8 +16537,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I187" t="n">
-        <v>2.9</v>
+        <v>5.5</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -16628,7 +16586,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 38126-2026</t>
+          <t>A 38463-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -16642,10 +16600,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16657,13 +16615,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I188" t="n">
-        <v>5.5</v>
+        <v>3.4</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -16706,7 +16659,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 32506-2026</t>
+          <t>A 32508-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -16723,7 +16676,7 @@
         <v>46239</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16784,7 +16737,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 38651-2026</t>
+          <t>A 32506-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -16798,10 +16751,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46283</v>
+        <v>46239</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16819,7 +16772,7 @@
         </is>
       </c>
       <c r="I190" t="n">
-        <v>11.3</v>
+        <v>1.1</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -16862,7 +16815,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 38463-2026</t>
+          <t>A 38659-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -16876,10 +16829,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16891,8 +16844,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I191" t="n">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -16935,7 +16893,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 32508-2026</t>
+          <t>A 32810-2026</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -16949,10 +16907,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46239</v>
+        <v>46241</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16964,13 +16922,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I192" t="n">
-        <v>1.1</v>
+        <v>6.1</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -17013,7 +16966,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 38659-2026</t>
+          <t>A 38651-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -17030,7 +16983,7 @@
         <v>46283</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17048,7 +17001,7 @@
         </is>
       </c>
       <c r="I193" t="n">
-        <v>4.6</v>
+        <v>11.3</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -17091,7 +17044,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 38738-2022</t>
+          <t>A 8059-2024</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -17105,10 +17058,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>44816</v>
+        <v>45351</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17126,7 +17079,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -17169,7 +17122,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 32810-2026</t>
+          <t>A 54515-2023</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -17183,10 +17136,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>46241</v>
+        <v>45233</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17199,7 +17152,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>6.1</v>
+        <v>1</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -17242,7 +17195,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 61750-2021</t>
+          <t>A 38738-2022</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -17256,10 +17209,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>44501</v>
+        <v>44816</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17277,7 +17230,7 @@
         </is>
       </c>
       <c r="I196" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -17320,7 +17273,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 7472-2025</t>
+          <t>A 12729-2024</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -17334,10 +17287,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>45705</v>
+        <v>45384</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17355,7 +17308,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -17398,7 +17351,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 50207-2024</t>
+          <t>A 10320-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -17412,10 +17365,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45600</v>
+        <v>44986</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17428,7 +17381,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>1.2</v>
+        <v>2.6</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -17471,7 +17424,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 50208-2024</t>
+          <t>A 7472-2025</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -17485,10 +17438,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>45600</v>
+        <v>45705</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17500,8 +17453,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I199" t="n">
-        <v>0.4</v>
+        <v>2.6</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -17544,7 +17502,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 12108-2024</t>
+          <t>A 7975-2025</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -17558,10 +17516,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45376</v>
+        <v>45707</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17573,8 +17531,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I200" t="n">
-        <v>7.7</v>
+        <v>5.3</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -17634,7 +17597,7 @@
         <v>45764</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17695,7 +17658,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 31872-2026</t>
+          <t>A 58629-2024</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -17709,10 +17672,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>46231</v>
+        <v>45635</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17730,7 +17693,7 @@
         </is>
       </c>
       <c r="I202" t="n">
-        <v>5.2</v>
+        <v>1.4</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -17773,7 +17736,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 32154-2023</t>
+          <t>A 27438-2024</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -17787,10 +17750,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45119</v>
+        <v>45474</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17803,7 +17766,7 @@
         </is>
       </c>
       <c r="I203" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -17846,7 +17809,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 27438-2024</t>
+          <t>A 50102-2023</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -17860,10 +17823,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>45474</v>
+        <v>45215</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17875,8 +17838,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I204" t="n">
-        <v>2.6</v>
+        <v>3.9</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -17919,7 +17887,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 46288-2024</t>
+          <t>A 51996-2023</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -17933,10 +17901,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45581</v>
+        <v>45223</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17954,7 +17922,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>3.7</v>
+        <v>2</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -17997,7 +17965,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 51996-2023</t>
+          <t>A 62982-2023</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -18011,10 +17979,10 @@
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45223</v>
+        <v>45272</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18026,13 +17994,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H206" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I206" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -18075,7 +18038,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 58629-2024</t>
+          <t>A 46288-2024</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -18089,10 +18052,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>45635</v>
+        <v>45581</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18110,7 +18073,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>1.4</v>
+        <v>3.7</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -18153,7 +18116,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 50102-2023</t>
+          <t>A 21935-2024</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -18167,10 +18130,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>45215</v>
+        <v>45443</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18188,7 +18151,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>3.9</v>
+        <v>1.8</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -18231,7 +18194,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 41890-2026</t>
+          <t>A 31872-2026</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -18245,10 +18208,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>46303</v>
+        <v>46231</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18266,7 +18229,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>6.3</v>
+        <v>5.2</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -18309,7 +18272,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 62982-2023</t>
+          <t>A 23460-2024</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -18323,10 +18286,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45272</v>
+        <v>45453</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18339,7 +18302,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>3.5</v>
+        <v>0.7</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -18382,7 +18345,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 35213-2026</t>
+          <t>A 5218-2024</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -18396,10 +18359,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>46260</v>
+        <v>45330</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18417,7 +18380,7 @@
         </is>
       </c>
       <c r="I211" t="n">
-        <v>9.5</v>
+        <v>3.3</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -18460,7 +18423,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 21935-2024</t>
+          <t>A 24707-2025</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -18474,10 +18437,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>45443</v>
+        <v>45798</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18489,13 +18452,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H212" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I212" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -18538,7 +18496,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 23460-2024</t>
+          <t>A 41890-2026</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -18552,10 +18510,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45453</v>
+        <v>46303</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18567,8 +18525,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I213" t="n">
-        <v>0.7</v>
+        <v>6.3</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -18611,7 +18574,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 42336-2026</t>
+          <t>A 35213-2026</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -18625,10 +18588,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>46307</v>
+        <v>46260</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18646,7 +18609,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>7.1</v>
+        <v>9.5</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -18689,7 +18652,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 24707-2025</t>
+          <t>A 26783-2025</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -18703,10 +18666,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45798</v>
+        <v>45810</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18719,7 +18682,7 @@
         </is>
       </c>
       <c r="I215" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -18762,7 +18725,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 5218-2024</t>
+          <t>A 26820-2025</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -18776,10 +18739,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>45330</v>
+        <v>45810</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18791,13 +18754,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I216" t="n">
-        <v>3.3</v>
+        <v>0.7</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -18857,7 +18815,7 @@
         <v>46195</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18913,7 +18871,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 26820-2025</t>
+          <t>A 42336-2026</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -18927,10 +18885,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45810</v>
+        <v>46307</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18942,8 +18900,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I218" t="n">
-        <v>0.7</v>
+        <v>7.1</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -18986,7 +18949,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 26783-2025</t>
+          <t>A 28367-2025</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -19000,10 +18963,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45810</v>
+        <v>45819</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19015,8 +18978,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I219" t="n">
-        <v>2.5</v>
+        <v>6.1</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -19059,7 +19027,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 36345-2026</t>
+          <t>A 28368-2025</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -19073,10 +19041,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>46268</v>
+        <v>45819</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19088,8 +19056,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I220" t="n">
-        <v>0.3</v>
+        <v>8.1</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -19132,7 +19105,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 28367-2025</t>
+          <t>A 23066-2022</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -19146,10 +19119,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45819</v>
+        <v>44719</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19161,13 +19134,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H221" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I221" t="n">
-        <v>6.1</v>
+        <v>2.4</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -19210,7 +19178,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 28368-2025</t>
+          <t>A 41889-2026</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -19224,10 +19192,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>45819</v>
+        <v>46303</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19245,7 +19213,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>8.1</v>
+        <v>5.6</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -19305,7 +19273,7 @@
         <v>46268</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19378,7 +19346,7 @@
         <v>46268</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19434,7 +19402,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 41889-2026</t>
+          <t>A 36345-2026</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -19448,10 +19416,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>46303</v>
+        <v>46268</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19463,13 +19431,8 @@
           <t>DEGERFORS</t>
         </is>
       </c>
-      <c r="H225" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I225" t="n">
-        <v>5.6</v>
+        <v>0.3</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -19512,7 +19475,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 23066-2022</t>
+          <t>A 33404-2025</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -19526,10 +19489,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>44719</v>
+        <v>45841</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19542,7 +19505,7 @@
         </is>
       </c>
       <c r="I226" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -19585,7 +19548,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 33404-2025</t>
+          <t>A 59863-2024</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -19599,10 +19562,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45841</v>
+        <v>45639</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19615,7 +19578,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -19658,7 +19621,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 59863-2024</t>
+          <t>A 37333-2025</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -19668,14 +19631,14 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45639</v>
+        <v>45876</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19688,7 +19651,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -19731,7 +19694,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 37333-2025</t>
+          <t>A 37265-2025</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -19741,14 +19704,14 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D229" s="1" t="n">
         <v>45876</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19761,7 +19724,7 @@
         </is>
       </c>
       <c r="I229" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -19804,7 +19767,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 37265-2025</t>
+          <t>A 15594-2025</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -19818,10 +19781,10 @@
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45876</v>
+        <v>45747</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19834,7 +19797,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -19877,24 +19840,24 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 15594-2025</t>
+          <t>S 479-2022</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Skogsbilväg</t>
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>45747</v>
+        <v>44587</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19907,7 +19870,7 @@
         </is>
       </c>
       <c r="I231" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -19950,7 +19913,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>S 479-2022</t>
+          <t>S 1697-2025</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -19960,14 +19923,14 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Skogsbilväg</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>44587</v>
+        <v>45805</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19979,8 +19942,13 @@
           <t>DEGERFORS</t>
         </is>
       </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I232" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -20023,7 +19991,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>S 1697-2025</t>
+          <t>S 1694-2025</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -20040,7 +20008,7 @@
         <v>45805</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20058,7 +20026,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -20101,7 +20069,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>S 1694-2025</t>
+          <t>S 794-2025</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -20115,10 +20083,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45805</v>
+        <v>45729</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20136,7 +20104,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -20179,7 +20147,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>S 794-2025</t>
+          <t>S 793-2025</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -20196,7 +20164,7 @@
         <v>45729</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20214,7 +20182,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -20257,7 +20225,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>S 793-2025</t>
+          <t>S 963-2025</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -20271,10 +20239,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45729</v>
+        <v>45742</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20292,7 +20260,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -20335,7 +20303,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>S 963-2025</t>
+          <t>S 964-2025</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -20352,7 +20320,7 @@
         <v>45742</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20370,7 +20338,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -20410,10 +20378,10 @@
       </c>
       <c r="V237" s="2" t="inlineStr"/>
     </row>
-    <row r="238" ht="15" customHeight="1">
+    <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>S 964-2025</t>
+          <t>S 2595-2025</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -20427,10 +20395,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45742</v>
+        <v>45916</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20448,7 +20416,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -20487,84 +20455,6 @@
         <v>0</v>
       </c>
       <c r="V238" s="2" t="inlineStr"/>
-    </row>
-    <row r="239">
-      <c r="A239" t="inlineStr">
-        <is>
-          <t>S 2595-2025</t>
-        </is>
-      </c>
-      <c r="B2